--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="315">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -640,6 +640,12 @@
     <t>['34', '64']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['44', '50']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -950,6 +956,9 @@
   </si>
   <si>
     <t>['21', '71']</t>
+  </si>
+  <si>
+    <t>['75', '84']</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1567,7 +1576,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1773,7 +1782,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2185,7 +2194,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2597,7 +2606,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2803,7 +2812,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3009,7 +3018,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3215,7 +3224,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3627,7 +3636,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3911,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.3</v>
@@ -4039,7 +4048,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4117,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ14">
         <v>1.89</v>
@@ -4326,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4451,7 +4460,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4657,7 +4666,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4738,7 +4747,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4863,7 +4872,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5275,7 +5284,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5687,7 +5696,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6511,7 +6520,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6717,7 +6726,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6923,7 +6932,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7335,7 +7344,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7541,7 +7550,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7825,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR32">
         <v>0.9399999999999999</v>
@@ -7953,7 +7962,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8031,7 +8040,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>2.5</v>
@@ -8159,7 +8168,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8571,7 +8580,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8777,7 +8786,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8858,7 +8867,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR37">
         <v>2.14</v>
@@ -8983,7 +8992,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9395,7 +9404,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9601,7 +9610,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9807,7 +9816,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10013,7 +10022,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10425,7 +10434,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10837,7 +10846,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11043,7 +11052,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11124,7 +11133,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR48">
         <v>1.7</v>
@@ -11249,7 +11258,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11455,7 +11464,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11533,7 +11542,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>1.8</v>
@@ -11867,7 +11876,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12073,7 +12082,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12151,7 +12160,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ53">
         <v>0.8</v>
@@ -12279,7 +12288,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12360,7 +12369,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ54">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR54">
         <v>1.87</v>
@@ -12485,7 +12494,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12691,7 +12700,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12897,7 +12906,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13103,7 +13112,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13515,7 +13524,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13721,7 +13730,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14133,7 +14142,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14339,7 +14348,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14420,7 +14429,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR64">
         <v>2.51</v>
@@ -14751,7 +14760,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14832,7 +14841,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.63</v>
@@ -15241,7 +15250,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ68">
         <v>1.7</v>
@@ -15369,7 +15378,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15447,7 +15456,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1.11</v>
@@ -15575,7 +15584,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15781,7 +15790,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16193,7 +16202,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16811,7 +16820,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17017,7 +17026,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17716,7 +17725,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR80">
         <v>1.52</v>
@@ -17841,7 +17850,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18047,7 +18056,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18253,7 +18262,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18459,7 +18468,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18537,7 +18546,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>0.11</v>
@@ -18665,7 +18674,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18871,7 +18880,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19077,7 +19086,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19155,7 +19164,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ87">
         <v>1.56</v>
@@ -19283,7 +19292,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19489,7 +19498,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19695,7 +19704,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20725,7 +20734,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20806,7 +20815,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ95">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -21012,7 +21021,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ96">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR96">
         <v>1.59</v>
@@ -21137,7 +21146,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21343,7 +21352,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21755,7 +21764,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q100">
         <v>1.95</v>
@@ -21961,7 +21970,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22245,7 +22254,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ102">
         <v>1.7</v>
@@ -22579,7 +22588,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22991,7 +23000,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23197,7 +23206,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23609,7 +23618,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23687,7 +23696,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ109">
         <v>0.89</v>
@@ -23815,7 +23824,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24227,7 +24236,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24308,7 +24317,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ112">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24433,7 +24442,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24639,7 +24648,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24845,7 +24854,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -24926,7 +24935,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR115">
         <v>1.64</v>
@@ -25051,7 +25060,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25257,7 +25266,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25463,7 +25472,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25669,7 +25678,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25875,7 +25884,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26081,7 +26090,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26287,7 +26296,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26365,7 +26374,7 @@
         <v>1.43</v>
       </c>
       <c r="AP122">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ122">
         <v>1.7</v>
@@ -26905,7 +26914,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27111,7 +27120,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27189,7 +27198,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ126">
         <v>2.22</v>
@@ -27601,7 +27610,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ128">
         <v>0.8</v>
@@ -27729,7 +27738,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27935,7 +27944,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28016,7 +28025,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR130">
         <v>1.78</v>
@@ -28347,7 +28356,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28553,7 +28562,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28759,7 +28768,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28840,7 +28849,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR134">
         <v>1.67</v>
@@ -29171,7 +29180,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29377,7 +29386,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29583,7 +29592,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29995,7 +30004,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30407,7 +30416,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31025,7 +31034,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31231,7 +31240,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31309,7 +31318,7 @@
         <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ146">
         <v>1.3</v>
@@ -31437,7 +31446,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32055,7 +32064,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32136,7 +32145,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ150">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32339,7 +32348,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>0.3</v>
@@ -32467,7 +32476,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32548,7 +32557,7 @@
         <v>1</v>
       </c>
       <c r="AQ152">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR152">
         <v>1.2</v>
@@ -32879,7 +32888,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33085,7 +33094,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33166,7 +33175,7 @@
         <v>1</v>
       </c>
       <c r="AQ155">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR155">
         <v>1.57</v>
@@ -33291,7 +33300,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -34321,7 +34330,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34527,7 +34536,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34605,7 +34614,7 @@
         <v>2.44</v>
       </c>
       <c r="AP162">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ162">
         <v>2.5</v>
@@ -34733,7 +34742,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34811,10 +34820,10 @@
         <v>1.67</v>
       </c>
       <c r="AP163">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ163">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -34939,7 +34948,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35145,7 +35154,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35557,7 +35566,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35763,7 +35772,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -35969,7 +35978,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36175,7 +36184,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36587,7 +36596,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36744,6 +36753,418 @@
       </c>
       <c r="BP172">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7491666</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45688.60416666666</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>81</v>
+      </c>
+      <c r="H173" t="s">
+        <v>76</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
+        <v>208</v>
+      </c>
+      <c r="P173" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q173">
+        <v>2.65</v>
+      </c>
+      <c r="R173">
+        <v>2.2</v>
+      </c>
+      <c r="S173">
+        <v>3.3</v>
+      </c>
+      <c r="T173">
+        <v>1.3</v>
+      </c>
+      <c r="U173">
+        <v>3.2</v>
+      </c>
+      <c r="V173">
+        <v>2.3</v>
+      </c>
+      <c r="W173">
+        <v>1.53</v>
+      </c>
+      <c r="X173">
+        <v>5.5</v>
+      </c>
+      <c r="Y173">
+        <v>1.13</v>
+      </c>
+      <c r="Z173">
+        <v>2.33</v>
+      </c>
+      <c r="AA173">
+        <v>3.66</v>
+      </c>
+      <c r="AB173">
+        <v>2.85</v>
+      </c>
+      <c r="AC173">
+        <v>1.04</v>
+      </c>
+      <c r="AD173">
+        <v>10</v>
+      </c>
+      <c r="AE173">
+        <v>1.22</v>
+      </c>
+      <c r="AF173">
+        <v>4.2</v>
+      </c>
+      <c r="AG173">
+        <v>1.67</v>
+      </c>
+      <c r="AH173">
+        <v>2.21</v>
+      </c>
+      <c r="AI173">
+        <v>1.55</v>
+      </c>
+      <c r="AJ173">
+        <v>2.3</v>
+      </c>
+      <c r="AK173">
+        <v>1.37</v>
+      </c>
+      <c r="AL173">
+        <v>1.28</v>
+      </c>
+      <c r="AM173">
+        <v>1.63</v>
+      </c>
+      <c r="AN173">
+        <v>1.89</v>
+      </c>
+      <c r="AO173">
+        <v>1.33</v>
+      </c>
+      <c r="AP173">
+        <v>2</v>
+      </c>
+      <c r="AQ173">
+        <v>1.2</v>
+      </c>
+      <c r="AR173">
+        <v>1.57</v>
+      </c>
+      <c r="AS173">
+        <v>1.77</v>
+      </c>
+      <c r="AT173">
+        <v>3.34</v>
+      </c>
+      <c r="AU173">
+        <v>7</v>
+      </c>
+      <c r="AV173">
+        <v>2</v>
+      </c>
+      <c r="AW173">
+        <v>7</v>
+      </c>
+      <c r="AX173">
+        <v>10</v>
+      </c>
+      <c r="AY173">
+        <v>15</v>
+      </c>
+      <c r="AZ173">
+        <v>13</v>
+      </c>
+      <c r="BA173">
+        <v>6</v>
+      </c>
+      <c r="BB173">
+        <v>1</v>
+      </c>
+      <c r="BC173">
+        <v>7</v>
+      </c>
+      <c r="BD173">
+        <v>1.81</v>
+      </c>
+      <c r="BE173">
+        <v>6.75</v>
+      </c>
+      <c r="BF173">
+        <v>2.17</v>
+      </c>
+      <c r="BG173">
+        <v>1.19</v>
+      </c>
+      <c r="BH173">
+        <v>4.1</v>
+      </c>
+      <c r="BI173">
+        <v>1.33</v>
+      </c>
+      <c r="BJ173">
+        <v>2.95</v>
+      </c>
+      <c r="BK173">
+        <v>1.54</v>
+      </c>
+      <c r="BL173">
+        <v>2.3</v>
+      </c>
+      <c r="BM173">
+        <v>1.85</v>
+      </c>
+      <c r="BN173">
+        <v>1.83</v>
+      </c>
+      <c r="BO173">
+        <v>2.32</v>
+      </c>
+      <c r="BP173">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7491665</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45688.60416666666</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>82</v>
+      </c>
+      <c r="H174" t="s">
+        <v>71</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
+      <c r="M174">
+        <v>2</v>
+      </c>
+      <c r="N174">
+        <v>4</v>
+      </c>
+      <c r="O174" t="s">
+        <v>209</v>
+      </c>
+      <c r="P174" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q174">
+        <v>2.7</v>
+      </c>
+      <c r="R174">
+        <v>2.51</v>
+      </c>
+      <c r="S174">
+        <v>3.53</v>
+      </c>
+      <c r="T174">
+        <v>1.24</v>
+      </c>
+      <c r="U174">
+        <v>3.64</v>
+      </c>
+      <c r="V174">
+        <v>2.3</v>
+      </c>
+      <c r="W174">
+        <v>1.62</v>
+      </c>
+      <c r="X174">
+        <v>5.3</v>
+      </c>
+      <c r="Y174">
+        <v>1.12</v>
+      </c>
+      <c r="Z174">
+        <v>2.2</v>
+      </c>
+      <c r="AA174">
+        <v>3.88</v>
+      </c>
+      <c r="AB174">
+        <v>2.93</v>
+      </c>
+      <c r="AC174">
+        <v>1.01</v>
+      </c>
+      <c r="AD174">
+        <v>13</v>
+      </c>
+      <c r="AE174">
+        <v>1.1</v>
+      </c>
+      <c r="AF174">
+        <v>5.15</v>
+      </c>
+      <c r="AG174">
+        <v>1.55</v>
+      </c>
+      <c r="AH174">
+        <v>2.35</v>
+      </c>
+      <c r="AI174">
+        <v>1.44</v>
+      </c>
+      <c r="AJ174">
+        <v>2.57</v>
+      </c>
+      <c r="AK174">
+        <v>1.4</v>
+      </c>
+      <c r="AL174">
+        <v>1.26</v>
+      </c>
+      <c r="AM174">
+        <v>1.69</v>
+      </c>
+      <c r="AN174">
+        <v>1.6</v>
+      </c>
+      <c r="AO174">
+        <v>1.5</v>
+      </c>
+      <c r="AP174">
+        <v>1.55</v>
+      </c>
+      <c r="AQ174">
+        <v>1.45</v>
+      </c>
+      <c r="AR174">
+        <v>1.47</v>
+      </c>
+      <c r="AS174">
+        <v>1.16</v>
+      </c>
+      <c r="AT174">
+        <v>2.63</v>
+      </c>
+      <c r="AU174">
+        <v>7</v>
+      </c>
+      <c r="AV174">
+        <v>5</v>
+      </c>
+      <c r="AW174">
+        <v>8</v>
+      </c>
+      <c r="AX174">
+        <v>10</v>
+      </c>
+      <c r="AY174">
+        <v>20</v>
+      </c>
+      <c r="AZ174">
+        <v>19</v>
+      </c>
+      <c r="BA174">
+        <v>7</v>
+      </c>
+      <c r="BB174">
+        <v>7</v>
+      </c>
+      <c r="BC174">
+        <v>14</v>
+      </c>
+      <c r="BD174">
+        <v>1.8</v>
+      </c>
+      <c r="BE174">
+        <v>6.4</v>
+      </c>
+      <c r="BF174">
+        <v>2.2</v>
+      </c>
+      <c r="BG174">
+        <v>1.3</v>
+      </c>
+      <c r="BH174">
+        <v>3.1</v>
+      </c>
+      <c r="BI174">
+        <v>1.52</v>
+      </c>
+      <c r="BJ174">
+        <v>2.33</v>
+      </c>
+      <c r="BK174">
+        <v>1.85</v>
+      </c>
+      <c r="BL174">
+        <v>1.83</v>
+      </c>
+      <c r="BM174">
+        <v>2.32</v>
+      </c>
+      <c r="BN174">
+        <v>1.53</v>
+      </c>
+      <c r="BO174">
+        <v>2.95</v>
+      </c>
+      <c r="BP174">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,24 @@
     <t>['44', '50']</t>
   </si>
   <si>
+    <t>['45', '90+2']</t>
+  </si>
+  <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['9', '15', '60']</t>
+  </si>
+  <si>
+    <t>['69', '90+3']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['50', '90+2']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -794,9 +812,6 @@
   </si>
   <si>
     <t>['13', '18', '33', '88']</t>
-  </si>
-  <si>
-    <t>['63']</t>
   </si>
   <si>
     <t>['76', '80']</t>
@@ -959,6 +974,24 @@
   </si>
   <si>
     <t>['75', '84']</t>
+  </si>
+  <si>
+    <t>['13', '30']</t>
+  </si>
+  <si>
+    <t>['13', '52']</t>
+  </si>
+  <si>
+    <t>['29', '45+2', '55', '65', '74']</t>
+  </si>
+  <si>
+    <t>['21', '50']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
+    <t>['52', '79']</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1576,7 +1609,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1782,7 +1815,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2194,7 +2227,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2606,7 +2639,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2684,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7">
         <v>0.3</v>
@@ -2812,7 +2845,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3018,7 +3051,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3099,7 +3132,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ9">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3224,7 +3257,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3508,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ11">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3636,7 +3669,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3714,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4048,7 +4081,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4129,7 +4162,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ14">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4332,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ15">
         <v>1.45</v>
@@ -4460,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4538,10 +4571,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ16">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4666,7 +4699,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4744,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17">
         <v>1.2</v>
@@ -4872,7 +4905,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4950,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5159,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5284,7 +5317,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5696,7 +5729,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6520,7 +6553,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6726,7 +6759,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6932,7 +6965,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7216,10 +7249,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ29">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7344,7 +7377,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7422,10 +7455,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR30">
         <v>0.79</v>
@@ -7550,7 +7583,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7628,10 +7661,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ31">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.09</v>
@@ -7962,7 +7995,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8043,7 +8076,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR33">
         <v>1.09</v>
@@ -8168,7 +8201,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8246,10 +8279,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ34">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR34">
         <v>1.8</v>
@@ -8452,10 +8485,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ35">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR35">
         <v>1.49</v>
@@ -8580,7 +8613,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8658,10 +8691,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ36">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8786,7 +8819,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8864,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ37">
         <v>1.45</v>
@@ -8992,7 +9025,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9404,7 +9437,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9610,7 +9643,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9816,7 +9849,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10022,7 +10055,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10103,7 +10136,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR43">
         <v>2.41</v>
@@ -10434,7 +10467,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10718,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ46">
         <v>0.11</v>
@@ -10846,7 +10879,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -10924,10 +10957,10 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -11052,7 +11085,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11130,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ48">
         <v>1.2</v>
@@ -11258,7 +11291,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11336,10 +11369,10 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11464,7 +11497,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11545,7 +11578,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR50">
         <v>0.97</v>
@@ -11748,10 +11781,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -11876,7 +11909,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11954,7 +11987,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ52">
         <v>1.56</v>
@@ -12082,7 +12115,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12163,7 +12196,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12288,7 +12321,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12494,7 +12527,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12572,10 +12605,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ55">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12700,7 +12733,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12906,7 +12939,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13112,7 +13145,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13190,7 +13223,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ58">
         <v>1.7</v>
@@ -13396,7 +13429,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
         <v>1.7</v>
@@ -13524,7 +13557,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13605,7 +13638,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ60">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13730,7 +13763,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14142,7 +14175,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14348,7 +14381,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14632,7 +14665,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ65">
         <v>0.11</v>
@@ -14760,7 +14793,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15047,7 +15080,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ67">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR67">
         <v>2.27</v>
@@ -15378,7 +15411,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15459,7 +15492,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>0.99</v>
@@ -15584,7 +15617,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15662,10 +15695,10 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ70">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR70">
         <v>1.66</v>
@@ -15790,7 +15823,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15871,7 +15904,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16074,10 +16107,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16202,7 +16235,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16280,7 +16313,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
@@ -16489,7 +16522,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ74">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16820,7 +16853,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17026,7 +17059,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17104,7 +17137,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ77">
         <v>2.22</v>
@@ -17516,7 +17549,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ79">
         <v>1.7</v>
@@ -17850,7 +17883,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18056,7 +18089,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18134,10 +18167,10 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ82">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR82">
         <v>1.62</v>
@@ -18262,7 +18295,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18468,7 +18501,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18674,7 +18707,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18755,7 +18788,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ85">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR85">
         <v>1.57</v>
@@ -18880,7 +18913,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -18958,10 +18991,10 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.49</v>
@@ -19086,7 +19119,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19292,7 +19325,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19370,7 +19403,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88">
         <v>1.7</v>
@@ -19498,7 +19531,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19579,7 +19612,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ89">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19704,7 +19737,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19785,7 +19818,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ90">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR90">
         <v>1.7</v>
@@ -19988,10 +20021,10 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.66</v>
@@ -20606,7 +20639,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ94">
         <v>1.33</v>
@@ -20734,7 +20767,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21146,7 +21179,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21227,7 +21260,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ97">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21352,7 +21385,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21430,10 +21463,10 @@
         <v>2.4</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ98">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR98">
         <v>1.68</v>
@@ -21636,7 +21669,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ99">
         <v>0.3</v>
@@ -21764,7 +21797,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="Q100">
         <v>1.95</v>
@@ -21842,7 +21875,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ100">
         <v>0.8</v>
@@ -21970,7 +22003,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22048,7 +22081,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ101">
         <v>1.56</v>
@@ -22463,7 +22496,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR103">
         <v>1.96</v>
@@ -22588,7 +22621,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22669,7 +22702,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ104">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -22875,7 +22908,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ105">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR105">
         <v>1.68</v>
@@ -23000,7 +23033,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23078,7 +23111,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
         <v>1.7</v>
@@ -23206,7 +23239,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23287,7 +23320,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ107">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23490,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ108">
         <v>0.11</v>
@@ -23618,7 +23651,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23699,7 +23732,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ109">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -23824,7 +23857,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23902,7 +23935,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ110">
         <v>0.8</v>
@@ -24111,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR111">
         <v>1.23</v>
@@ -24236,7 +24269,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24442,7 +24475,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24523,7 +24556,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ113">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR113">
         <v>1.37</v>
@@ -24648,7 +24681,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24726,7 +24759,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ114">
         <v>1.33</v>
@@ -24854,7 +24887,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25060,7 +25093,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25138,7 +25171,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ116">
         <v>1.3</v>
@@ -25266,7 +25299,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25344,7 +25377,7 @@
         <v>0.33</v>
       </c>
       <c r="AP117">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ117">
         <v>0.3</v>
@@ -25472,7 +25505,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25550,10 +25583,10 @@
         <v>2.17</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ118">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR118">
         <v>1.21</v>
@@ -25678,7 +25711,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25759,7 +25792,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ119">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR119">
         <v>1.77</v>
@@ -25884,7 +25917,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -25962,7 +25995,7 @@
         <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ120">
         <v>1.7</v>
@@ -26090,7 +26123,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26171,7 +26204,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ121">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -26296,7 +26329,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26580,7 +26613,7 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ123">
         <v>0.11</v>
@@ -26789,7 +26822,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ124">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.46</v>
@@ -26914,7 +26947,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27120,7 +27153,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27407,7 +27440,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27738,7 +27771,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27816,7 +27849,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ129">
         <v>1.3</v>
@@ -27944,7 +27977,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28022,7 +28055,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ130">
         <v>1.45</v>
@@ -28231,7 +28264,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ131">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR131">
         <v>1.46</v>
@@ -28356,7 +28389,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28437,7 +28470,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ132">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR132">
         <v>1.64</v>
@@ -28562,7 +28595,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28643,7 +28676,7 @@
         <v>1</v>
       </c>
       <c r="AQ133">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR133">
         <v>1.17</v>
@@ -28768,7 +28801,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28846,7 +28879,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ134">
         <v>1.2</v>
@@ -29052,7 +29085,7 @@
         <v>0.29</v>
       </c>
       <c r="AP135">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ135">
         <v>0.3</v>
@@ -29180,7 +29213,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29258,10 +29291,10 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29386,7 +29419,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29592,7 +29625,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29673,7 +29706,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ138">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.37</v>
@@ -29876,7 +29909,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ139">
         <v>2.22</v>
@@ -30004,7 +30037,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30416,7 +30449,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30909,7 +30942,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ144">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31034,7 +31067,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31112,7 +31145,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ145">
         <v>1.33</v>
@@ -31240,7 +31273,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31446,7 +31479,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31524,10 +31557,10 @@
         <v>2.38</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ147">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -31730,10 +31763,10 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR148">
         <v>1.74</v>
@@ -31939,7 +31972,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR149">
         <v>1.2</v>
@@ -32064,7 +32097,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32142,7 +32175,7 @@
         <v>1.5</v>
       </c>
       <c r="AP150">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ150">
         <v>1.45</v>
@@ -32476,7 +32509,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32554,7 +32587,7 @@
         <v>1.57</v>
       </c>
       <c r="AP152">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ152">
         <v>1.2</v>
@@ -32763,7 +32796,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ153">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR153">
         <v>1.76</v>
@@ -32888,7 +32921,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -32966,10 +32999,10 @@
         <v>2</v>
       </c>
       <c r="AP154">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ154">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR154">
         <v>1.69</v>
@@ -33094,7 +33127,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33172,7 +33205,7 @@
         <v>1.38</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ155">
         <v>1.2</v>
@@ -33300,7 +33333,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -33378,10 +33411,10 @@
         <v>0.63</v>
       </c>
       <c r="AP156">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ156">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR156">
         <v>1.25</v>
@@ -33584,10 +33617,10 @@
         <v>0.89</v>
       </c>
       <c r="AP157">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ157">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR157">
         <v>1.65</v>
@@ -33790,7 +33823,7 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ158">
         <v>1.3</v>
@@ -33999,7 +34032,7 @@
         <v>1</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR159">
         <v>1.15</v>
@@ -34202,10 +34235,10 @@
         <v>2.13</v>
       </c>
       <c r="AP160">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ160">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR160">
         <v>1.75</v>
@@ -34330,7 +34363,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34408,10 +34441,10 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ161">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34536,7 +34569,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34617,7 +34650,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ162">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR162">
         <v>1.5</v>
@@ -34742,7 +34775,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34948,7 +34981,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35154,7 +35187,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35566,7 +35599,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35772,7 +35805,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -35850,7 +35883,7 @@
         <v>0.89</v>
       </c>
       <c r="AP168">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ168">
         <v>0.8</v>
@@ -35978,7 +36011,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36184,7 +36217,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36596,7 +36629,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36677,7 +36710,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ172">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR172">
         <v>1.67</v>
@@ -37008,7 +37041,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37165,6 +37198,1448 @@
       </c>
       <c r="BP174">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7491669</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45689.375</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>79</v>
+      </c>
+      <c r="H175" t="s">
+        <v>73</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>210</v>
+      </c>
+      <c r="P175" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q175">
+        <v>4.1</v>
+      </c>
+      <c r="R175">
+        <v>2.25</v>
+      </c>
+      <c r="S175">
+        <v>2.3</v>
+      </c>
+      <c r="T175">
+        <v>1.31</v>
+      </c>
+      <c r="U175">
+        <v>3.1</v>
+      </c>
+      <c r="V175">
+        <v>2.4</v>
+      </c>
+      <c r="W175">
+        <v>1.49</v>
+      </c>
+      <c r="X175">
+        <v>5.75</v>
+      </c>
+      <c r="Y175">
+        <v>1.12</v>
+      </c>
+      <c r="Z175">
+        <v>4.2</v>
+      </c>
+      <c r="AA175">
+        <v>3.94</v>
+      </c>
+      <c r="AB175">
+        <v>1.84</v>
+      </c>
+      <c r="AC175">
+        <v>1.04</v>
+      </c>
+      <c r="AD175">
+        <v>10</v>
+      </c>
+      <c r="AE175">
+        <v>1.22</v>
+      </c>
+      <c r="AF175">
+        <v>4.2</v>
+      </c>
+      <c r="AG175">
+        <v>1.65</v>
+      </c>
+      <c r="AH175">
+        <v>2.05</v>
+      </c>
+      <c r="AI175">
+        <v>1.65</v>
+      </c>
+      <c r="AJ175">
+        <v>2.1</v>
+      </c>
+      <c r="AK175">
+        <v>1.95</v>
+      </c>
+      <c r="AL175">
+        <v>1.25</v>
+      </c>
+      <c r="AM175">
+        <v>1.24</v>
+      </c>
+      <c r="AN175">
+        <v>1</v>
+      </c>
+      <c r="AO175">
+        <v>1.8</v>
+      </c>
+      <c r="AP175">
+        <v>1.18</v>
+      </c>
+      <c r="AQ175">
+        <v>1.64</v>
+      </c>
+      <c r="AR175">
+        <v>1.23</v>
+      </c>
+      <c r="AS175">
+        <v>1.48</v>
+      </c>
+      <c r="AT175">
+        <v>2.71</v>
+      </c>
+      <c r="AU175">
+        <v>3</v>
+      </c>
+      <c r="AV175">
+        <v>2</v>
+      </c>
+      <c r="AW175">
+        <v>4</v>
+      </c>
+      <c r="AX175">
+        <v>12</v>
+      </c>
+      <c r="AY175">
+        <v>9</v>
+      </c>
+      <c r="AZ175">
+        <v>15</v>
+      </c>
+      <c r="BA175">
+        <v>4</v>
+      </c>
+      <c r="BB175">
+        <v>12</v>
+      </c>
+      <c r="BC175">
+        <v>16</v>
+      </c>
+      <c r="BD175">
+        <v>2.55</v>
+      </c>
+      <c r="BE175">
+        <v>6.5</v>
+      </c>
+      <c r="BF175">
+        <v>1.64</v>
+      </c>
+      <c r="BG175">
+        <v>1.21</v>
+      </c>
+      <c r="BH175">
+        <v>3.8</v>
+      </c>
+      <c r="BI175">
+        <v>1.38</v>
+      </c>
+      <c r="BJ175">
+        <v>2.75</v>
+      </c>
+      <c r="BK175">
+        <v>1.62</v>
+      </c>
+      <c r="BL175">
+        <v>2.14</v>
+      </c>
+      <c r="BM175">
+        <v>1.96</v>
+      </c>
+      <c r="BN175">
+        <v>1.73</v>
+      </c>
+      <c r="BO175">
+        <v>2.43</v>
+      </c>
+      <c r="BP175">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7491668</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45689.375</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>86</v>
+      </c>
+      <c r="H176" t="s">
+        <v>70</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>2</v>
+      </c>
+      <c r="K176">
+        <v>3</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>2</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>211</v>
+      </c>
+      <c r="P176" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q176">
+        <v>4.33</v>
+      </c>
+      <c r="R176">
+        <v>2.25</v>
+      </c>
+      <c r="S176">
+        <v>2.2</v>
+      </c>
+      <c r="T176">
+        <v>1.31</v>
+      </c>
+      <c r="U176">
+        <v>3.1</v>
+      </c>
+      <c r="V176">
+        <v>2.45</v>
+      </c>
+      <c r="W176">
+        <v>1.47</v>
+      </c>
+      <c r="X176">
+        <v>6</v>
+      </c>
+      <c r="Y176">
+        <v>1.11</v>
+      </c>
+      <c r="Z176">
+        <v>4.8</v>
+      </c>
+      <c r="AA176">
+        <v>3.97</v>
+      </c>
+      <c r="AB176">
+        <v>1.74</v>
+      </c>
+      <c r="AC176">
+        <v>1.05</v>
+      </c>
+      <c r="AD176">
+        <v>9.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.25</v>
+      </c>
+      <c r="AF176">
+        <v>3.9</v>
+      </c>
+      <c r="AG176">
+        <v>1.81</v>
+      </c>
+      <c r="AH176">
+        <v>2.01</v>
+      </c>
+      <c r="AI176">
+        <v>1.7</v>
+      </c>
+      <c r="AJ176">
+        <v>2</v>
+      </c>
+      <c r="AK176">
+        <v>2.05</v>
+      </c>
+      <c r="AL176">
+        <v>1.22</v>
+      </c>
+      <c r="AM176">
+        <v>1.2</v>
+      </c>
+      <c r="AN176">
+        <v>1.33</v>
+      </c>
+      <c r="AO176">
+        <v>1.89</v>
+      </c>
+      <c r="AP176">
+        <v>1.2</v>
+      </c>
+      <c r="AQ176">
+        <v>2</v>
+      </c>
+      <c r="AR176">
+        <v>1.21</v>
+      </c>
+      <c r="AS176">
+        <v>1.53</v>
+      </c>
+      <c r="AT176">
+        <v>2.74</v>
+      </c>
+      <c r="AU176">
+        <v>5</v>
+      </c>
+      <c r="AV176">
+        <v>6</v>
+      </c>
+      <c r="AW176">
+        <v>11</v>
+      </c>
+      <c r="AX176">
+        <v>9</v>
+      </c>
+      <c r="AY176">
+        <v>17</v>
+      </c>
+      <c r="AZ176">
+        <v>16</v>
+      </c>
+      <c r="BA176">
+        <v>10</v>
+      </c>
+      <c r="BB176">
+        <v>4</v>
+      </c>
+      <c r="BC176">
+        <v>14</v>
+      </c>
+      <c r="BD176">
+        <v>2.7</v>
+      </c>
+      <c r="BE176">
+        <v>6.5</v>
+      </c>
+      <c r="BF176">
+        <v>1.57</v>
+      </c>
+      <c r="BG176">
+        <v>1.36</v>
+      </c>
+      <c r="BH176">
+        <v>2.8</v>
+      </c>
+      <c r="BI176">
+        <v>1.61</v>
+      </c>
+      <c r="BJ176">
+        <v>2.15</v>
+      </c>
+      <c r="BK176">
+        <v>1.98</v>
+      </c>
+      <c r="BL176">
+        <v>1.72</v>
+      </c>
+      <c r="BM176">
+        <v>2.5</v>
+      </c>
+      <c r="BN176">
+        <v>1.46</v>
+      </c>
+      <c r="BO176">
+        <v>3.3</v>
+      </c>
+      <c r="BP176">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7491661</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45689.375</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>83</v>
+      </c>
+      <c r="H177" t="s">
+        <v>78</v>
+      </c>
+      <c r="I177">
+        <v>2</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>3</v>
+      </c>
+      <c r="L177">
+        <v>3</v>
+      </c>
+      <c r="M177">
+        <v>2</v>
+      </c>
+      <c r="N177">
+        <v>5</v>
+      </c>
+      <c r="O177" t="s">
+        <v>212</v>
+      </c>
+      <c r="P177" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q177">
+        <v>2.2</v>
+      </c>
+      <c r="R177">
+        <v>2.2</v>
+      </c>
+      <c r="S177">
+        <v>4.6</v>
+      </c>
+      <c r="T177">
+        <v>1.34</v>
+      </c>
+      <c r="U177">
+        <v>3</v>
+      </c>
+      <c r="V177">
+        <v>2.55</v>
+      </c>
+      <c r="W177">
+        <v>1.44</v>
+      </c>
+      <c r="X177">
+        <v>6.25</v>
+      </c>
+      <c r="Y177">
+        <v>1.1</v>
+      </c>
+      <c r="Z177">
+        <v>1.64</v>
+      </c>
+      <c r="AA177">
+        <v>4.2</v>
+      </c>
+      <c r="AB177">
+        <v>5.4</v>
+      </c>
+      <c r="AC177">
+        <v>1.05</v>
+      </c>
+      <c r="AD177">
+        <v>9.5</v>
+      </c>
+      <c r="AE177">
+        <v>1.25</v>
+      </c>
+      <c r="AF177">
+        <v>3.75</v>
+      </c>
+      <c r="AG177">
+        <v>1.81</v>
+      </c>
+      <c r="AH177">
+        <v>2.01</v>
+      </c>
+      <c r="AI177">
+        <v>1.77</v>
+      </c>
+      <c r="AJ177">
+        <v>1.93</v>
+      </c>
+      <c r="AK177">
+        <v>1.19</v>
+      </c>
+      <c r="AL177">
+        <v>1.24</v>
+      </c>
+      <c r="AM177">
+        <v>2.1</v>
+      </c>
+      <c r="AN177">
+        <v>1</v>
+      </c>
+      <c r="AO177">
+        <v>0.8</v>
+      </c>
+      <c r="AP177">
+        <v>1.18</v>
+      </c>
+      <c r="AQ177">
+        <v>0.73</v>
+      </c>
+      <c r="AR177">
+        <v>1.61</v>
+      </c>
+      <c r="AS177">
+        <v>1.1</v>
+      </c>
+      <c r="AT177">
+        <v>2.71</v>
+      </c>
+      <c r="AU177">
+        <v>4</v>
+      </c>
+      <c r="AV177">
+        <v>8</v>
+      </c>
+      <c r="AW177">
+        <v>8</v>
+      </c>
+      <c r="AX177">
+        <v>15</v>
+      </c>
+      <c r="AY177">
+        <v>16</v>
+      </c>
+      <c r="AZ177">
+        <v>28</v>
+      </c>
+      <c r="BA177">
+        <v>0</v>
+      </c>
+      <c r="BB177">
+        <v>4</v>
+      </c>
+      <c r="BC177">
+        <v>4</v>
+      </c>
+      <c r="BD177">
+        <v>1.5</v>
+      </c>
+      <c r="BE177">
+        <v>7</v>
+      </c>
+      <c r="BF177">
+        <v>2.8</v>
+      </c>
+      <c r="BG177">
+        <v>1.24</v>
+      </c>
+      <c r="BH177">
+        <v>3.55</v>
+      </c>
+      <c r="BI177">
+        <v>1.41</v>
+      </c>
+      <c r="BJ177">
+        <v>2.63</v>
+      </c>
+      <c r="BK177">
+        <v>1.67</v>
+      </c>
+      <c r="BL177">
+        <v>2.05</v>
+      </c>
+      <c r="BM177">
+        <v>2.05</v>
+      </c>
+      <c r="BN177">
+        <v>1.67</v>
+      </c>
+      <c r="BO177">
+        <v>2.55</v>
+      </c>
+      <c r="BP177">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7491664</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45689.6875</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>75</v>
+      </c>
+      <c r="H178" t="s">
+        <v>74</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>2</v>
+      </c>
+      <c r="K178">
+        <v>2</v>
+      </c>
+      <c r="L178">
+        <v>2</v>
+      </c>
+      <c r="M178">
+        <v>5</v>
+      </c>
+      <c r="N178">
+        <v>7</v>
+      </c>
+      <c r="O178" t="s">
+        <v>213</v>
+      </c>
+      <c r="P178" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q178">
+        <v>2.75</v>
+      </c>
+      <c r="R178">
+        <v>2.38</v>
+      </c>
+      <c r="S178">
+        <v>3.25</v>
+      </c>
+      <c r="T178">
+        <v>1.29</v>
+      </c>
+      <c r="U178">
+        <v>3.5</v>
+      </c>
+      <c r="V178">
+        <v>2.38</v>
+      </c>
+      <c r="W178">
+        <v>1.53</v>
+      </c>
+      <c r="X178">
+        <v>5.5</v>
+      </c>
+      <c r="Y178">
+        <v>1.14</v>
+      </c>
+      <c r="Z178">
+        <v>2.53</v>
+      </c>
+      <c r="AA178">
+        <v>3.84</v>
+      </c>
+      <c r="AB178">
+        <v>2.64</v>
+      </c>
+      <c r="AC178">
+        <v>1.01</v>
+      </c>
+      <c r="AD178">
+        <v>13</v>
+      </c>
+      <c r="AE178">
+        <v>1.18</v>
+      </c>
+      <c r="AF178">
+        <v>4.75</v>
+      </c>
+      <c r="AG178">
+        <v>1.52</v>
+      </c>
+      <c r="AH178">
+        <v>2.43</v>
+      </c>
+      <c r="AI178">
+        <v>1.5</v>
+      </c>
+      <c r="AJ178">
+        <v>2.5</v>
+      </c>
+      <c r="AK178">
+        <v>1.39</v>
+      </c>
+      <c r="AL178">
+        <v>1.29</v>
+      </c>
+      <c r="AM178">
+        <v>1.58</v>
+      </c>
+      <c r="AN178">
+        <v>1.22</v>
+      </c>
+      <c r="AO178">
+        <v>2.5</v>
+      </c>
+      <c r="AP178">
+        <v>1.1</v>
+      </c>
+      <c r="AQ178">
+        <v>2.55</v>
+      </c>
+      <c r="AR178">
+        <v>1.59</v>
+      </c>
+      <c r="AS178">
+        <v>1.44</v>
+      </c>
+      <c r="AT178">
+        <v>3.03</v>
+      </c>
+      <c r="AU178">
+        <v>9</v>
+      </c>
+      <c r="AV178">
+        <v>12</v>
+      </c>
+      <c r="AW178">
+        <v>10</v>
+      </c>
+      <c r="AX178">
+        <v>6</v>
+      </c>
+      <c r="AY178">
+        <v>22</v>
+      </c>
+      <c r="AZ178">
+        <v>20</v>
+      </c>
+      <c r="BA178">
+        <v>4</v>
+      </c>
+      <c r="BB178">
+        <v>6</v>
+      </c>
+      <c r="BC178">
+        <v>10</v>
+      </c>
+      <c r="BD178">
+        <v>1.84</v>
+      </c>
+      <c r="BE178">
+        <v>6.5</v>
+      </c>
+      <c r="BF178">
+        <v>2.15</v>
+      </c>
+      <c r="BG178">
+        <v>1.21</v>
+      </c>
+      <c r="BH178">
+        <v>3.8</v>
+      </c>
+      <c r="BI178">
+        <v>1.38</v>
+      </c>
+      <c r="BJ178">
+        <v>2.7</v>
+      </c>
+      <c r="BK178">
+        <v>1.64</v>
+      </c>
+      <c r="BL178">
+        <v>2.1</v>
+      </c>
+      <c r="BM178">
+        <v>1.98</v>
+      </c>
+      <c r="BN178">
+        <v>1.72</v>
+      </c>
+      <c r="BO178">
+        <v>2.48</v>
+      </c>
+      <c r="BP178">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7491663</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45690.39583333334</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>85</v>
+      </c>
+      <c r="H179" t="s">
+        <v>77</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>2</v>
+      </c>
+      <c r="N179">
+        <v>3</v>
+      </c>
+      <c r="O179" t="s">
+        <v>214</v>
+      </c>
+      <c r="P179" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q179">
+        <v>2.2</v>
+      </c>
+      <c r="R179">
+        <v>2.4</v>
+      </c>
+      <c r="S179">
+        <v>4.75</v>
+      </c>
+      <c r="T179">
+        <v>1.29</v>
+      </c>
+      <c r="U179">
+        <v>3.5</v>
+      </c>
+      <c r="V179">
+        <v>2.38</v>
+      </c>
+      <c r="W179">
+        <v>1.53</v>
+      </c>
+      <c r="X179">
+        <v>5.5</v>
+      </c>
+      <c r="Y179">
+        <v>1.14</v>
+      </c>
+      <c r="Z179">
+        <v>1.73</v>
+      </c>
+      <c r="AA179">
+        <v>4.2</v>
+      </c>
+      <c r="AB179">
+        <v>4.6</v>
+      </c>
+      <c r="AC179">
+        <v>1.04</v>
+      </c>
+      <c r="AD179">
+        <v>10</v>
+      </c>
+      <c r="AE179">
+        <v>1.17</v>
+      </c>
+      <c r="AF179">
+        <v>4.75</v>
+      </c>
+      <c r="AG179">
+        <v>1.53</v>
+      </c>
+      <c r="AH179">
+        <v>2.2</v>
+      </c>
+      <c r="AI179">
+        <v>1.57</v>
+      </c>
+      <c r="AJ179">
+        <v>2.25</v>
+      </c>
+      <c r="AK179">
+        <v>1.2</v>
+      </c>
+      <c r="AL179">
+        <v>1.23</v>
+      </c>
+      <c r="AM179">
+        <v>2.1</v>
+      </c>
+      <c r="AN179">
+        <v>1.56</v>
+      </c>
+      <c r="AO179">
+        <v>1</v>
+      </c>
+      <c r="AP179">
+        <v>1.4</v>
+      </c>
+      <c r="AQ179">
+        <v>1.2</v>
+      </c>
+      <c r="AR179">
+        <v>1.64</v>
+      </c>
+      <c r="AS179">
+        <v>1.26</v>
+      </c>
+      <c r="AT179">
+        <v>2.9</v>
+      </c>
+      <c r="AU179">
+        <v>8</v>
+      </c>
+      <c r="AV179">
+        <v>7</v>
+      </c>
+      <c r="AW179">
+        <v>7</v>
+      </c>
+      <c r="AX179">
+        <v>4</v>
+      </c>
+      <c r="AY179">
+        <v>17</v>
+      </c>
+      <c r="AZ179">
+        <v>11</v>
+      </c>
+      <c r="BA179">
+        <v>6</v>
+      </c>
+      <c r="BB179">
+        <v>6</v>
+      </c>
+      <c r="BC179">
+        <v>12</v>
+      </c>
+      <c r="BD179">
+        <v>1.53</v>
+      </c>
+      <c r="BE179">
+        <v>6.75</v>
+      </c>
+      <c r="BF179">
+        <v>2.7</v>
+      </c>
+      <c r="BG179">
+        <v>1.2</v>
+      </c>
+      <c r="BH179">
+        <v>3.95</v>
+      </c>
+      <c r="BI179">
+        <v>1.35</v>
+      </c>
+      <c r="BJ179">
+        <v>2.88</v>
+      </c>
+      <c r="BK179">
+        <v>1.58</v>
+      </c>
+      <c r="BL179">
+        <v>2.18</v>
+      </c>
+      <c r="BM179">
+        <v>1.92</v>
+      </c>
+      <c r="BN179">
+        <v>1.77</v>
+      </c>
+      <c r="BO179">
+        <v>2.4</v>
+      </c>
+      <c r="BP179">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7491667</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45690.39583333334</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>80</v>
+      </c>
+      <c r="H180" t="s">
+        <v>87</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>2</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>215</v>
+      </c>
+      <c r="P180" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q180">
+        <v>2.5</v>
+      </c>
+      <c r="R180">
+        <v>2.25</v>
+      </c>
+      <c r="S180">
+        <v>4.33</v>
+      </c>
+      <c r="T180">
+        <v>1.36</v>
+      </c>
+      <c r="U180">
+        <v>3</v>
+      </c>
+      <c r="V180">
+        <v>2.63</v>
+      </c>
+      <c r="W180">
+        <v>1.44</v>
+      </c>
+      <c r="X180">
+        <v>7</v>
+      </c>
+      <c r="Y180">
+        <v>1.1</v>
+      </c>
+      <c r="Z180">
+        <v>1.91</v>
+      </c>
+      <c r="AA180">
+        <v>3.82</v>
+      </c>
+      <c r="AB180">
+        <v>3.99</v>
+      </c>
+      <c r="AC180">
+        <v>1.05</v>
+      </c>
+      <c r="AD180">
+        <v>9.5</v>
+      </c>
+      <c r="AE180">
+        <v>1.25</v>
+      </c>
+      <c r="AF180">
+        <v>3.75</v>
+      </c>
+      <c r="AG180">
+        <v>1.82</v>
+      </c>
+      <c r="AH180">
+        <v>2</v>
+      </c>
+      <c r="AI180">
+        <v>1.73</v>
+      </c>
+      <c r="AJ180">
+        <v>2</v>
+      </c>
+      <c r="AK180">
+        <v>1.25</v>
+      </c>
+      <c r="AL180">
+        <v>1.27</v>
+      </c>
+      <c r="AM180">
+        <v>1.87</v>
+      </c>
+      <c r="AN180">
+        <v>1.67</v>
+      </c>
+      <c r="AO180">
+        <v>1.11</v>
+      </c>
+      <c r="AP180">
+        <v>1.8</v>
+      </c>
+      <c r="AQ180">
+        <v>1</v>
+      </c>
+      <c r="AR180">
+        <v>1.74</v>
+      </c>
+      <c r="AS180">
+        <v>1.24</v>
+      </c>
+      <c r="AT180">
+        <v>2.98</v>
+      </c>
+      <c r="AU180">
+        <v>5</v>
+      </c>
+      <c r="AV180">
+        <v>6</v>
+      </c>
+      <c r="AW180">
+        <v>11</v>
+      </c>
+      <c r="AX180">
+        <v>13</v>
+      </c>
+      <c r="AY180">
+        <v>22</v>
+      </c>
+      <c r="AZ180">
+        <v>23</v>
+      </c>
+      <c r="BA180">
+        <v>4</v>
+      </c>
+      <c r="BB180">
+        <v>4</v>
+      </c>
+      <c r="BC180">
+        <v>8</v>
+      </c>
+      <c r="BD180">
+        <v>1.61</v>
+      </c>
+      <c r="BE180">
+        <v>7</v>
+      </c>
+      <c r="BF180">
+        <v>2.5</v>
+      </c>
+      <c r="BG180">
+        <v>1.2</v>
+      </c>
+      <c r="BH180">
+        <v>3.95</v>
+      </c>
+      <c r="BI180">
+        <v>1.34</v>
+      </c>
+      <c r="BJ180">
+        <v>2.9</v>
+      </c>
+      <c r="BK180">
+        <v>1.57</v>
+      </c>
+      <c r="BL180">
+        <v>2.23</v>
+      </c>
+      <c r="BM180">
+        <v>1.9</v>
+      </c>
+      <c r="BN180">
+        <v>1.79</v>
+      </c>
+      <c r="BO180">
+        <v>2.35</v>
+      </c>
+      <c r="BP180">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7491662</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45690.39583333334</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>84</v>
+      </c>
+      <c r="H181" t="s">
+        <v>72</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>4</v>
+      </c>
+      <c r="O181" t="s">
+        <v>176</v>
+      </c>
+      <c r="P181" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q181">
+        <v>2.5</v>
+      </c>
+      <c r="R181">
+        <v>2.3</v>
+      </c>
+      <c r="S181">
+        <v>4</v>
+      </c>
+      <c r="T181">
+        <v>1.33</v>
+      </c>
+      <c r="U181">
+        <v>3.25</v>
+      </c>
+      <c r="V181">
+        <v>2.5</v>
+      </c>
+      <c r="W181">
+        <v>1.5</v>
+      </c>
+      <c r="X181">
+        <v>6</v>
+      </c>
+      <c r="Y181">
+        <v>1.13</v>
+      </c>
+      <c r="Z181">
+        <v>1.89</v>
+      </c>
+      <c r="AA181">
+        <v>3.89</v>
+      </c>
+      <c r="AB181">
+        <v>4</v>
+      </c>
+      <c r="AC181">
+        <v>1.04</v>
+      </c>
+      <c r="AD181">
+        <v>10</v>
+      </c>
+      <c r="AE181">
+        <v>1.2</v>
+      </c>
+      <c r="AF181">
+        <v>4.2</v>
+      </c>
+      <c r="AG181">
+        <v>1.55</v>
+      </c>
+      <c r="AH181">
+        <v>2.2</v>
+      </c>
+      <c r="AI181">
+        <v>1.62</v>
+      </c>
+      <c r="AJ181">
+        <v>2.2</v>
+      </c>
+      <c r="AK181">
+        <v>1.25</v>
+      </c>
+      <c r="AL181">
+        <v>1.26</v>
+      </c>
+      <c r="AM181">
+        <v>1.88</v>
+      </c>
+      <c r="AN181">
+        <v>2</v>
+      </c>
+      <c r="AO181">
+        <v>0.89</v>
+      </c>
+      <c r="AP181">
+        <v>1.91</v>
+      </c>
+      <c r="AQ181">
+        <v>0.9</v>
+      </c>
+      <c r="AR181">
+        <v>1.76</v>
+      </c>
+      <c r="AS181">
+        <v>1.22</v>
+      </c>
+      <c r="AT181">
+        <v>2.98</v>
+      </c>
+      <c r="AU181">
+        <v>4</v>
+      </c>
+      <c r="AV181">
+        <v>4</v>
+      </c>
+      <c r="AW181">
+        <v>17</v>
+      </c>
+      <c r="AX181">
+        <v>12</v>
+      </c>
+      <c r="AY181">
+        <v>28</v>
+      </c>
+      <c r="AZ181">
+        <v>20</v>
+      </c>
+      <c r="BA181">
+        <v>6</v>
+      </c>
+      <c r="BB181">
+        <v>3</v>
+      </c>
+      <c r="BC181">
+        <v>9</v>
+      </c>
+      <c r="BD181">
+        <v>1.65</v>
+      </c>
+      <c r="BE181">
+        <v>6.75</v>
+      </c>
+      <c r="BF181">
+        <v>2.48</v>
+      </c>
+      <c r="BG181">
+        <v>1.19</v>
+      </c>
+      <c r="BH181">
+        <v>4</v>
+      </c>
+      <c r="BI181">
+        <v>1.34</v>
+      </c>
+      <c r="BJ181">
+        <v>2.9</v>
+      </c>
+      <c r="BK181">
+        <v>1.58</v>
+      </c>
+      <c r="BL181">
+        <v>2.2</v>
+      </c>
+      <c r="BM181">
+        <v>1.91</v>
+      </c>
+      <c r="BN181">
+        <v>1.77</v>
+      </c>
+      <c r="BO181">
+        <v>2.35</v>
+      </c>
+      <c r="BP181">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -37976,13 +37976,13 @@
         <v>20</v>
       </c>
       <c r="BA178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB178">
         <v>6</v>
       </c>
       <c r="BC178">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD178">
         <v>1.84</v>
@@ -38391,10 +38391,10 @@
         <v>4</v>
       </c>
       <c r="BB180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC180">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD180">
         <v>1.61</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,12 @@
     <t>['50', '90+2']</t>
   </si>
   <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['31', '37']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -992,6 +998,12 @@
   </si>
   <si>
     <t>['52', '79']</t>
+  </si>
+  <si>
+    <t>['45+3', '90+4']</t>
+  </si>
+  <si>
+    <t>['6']</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1621,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1690,7 +1702,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ2">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1815,7 +1827,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2102,7 +2114,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ4">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2227,7 +2239,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2639,7 +2651,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2845,7 +2857,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3051,7 +3063,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3129,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3257,7 +3269,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3669,7 +3681,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4081,7 +4093,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4493,7 +4505,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4699,7 +4711,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4905,7 +4917,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5189,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ19">
         <v>0.9</v>
@@ -5317,7 +5329,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5604,7 +5616,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ21">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -5729,7 +5741,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -5807,7 +5819,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ22">
         <v>1.7</v>
@@ -6013,7 +6025,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ23">
         <v>1.7</v>
@@ -6222,7 +6234,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ24">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6553,7 +6565,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6759,7 +6771,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6965,7 +6977,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7377,7 +7389,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7583,7 +7595,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7995,7 +8007,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8201,7 +8213,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8613,7 +8625,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8819,7 +8831,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9025,7 +9037,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9103,7 +9115,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ38">
         <v>1.7</v>
@@ -9437,7 +9449,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9643,7 +9655,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9849,7 +9861,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10055,7 +10067,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10339,7 +10351,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
         <v>1.33</v>
@@ -10467,7 +10479,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10754,7 +10766,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ46">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR46">
         <v>1.28</v>
@@ -10879,7 +10891,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11085,7 +11097,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11291,7 +11303,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11497,7 +11509,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11909,7 +11921,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11990,7 +12002,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR52">
         <v>1.99</v>
@@ -12115,7 +12127,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12321,7 +12333,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12527,7 +12539,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12733,7 +12745,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12939,7 +12951,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13017,7 +13029,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ57">
         <v>2.22</v>
@@ -13145,7 +13157,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13557,7 +13569,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13763,7 +13775,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13841,7 +13853,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ61">
         <v>1.3</v>
@@ -14175,7 +14187,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14381,7 +14393,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14668,7 +14680,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ65">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR65">
         <v>1.43</v>
@@ -14793,7 +14805,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15411,7 +15423,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15617,7 +15629,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15823,7 +15835,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16235,7 +16247,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16316,7 +16328,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR73">
         <v>1.59</v>
@@ -16853,7 +16865,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16931,7 +16943,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ76">
         <v>1.33</v>
@@ -17059,7 +17071,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17883,7 +17895,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17961,7 +17973,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
         <v>0.8</v>
@@ -18295,7 +18307,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18501,7 +18513,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18582,7 +18594,7 @@
         <v>2</v>
       </c>
       <c r="AQ84">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR84">
         <v>1.18</v>
@@ -18707,7 +18719,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18913,7 +18925,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19119,7 +19131,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19200,7 +19212,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ87">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR87">
         <v>1.33</v>
@@ -19325,7 +19337,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19531,7 +19543,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19737,7 +19749,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20227,7 +20239,7 @@
         <v>3</v>
       </c>
       <c r="AP92">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ92">
         <v>2.22</v>
@@ -20767,7 +20779,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20845,7 +20857,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ95">
         <v>1.2</v>
@@ -21179,7 +21191,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21385,7 +21397,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22003,7 +22015,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22084,7 +22096,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ101">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR101">
         <v>1.49</v>
@@ -22621,7 +22633,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23033,7 +23045,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23239,7 +23251,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23526,7 +23538,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ108">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR108">
         <v>1.53</v>
@@ -23651,7 +23663,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23857,7 +23869,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24141,7 +24153,7 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ111">
         <v>2</v>
@@ -24269,7 +24281,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24347,7 +24359,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ112">
         <v>1.45</v>
@@ -24475,7 +24487,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24681,7 +24693,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24887,7 +24899,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25093,7 +25105,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25299,7 +25311,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25505,7 +25517,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25711,7 +25723,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25917,7 +25929,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26123,7 +26135,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26329,7 +26341,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26616,7 +26628,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ123">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -26947,7 +26959,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27028,7 +27040,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ125">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR125">
         <v>1.52</v>
@@ -27153,7 +27165,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27771,7 +27783,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27977,7 +27989,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28261,7 +28273,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ131">
         <v>1.64</v>
@@ -28389,7 +28401,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28595,7 +28607,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28673,7 +28685,7 @@
         <v>2.29</v>
       </c>
       <c r="AP133">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ133">
         <v>2.55</v>
@@ -28801,7 +28813,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29213,7 +29225,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29419,7 +29431,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29500,7 +29512,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ137">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR137">
         <v>1.55</v>
@@ -29625,7 +29637,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30037,7 +30049,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30324,7 +30336,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR141">
         <v>1.46</v>
@@ -30449,7 +30461,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30939,7 +30951,7 @@
         <v>0.71</v>
       </c>
       <c r="AP144">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ144">
         <v>0.9</v>
@@ -31067,7 +31079,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31273,7 +31285,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31479,7 +31491,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31969,7 +31981,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ149">
         <v>0.73</v>
@@ -32097,7 +32109,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32509,7 +32521,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32921,7 +32933,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33127,7 +33139,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33333,7 +33345,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -34029,7 +34041,7 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ159">
         <v>1.2</v>
@@ -34363,7 +34375,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34569,7 +34581,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34775,7 +34787,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34981,7 +34993,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35187,7 +35199,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35265,7 +35277,7 @@
         <v>1.56</v>
       </c>
       <c r="AP165">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ165">
         <v>1.7</v>
@@ -35599,7 +35611,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35805,7 +35817,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36011,7 +36023,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36092,7 +36104,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ169">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36217,7 +36229,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36298,7 +36310,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR170">
         <v>1.46</v>
@@ -36629,7 +36641,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37041,7 +37053,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37453,7 +37465,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37659,7 +37671,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37865,7 +37877,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38071,7 +38083,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38277,7 +38289,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38483,7 +38495,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38640,6 +38652,418 @@
       </c>
       <c r="BP181">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7491678</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45695.60416666666</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>87</v>
+      </c>
+      <c r="H182" t="s">
+        <v>84</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>2</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>2</v>
+      </c>
+      <c r="N182">
+        <v>3</v>
+      </c>
+      <c r="O182" t="s">
+        <v>216</v>
+      </c>
+      <c r="P182" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q182">
+        <v>4</v>
+      </c>
+      <c r="R182">
+        <v>2.3</v>
+      </c>
+      <c r="S182">
+        <v>2.5</v>
+      </c>
+      <c r="T182">
+        <v>1.3</v>
+      </c>
+      <c r="U182">
+        <v>3.4</v>
+      </c>
+      <c r="V182">
+        <v>2.5</v>
+      </c>
+      <c r="W182">
+        <v>1.5</v>
+      </c>
+      <c r="X182">
+        <v>6</v>
+      </c>
+      <c r="Y182">
+        <v>1.13</v>
+      </c>
+      <c r="Z182">
+        <v>3.75</v>
+      </c>
+      <c r="AA182">
+        <v>4</v>
+      </c>
+      <c r="AB182">
+        <v>1.92</v>
+      </c>
+      <c r="AC182">
+        <v>1.04</v>
+      </c>
+      <c r="AD182">
+        <v>10</v>
+      </c>
+      <c r="AE182">
+        <v>1.2</v>
+      </c>
+      <c r="AF182">
+        <v>4.1</v>
+      </c>
+      <c r="AG182">
+        <v>1.57</v>
+      </c>
+      <c r="AH182">
+        <v>2.15</v>
+      </c>
+      <c r="AI182">
+        <v>1.57</v>
+      </c>
+      <c r="AJ182">
+        <v>2.25</v>
+      </c>
+      <c r="AK182">
+        <v>1.83</v>
+      </c>
+      <c r="AL182">
+        <v>1.25</v>
+      </c>
+      <c r="AM182">
+        <v>1.28</v>
+      </c>
+      <c r="AN182">
+        <v>1</v>
+      </c>
+      <c r="AO182">
+        <v>1.56</v>
+      </c>
+      <c r="AP182">
+        <v>0.91</v>
+      </c>
+      <c r="AQ182">
+        <v>1.7</v>
+      </c>
+      <c r="AR182">
+        <v>1.22</v>
+      </c>
+      <c r="AS182">
+        <v>1.43</v>
+      </c>
+      <c r="AT182">
+        <v>2.65</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>7</v>
+      </c>
+      <c r="AW182">
+        <v>3</v>
+      </c>
+      <c r="AX182">
+        <v>8</v>
+      </c>
+      <c r="AY182">
+        <v>8</v>
+      </c>
+      <c r="AZ182">
+        <v>17</v>
+      </c>
+      <c r="BA182">
+        <v>3</v>
+      </c>
+      <c r="BB182">
+        <v>7</v>
+      </c>
+      <c r="BC182">
+        <v>10</v>
+      </c>
+      <c r="BD182">
+        <v>2.55</v>
+      </c>
+      <c r="BE182">
+        <v>7</v>
+      </c>
+      <c r="BF182">
+        <v>1.58</v>
+      </c>
+      <c r="BG182">
+        <v>1.2</v>
+      </c>
+      <c r="BH182">
+        <v>3.9</v>
+      </c>
+      <c r="BI182">
+        <v>1.28</v>
+      </c>
+      <c r="BJ182">
+        <v>3.2</v>
+      </c>
+      <c r="BK182">
+        <v>1.51</v>
+      </c>
+      <c r="BL182">
+        <v>2.3</v>
+      </c>
+      <c r="BM182">
+        <v>1.88</v>
+      </c>
+      <c r="BN182">
+        <v>1.75</v>
+      </c>
+      <c r="BO182">
+        <v>2.45</v>
+      </c>
+      <c r="BP182">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7491674</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45695.60416666666</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>77</v>
+      </c>
+      <c r="H183" t="s">
+        <v>79</v>
+      </c>
+      <c r="I183">
+        <v>2</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>3</v>
+      </c>
+      <c r="L183">
+        <v>2</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183" t="s">
+        <v>217</v>
+      </c>
+      <c r="P183" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q183">
+        <v>2.4</v>
+      </c>
+      <c r="R183">
+        <v>2.3</v>
+      </c>
+      <c r="S183">
+        <v>4.5</v>
+      </c>
+      <c r="T183">
+        <v>1.33</v>
+      </c>
+      <c r="U183">
+        <v>3.25</v>
+      </c>
+      <c r="V183">
+        <v>2.63</v>
+      </c>
+      <c r="W183">
+        <v>1.44</v>
+      </c>
+      <c r="X183">
+        <v>6.5</v>
+      </c>
+      <c r="Y183">
+        <v>1.11</v>
+      </c>
+      <c r="Z183">
+        <v>1.71</v>
+      </c>
+      <c r="AA183">
+        <v>4.1</v>
+      </c>
+      <c r="AB183">
+        <v>4.8</v>
+      </c>
+      <c r="AC183">
+        <v>1.04</v>
+      </c>
+      <c r="AD183">
+        <v>10</v>
+      </c>
+      <c r="AE183">
+        <v>1.22</v>
+      </c>
+      <c r="AF183">
+        <v>3.85</v>
+      </c>
+      <c r="AG183">
+        <v>1.67</v>
+      </c>
+      <c r="AH183">
+        <v>2</v>
+      </c>
+      <c r="AI183">
+        <v>1.67</v>
+      </c>
+      <c r="AJ183">
+        <v>2.1</v>
+      </c>
+      <c r="AK183">
+        <v>1.23</v>
+      </c>
+      <c r="AL183">
+        <v>1.26</v>
+      </c>
+      <c r="AM183">
+        <v>1.93</v>
+      </c>
+      <c r="AN183">
+        <v>1.1</v>
+      </c>
+      <c r="AO183">
+        <v>0.11</v>
+      </c>
+      <c r="AP183">
+        <v>1.27</v>
+      </c>
+      <c r="AQ183">
+        <v>0.1</v>
+      </c>
+      <c r="AR183">
+        <v>1.4</v>
+      </c>
+      <c r="AS183">
+        <v>1.11</v>
+      </c>
+      <c r="AT183">
+        <v>2.51</v>
+      </c>
+      <c r="AU183">
+        <v>6</v>
+      </c>
+      <c r="AV183">
+        <v>3</v>
+      </c>
+      <c r="AW183">
+        <v>15</v>
+      </c>
+      <c r="AX183">
+        <v>11</v>
+      </c>
+      <c r="AY183">
+        <v>29</v>
+      </c>
+      <c r="AZ183">
+        <v>18</v>
+      </c>
+      <c r="BA183">
+        <v>9</v>
+      </c>
+      <c r="BB183">
+        <v>3</v>
+      </c>
+      <c r="BC183">
+        <v>12</v>
+      </c>
+      <c r="BD183">
+        <v>1.57</v>
+      </c>
+      <c r="BE183">
+        <v>7</v>
+      </c>
+      <c r="BF183">
+        <v>2.65</v>
+      </c>
+      <c r="BG183">
+        <v>1.21</v>
+      </c>
+      <c r="BH183">
+        <v>3.8</v>
+      </c>
+      <c r="BI183">
+        <v>1.31</v>
+      </c>
+      <c r="BJ183">
+        <v>3</v>
+      </c>
+      <c r="BK183">
+        <v>1.57</v>
+      </c>
+      <c r="BL183">
+        <v>2.15</v>
+      </c>
+      <c r="BM183">
+        <v>1.98</v>
+      </c>
+      <c r="BN183">
+        <v>1.68</v>
+      </c>
+      <c r="BO183">
+        <v>2.65</v>
+      </c>
+      <c r="BP183">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,9 @@
     <t>['31', '37']</t>
   </si>
   <si>
+    <t>['27', '72', '78']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1004,6 +1007,15 @@
   </si>
   <si>
     <t>['6']</t>
+  </si>
+  <si>
+    <t>['12', '42', '64']</t>
+  </si>
+  <si>
+    <t>['5', '30', '33', '90+4']</t>
+  </si>
+  <si>
+    <t>['81', '90+7']</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1621,7 +1633,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1827,7 +1839,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1908,7 +1920,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2239,7 +2251,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2320,7 +2332,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ5">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2523,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2651,7 +2663,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2857,7 +2869,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2935,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8">
         <v>2.22</v>
@@ -3063,7 +3075,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3269,7 +3281,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3347,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ10">
         <v>1.7</v>
@@ -3681,7 +3693,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4093,7 +4105,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4505,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4711,7 +4723,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4917,7 +4929,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5329,7 +5341,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5410,7 +5422,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>1.6</v>
@@ -5741,7 +5753,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6028,7 +6040,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ23">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR23">
         <v>2.28</v>
@@ -6565,7 +6577,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6643,7 +6655,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ26">
         <v>2.22</v>
@@ -6771,7 +6783,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6849,10 +6861,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.43</v>
@@ -6977,7 +6989,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7055,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ28">
         <v>1.3</v>
@@ -7389,7 +7401,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7595,7 +7607,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8007,7 +8019,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8213,7 +8225,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8625,7 +8637,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8831,7 +8843,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9037,7 +9049,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9118,7 +9130,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ38">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR38">
         <v>1.52</v>
@@ -9449,7 +9461,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9655,7 +9667,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9733,10 +9745,10 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ41">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.64</v>
@@ -9861,7 +9873,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -9939,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ42">
         <v>0.3</v>
@@ -10067,7 +10079,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10354,7 +10366,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
         <v>1.68</v>
@@ -10479,7 +10491,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10891,7 +10903,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11097,7 +11109,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11303,7 +11315,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11509,7 +11521,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11921,7 +11933,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12127,7 +12139,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12333,7 +12345,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12411,7 +12423,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ54">
         <v>1.45</v>
@@ -12539,7 +12551,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12745,7 +12757,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12823,7 +12835,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ56">
         <v>0.3</v>
@@ -12951,7 +12963,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13157,7 +13169,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13238,7 +13250,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ58">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13569,7 +13581,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13647,7 +13659,7 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ60">
         <v>2.55</v>
@@ -13775,7 +13787,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14062,7 +14074,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ62">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.64</v>
@@ -14187,7 +14199,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14268,7 +14280,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.36</v>
@@ -14393,7 +14405,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14805,7 +14817,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15423,7 +15435,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15629,7 +15641,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15835,7 +15847,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15913,7 +15925,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ71">
         <v>1.2</v>
@@ -16247,7 +16259,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16531,7 +16543,7 @@
         <v>1.67</v>
       </c>
       <c r="AP74">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16865,7 +16877,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16946,7 +16958,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -17071,7 +17083,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17564,7 +17576,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ79">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR79">
         <v>1.72</v>
@@ -17767,7 +17779,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ80">
         <v>1.45</v>
@@ -17895,7 +17907,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17976,7 +17988,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.41</v>
@@ -18307,7 +18319,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18388,7 +18400,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ83">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR83">
         <v>2.13</v>
@@ -18513,7 +18525,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18719,7 +18731,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18925,7 +18937,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19131,7 +19143,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19337,7 +19349,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19543,7 +19555,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19621,7 +19633,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
         <v>0.73</v>
@@ -19749,7 +19761,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19827,7 +19839,7 @@
         <v>0.25</v>
       </c>
       <c r="AP90">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ90">
         <v>0.9</v>
@@ -20445,7 +20457,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ93">
         <v>1.3</v>
@@ -20654,7 +20666,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ94">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
         <v>1.29</v>
@@ -20779,7 +20791,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21191,7 +21203,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21397,7 +21409,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21890,7 +21902,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ100">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.62</v>
@@ -22015,7 +22027,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22633,7 +22645,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22711,7 +22723,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ104">
         <v>1.64</v>
@@ -22917,7 +22929,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ105">
         <v>0.73</v>
@@ -23045,7 +23057,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23126,7 +23138,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR106">
         <v>1.62</v>
@@ -23251,7 +23263,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23663,7 +23675,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23869,7 +23881,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23950,7 +23962,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ110">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>1.5</v>
@@ -24281,7 +24293,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24487,7 +24499,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24693,7 +24705,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24774,7 +24786,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ114">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
         <v>1.54</v>
@@ -24899,7 +24911,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25105,7 +25117,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25311,7 +25323,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25517,7 +25529,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25723,7 +25735,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25801,7 +25813,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ119">
         <v>1.64</v>
@@ -25929,7 +25941,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26135,7 +26147,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26341,7 +26353,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26422,7 +26434,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ122">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR122">
         <v>1.56</v>
@@ -26831,7 +26843,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26959,7 +26971,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27165,7 +27177,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27449,7 +27461,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ127">
         <v>1.2</v>
@@ -27658,7 +27670,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ128">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -27783,7 +27795,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27989,7 +28001,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28401,7 +28413,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28607,7 +28619,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28813,7 +28825,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29225,7 +29237,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29431,7 +29443,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29637,7 +29649,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30049,7 +30061,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30127,10 +30139,10 @@
         <v>1.63</v>
       </c>
       <c r="AP140">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ140">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR140">
         <v>1.64</v>
@@ -30333,7 +30345,7 @@
         <v>1.43</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ141">
         <v>1.7</v>
@@ -30461,7 +30473,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30539,7 +30551,7 @@
         <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ142">
         <v>1.7</v>
@@ -30748,7 +30760,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ143">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR143">
         <v>1.88</v>
@@ -31079,7 +31091,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31160,7 +31172,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ145">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR145">
         <v>1.36</v>
@@ -31285,7 +31297,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31491,7 +31503,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32109,7 +32121,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32521,7 +32533,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32933,7 +32945,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33139,7 +33151,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33345,7 +33357,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -34375,7 +34387,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34581,7 +34593,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34787,7 +34799,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34993,7 +35005,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35071,7 +35083,7 @@
         <v>0.22</v>
       </c>
       <c r="AP164">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ164">
         <v>0.3</v>
@@ -35199,7 +35211,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35486,7 +35498,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ166">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR166">
         <v>1.82</v>
@@ -35611,7 +35623,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35817,7 +35829,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -35898,7 +35910,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ168">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36023,7 +36035,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36229,7 +36241,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36307,7 +36319,7 @@
         <v>0.13</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ170">
         <v>0.1</v>
@@ -36513,10 +36525,10 @@
         <v>1.56</v>
       </c>
       <c r="AP171">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ171">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -36641,7 +36653,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37053,7 +37065,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37465,7 +37477,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37671,7 +37683,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37877,7 +37889,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38083,7 +38095,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38289,7 +38301,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38495,7 +38507,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38701,7 +38713,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38907,7 +38919,7 @@
         <v>217</v>
       </c>
       <c r="P183" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q183">
         <v>2.4</v>
@@ -39064,6 +39076,624 @@
       </c>
       <c r="BP183">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7491671</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45696.375</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>76</v>
+      </c>
+      <c r="H184" t="s">
+        <v>82</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>2</v>
+      </c>
+      <c r="K184">
+        <v>2</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>3</v>
+      </c>
+      <c r="N184">
+        <v>3</v>
+      </c>
+      <c r="O184" t="s">
+        <v>92</v>
+      </c>
+      <c r="P184" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q184">
+        <v>2.63</v>
+      </c>
+      <c r="R184">
+        <v>2.38</v>
+      </c>
+      <c r="S184">
+        <v>3.5</v>
+      </c>
+      <c r="T184">
+        <v>1.29</v>
+      </c>
+      <c r="U184">
+        <v>3.5</v>
+      </c>
+      <c r="V184">
+        <v>2.38</v>
+      </c>
+      <c r="W184">
+        <v>1.53</v>
+      </c>
+      <c r="X184">
+        <v>5.5</v>
+      </c>
+      <c r="Y184">
+        <v>1.14</v>
+      </c>
+      <c r="Z184">
+        <v>2.22</v>
+      </c>
+      <c r="AA184">
+        <v>3.26</v>
+      </c>
+      <c r="AB184">
+        <v>3.59</v>
+      </c>
+      <c r="AC184">
+        <v>1.04</v>
+      </c>
+      <c r="AD184">
+        <v>10</v>
+      </c>
+      <c r="AE184">
+        <v>1.17</v>
+      </c>
+      <c r="AF184">
+        <v>4.6</v>
+      </c>
+      <c r="AG184">
+        <v>1.57</v>
+      </c>
+      <c r="AH184">
+        <v>2.15</v>
+      </c>
+      <c r="AI184">
+        <v>1.44</v>
+      </c>
+      <c r="AJ184">
+        <v>2.63</v>
+      </c>
+      <c r="AK184">
+        <v>1.34</v>
+      </c>
+      <c r="AL184">
+        <v>1.28</v>
+      </c>
+      <c r="AM184">
+        <v>1.68</v>
+      </c>
+      <c r="AN184">
+        <v>1.3</v>
+      </c>
+      <c r="AO184">
+        <v>1.33</v>
+      </c>
+      <c r="AP184">
+        <v>1.18</v>
+      </c>
+      <c r="AQ184">
+        <v>1.5</v>
+      </c>
+      <c r="AR184">
+        <v>1.56</v>
+      </c>
+      <c r="AS184">
+        <v>1.4</v>
+      </c>
+      <c r="AT184">
+        <v>2.96</v>
+      </c>
+      <c r="AU184">
+        <v>3</v>
+      </c>
+      <c r="AV184">
+        <v>5</v>
+      </c>
+      <c r="AW184">
+        <v>12</v>
+      </c>
+      <c r="AX184">
+        <v>8</v>
+      </c>
+      <c r="AY184">
+        <v>18</v>
+      </c>
+      <c r="AZ184">
+        <v>15</v>
+      </c>
+      <c r="BA184">
+        <v>2</v>
+      </c>
+      <c r="BB184">
+        <v>4</v>
+      </c>
+      <c r="BC184">
+        <v>6</v>
+      </c>
+      <c r="BD184">
+        <v>1.75</v>
+      </c>
+      <c r="BE184">
+        <v>6.75</v>
+      </c>
+      <c r="BF184">
+        <v>2.28</v>
+      </c>
+      <c r="BG184">
+        <v>1.25</v>
+      </c>
+      <c r="BH184">
+        <v>3.45</v>
+      </c>
+      <c r="BI184">
+        <v>1.31</v>
+      </c>
+      <c r="BJ184">
+        <v>3</v>
+      </c>
+      <c r="BK184">
+        <v>1.57</v>
+      </c>
+      <c r="BL184">
+        <v>2.15</v>
+      </c>
+      <c r="BM184">
+        <v>1.98</v>
+      </c>
+      <c r="BN184">
+        <v>1.68</v>
+      </c>
+      <c r="BO184">
+        <v>2.6</v>
+      </c>
+      <c r="BP184">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7491676</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45696.375</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>74</v>
+      </c>
+      <c r="H185" t="s">
+        <v>81</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>3</v>
+      </c>
+      <c r="K185">
+        <v>4</v>
+      </c>
+      <c r="L185">
+        <v>3</v>
+      </c>
+      <c r="M185">
+        <v>4</v>
+      </c>
+      <c r="N185">
+        <v>7</v>
+      </c>
+      <c r="O185" t="s">
+        <v>218</v>
+      </c>
+      <c r="P185" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q185">
+        <v>2.75</v>
+      </c>
+      <c r="R185">
+        <v>2.4</v>
+      </c>
+      <c r="S185">
+        <v>3.4</v>
+      </c>
+      <c r="T185">
+        <v>1.29</v>
+      </c>
+      <c r="U185">
+        <v>3.5</v>
+      </c>
+      <c r="V185">
+        <v>2.25</v>
+      </c>
+      <c r="W185">
+        <v>1.57</v>
+      </c>
+      <c r="X185">
+        <v>5.5</v>
+      </c>
+      <c r="Y185">
+        <v>1.14</v>
+      </c>
+      <c r="Z185">
+        <v>2.17</v>
+      </c>
+      <c r="AA185">
+        <v>3.86</v>
+      </c>
+      <c r="AB185">
+        <v>3.16</v>
+      </c>
+      <c r="AC185">
+        <v>1.04</v>
+      </c>
+      <c r="AD185">
+        <v>10</v>
+      </c>
+      <c r="AE185">
+        <v>1.16</v>
+      </c>
+      <c r="AF185">
+        <v>4.8</v>
+      </c>
+      <c r="AG185">
+        <v>1.53</v>
+      </c>
+      <c r="AH185">
+        <v>2.25</v>
+      </c>
+      <c r="AI185">
+        <v>1.5</v>
+      </c>
+      <c r="AJ185">
+        <v>2.5</v>
+      </c>
+      <c r="AK185">
+        <v>1.38</v>
+      </c>
+      <c r="AL185">
+        <v>1.25</v>
+      </c>
+      <c r="AM185">
+        <v>1.68</v>
+      </c>
+      <c r="AN185">
+        <v>0.78</v>
+      </c>
+      <c r="AO185">
+        <v>0.8</v>
+      </c>
+      <c r="AP185">
+        <v>0.7</v>
+      </c>
+      <c r="AQ185">
+        <v>1</v>
+      </c>
+      <c r="AR185">
+        <v>1.66</v>
+      </c>
+      <c r="AS185">
+        <v>1.52</v>
+      </c>
+      <c r="AT185">
+        <v>3.18</v>
+      </c>
+      <c r="AU185">
+        <v>9</v>
+      </c>
+      <c r="AV185">
+        <v>7</v>
+      </c>
+      <c r="AW185">
+        <v>13</v>
+      </c>
+      <c r="AX185">
+        <v>4</v>
+      </c>
+      <c r="AY185">
+        <v>24</v>
+      </c>
+      <c r="AZ185">
+        <v>13</v>
+      </c>
+      <c r="BA185">
+        <v>10</v>
+      </c>
+      <c r="BB185">
+        <v>2</v>
+      </c>
+      <c r="BC185">
+        <v>12</v>
+      </c>
+      <c r="BD185">
+        <v>1.84</v>
+      </c>
+      <c r="BE185">
+        <v>6.75</v>
+      </c>
+      <c r="BF185">
+        <v>2.15</v>
+      </c>
+      <c r="BG185">
+        <v>1.17</v>
+      </c>
+      <c r="BH185">
+        <v>4.35</v>
+      </c>
+      <c r="BI185">
+        <v>1.25</v>
+      </c>
+      <c r="BJ185">
+        <v>3.5</v>
+      </c>
+      <c r="BK185">
+        <v>1.46</v>
+      </c>
+      <c r="BL185">
+        <v>2.45</v>
+      </c>
+      <c r="BM185">
+        <v>1.8</v>
+      </c>
+      <c r="BN185">
+        <v>1.85</v>
+      </c>
+      <c r="BO185">
+        <v>2.3</v>
+      </c>
+      <c r="BP185">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7491677</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45696.375</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>78</v>
+      </c>
+      <c r="H186" t="s">
+        <v>85</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>2</v>
+      </c>
+      <c r="N186">
+        <v>2</v>
+      </c>
+      <c r="O186" t="s">
+        <v>92</v>
+      </c>
+      <c r="P186" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q186">
+        <v>3.4</v>
+      </c>
+      <c r="R186">
+        <v>2.2</v>
+      </c>
+      <c r="S186">
+        <v>3</v>
+      </c>
+      <c r="T186">
+        <v>1.36</v>
+      </c>
+      <c r="U186">
+        <v>3</v>
+      </c>
+      <c r="V186">
+        <v>2.75</v>
+      </c>
+      <c r="W186">
+        <v>1.4</v>
+      </c>
+      <c r="X186">
+        <v>7</v>
+      </c>
+      <c r="Y186">
+        <v>1.1</v>
+      </c>
+      <c r="Z186">
+        <v>2.86</v>
+      </c>
+      <c r="AA186">
+        <v>3.67</v>
+      </c>
+      <c r="AB186">
+        <v>2.42</v>
+      </c>
+      <c r="AC186">
+        <v>1.05</v>
+      </c>
+      <c r="AD186">
+        <v>9.5</v>
+      </c>
+      <c r="AE186">
+        <v>1.25</v>
+      </c>
+      <c r="AF186">
+        <v>3.55</v>
+      </c>
+      <c r="AG186">
+        <v>1.84</v>
+      </c>
+      <c r="AH186">
+        <v>1.97</v>
+      </c>
+      <c r="AI186">
+        <v>1.67</v>
+      </c>
+      <c r="AJ186">
+        <v>2.1</v>
+      </c>
+      <c r="AK186">
+        <v>1.57</v>
+      </c>
+      <c r="AL186">
+        <v>1.29</v>
+      </c>
+      <c r="AM186">
+        <v>1.41</v>
+      </c>
+      <c r="AN186">
+        <v>1</v>
+      </c>
+      <c r="AO186">
+        <v>1.7</v>
+      </c>
+      <c r="AP186">
+        <v>0.9</v>
+      </c>
+      <c r="AQ186">
+        <v>1.82</v>
+      </c>
+      <c r="AR186">
+        <v>1.53</v>
+      </c>
+      <c r="AS186">
+        <v>1.4</v>
+      </c>
+      <c r="AT186">
+        <v>2.93</v>
+      </c>
+      <c r="AU186">
+        <v>4</v>
+      </c>
+      <c r="AV186">
+        <v>6</v>
+      </c>
+      <c r="AW186">
+        <v>4</v>
+      </c>
+      <c r="AX186">
+        <v>5</v>
+      </c>
+      <c r="AY186">
+        <v>8</v>
+      </c>
+      <c r="AZ186">
+        <v>12</v>
+      </c>
+      <c r="BA186">
+        <v>4</v>
+      </c>
+      <c r="BB186">
+        <v>5</v>
+      </c>
+      <c r="BC186">
+        <v>9</v>
+      </c>
+      <c r="BD186">
+        <v>2.08</v>
+      </c>
+      <c r="BE186">
+        <v>6.75</v>
+      </c>
+      <c r="BF186">
+        <v>1.89</v>
+      </c>
+      <c r="BG186">
+        <v>1.19</v>
+      </c>
+      <c r="BH186">
+        <v>4.1</v>
+      </c>
+      <c r="BI186">
+        <v>1.35</v>
+      </c>
+      <c r="BJ186">
+        <v>2.8</v>
+      </c>
+      <c r="BK186">
+        <v>1.63</v>
+      </c>
+      <c r="BL186">
+        <v>2.05</v>
+      </c>
+      <c r="BM186">
+        <v>2.1</v>
+      </c>
+      <c r="BN186">
+        <v>1.62</v>
+      </c>
+      <c r="BO186">
+        <v>2.8</v>
+      </c>
+      <c r="BP186">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1377,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ5">
         <v>1.82</v>
@@ -3362,7 +3362,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ10">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ24">
         <v>0.1</v>
@@ -9542,7 +9542,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ40">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR40">
         <v>1.31</v>
@@ -10569,7 +10569,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ45">
         <v>2.22</v>
@@ -13456,7 +13456,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ59">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -14277,7 +14277,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -15310,7 +15310,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ68">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -16749,7 +16749,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ75">
         <v>0.3</v>
@@ -19430,7 +19430,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ88">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR88">
         <v>1.59</v>
@@ -21281,7 +21281,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ97">
         <v>2</v>
@@ -22314,7 +22314,7 @@
         <v>2</v>
       </c>
       <c r="AQ102">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR102">
         <v>1.42</v>
@@ -24577,7 +24577,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ113">
         <v>0.73</v>
@@ -26022,7 +26022,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ120">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -29727,7 +29727,7 @@
         <v>0.86</v>
       </c>
       <c r="AP138">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30554,7 +30554,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ142">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR142">
         <v>1.45</v>
@@ -35292,7 +35292,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ165">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -36113,7 +36113,7 @@
         <v>1.38</v>
       </c>
       <c r="AP169">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ169">
         <v>1.7</v>
@@ -39694,6 +39694,212 @@
       </c>
       <c r="BP186">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7491675</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45696.6875</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>73</v>
+      </c>
+      <c r="H187" t="s">
+        <v>80</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
+        <v>92</v>
+      </c>
+      <c r="P187" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q187">
+        <v>2.38</v>
+      </c>
+      <c r="R187">
+        <v>2.4</v>
+      </c>
+      <c r="S187">
+        <v>4</v>
+      </c>
+      <c r="T187">
+        <v>1.29</v>
+      </c>
+      <c r="U187">
+        <v>3.5</v>
+      </c>
+      <c r="V187">
+        <v>2.38</v>
+      </c>
+      <c r="W187">
+        <v>1.53</v>
+      </c>
+      <c r="X187">
+        <v>5.5</v>
+      </c>
+      <c r="Y187">
+        <v>1.14</v>
+      </c>
+      <c r="Z187">
+        <v>1.86</v>
+      </c>
+      <c r="AA187">
+        <v>4</v>
+      </c>
+      <c r="AB187">
+        <v>4</v>
+      </c>
+      <c r="AC187">
+        <v>1.03</v>
+      </c>
+      <c r="AD187">
+        <v>11</v>
+      </c>
+      <c r="AE187">
+        <v>1.17</v>
+      </c>
+      <c r="AF187">
+        <v>4.6</v>
+      </c>
+      <c r="AG187">
+        <v>1.53</v>
+      </c>
+      <c r="AH187">
+        <v>2.25</v>
+      </c>
+      <c r="AI187">
+        <v>1.53</v>
+      </c>
+      <c r="AJ187">
+        <v>2.38</v>
+      </c>
+      <c r="AK187">
+        <v>1.24</v>
+      </c>
+      <c r="AL187">
+        <v>1.24</v>
+      </c>
+      <c r="AM187">
+        <v>1.95</v>
+      </c>
+      <c r="AN187">
+        <v>0.78</v>
+      </c>
+      <c r="AO187">
+        <v>1.7</v>
+      </c>
+      <c r="AP187">
+        <v>0.7</v>
+      </c>
+      <c r="AQ187">
+        <v>1.82</v>
+      </c>
+      <c r="AR187">
+        <v>1.44</v>
+      </c>
+      <c r="AS187">
+        <v>1.4</v>
+      </c>
+      <c r="AT187">
+        <v>2.84</v>
+      </c>
+      <c r="AU187">
+        <v>6</v>
+      </c>
+      <c r="AV187">
+        <v>6</v>
+      </c>
+      <c r="AW187">
+        <v>10</v>
+      </c>
+      <c r="AX187">
+        <v>9</v>
+      </c>
+      <c r="AY187">
+        <v>19</v>
+      </c>
+      <c r="AZ187">
+        <v>18</v>
+      </c>
+      <c r="BA187">
+        <v>6</v>
+      </c>
+      <c r="BB187">
+        <v>7</v>
+      </c>
+      <c r="BC187">
+        <v>13</v>
+      </c>
+      <c r="BD187">
+        <v>1.67</v>
+      </c>
+      <c r="BE187">
+        <v>6.75</v>
+      </c>
+      <c r="BF187">
+        <v>2.43</v>
+      </c>
+      <c r="BG187">
+        <v>1.23</v>
+      </c>
+      <c r="BH187">
+        <v>3.65</v>
+      </c>
+      <c r="BI187">
+        <v>1.31</v>
+      </c>
+      <c r="BJ187">
+        <v>3</v>
+      </c>
+      <c r="BK187">
+        <v>1.57</v>
+      </c>
+      <c r="BL187">
+        <v>2.15</v>
+      </c>
+      <c r="BM187">
+        <v>1.98</v>
+      </c>
+      <c r="BN187">
+        <v>1.68</v>
+      </c>
+      <c r="BO187">
+        <v>2.65</v>
+      </c>
+      <c r="BP187">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,12 @@
     <t>['27', '72', '78']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -955,9 +961,6 @@
     <t>['69', '72']</t>
   </si>
   <si>
-    <t>['35']</t>
-  </si>
-  <si>
     <t>['16', '69']</t>
   </si>
   <si>
@@ -1016,6 +1019,9 @@
   </si>
   <si>
     <t>['81', '90+7']</t>
+  </si>
+  <si>
+    <t>['36', '74']</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1639,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1711,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2">
         <v>1.7</v>
@@ -1839,7 +1845,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1917,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2123,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ4">
         <v>0.1</v>
@@ -2251,7 +2257,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2663,7 +2669,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2744,7 +2750,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ7">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2869,7 +2875,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2950,7 +2956,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ8">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3075,7 +3081,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3281,7 +3287,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3693,7 +3699,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3980,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4105,7 +4111,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4517,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4723,7 +4729,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4929,7 +4935,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5341,7 +5347,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5419,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>1.5</v>
@@ -5625,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ21">
         <v>1.7</v>
@@ -5753,7 +5759,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6449,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR25">
         <v>2.21</v>
@@ -6577,7 +6583,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6658,7 +6664,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ26">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR26">
         <v>1.22</v>
@@ -6783,7 +6789,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6989,7 +6995,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7070,7 +7076,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ28">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR28">
         <v>1.96</v>
@@ -7401,7 +7407,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7607,7 +7613,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8019,7 +8025,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8225,7 +8231,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8637,7 +8643,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8843,7 +8849,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9049,7 +9055,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9333,10 +9339,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ39">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR39">
         <v>1.65</v>
@@ -9461,7 +9467,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9539,7 +9545,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ40">
         <v>1.82</v>
@@ -9667,7 +9673,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9873,7 +9879,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -9954,7 +9960,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ42">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR42">
         <v>1.72</v>
@@ -10079,7 +10085,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10157,7 +10163,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
         <v>2.55</v>
@@ -10491,7 +10497,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10572,7 +10578,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ45">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR45">
         <v>1.24</v>
@@ -10903,7 +10909,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11109,7 +11115,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11315,7 +11321,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11521,7 +11527,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11933,7 +11939,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12139,7 +12145,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12345,7 +12351,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12551,7 +12557,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12757,7 +12763,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12838,7 +12844,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ56">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -12963,7 +12969,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13044,7 +13050,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ57">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13169,7 +13175,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13581,7 +13587,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13787,7 +13793,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13868,7 +13874,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
         <v>1.4</v>
@@ -14071,7 +14077,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14199,7 +14205,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14405,7 +14411,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14483,7 +14489,7 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64">
         <v>1.45</v>
@@ -14817,7 +14823,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14895,7 +14901,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ66">
         <v>1.2</v>
@@ -15101,7 +15107,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ67">
         <v>0.73</v>
@@ -15435,7 +15441,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15641,7 +15647,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15847,7 +15853,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16259,7 +16265,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16752,7 +16758,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ75">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16877,7 +16883,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17083,7 +17089,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17164,7 +17170,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ77">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR77">
         <v>1.26</v>
@@ -17367,10 +17373,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ78">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17907,7 +17913,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18319,7 +18325,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18397,7 +18403,7 @@
         <v>1.2</v>
       </c>
       <c r="AP83">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ83">
         <v>1.82</v>
@@ -18525,7 +18531,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18731,7 +18737,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18809,7 +18815,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ85">
         <v>1.64</v>
@@ -18937,7 +18943,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19143,7 +19149,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19349,7 +19355,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19555,7 +19561,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19761,7 +19767,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20254,7 +20260,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ92">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR92">
         <v>1.28</v>
@@ -20460,7 +20466,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ93">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR93">
         <v>1.52</v>
@@ -20791,7 +20797,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21075,7 +21081,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ96">
         <v>1.45</v>
@@ -21203,7 +21209,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21409,7 +21415,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21696,7 +21702,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ99">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR99">
         <v>1.63</v>
@@ -22027,7 +22033,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22517,7 +22523,7 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ103">
         <v>1.2</v>
@@ -22645,7 +22651,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23057,7 +23063,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23263,7 +23269,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23341,7 +23347,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23675,7 +23681,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23881,7 +23887,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24293,7 +24299,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24499,7 +24505,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24705,7 +24711,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24911,7 +24917,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -24989,7 +24995,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -25117,7 +25123,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25198,7 +25204,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25323,7 +25329,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25404,7 +25410,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ117">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR117">
         <v>1.79</v>
@@ -25529,7 +25535,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25735,7 +25741,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25941,7 +25947,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26147,7 +26153,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26225,7 +26231,7 @@
         <v>0.67</v>
       </c>
       <c r="AP121">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121">
         <v>0.9</v>
@@ -26353,7 +26359,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26971,7 +26977,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27049,7 +27055,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ125">
         <v>1.7</v>
@@ -27177,7 +27183,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27258,7 +27264,7 @@
         <v>2</v>
       </c>
       <c r="AQ126">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27795,7 +27801,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27876,7 +27882,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ129">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR129">
         <v>1.5</v>
@@ -28001,7 +28007,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28413,7 +28419,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28491,7 +28497,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ132">
         <v>0.73</v>
@@ -28619,7 +28625,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28825,7 +28831,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29112,7 +29118,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ135">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR135">
         <v>1.54</v>
@@ -29237,7 +29243,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29443,7 +29449,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29521,7 +29527,7 @@
         <v>0.14</v>
       </c>
       <c r="AP137">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ137">
         <v>0.1</v>
@@ -29649,7 +29655,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29936,7 +29942,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ139">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR139">
         <v>1.49</v>
@@ -30061,7 +30067,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30473,7 +30479,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30757,7 +30763,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -31091,7 +31097,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31297,7 +31303,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31378,7 +31384,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ146">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR146">
         <v>1.51</v>
@@ -31503,7 +31509,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32121,7 +32127,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32408,7 +32414,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR151">
         <v>1.49</v>
@@ -32533,7 +32539,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32817,7 +32823,7 @@
         <v>1.75</v>
       </c>
       <c r="AP153">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ153">
         <v>1.64</v>
@@ -32945,7 +32951,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33151,7 +33157,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33357,7 +33363,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>313</v>
+        <v>220</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -33850,7 +33856,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ158">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR158">
         <v>1.3</v>
@@ -34387,7 +34393,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34593,7 +34599,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34799,7 +34805,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35005,7 +35011,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35086,7 +35092,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ164">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR164">
         <v>1.62</v>
@@ -35211,7 +35217,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35495,7 +35501,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ166">
         <v>1.5</v>
@@ -35623,7 +35629,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35701,10 +35707,10 @@
         <v>2.13</v>
       </c>
       <c r="AP167">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ167">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AR167">
         <v>1.61</v>
@@ -35829,7 +35835,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36035,7 +36041,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36241,7 +36247,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36653,7 +36659,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36731,7 +36737,7 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37065,7 +37071,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37477,7 +37483,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37683,7 +37689,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37889,7 +37895,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38095,7 +38101,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38301,7 +38307,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38507,7 +38513,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38713,7 +38719,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38919,7 +38925,7 @@
         <v>217</v>
       </c>
       <c r="P183" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q183">
         <v>2.4</v>
@@ -39125,7 +39131,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39239,10 +39245,10 @@
         <v>2</v>
       </c>
       <c r="BB184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC184">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD184">
         <v>1.75</v>
@@ -39331,7 +39337,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39537,7 +39543,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39900,6 +39906,624 @@
       </c>
       <c r="BP187">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7491670</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45697.39583333334</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>70</v>
+      </c>
+      <c r="H188" t="s">
+        <v>75</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>1</v>
+      </c>
+      <c r="O188" t="s">
+        <v>219</v>
+      </c>
+      <c r="P188" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q188">
+        <v>2.25</v>
+      </c>
+      <c r="R188">
+        <v>2.4</v>
+      </c>
+      <c r="S188">
+        <v>4.5</v>
+      </c>
+      <c r="T188">
+        <v>1.3</v>
+      </c>
+      <c r="U188">
+        <v>3.4</v>
+      </c>
+      <c r="V188">
+        <v>2.38</v>
+      </c>
+      <c r="W188">
+        <v>1.53</v>
+      </c>
+      <c r="X188">
+        <v>6</v>
+      </c>
+      <c r="Y188">
+        <v>1.13</v>
+      </c>
+      <c r="Z188">
+        <v>1.76</v>
+      </c>
+      <c r="AA188">
+        <v>4.2</v>
+      </c>
+      <c r="AB188">
+        <v>4.4</v>
+      </c>
+      <c r="AC188">
+        <v>1.04</v>
+      </c>
+      <c r="AD188">
+        <v>10</v>
+      </c>
+      <c r="AE188">
+        <v>1.18</v>
+      </c>
+      <c r="AF188">
+        <v>4.4</v>
+      </c>
+      <c r="AG188">
+        <v>1.57</v>
+      </c>
+      <c r="AH188">
+        <v>2.15</v>
+      </c>
+      <c r="AI188">
+        <v>1.62</v>
+      </c>
+      <c r="AJ188">
+        <v>2.2</v>
+      </c>
+      <c r="AK188">
+        <v>1.23</v>
+      </c>
+      <c r="AL188">
+        <v>1.24</v>
+      </c>
+      <c r="AM188">
+        <v>2</v>
+      </c>
+      <c r="AN188">
+        <v>1.7</v>
+      </c>
+      <c r="AO188">
+        <v>1.3</v>
+      </c>
+      <c r="AP188">
+        <v>1.82</v>
+      </c>
+      <c r="AQ188">
+        <v>1.18</v>
+      </c>
+      <c r="AR188">
+        <v>1.83</v>
+      </c>
+      <c r="AS188">
+        <v>1.39</v>
+      </c>
+      <c r="AT188">
+        <v>3.22</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>3</v>
+      </c>
+      <c r="AW188">
+        <v>9</v>
+      </c>
+      <c r="AX188">
+        <v>9</v>
+      </c>
+      <c r="AY188">
+        <v>15</v>
+      </c>
+      <c r="AZ188">
+        <v>13</v>
+      </c>
+      <c r="BA188">
+        <v>4</v>
+      </c>
+      <c r="BB188">
+        <v>4</v>
+      </c>
+      <c r="BC188">
+        <v>8</v>
+      </c>
+      <c r="BD188">
+        <v>1.57</v>
+      </c>
+      <c r="BE188">
+        <v>6.75</v>
+      </c>
+      <c r="BF188">
+        <v>2.65</v>
+      </c>
+      <c r="BG188">
+        <v>1.26</v>
+      </c>
+      <c r="BH188">
+        <v>3.4</v>
+      </c>
+      <c r="BI188">
+        <v>1.32</v>
+      </c>
+      <c r="BJ188">
+        <v>3</v>
+      </c>
+      <c r="BK188">
+        <v>1.57</v>
+      </c>
+      <c r="BL188">
+        <v>2.15</v>
+      </c>
+      <c r="BM188">
+        <v>1.98</v>
+      </c>
+      <c r="BN188">
+        <v>1.68</v>
+      </c>
+      <c r="BO188">
+        <v>2.65</v>
+      </c>
+      <c r="BP188">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7491672</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45697.39583333334</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>71</v>
+      </c>
+      <c r="H189" t="s">
+        <v>86</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>2</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>92</v>
+      </c>
+      <c r="P189" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q189">
+        <v>2.38</v>
+      </c>
+      <c r="R189">
+        <v>2.38</v>
+      </c>
+      <c r="S189">
+        <v>4.33</v>
+      </c>
+      <c r="T189">
+        <v>1.3</v>
+      </c>
+      <c r="U189">
+        <v>3.4</v>
+      </c>
+      <c r="V189">
+        <v>2.5</v>
+      </c>
+      <c r="W189">
+        <v>1.5</v>
+      </c>
+      <c r="X189">
+        <v>6</v>
+      </c>
+      <c r="Y189">
+        <v>1.13</v>
+      </c>
+      <c r="Z189">
+        <v>1.87</v>
+      </c>
+      <c r="AA189">
+        <v>4.4</v>
+      </c>
+      <c r="AB189">
+        <v>3.67</v>
+      </c>
+      <c r="AC189">
+        <v>1.03</v>
+      </c>
+      <c r="AD189">
+        <v>11</v>
+      </c>
+      <c r="AE189">
+        <v>1.18</v>
+      </c>
+      <c r="AF189">
+        <v>4.5</v>
+      </c>
+      <c r="AG189">
+        <v>1.53</v>
+      </c>
+      <c r="AH189">
+        <v>2.25</v>
+      </c>
+      <c r="AI189">
+        <v>1.62</v>
+      </c>
+      <c r="AJ189">
+        <v>2.2</v>
+      </c>
+      <c r="AK189">
+        <v>1.24</v>
+      </c>
+      <c r="AL189">
+        <v>1.24</v>
+      </c>
+      <c r="AM189">
+        <v>1.95</v>
+      </c>
+      <c r="AN189">
+        <v>1.56</v>
+      </c>
+      <c r="AO189">
+        <v>0.3</v>
+      </c>
+      <c r="AP189">
+        <v>1.4</v>
+      </c>
+      <c r="AQ189">
+        <v>0.55</v>
+      </c>
+      <c r="AR189">
+        <v>1.59</v>
+      </c>
+      <c r="AS189">
+        <v>1.1</v>
+      </c>
+      <c r="AT189">
+        <v>2.69</v>
+      </c>
+      <c r="AU189">
+        <v>5</v>
+      </c>
+      <c r="AV189">
+        <v>8</v>
+      </c>
+      <c r="AW189">
+        <v>24</v>
+      </c>
+      <c r="AX189">
+        <v>6</v>
+      </c>
+      <c r="AY189">
+        <v>40</v>
+      </c>
+      <c r="AZ189">
+        <v>17</v>
+      </c>
+      <c r="BA189">
+        <v>10</v>
+      </c>
+      <c r="BB189">
+        <v>5</v>
+      </c>
+      <c r="BC189">
+        <v>15</v>
+      </c>
+      <c r="BD189">
+        <v>1.58</v>
+      </c>
+      <c r="BE189">
+        <v>6.75</v>
+      </c>
+      <c r="BF189">
+        <v>2.55</v>
+      </c>
+      <c r="BG189">
+        <v>1.19</v>
+      </c>
+      <c r="BH189">
+        <v>4</v>
+      </c>
+      <c r="BI189">
+        <v>1.28</v>
+      </c>
+      <c r="BJ189">
+        <v>3.2</v>
+      </c>
+      <c r="BK189">
+        <v>1.51</v>
+      </c>
+      <c r="BL189">
+        <v>2.3</v>
+      </c>
+      <c r="BM189">
+        <v>1.9</v>
+      </c>
+      <c r="BN189">
+        <v>1.75</v>
+      </c>
+      <c r="BO189">
+        <v>2.45</v>
+      </c>
+      <c r="BP189">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7491673</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45697.39583333334</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>72</v>
+      </c>
+      <c r="H190" t="s">
+        <v>83</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>220</v>
+      </c>
+      <c r="P190" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q190">
+        <v>2.63</v>
+      </c>
+      <c r="R190">
+        <v>2.25</v>
+      </c>
+      <c r="S190">
+        <v>3.75</v>
+      </c>
+      <c r="T190">
+        <v>1.33</v>
+      </c>
+      <c r="U190">
+        <v>3.25</v>
+      </c>
+      <c r="V190">
+        <v>2.63</v>
+      </c>
+      <c r="W190">
+        <v>1.44</v>
+      </c>
+      <c r="X190">
+        <v>6.5</v>
+      </c>
+      <c r="Y190">
+        <v>1.11</v>
+      </c>
+      <c r="Z190">
+        <v>2.12</v>
+      </c>
+      <c r="AA190">
+        <v>3.66</v>
+      </c>
+      <c r="AB190">
+        <v>3.45</v>
+      </c>
+      <c r="AC190">
+        <v>1.05</v>
+      </c>
+      <c r="AD190">
+        <v>9.5</v>
+      </c>
+      <c r="AE190">
+        <v>1.22</v>
+      </c>
+      <c r="AF190">
+        <v>3.85</v>
+      </c>
+      <c r="AG190">
+        <v>1.75</v>
+      </c>
+      <c r="AH190">
+        <v>1.91</v>
+      </c>
+      <c r="AI190">
+        <v>1.62</v>
+      </c>
+      <c r="AJ190">
+        <v>2.2</v>
+      </c>
+      <c r="AK190">
+        <v>1.32</v>
+      </c>
+      <c r="AL190">
+        <v>1.28</v>
+      </c>
+      <c r="AM190">
+        <v>1.72</v>
+      </c>
+      <c r="AN190">
+        <v>2.3</v>
+      </c>
+      <c r="AO190">
+        <v>2.22</v>
+      </c>
+      <c r="AP190">
+        <v>2.18</v>
+      </c>
+      <c r="AQ190">
+        <v>2.1</v>
+      </c>
+      <c r="AR190">
+        <v>1.76</v>
+      </c>
+      <c r="AS190">
+        <v>1.37</v>
+      </c>
+      <c r="AT190">
+        <v>3.13</v>
+      </c>
+      <c r="AU190">
+        <v>3</v>
+      </c>
+      <c r="AV190">
+        <v>3</v>
+      </c>
+      <c r="AW190">
+        <v>11</v>
+      </c>
+      <c r="AX190">
+        <v>4</v>
+      </c>
+      <c r="AY190">
+        <v>15</v>
+      </c>
+      <c r="AZ190">
+        <v>7</v>
+      </c>
+      <c r="BA190">
+        <v>6</v>
+      </c>
+      <c r="BB190">
+        <v>1</v>
+      </c>
+      <c r="BC190">
+        <v>7</v>
+      </c>
+      <c r="BD190">
+        <v>1.79</v>
+      </c>
+      <c r="BE190">
+        <v>6.75</v>
+      </c>
+      <c r="BF190">
+        <v>2.23</v>
+      </c>
+      <c r="BG190">
+        <v>1.18</v>
+      </c>
+      <c r="BH190">
+        <v>4.1</v>
+      </c>
+      <c r="BI190">
+        <v>1.28</v>
+      </c>
+      <c r="BJ190">
+        <v>3.2</v>
+      </c>
+      <c r="BK190">
+        <v>1.51</v>
+      </c>
+      <c r="BL190">
+        <v>2.3</v>
+      </c>
+      <c r="BM190">
+        <v>1.88</v>
+      </c>
+      <c r="BN190">
+        <v>1.75</v>
+      </c>
+      <c r="BO190">
+        <v>2.45</v>
+      </c>
+      <c r="BP190">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -677,6 +677,12 @@
   </si>
   <si>
     <t>['35']</t>
+  </si>
+  <si>
+    <t>['73', '79', '90+2']</t>
+  </si>
+  <si>
+    <t>['81', '84']</t>
   </si>
   <si>
     <t>['5', '35']</t>
@@ -1383,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1639,7 +1645,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1845,7 +1851,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2257,7 +2263,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2541,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2669,7 +2675,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2875,7 +2881,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3081,7 +3087,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3162,7 +3168,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3287,7 +3293,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3699,7 +3705,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4111,7 +4117,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4192,7 +4198,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ14">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4523,7 +4529,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4729,7 +4735,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4807,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ17">
         <v>1.2</v>
@@ -4935,7 +4941,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5347,7 +5353,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5759,7 +5765,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6583,7 +6589,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6789,7 +6795,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6995,7 +7001,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7073,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ28">
         <v>1.18</v>
@@ -7407,7 +7413,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7613,7 +7619,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7694,7 +7700,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR31">
         <v>1.09</v>
@@ -8025,7 +8031,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8231,7 +8237,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8515,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ35">
         <v>0.73</v>
@@ -8643,7 +8649,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8724,7 +8730,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8849,7 +8855,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9055,7 +9061,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9467,7 +9473,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9673,7 +9679,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9879,7 +9885,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10085,7 +10091,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10497,7 +10503,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10909,7 +10915,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -10987,7 +10993,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ47">
         <v>0.9</v>
@@ -11115,7 +11121,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11321,7 +11327,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11402,7 +11408,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11527,7 +11533,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11939,7 +11945,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12145,7 +12151,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12351,7 +12357,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12429,7 +12435,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ54">
         <v>1.45</v>
@@ -12557,7 +12563,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12638,7 +12644,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12763,7 +12769,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12969,7 +12975,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13175,7 +13181,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13587,7 +13593,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13793,7 +13799,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14205,7 +14211,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14411,7 +14417,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14695,7 +14701,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65">
         <v>0.1</v>
@@ -14823,7 +14829,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15441,7 +15447,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15522,7 +15528,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR69">
         <v>0.99</v>
@@ -15647,7 +15653,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15853,7 +15859,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15931,7 +15937,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ71">
         <v>1.2</v>
@@ -16265,7 +16271,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16552,7 +16558,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16883,7 +16889,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17089,7 +17095,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17913,7 +17919,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18325,7 +18331,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18531,7 +18537,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18737,7 +18743,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18943,7 +18949,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19149,7 +19155,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19355,7 +19361,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19561,7 +19567,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19767,7 +19773,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19845,7 +19851,7 @@
         <v>0.25</v>
       </c>
       <c r="AP90">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ90">
         <v>0.9</v>
@@ -20054,7 +20060,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR91">
         <v>1.66</v>
@@ -20797,7 +20803,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21209,7 +21215,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21290,7 +21296,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21415,7 +21421,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21699,7 +21705,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ99">
         <v>0.55</v>
@@ -22033,7 +22039,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22651,7 +22657,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22935,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ105">
         <v>0.73</v>
@@ -23063,7 +23069,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23269,7 +23275,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23350,7 +23356,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23681,7 +23687,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23887,7 +23893,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23965,7 +23971,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24174,7 +24180,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR111">
         <v>1.23</v>
@@ -24299,7 +24305,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24505,7 +24511,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24711,7 +24717,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24917,7 +24923,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25123,7 +25129,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25329,7 +25335,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25535,7 +25541,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25741,7 +25747,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25819,7 +25825,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ119">
         <v>1.64</v>
@@ -25947,7 +25953,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26153,7 +26159,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26359,7 +26365,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26852,7 +26858,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR124">
         <v>1.46</v>
@@ -26977,7 +26983,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27183,7 +27189,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27801,7 +27807,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27879,7 +27885,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ129">
         <v>1.18</v>
@@ -28007,7 +28013,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28419,7 +28425,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28625,7 +28631,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28831,7 +28837,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29243,7 +29249,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29324,7 +29330,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29449,7 +29455,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29655,7 +29661,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29736,7 +29742,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR138">
         <v>1.37</v>
@@ -30067,7 +30073,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30145,7 +30151,7 @@
         <v>1.63</v>
       </c>
       <c r="AP140">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ140">
         <v>1.82</v>
@@ -30479,7 +30485,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31097,7 +31103,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31303,7 +31309,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31509,7 +31515,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32127,7 +32133,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32205,7 +32211,7 @@
         <v>1.5</v>
       </c>
       <c r="AP150">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ150">
         <v>1.45</v>
@@ -32539,7 +32545,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32951,7 +32957,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33032,7 +33038,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ154">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR154">
         <v>1.69</v>
@@ -33157,7 +33163,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -34268,7 +34274,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ160">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR160">
         <v>1.75</v>
@@ -34393,7 +34399,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34471,7 +34477,7 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ161">
         <v>1.64</v>
@@ -34599,7 +34605,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34805,7 +34811,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35011,7 +35017,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35089,7 +35095,7 @@
         <v>0.22</v>
       </c>
       <c r="AP164">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ164">
         <v>0.55</v>
@@ -35217,7 +35223,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35629,7 +35635,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35835,7 +35841,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36041,7 +36047,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36247,7 +36253,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36659,7 +36665,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36740,7 +36746,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ172">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR172">
         <v>1.67</v>
@@ -37071,7 +37077,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37483,7 +37489,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37564,7 +37570,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ176">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37689,7 +37695,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37895,7 +37901,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38101,7 +38107,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38179,7 +38185,7 @@
         <v>1</v>
       </c>
       <c r="AP179">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ179">
         <v>1.2</v>
@@ -38307,7 +38313,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38388,7 +38394,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR180">
         <v>1.74</v>
@@ -38513,7 +38519,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38719,7 +38725,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38925,7 +38931,7 @@
         <v>217</v>
       </c>
       <c r="P183" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q183">
         <v>2.4</v>
@@ -39131,7 +39137,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39337,7 +39343,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39415,7 +39421,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39543,7 +39549,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40161,7 +40167,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40524,6 +40530,418 @@
       </c>
       <c r="BP190">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7491685</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45702.60416666666</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>74</v>
+      </c>
+      <c r="H191" t="s">
+        <v>70</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>3</v>
+      </c>
+      <c r="O191" t="s">
+        <v>221</v>
+      </c>
+      <c r="P191" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q191">
+        <v>3.2</v>
+      </c>
+      <c r="R191">
+        <v>2.25</v>
+      </c>
+      <c r="S191">
+        <v>2.8</v>
+      </c>
+      <c r="T191">
+        <v>1.29</v>
+      </c>
+      <c r="U191">
+        <v>3.3</v>
+      </c>
+      <c r="V191">
+        <v>2.25</v>
+      </c>
+      <c r="W191">
+        <v>1.55</v>
+      </c>
+      <c r="X191">
+        <v>5.25</v>
+      </c>
+      <c r="Y191">
+        <v>1.14</v>
+      </c>
+      <c r="Z191">
+        <v>3.07</v>
+      </c>
+      <c r="AA191">
+        <v>3.73</v>
+      </c>
+      <c r="AB191">
+        <v>2.26</v>
+      </c>
+      <c r="AC191">
+        <v>1.04</v>
+      </c>
+      <c r="AD191">
+        <v>10</v>
+      </c>
+      <c r="AE191">
+        <v>1.18</v>
+      </c>
+      <c r="AF191">
+        <v>4.5</v>
+      </c>
+      <c r="AG191">
+        <v>1.57</v>
+      </c>
+      <c r="AH191">
+        <v>2.15</v>
+      </c>
+      <c r="AI191">
+        <v>1.51</v>
+      </c>
+      <c r="AJ191">
+        <v>2.37</v>
+      </c>
+      <c r="AK191">
+        <v>1.57</v>
+      </c>
+      <c r="AL191">
+        <v>1.28</v>
+      </c>
+      <c r="AM191">
+        <v>1.42</v>
+      </c>
+      <c r="AN191">
+        <v>0.7</v>
+      </c>
+      <c r="AO191">
+        <v>2</v>
+      </c>
+      <c r="AP191">
+        <v>0.91</v>
+      </c>
+      <c r="AQ191">
+        <v>1.82</v>
+      </c>
+      <c r="AR191">
+        <v>1.77</v>
+      </c>
+      <c r="AS191">
+        <v>1.55</v>
+      </c>
+      <c r="AT191">
+        <v>3.32</v>
+      </c>
+      <c r="AU191">
+        <v>8</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>6</v>
+      </c>
+      <c r="AX191">
+        <v>8</v>
+      </c>
+      <c r="AY191">
+        <v>16</v>
+      </c>
+      <c r="AZ191">
+        <v>17</v>
+      </c>
+      <c r="BA191">
+        <v>3</v>
+      </c>
+      <c r="BB191">
+        <v>14</v>
+      </c>
+      <c r="BC191">
+        <v>17</v>
+      </c>
+      <c r="BD191">
+        <v>2.08</v>
+      </c>
+      <c r="BE191">
+        <v>6.4</v>
+      </c>
+      <c r="BF191">
+        <v>1.91</v>
+      </c>
+      <c r="BG191">
+        <v>1.32</v>
+      </c>
+      <c r="BH191">
+        <v>3.05</v>
+      </c>
+      <c r="BI191">
+        <v>1.55</v>
+      </c>
+      <c r="BJ191">
+        <v>2.25</v>
+      </c>
+      <c r="BK191">
+        <v>1.9</v>
+      </c>
+      <c r="BL191">
+        <v>1.79</v>
+      </c>
+      <c r="BM191">
+        <v>2.4</v>
+      </c>
+      <c r="BN191">
+        <v>1.5</v>
+      </c>
+      <c r="BO191">
+        <v>3.1</v>
+      </c>
+      <c r="BP191">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7491680</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45702.60416666666</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>85</v>
+      </c>
+      <c r="H192" t="s">
+        <v>87</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>2</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>2</v>
+      </c>
+      <c r="O192" t="s">
+        <v>222</v>
+      </c>
+      <c r="P192" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q192">
+        <v>2.2</v>
+      </c>
+      <c r="R192">
+        <v>2.25</v>
+      </c>
+      <c r="S192">
+        <v>4.33</v>
+      </c>
+      <c r="T192">
+        <v>1.32</v>
+      </c>
+      <c r="U192">
+        <v>3.1</v>
+      </c>
+      <c r="V192">
+        <v>2.45</v>
+      </c>
+      <c r="W192">
+        <v>1.49</v>
+      </c>
+      <c r="X192">
+        <v>5.75</v>
+      </c>
+      <c r="Y192">
+        <v>1.11</v>
+      </c>
+      <c r="Z192">
+        <v>1.76</v>
+      </c>
+      <c r="AA192">
+        <v>4</v>
+      </c>
+      <c r="AB192">
+        <v>4.6</v>
+      </c>
+      <c r="AC192">
+        <v>1.04</v>
+      </c>
+      <c r="AD192">
+        <v>10</v>
+      </c>
+      <c r="AE192">
+        <v>1.22</v>
+      </c>
+      <c r="AF192">
+        <v>3.9</v>
+      </c>
+      <c r="AG192">
+        <v>1.82</v>
+      </c>
+      <c r="AH192">
+        <v>2</v>
+      </c>
+      <c r="AI192">
+        <v>1.7</v>
+      </c>
+      <c r="AJ192">
+        <v>2</v>
+      </c>
+      <c r="AK192">
+        <v>1.2</v>
+      </c>
+      <c r="AL192">
+        <v>1.24</v>
+      </c>
+      <c r="AM192">
+        <v>2.05</v>
+      </c>
+      <c r="AN192">
+        <v>1.4</v>
+      </c>
+      <c r="AO192">
+        <v>1</v>
+      </c>
+      <c r="AP192">
+        <v>1.55</v>
+      </c>
+      <c r="AQ192">
+        <v>0.91</v>
+      </c>
+      <c r="AR192">
+        <v>1.67</v>
+      </c>
+      <c r="AS192">
+        <v>1.3</v>
+      </c>
+      <c r="AT192">
+        <v>2.97</v>
+      </c>
+      <c r="AU192">
+        <v>7</v>
+      </c>
+      <c r="AV192">
+        <v>3</v>
+      </c>
+      <c r="AW192">
+        <v>7</v>
+      </c>
+      <c r="AX192">
+        <v>8</v>
+      </c>
+      <c r="AY192">
+        <v>19</v>
+      </c>
+      <c r="AZ192">
+        <v>13</v>
+      </c>
+      <c r="BA192">
+        <v>9</v>
+      </c>
+      <c r="BB192">
+        <v>1</v>
+      </c>
+      <c r="BC192">
+        <v>10</v>
+      </c>
+      <c r="BD192">
+        <v>1.58</v>
+      </c>
+      <c r="BE192">
+        <v>6.5</v>
+      </c>
+      <c r="BF192">
+        <v>2.65</v>
+      </c>
+      <c r="BG192">
+        <v>1.37</v>
+      </c>
+      <c r="BH192">
+        <v>2.8</v>
+      </c>
+      <c r="BI192">
+        <v>1.62</v>
+      </c>
+      <c r="BJ192">
+        <v>2.14</v>
+      </c>
+      <c r="BK192">
+        <v>2</v>
+      </c>
+      <c r="BL192">
+        <v>1.71</v>
+      </c>
+      <c r="BM192">
+        <v>2.55</v>
+      </c>
+      <c r="BN192">
+        <v>1.44</v>
+      </c>
+      <c r="BO192">
+        <v>3.4</v>
+      </c>
+      <c r="BP192">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,12 @@
     <t>['81', '84']</t>
   </si>
   <si>
+    <t>['6', '45']</t>
+  </si>
+  <si>
+    <t>['55', '58']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1028,6 +1034,9 @@
   </si>
   <si>
     <t>['36', '74']</t>
+  </si>
+  <si>
+    <t>['13']</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1645,7 +1654,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1851,7 +1860,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2263,7 +2272,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2675,7 +2684,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2881,7 +2890,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3087,7 +3096,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3293,7 +3302,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3705,7 +3714,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3783,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4117,7 +4126,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4195,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
         <v>1.82</v>
@@ -4401,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>1.45</v>
@@ -4529,7 +4538,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4610,7 +4619,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ16">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4735,7 +4744,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4816,7 +4825,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4941,7 +4950,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5019,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18">
         <v>2.55</v>
@@ -5228,7 +5237,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ19">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5353,7 +5362,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5765,7 +5774,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6589,7 +6598,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6795,7 +6804,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7001,7 +7010,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7285,10 +7294,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ29">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7413,7 +7422,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7494,7 +7503,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ30">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR30">
         <v>0.79</v>
@@ -7619,7 +7628,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7903,10 +7912,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR32">
         <v>0.9399999999999999</v>
@@ -8031,7 +8040,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8237,7 +8246,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8315,10 +8324,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR34">
         <v>1.8</v>
@@ -8649,7 +8658,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8855,7 +8864,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8933,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
         <v>1.45</v>
@@ -9061,7 +9070,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9473,7 +9482,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9679,7 +9688,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9885,7 +9894,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10091,7 +10100,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10503,7 +10512,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10915,7 +10924,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -10996,7 +11005,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ47">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -11121,7 +11130,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11202,7 +11211,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ48">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR48">
         <v>1.7</v>
@@ -11327,7 +11336,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11405,7 +11414,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49">
         <v>1.82</v>
@@ -11533,7 +11542,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11614,7 +11623,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR50">
         <v>0.97</v>
@@ -11817,10 +11826,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -11945,7 +11954,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12023,7 +12032,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ52">
         <v>1.7</v>
@@ -12151,7 +12160,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12229,7 +12238,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
         <v>0.73</v>
@@ -12357,7 +12366,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12563,7 +12572,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12769,7 +12778,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12975,7 +12984,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13181,7 +13190,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13593,7 +13602,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13799,7 +13808,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14211,7 +14220,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14417,7 +14426,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14829,7 +14838,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14910,7 +14919,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR66">
         <v>1.63</v>
@@ -15319,7 +15328,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
         <v>1.82</v>
@@ -15447,7 +15456,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15653,7 +15662,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15734,7 +15743,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ70">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.66</v>
@@ -15859,7 +15868,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15940,7 +15949,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ71">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16143,10 +16152,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16271,7 +16280,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16349,7 +16358,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ73">
         <v>1.7</v>
@@ -16889,7 +16898,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17095,7 +17104,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17585,7 +17594,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
         <v>1.82</v>
@@ -17919,7 +17928,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18331,7 +18340,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18537,7 +18546,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18743,7 +18752,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18824,7 +18833,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ85">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
         <v>1.57</v>
@@ -18949,7 +18958,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19030,7 +19039,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR86">
         <v>1.49</v>
@@ -19155,7 +19164,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19233,7 +19242,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87">
         <v>1.7</v>
@@ -19361,7 +19370,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19439,7 +19448,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ88">
         <v>1.82</v>
@@ -19567,7 +19576,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19773,7 +19782,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19854,7 +19863,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ90">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR90">
         <v>1.7</v>
@@ -20057,7 +20066,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ91">
         <v>0.91</v>
@@ -20803,7 +20812,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20884,7 +20893,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -21215,7 +21224,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21421,7 +21430,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21499,7 +21508,7 @@
         <v>2.4</v>
       </c>
       <c r="AP98">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ98">
         <v>2.55</v>
@@ -22039,7 +22048,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22117,7 +22126,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ101">
         <v>1.7</v>
@@ -22532,7 +22541,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ103">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR103">
         <v>1.96</v>
@@ -22657,7 +22666,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22738,7 +22747,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ104">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -23069,7 +23078,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23147,7 +23156,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ106">
         <v>1.82</v>
@@ -23275,7 +23284,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23687,7 +23696,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23765,10 +23774,10 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -23893,7 +23902,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24305,7 +24314,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24511,7 +24520,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24717,7 +24726,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24795,7 +24804,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ114">
         <v>1.5</v>
@@ -24923,7 +24932,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25004,7 +25013,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR115">
         <v>1.64</v>
@@ -25129,7 +25138,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25335,7 +25344,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25413,7 +25422,7 @@
         <v>0.33</v>
       </c>
       <c r="AP117">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ117">
         <v>0.55</v>
@@ -25541,7 +25550,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25747,7 +25756,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25828,7 +25837,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ119">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR119">
         <v>1.77</v>
@@ -25953,7 +25962,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26159,7 +26168,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26240,7 +26249,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ121">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -26365,7 +26374,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26443,7 +26452,7 @@
         <v>1.43</v>
       </c>
       <c r="AP122">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122">
         <v>1.82</v>
@@ -26649,7 +26658,7 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
         <v>0.1</v>
@@ -26983,7 +26992,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27189,7 +27198,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27476,7 +27485,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ127">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27679,7 +27688,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27807,7 +27816,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28013,7 +28022,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28091,7 +28100,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ130">
         <v>1.45</v>
@@ -28300,7 +28309,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ131">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.46</v>
@@ -28425,7 +28434,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28631,7 +28640,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28837,7 +28846,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28918,7 +28927,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ134">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR134">
         <v>1.67</v>
@@ -29121,7 +29130,7 @@
         <v>0.29</v>
       </c>
       <c r="AP135">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ135">
         <v>0.55</v>
@@ -29249,7 +29258,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29455,7 +29464,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29661,7 +29670,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30073,7 +30082,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30485,7 +30494,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30978,7 +30987,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ144">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31103,7 +31112,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31181,7 +31190,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ145">
         <v>1.5</v>
@@ -31309,7 +31318,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31387,7 +31396,7 @@
         <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ146">
         <v>1.18</v>
@@ -31515,7 +31524,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31593,7 +31602,7 @@
         <v>2.38</v>
       </c>
       <c r="AP147">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
         <v>2.55</v>
@@ -31802,7 +31811,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ148">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR148">
         <v>1.74</v>
@@ -32133,7 +32142,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32545,7 +32554,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32626,7 +32635,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ152">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR152">
         <v>1.2</v>
@@ -32832,7 +32841,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ153">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR153">
         <v>1.76</v>
@@ -32957,7 +32966,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33035,7 +33044,7 @@
         <v>2</v>
       </c>
       <c r="AP154">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ154">
         <v>1.82</v>
@@ -33163,7 +33172,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33241,10 +33250,10 @@
         <v>1.38</v>
       </c>
       <c r="AP155">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ155">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR155">
         <v>1.57</v>
@@ -33450,7 +33459,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ156">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR156">
         <v>1.25</v>
@@ -33653,7 +33662,7 @@
         <v>0.89</v>
       </c>
       <c r="AP157">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ157">
         <v>0.73</v>
@@ -33859,7 +33868,7 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ158">
         <v>1.18</v>
@@ -34068,7 +34077,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ159">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR159">
         <v>1.15</v>
@@ -34399,7 +34408,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34480,7 +34489,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ161">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34605,7 +34614,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34683,7 +34692,7 @@
         <v>2.44</v>
       </c>
       <c r="AP162">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
         <v>2.55</v>
@@ -34811,7 +34820,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35017,7 +35026,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35223,7 +35232,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35635,7 +35644,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35841,7 +35850,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36047,7 +36056,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36253,7 +36262,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36665,7 +36674,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36952,7 +36961,7 @@
         <v>2</v>
       </c>
       <c r="AQ173">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR173">
         <v>1.57</v>
@@ -37077,7 +37086,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37155,7 +37164,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ174">
         <v>1.45</v>
@@ -37364,7 +37373,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ175">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR175">
         <v>1.23</v>
@@ -37489,7 +37498,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37567,7 +37576,7 @@
         <v>1.89</v>
       </c>
       <c r="AP176">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ176">
         <v>1.82</v>
@@ -37695,7 +37704,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37773,7 +37782,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ177">
         <v>0.73</v>
@@ -37901,7 +37910,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38107,7 +38116,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38188,7 +38197,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ179">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR179">
         <v>1.64</v>
@@ -38313,7 +38322,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38391,7 +38400,7 @@
         <v>1.11</v>
       </c>
       <c r="AP180">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ180">
         <v>0.91</v>
@@ -38519,7 +38528,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38600,7 +38609,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ181">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR181">
         <v>1.76</v>
@@ -38725,7 +38734,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38931,7 +38940,7 @@
         <v>217</v>
       </c>
       <c r="P183" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q183">
         <v>2.4</v>
@@ -39137,7 +39146,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39343,7 +39352,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39549,7 +39558,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40167,7 +40176,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40942,6 +40951,830 @@
       </c>
       <c r="BP192">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7491682</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45703.375</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>82</v>
+      </c>
+      <c r="H193" t="s">
+        <v>77</v>
+      </c>
+      <c r="I193">
+        <v>2</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>2</v>
+      </c>
+      <c r="L193">
+        <v>2</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>2</v>
+      </c>
+      <c r="O193" t="s">
+        <v>223</v>
+      </c>
+      <c r="P193" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q193">
+        <v>2.25</v>
+      </c>
+      <c r="R193">
+        <v>2.3</v>
+      </c>
+      <c r="S193">
+        <v>4.1</v>
+      </c>
+      <c r="T193">
+        <v>1.28</v>
+      </c>
+      <c r="U193">
+        <v>3.4</v>
+      </c>
+      <c r="V193">
+        <v>2.2</v>
+      </c>
+      <c r="W193">
+        <v>1.58</v>
+      </c>
+      <c r="X193">
+        <v>5</v>
+      </c>
+      <c r="Y193">
+        <v>1.15</v>
+      </c>
+      <c r="Z193">
+        <v>1.8</v>
+      </c>
+      <c r="AA193">
+        <v>4.1</v>
+      </c>
+      <c r="AB193">
+        <v>4.2</v>
+      </c>
+      <c r="AC193">
+        <v>1.01</v>
+      </c>
+      <c r="AD193">
+        <v>13</v>
+      </c>
+      <c r="AE193">
+        <v>1.18</v>
+      </c>
+      <c r="AF193">
+        <v>4.75</v>
+      </c>
+      <c r="AG193">
+        <v>1.53</v>
+      </c>
+      <c r="AH193">
+        <v>2.4</v>
+      </c>
+      <c r="AI193">
+        <v>1.53</v>
+      </c>
+      <c r="AJ193">
+        <v>2.3</v>
+      </c>
+      <c r="AK193">
+        <v>1.22</v>
+      </c>
+      <c r="AL193">
+        <v>1.24</v>
+      </c>
+      <c r="AM193">
+        <v>2</v>
+      </c>
+      <c r="AN193">
+        <v>1.55</v>
+      </c>
+      <c r="AO193">
+        <v>1.2</v>
+      </c>
+      <c r="AP193">
+        <v>1.67</v>
+      </c>
+      <c r="AQ193">
+        <v>1.09</v>
+      </c>
+      <c r="AR193">
+        <v>1.5</v>
+      </c>
+      <c r="AS193">
+        <v>1.3</v>
+      </c>
+      <c r="AT193">
+        <v>2.8</v>
+      </c>
+      <c r="AU193">
+        <v>5</v>
+      </c>
+      <c r="AV193">
+        <v>3</v>
+      </c>
+      <c r="AW193">
+        <v>7</v>
+      </c>
+      <c r="AX193">
+        <v>7</v>
+      </c>
+      <c r="AY193">
+        <v>14</v>
+      </c>
+      <c r="AZ193">
+        <v>12</v>
+      </c>
+      <c r="BA193">
+        <v>6</v>
+      </c>
+      <c r="BB193">
+        <v>3</v>
+      </c>
+      <c r="BC193">
+        <v>9</v>
+      </c>
+      <c r="BD193">
+        <v>1.58</v>
+      </c>
+      <c r="BE193">
+        <v>6.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.65</v>
+      </c>
+      <c r="BG193">
+        <v>1.32</v>
+      </c>
+      <c r="BH193">
+        <v>3.05</v>
+      </c>
+      <c r="BI193">
+        <v>1.54</v>
+      </c>
+      <c r="BJ193">
+        <v>2.3</v>
+      </c>
+      <c r="BK193">
+        <v>1.88</v>
+      </c>
+      <c r="BL193">
+        <v>1.8</v>
+      </c>
+      <c r="BM193">
+        <v>2.38</v>
+      </c>
+      <c r="BN193">
+        <v>1.5</v>
+      </c>
+      <c r="BO193">
+        <v>3.05</v>
+      </c>
+      <c r="BP193">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7491684</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45703.375</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>80</v>
+      </c>
+      <c r="H194" t="s">
+        <v>72</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194" t="s">
+        <v>92</v>
+      </c>
+      <c r="P194" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q194">
+        <v>3.1</v>
+      </c>
+      <c r="R194">
+        <v>2.15</v>
+      </c>
+      <c r="S194">
+        <v>2.95</v>
+      </c>
+      <c r="T194">
+        <v>1.33</v>
+      </c>
+      <c r="U194">
+        <v>3</v>
+      </c>
+      <c r="V194">
+        <v>2.45</v>
+      </c>
+      <c r="W194">
+        <v>1.47</v>
+      </c>
+      <c r="X194">
+        <v>6</v>
+      </c>
+      <c r="Y194">
+        <v>1.11</v>
+      </c>
+      <c r="Z194">
+        <v>2.86</v>
+      </c>
+      <c r="AA194">
+        <v>3.51</v>
+      </c>
+      <c r="AB194">
+        <v>2.5</v>
+      </c>
+      <c r="AC194">
+        <v>1.04</v>
+      </c>
+      <c r="AD194">
+        <v>10</v>
+      </c>
+      <c r="AE194">
+        <v>1.21</v>
+      </c>
+      <c r="AF194">
+        <v>4</v>
+      </c>
+      <c r="AG194">
+        <v>1.67</v>
+      </c>
+      <c r="AH194">
+        <v>2</v>
+      </c>
+      <c r="AI194">
+        <v>1.61</v>
+      </c>
+      <c r="AJ194">
+        <v>2.15</v>
+      </c>
+      <c r="AK194">
+        <v>1.51</v>
+      </c>
+      <c r="AL194">
+        <v>1.29</v>
+      </c>
+      <c r="AM194">
+        <v>1.46</v>
+      </c>
+      <c r="AN194">
+        <v>1.8</v>
+      </c>
+      <c r="AO194">
+        <v>0.9</v>
+      </c>
+      <c r="AP194">
+        <v>1.73</v>
+      </c>
+      <c r="AQ194">
+        <v>0.91</v>
+      </c>
+      <c r="AR194">
+        <v>1.74</v>
+      </c>
+      <c r="AS194">
+        <v>1.26</v>
+      </c>
+      <c r="AT194">
+        <v>3</v>
+      </c>
+      <c r="AU194">
+        <v>6</v>
+      </c>
+      <c r="AV194">
+        <v>7</v>
+      </c>
+      <c r="AW194">
+        <v>14</v>
+      </c>
+      <c r="AX194">
+        <v>19</v>
+      </c>
+      <c r="AY194">
+        <v>24</v>
+      </c>
+      <c r="AZ194">
+        <v>35</v>
+      </c>
+      <c r="BA194">
+        <v>2</v>
+      </c>
+      <c r="BB194">
+        <v>9</v>
+      </c>
+      <c r="BC194">
+        <v>11</v>
+      </c>
+      <c r="BD194">
+        <v>2</v>
+      </c>
+      <c r="BE194">
+        <v>6.4</v>
+      </c>
+      <c r="BF194">
+        <v>1.98</v>
+      </c>
+      <c r="BG194">
+        <v>1.35</v>
+      </c>
+      <c r="BH194">
+        <v>2.88</v>
+      </c>
+      <c r="BI194">
+        <v>1.61</v>
+      </c>
+      <c r="BJ194">
+        <v>2.15</v>
+      </c>
+      <c r="BK194">
+        <v>1.98</v>
+      </c>
+      <c r="BL194">
+        <v>1.72</v>
+      </c>
+      <c r="BM194">
+        <v>2.5</v>
+      </c>
+      <c r="BN194">
+        <v>1.46</v>
+      </c>
+      <c r="BO194">
+        <v>3.3</v>
+      </c>
+      <c r="BP194">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7491686</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45703.375</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>86</v>
+      </c>
+      <c r="H195" t="s">
+        <v>76</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
+        <v>134</v>
+      </c>
+      <c r="P195" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q195">
+        <v>3.1</v>
+      </c>
+      <c r="R195">
+        <v>2.2</v>
+      </c>
+      <c r="S195">
+        <v>2.85</v>
+      </c>
+      <c r="T195">
+        <v>1.32</v>
+      </c>
+      <c r="U195">
+        <v>3.1</v>
+      </c>
+      <c r="V195">
+        <v>2.45</v>
+      </c>
+      <c r="W195">
+        <v>1.49</v>
+      </c>
+      <c r="X195">
+        <v>5.75</v>
+      </c>
+      <c r="Y195">
+        <v>1.11</v>
+      </c>
+      <c r="Z195">
+        <v>3.35</v>
+      </c>
+      <c r="AA195">
+        <v>3.64</v>
+      </c>
+      <c r="AB195">
+        <v>2.16</v>
+      </c>
+      <c r="AC195">
+        <v>1.04</v>
+      </c>
+      <c r="AD195">
+        <v>10</v>
+      </c>
+      <c r="AE195">
+        <v>1.22</v>
+      </c>
+      <c r="AF195">
+        <v>3.95</v>
+      </c>
+      <c r="AG195">
+        <v>1.6</v>
+      </c>
+      <c r="AH195">
+        <v>2.1</v>
+      </c>
+      <c r="AI195">
+        <v>1.58</v>
+      </c>
+      <c r="AJ195">
+        <v>2.2</v>
+      </c>
+      <c r="AK195">
+        <v>1.55</v>
+      </c>
+      <c r="AL195">
+        <v>1.28</v>
+      </c>
+      <c r="AM195">
+        <v>1.43</v>
+      </c>
+      <c r="AN195">
+        <v>1.2</v>
+      </c>
+      <c r="AO195">
+        <v>1.2</v>
+      </c>
+      <c r="AP195">
+        <v>1.36</v>
+      </c>
+      <c r="AQ195">
+        <v>1.09</v>
+      </c>
+      <c r="AR195">
+        <v>1.27</v>
+      </c>
+      <c r="AS195">
+        <v>1.71</v>
+      </c>
+      <c r="AT195">
+        <v>2.98</v>
+      </c>
+      <c r="AU195">
+        <v>10</v>
+      </c>
+      <c r="AV195">
+        <v>3</v>
+      </c>
+      <c r="AW195">
+        <v>3</v>
+      </c>
+      <c r="AX195">
+        <v>10</v>
+      </c>
+      <c r="AY195">
+        <v>14</v>
+      </c>
+      <c r="AZ195">
+        <v>18</v>
+      </c>
+      <c r="BA195">
+        <v>3</v>
+      </c>
+      <c r="BB195">
+        <v>1</v>
+      </c>
+      <c r="BC195">
+        <v>4</v>
+      </c>
+      <c r="BD195">
+        <v>2.07</v>
+      </c>
+      <c r="BE195">
+        <v>6.4</v>
+      </c>
+      <c r="BF195">
+        <v>1.94</v>
+      </c>
+      <c r="BG195">
+        <v>1.34</v>
+      </c>
+      <c r="BH195">
+        <v>2.9</v>
+      </c>
+      <c r="BI195">
+        <v>1.58</v>
+      </c>
+      <c r="BJ195">
+        <v>2.18</v>
+      </c>
+      <c r="BK195">
+        <v>1.95</v>
+      </c>
+      <c r="BL195">
+        <v>1.74</v>
+      </c>
+      <c r="BM195">
+        <v>2.48</v>
+      </c>
+      <c r="BN195">
+        <v>1.47</v>
+      </c>
+      <c r="BO195">
+        <v>3.15</v>
+      </c>
+      <c r="BP195">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7491679</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45703.6875</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>83</v>
+      </c>
+      <c r="H196" t="s">
+        <v>73</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>2</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>224</v>
+      </c>
+      <c r="P196" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q196">
+        <v>2.65</v>
+      </c>
+      <c r="R196">
+        <v>2.3</v>
+      </c>
+      <c r="S196">
+        <v>3.25</v>
+      </c>
+      <c r="T196">
+        <v>1.27</v>
+      </c>
+      <c r="U196">
+        <v>3.4</v>
+      </c>
+      <c r="V196">
+        <v>2.2</v>
+      </c>
+      <c r="W196">
+        <v>1.58</v>
+      </c>
+      <c r="X196">
+        <v>5</v>
+      </c>
+      <c r="Y196">
+        <v>1.15</v>
+      </c>
+      <c r="Z196">
+        <v>2.29</v>
+      </c>
+      <c r="AA196">
+        <v>3.69</v>
+      </c>
+      <c r="AB196">
+        <v>3.05</v>
+      </c>
+      <c r="AC196">
+        <v>1.04</v>
+      </c>
+      <c r="AD196">
+        <v>10</v>
+      </c>
+      <c r="AE196">
+        <v>1.17</v>
+      </c>
+      <c r="AF196">
+        <v>4.6</v>
+      </c>
+      <c r="AG196">
+        <v>1.5</v>
+      </c>
+      <c r="AH196">
+        <v>2.48</v>
+      </c>
+      <c r="AI196">
+        <v>1.47</v>
+      </c>
+      <c r="AJ196">
+        <v>2.45</v>
+      </c>
+      <c r="AK196">
+        <v>1.39</v>
+      </c>
+      <c r="AL196">
+        <v>1.27</v>
+      </c>
+      <c r="AM196">
+        <v>1.63</v>
+      </c>
+      <c r="AN196">
+        <v>1.18</v>
+      </c>
+      <c r="AO196">
+        <v>1.64</v>
+      </c>
+      <c r="AP196">
+        <v>1.33</v>
+      </c>
+      <c r="AQ196">
+        <v>1.5</v>
+      </c>
+      <c r="AR196">
+        <v>1.57</v>
+      </c>
+      <c r="AS196">
+        <v>1.47</v>
+      </c>
+      <c r="AT196">
+        <v>3.04</v>
+      </c>
+      <c r="AU196">
+        <v>4</v>
+      </c>
+      <c r="AV196">
+        <v>6</v>
+      </c>
+      <c r="AW196">
+        <v>5</v>
+      </c>
+      <c r="AX196">
+        <v>16</v>
+      </c>
+      <c r="AY196">
+        <v>10</v>
+      </c>
+      <c r="AZ196">
+        <v>27</v>
+      </c>
+      <c r="BA196">
+        <v>4</v>
+      </c>
+      <c r="BB196">
+        <v>7</v>
+      </c>
+      <c r="BC196">
+        <v>11</v>
+      </c>
+      <c r="BD196">
+        <v>1.84</v>
+      </c>
+      <c r="BE196">
+        <v>6.75</v>
+      </c>
+      <c r="BF196">
+        <v>2.15</v>
+      </c>
+      <c r="BG196">
+        <v>1.2</v>
+      </c>
+      <c r="BH196">
+        <v>3.9</v>
+      </c>
+      <c r="BI196">
+        <v>1.36</v>
+      </c>
+      <c r="BJ196">
+        <v>2.8</v>
+      </c>
+      <c r="BK196">
+        <v>1.6</v>
+      </c>
+      <c r="BL196">
+        <v>2.17</v>
+      </c>
+      <c r="BM196">
+        <v>1.96</v>
+      </c>
+      <c r="BN196">
+        <v>1.73</v>
+      </c>
+      <c r="BO196">
+        <v>2.43</v>
+      </c>
+      <c r="BP196">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="343">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,15 @@
     <t>['55', '58']</t>
   </si>
   <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['6', '34']</t>
+  </si>
+  <si>
+    <t>['85', '90+3']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1019,9 +1028,6 @@
   </si>
   <si>
     <t>['45+3', '90+4']</t>
-  </si>
-  <si>
-    <t>['6']</t>
   </si>
   <si>
     <t>['12', '42', '64']</t>
@@ -1398,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1654,7 +1660,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1735,7 +1741,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ2">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1860,7 +1866,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2272,7 +2278,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2684,7 +2690,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2762,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7">
         <v>0.55</v>
@@ -2890,7 +2896,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3096,7 +3102,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3302,7 +3308,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3586,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3714,7 +3720,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3998,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ13">
         <v>1.18</v>
@@ -4126,7 +4132,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4413,7 +4419,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4538,7 +4544,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4744,7 +4750,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4950,7 +4956,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5362,7 +5368,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5649,7 +5655,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ21">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -5774,7 +5780,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6598,7 +6604,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6804,7 +6810,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7010,7 +7016,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7422,7 +7428,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7500,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30">
         <v>1.09</v>
@@ -7628,7 +7634,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8040,7 +8046,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8118,7 +8124,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ33">
         <v>2.55</v>
@@ -8246,7 +8252,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8533,7 +8539,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ35">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR35">
         <v>1.49</v>
@@ -8658,7 +8664,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8736,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36">
         <v>1.82</v>
@@ -8864,7 +8870,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8945,7 +8951,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ37">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>2.14</v>
@@ -9070,7 +9076,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9482,7 +9488,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9688,7 +9694,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9894,7 +9900,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10100,7 +10106,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10512,7 +10518,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10924,7 +10930,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11130,7 +11136,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11208,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48">
         <v>1.09</v>
@@ -11336,7 +11342,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11542,7 +11548,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11620,7 +11626,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ50">
         <v>1.5</v>
@@ -11954,7 +11960,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12035,7 +12041,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ52">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR52">
         <v>1.99</v>
@@ -12160,7 +12166,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12241,7 +12247,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12366,7 +12372,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12447,7 +12453,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ54">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR54">
         <v>1.87</v>
@@ -12572,7 +12578,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12650,7 +12656,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ55">
         <v>0.91</v>
@@ -12778,7 +12784,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12984,7 +12990,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13190,7 +13196,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13474,7 +13480,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ59">
         <v>1.82</v>
@@ -13602,7 +13608,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13808,7 +13814,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14220,7 +14226,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14426,7 +14432,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14507,7 +14513,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ64">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR64">
         <v>2.51</v>
@@ -14838,7 +14844,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15125,7 +15131,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ67">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>2.27</v>
@@ -15456,7 +15462,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15534,7 +15540,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ69">
         <v>0.91</v>
@@ -15662,7 +15668,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15740,7 +15746,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ70">
         <v>1.5</v>
@@ -15868,7 +15874,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16280,7 +16286,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16361,7 +16367,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ73">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR73">
         <v>1.59</v>
@@ -16898,7 +16904,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17104,7 +17110,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17182,7 +17188,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ77">
         <v>2.1</v>
@@ -17803,7 +17809,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ80">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
         <v>1.52</v>
@@ -17928,7 +17934,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18340,7 +18346,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18546,7 +18552,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18624,7 +18630,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ84">
         <v>0.1</v>
@@ -18752,7 +18758,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18958,7 +18964,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19036,7 +19042,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ86">
         <v>1.09</v>
@@ -19164,7 +19170,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19245,7 +19251,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR87">
         <v>1.33</v>
@@ -19370,7 +19376,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19576,7 +19582,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19657,7 +19663,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19782,7 +19788,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20684,7 +20690,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ94">
         <v>1.5</v>
@@ -20812,7 +20818,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21099,7 +21105,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ96">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR96">
         <v>1.59</v>
@@ -21224,7 +21230,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21430,7 +21436,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22048,7 +22054,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22129,7 +22135,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ101">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR101">
         <v>1.49</v>
@@ -22332,7 +22338,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ102">
         <v>1.82</v>
@@ -22666,7 +22672,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22953,7 +22959,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ105">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR105">
         <v>1.68</v>
@@ -23078,7 +23084,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23284,7 +23290,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23568,7 +23574,7 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ108">
         <v>0.1</v>
@@ -23696,7 +23702,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23902,7 +23908,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24314,7 +24320,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24395,7 +24401,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ112">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24520,7 +24526,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24601,7 +24607,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ113">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
         <v>1.37</v>
@@ -24726,7 +24732,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24932,7 +24938,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25138,7 +25144,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25344,7 +25350,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25550,7 +25556,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25628,7 +25634,7 @@
         <v>2.17</v>
       </c>
       <c r="AP118">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ118">
         <v>2.55</v>
@@ -25756,7 +25762,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25962,7 +25968,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26040,7 +26046,7 @@
         <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ120">
         <v>1.82</v>
@@ -26168,7 +26174,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26374,7 +26380,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26992,7 +26998,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27073,7 +27079,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ125">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR125">
         <v>1.52</v>
@@ -27198,7 +27204,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27276,7 +27282,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ126">
         <v>2.1</v>
@@ -27816,7 +27822,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28022,7 +28028,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28103,7 +28109,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ130">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR130">
         <v>1.78</v>
@@ -28434,7 +28440,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28515,7 +28521,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ132">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR132">
         <v>1.64</v>
@@ -28640,7 +28646,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28846,7 +28852,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29258,7 +29264,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29336,7 +29342,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ136">
         <v>1.82</v>
@@ -29464,7 +29470,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29670,7 +29676,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29954,7 +29960,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ139">
         <v>2.1</v>
@@ -30082,7 +30088,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30369,7 +30375,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ141">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR141">
         <v>1.46</v>
@@ -30494,7 +30500,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31112,7 +31118,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31318,7 +31324,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31524,7 +31530,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32017,7 +32023,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ149">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR149">
         <v>1.2</v>
@@ -32142,7 +32148,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32223,7 +32229,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ150">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32426,7 +32432,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ151">
         <v>0.55</v>
@@ -32554,7 +32560,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32632,7 +32638,7 @@
         <v>1.57</v>
       </c>
       <c r="AP152">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ152">
         <v>1.09</v>
@@ -32966,7 +32972,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33172,7 +33178,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33456,7 +33462,7 @@
         <v>0.63</v>
       </c>
       <c r="AP156">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ156">
         <v>0.91</v>
@@ -33665,7 +33671,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ157">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR157">
         <v>1.65</v>
@@ -34408,7 +34414,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34614,7 +34620,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34820,7 +34826,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34898,10 +34904,10 @@
         <v>1.67</v>
       </c>
       <c r="AP163">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ163">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35026,7 +35032,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35232,7 +35238,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35644,7 +35650,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35850,7 +35856,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -35928,7 +35934,7 @@
         <v>0.89</v>
       </c>
       <c r="AP168">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ168">
         <v>1</v>
@@ -36056,7 +36062,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36137,7 +36143,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ169">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36262,7 +36268,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36674,7 +36680,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36958,7 +36964,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ173">
         <v>1.09</v>
@@ -37086,7 +37092,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37167,7 +37173,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ174">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR174">
         <v>1.47</v>
@@ -37370,7 +37376,7 @@
         <v>1.8</v>
       </c>
       <c r="AP175">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ175">
         <v>1.5</v>
@@ -37498,7 +37504,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37704,7 +37710,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37785,7 +37791,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ177">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR177">
         <v>1.61</v>
@@ -37910,7 +37916,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37988,7 +37994,7 @@
         <v>2.5</v>
       </c>
       <c r="AP178">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ178">
         <v>2.55</v>
@@ -38116,7 +38122,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38322,7 +38328,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38528,7 +38534,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38734,7 +38740,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38815,7 +38821,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ182">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR182">
         <v>1.22</v>
@@ -38940,7 +38946,7 @@
         <v>217</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>225</v>
       </c>
       <c r="Q183">
         <v>2.4</v>
@@ -39146,7 +39152,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39352,7 +39358,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39558,7 +39564,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40176,7 +40182,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -41618,7 +41624,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -41775,6 +41781,624 @@
       </c>
       <c r="BP196">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7491687</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45704.39583333334</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>79</v>
+      </c>
+      <c r="H197" t="s">
+        <v>84</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>2</v>
+      </c>
+      <c r="O197" t="s">
+        <v>225</v>
+      </c>
+      <c r="P197" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q197">
+        <v>5</v>
+      </c>
+      <c r="R197">
+        <v>2.38</v>
+      </c>
+      <c r="S197">
+        <v>2.2</v>
+      </c>
+      <c r="T197">
+        <v>1.33</v>
+      </c>
+      <c r="U197">
+        <v>3.25</v>
+      </c>
+      <c r="V197">
+        <v>2.5</v>
+      </c>
+      <c r="W197">
+        <v>1.5</v>
+      </c>
+      <c r="X197">
+        <v>6.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.11</v>
+      </c>
+      <c r="Z197">
+        <v>5.2</v>
+      </c>
+      <c r="AA197">
+        <v>4.33</v>
+      </c>
+      <c r="AB197">
+        <v>1.64</v>
+      </c>
+      <c r="AC197">
+        <v>1.04</v>
+      </c>
+      <c r="AD197">
+        <v>10</v>
+      </c>
+      <c r="AE197">
+        <v>1.21</v>
+      </c>
+      <c r="AF197">
+        <v>4.1</v>
+      </c>
+      <c r="AG197">
+        <v>1.57</v>
+      </c>
+      <c r="AH197">
+        <v>2.15</v>
+      </c>
+      <c r="AI197">
+        <v>1.73</v>
+      </c>
+      <c r="AJ197">
+        <v>2</v>
+      </c>
+      <c r="AK197">
+        <v>2.2</v>
+      </c>
+      <c r="AL197">
+        <v>1.23</v>
+      </c>
+      <c r="AM197">
+        <v>1.17</v>
+      </c>
+      <c r="AN197">
+        <v>1.18</v>
+      </c>
+      <c r="AO197">
+        <v>1.7</v>
+      </c>
+      <c r="AP197">
+        <v>1.17</v>
+      </c>
+      <c r="AQ197">
+        <v>1.64</v>
+      </c>
+      <c r="AR197">
+        <v>1.21</v>
+      </c>
+      <c r="AS197">
+        <v>1.48</v>
+      </c>
+      <c r="AT197">
+        <v>2.69</v>
+      </c>
+      <c r="AU197">
+        <v>6</v>
+      </c>
+      <c r="AV197">
+        <v>7</v>
+      </c>
+      <c r="AW197">
+        <v>11</v>
+      </c>
+      <c r="AX197">
+        <v>5</v>
+      </c>
+      <c r="AY197">
+        <v>23</v>
+      </c>
+      <c r="AZ197">
+        <v>17</v>
+      </c>
+      <c r="BA197">
+        <v>9</v>
+      </c>
+      <c r="BB197">
+        <v>7</v>
+      </c>
+      <c r="BC197">
+        <v>16</v>
+      </c>
+      <c r="BD197">
+        <v>3.3</v>
+      </c>
+      <c r="BE197">
+        <v>8</v>
+      </c>
+      <c r="BF197">
+        <v>1.38</v>
+      </c>
+      <c r="BG197">
+        <v>1.12</v>
+      </c>
+      <c r="BH197">
+        <v>5.1</v>
+      </c>
+      <c r="BI197">
+        <v>1.23</v>
+      </c>
+      <c r="BJ197">
+        <v>3.65</v>
+      </c>
+      <c r="BK197">
+        <v>1.4</v>
+      </c>
+      <c r="BL197">
+        <v>2.7</v>
+      </c>
+      <c r="BM197">
+        <v>1.61</v>
+      </c>
+      <c r="BN197">
+        <v>2.14</v>
+      </c>
+      <c r="BO197">
+        <v>1.95</v>
+      </c>
+      <c r="BP197">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7491681</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45704.39583333334</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>75</v>
+      </c>
+      <c r="H198" t="s">
+        <v>71</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>3</v>
+      </c>
+      <c r="L198">
+        <v>2</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>3</v>
+      </c>
+      <c r="O198" t="s">
+        <v>226</v>
+      </c>
+      <c r="P198" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q198">
+        <v>2.6</v>
+      </c>
+      <c r="R198">
+        <v>2.4</v>
+      </c>
+      <c r="S198">
+        <v>3.75</v>
+      </c>
+      <c r="T198">
+        <v>1.29</v>
+      </c>
+      <c r="U198">
+        <v>3.5</v>
+      </c>
+      <c r="V198">
+        <v>2.38</v>
+      </c>
+      <c r="W198">
+        <v>1.53</v>
+      </c>
+      <c r="X198">
+        <v>5.5</v>
+      </c>
+      <c r="Y198">
+        <v>1.14</v>
+      </c>
+      <c r="Z198">
+        <v>2.06</v>
+      </c>
+      <c r="AA198">
+        <v>3.84</v>
+      </c>
+      <c r="AB198">
+        <v>3.45</v>
+      </c>
+      <c r="AC198">
+        <v>1.04</v>
+      </c>
+      <c r="AD198">
+        <v>10</v>
+      </c>
+      <c r="AE198">
+        <v>1.17</v>
+      </c>
+      <c r="AF198">
+        <v>4.6</v>
+      </c>
+      <c r="AG198">
+        <v>1.53</v>
+      </c>
+      <c r="AH198">
+        <v>2.25</v>
+      </c>
+      <c r="AI198">
+        <v>1.5</v>
+      </c>
+      <c r="AJ198">
+        <v>2.5</v>
+      </c>
+      <c r="AK198">
+        <v>1.32</v>
+      </c>
+      <c r="AL198">
+        <v>1.25</v>
+      </c>
+      <c r="AM198">
+        <v>1.73</v>
+      </c>
+      <c r="AN198">
+        <v>1.1</v>
+      </c>
+      <c r="AO198">
+        <v>1.45</v>
+      </c>
+      <c r="AP198">
+        <v>1.27</v>
+      </c>
+      <c r="AQ198">
+        <v>1.33</v>
+      </c>
+      <c r="AR198">
+        <v>1.64</v>
+      </c>
+      <c r="AS198">
+        <v>1.21</v>
+      </c>
+      <c r="AT198">
+        <v>2.85</v>
+      </c>
+      <c r="AU198">
+        <v>4</v>
+      </c>
+      <c r="AV198">
+        <v>6</v>
+      </c>
+      <c r="AW198">
+        <v>17</v>
+      </c>
+      <c r="AX198">
+        <v>9</v>
+      </c>
+      <c r="AY198">
+        <v>29</v>
+      </c>
+      <c r="AZ198">
+        <v>17</v>
+      </c>
+      <c r="BA198">
+        <v>7</v>
+      </c>
+      <c r="BB198">
+        <v>3</v>
+      </c>
+      <c r="BC198">
+        <v>10</v>
+      </c>
+      <c r="BD198">
+        <v>1.74</v>
+      </c>
+      <c r="BE198">
+        <v>6.5</v>
+      </c>
+      <c r="BF198">
+        <v>2.32</v>
+      </c>
+      <c r="BG198">
+        <v>1.3</v>
+      </c>
+      <c r="BH198">
+        <v>3.05</v>
+      </c>
+      <c r="BI198">
+        <v>1.53</v>
+      </c>
+      <c r="BJ198">
+        <v>2.32</v>
+      </c>
+      <c r="BK198">
+        <v>1.86</v>
+      </c>
+      <c r="BL198">
+        <v>1.82</v>
+      </c>
+      <c r="BM198">
+        <v>2.33</v>
+      </c>
+      <c r="BN198">
+        <v>1.52</v>
+      </c>
+      <c r="BO198">
+        <v>3.05</v>
+      </c>
+      <c r="BP198">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7491683</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45704.39583333334</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>81</v>
+      </c>
+      <c r="H199" t="s">
+        <v>78</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>2</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>227</v>
+      </c>
+      <c r="P199" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q199">
+        <v>2.38</v>
+      </c>
+      <c r="R199">
+        <v>2.3</v>
+      </c>
+      <c r="S199">
+        <v>4.5</v>
+      </c>
+      <c r="T199">
+        <v>1.33</v>
+      </c>
+      <c r="U199">
+        <v>3.25</v>
+      </c>
+      <c r="V199">
+        <v>2.63</v>
+      </c>
+      <c r="W199">
+        <v>1.44</v>
+      </c>
+      <c r="X199">
+        <v>6.5</v>
+      </c>
+      <c r="Y199">
+        <v>1.11</v>
+      </c>
+      <c r="Z199">
+        <v>1.88</v>
+      </c>
+      <c r="AA199">
+        <v>4.2</v>
+      </c>
+      <c r="AB199">
+        <v>3.81</v>
+      </c>
+      <c r="AC199">
+        <v>1.04</v>
+      </c>
+      <c r="AD199">
+        <v>10</v>
+      </c>
+      <c r="AE199">
+        <v>1.22</v>
+      </c>
+      <c r="AF199">
+        <v>3.85</v>
+      </c>
+      <c r="AG199">
+        <v>1.7</v>
+      </c>
+      <c r="AH199">
+        <v>1.95</v>
+      </c>
+      <c r="AI199">
+        <v>1.73</v>
+      </c>
+      <c r="AJ199">
+        <v>2</v>
+      </c>
+      <c r="AK199">
+        <v>1.24</v>
+      </c>
+      <c r="AL199">
+        <v>1.26</v>
+      </c>
+      <c r="AM199">
+        <v>1.9</v>
+      </c>
+      <c r="AN199">
+        <v>2</v>
+      </c>
+      <c r="AO199">
+        <v>0.73</v>
+      </c>
+      <c r="AP199">
+        <v>2.09</v>
+      </c>
+      <c r="AQ199">
+        <v>0.67</v>
+      </c>
+      <c r="AR199">
+        <v>1.58</v>
+      </c>
+      <c r="AS199">
+        <v>1.23</v>
+      </c>
+      <c r="AT199">
+        <v>2.81</v>
+      </c>
+      <c r="AU199">
+        <v>7</v>
+      </c>
+      <c r="AV199">
+        <v>2</v>
+      </c>
+      <c r="AW199">
+        <v>12</v>
+      </c>
+      <c r="AX199">
+        <v>5</v>
+      </c>
+      <c r="AY199">
+        <v>24</v>
+      </c>
+      <c r="AZ199">
+        <v>10</v>
+      </c>
+      <c r="BA199">
+        <v>11</v>
+      </c>
+      <c r="BB199">
+        <v>5</v>
+      </c>
+      <c r="BC199">
+        <v>16</v>
+      </c>
+      <c r="BD199">
+        <v>1.7</v>
+      </c>
+      <c r="BE199">
+        <v>6.5</v>
+      </c>
+      <c r="BF199">
+        <v>2.4</v>
+      </c>
+      <c r="BG199">
+        <v>1.34</v>
+      </c>
+      <c r="BH199">
+        <v>2.9</v>
+      </c>
+      <c r="BI199">
+        <v>1.58</v>
+      </c>
+      <c r="BJ199">
+        <v>2.18</v>
+      </c>
+      <c r="BK199">
+        <v>1.95</v>
+      </c>
+      <c r="BL199">
+        <v>1.74</v>
+      </c>
+      <c r="BM199">
+        <v>2.48</v>
+      </c>
+      <c r="BN199">
+        <v>1.47</v>
+      </c>
+      <c r="BO199">
+        <v>3.2</v>
+      </c>
+      <c r="BP199">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -42150,10 +42150,10 @@
         <v>7</v>
       </c>
       <c r="BB198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC198">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD198">
         <v>1.74</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>['85', '90+3']</t>
+  </si>
+  <si>
+    <t>['42', '65', '78']</t>
   </si>
   <si>
     <t>['5', '35']</t>
@@ -1404,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1660,7 +1663,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1866,7 +1869,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2278,7 +2281,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2356,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ5">
         <v>1.82</v>
@@ -2690,7 +2693,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2896,7 +2899,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3102,7 +3105,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3308,7 +3311,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3389,7 +3392,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ10">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3720,7 +3723,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4132,7 +4135,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4544,7 +4547,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4622,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -4750,7 +4753,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4956,7 +4959,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5368,7 +5371,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5780,7 +5783,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -5861,7 +5864,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ22">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -6270,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ24">
         <v>0.1</v>
@@ -6604,7 +6607,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6810,7 +6813,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7016,7 +7019,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7428,7 +7431,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7634,7 +7637,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7712,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>0.91</v>
@@ -8046,7 +8049,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8252,7 +8255,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8664,7 +8667,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8870,7 +8873,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9076,7 +9079,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9488,7 +9491,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9569,7 +9572,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ40">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
         <v>1.31</v>
@@ -9694,7 +9697,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9900,7 +9903,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10106,7 +10109,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10518,7 +10521,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10596,7 +10599,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ45">
         <v>2.1</v>
@@ -10802,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.1</v>
@@ -10930,7 +10933,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11136,7 +11139,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11342,7 +11345,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11548,7 +11551,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11960,7 +11963,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12166,7 +12169,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12372,7 +12375,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12578,7 +12581,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12784,7 +12787,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12990,7 +12993,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13196,7 +13199,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13274,7 +13277,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>1.82</v>
@@ -13483,7 +13486,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ59">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13608,7 +13611,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13814,7 +13817,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14226,7 +14229,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14304,7 +14307,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -14432,7 +14435,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14844,7 +14847,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15337,7 +15340,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15462,7 +15465,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15668,7 +15671,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15874,7 +15877,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16286,7 +16289,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16776,7 +16779,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ75">
         <v>0.55</v>
@@ -16904,7 +16907,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17110,7 +17113,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17934,7 +17937,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18218,7 +18221,7 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>2.55</v>
@@ -18346,7 +18349,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18552,7 +18555,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18758,7 +18761,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18964,7 +18967,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19170,7 +19173,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19376,7 +19379,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19457,7 +19460,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ88">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
         <v>1.59</v>
@@ -19582,7 +19585,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19788,7 +19791,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20818,7 +20821,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21230,7 +21233,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21308,7 +21311,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ97">
         <v>1.82</v>
@@ -21436,7 +21439,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21926,7 +21929,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -22054,7 +22057,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22341,7 +22344,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ102">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR102">
         <v>1.42</v>
@@ -22672,7 +22675,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23084,7 +23087,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23290,7 +23293,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23702,7 +23705,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23908,7 +23911,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24320,7 +24323,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24526,7 +24529,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24604,7 +24607,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ113">
         <v>0.67</v>
@@ -24732,7 +24735,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24938,7 +24941,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25144,7 +25147,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25222,7 +25225,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>1.18</v>
@@ -25350,7 +25353,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25556,7 +25559,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25762,7 +25765,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25968,7 +25971,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26049,7 +26052,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ120">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26174,7 +26177,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26380,7 +26383,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26998,7 +27001,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27204,7 +27207,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27822,7 +27825,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28028,7 +28031,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28440,7 +28443,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28646,7 +28649,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28852,7 +28855,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28930,7 +28933,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>1.09</v>
@@ -29264,7 +29267,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29470,7 +29473,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29676,7 +29679,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29754,7 +29757,7 @@
         <v>0.86</v>
       </c>
       <c r="AP138">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ138">
         <v>0.91</v>
@@ -30088,7 +30091,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30500,7 +30503,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30581,7 +30584,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ142">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR142">
         <v>1.45</v>
@@ -31118,7 +31121,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31324,7 +31327,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31530,7 +31533,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31814,7 +31817,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
         <v>1.09</v>
@@ -32148,7 +32151,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32560,7 +32563,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32972,7 +32975,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33178,7 +33181,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -34286,7 +34289,7 @@
         <v>2.13</v>
       </c>
       <c r="AP160">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ160">
         <v>1.82</v>
@@ -34414,7 +34417,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34620,7 +34623,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34826,7 +34829,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35032,7 +35035,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35238,7 +35241,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35319,7 +35322,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ165">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -35650,7 +35653,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35856,7 +35859,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36062,7 +36065,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36140,7 +36143,7 @@
         <v>1.38</v>
       </c>
       <c r="AP169">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ169">
         <v>1.64</v>
@@ -36268,7 +36271,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36680,7 +36683,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37092,7 +37095,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37504,7 +37507,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37710,7 +37713,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37916,7 +37919,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38122,7 +38125,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38328,7 +38331,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38534,7 +38537,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38612,7 +38615,7 @@
         <v>0.89</v>
       </c>
       <c r="AP181">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>0.91</v>
@@ -38740,7 +38743,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39152,7 +39155,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39358,7 +39361,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39564,7 +39567,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39848,10 +39851,10 @@
         <v>1.7</v>
       </c>
       <c r="AP187">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ187">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR187">
         <v>1.44</v>
@@ -40182,7 +40185,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -41624,7 +41627,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42399,6 +42402,418 @@
       </c>
       <c r="BP199">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7491690</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45709.60416666666</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>84</v>
+      </c>
+      <c r="H200" t="s">
+        <v>80</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>3</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>3</v>
+      </c>
+      <c r="O200" t="s">
+        <v>228</v>
+      </c>
+      <c r="P200" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q200">
+        <v>2.2</v>
+      </c>
+      <c r="R200">
+        <v>2.3</v>
+      </c>
+      <c r="S200">
+        <v>4.4</v>
+      </c>
+      <c r="T200">
+        <v>1.27</v>
+      </c>
+      <c r="U200">
+        <v>3.4</v>
+      </c>
+      <c r="V200">
+        <v>2.15</v>
+      </c>
+      <c r="W200">
+        <v>1.62</v>
+      </c>
+      <c r="X200">
+        <v>4.75</v>
+      </c>
+      <c r="Y200">
+        <v>1.16</v>
+      </c>
+      <c r="Z200">
+        <v>1.72</v>
+      </c>
+      <c r="AA200">
+        <v>4.33</v>
+      </c>
+      <c r="AB200">
+        <v>4.5</v>
+      </c>
+      <c r="AC200">
+        <v>1.01</v>
+      </c>
+      <c r="AD200">
+        <v>13</v>
+      </c>
+      <c r="AE200">
+        <v>1.16</v>
+      </c>
+      <c r="AF200">
+        <v>4.9</v>
+      </c>
+      <c r="AG200">
+        <v>1.46</v>
+      </c>
+      <c r="AH200">
+        <v>2.6</v>
+      </c>
+      <c r="AI200">
+        <v>1.51</v>
+      </c>
+      <c r="AJ200">
+        <v>2.37</v>
+      </c>
+      <c r="AK200">
+        <v>1.19</v>
+      </c>
+      <c r="AL200">
+        <v>1.25</v>
+      </c>
+      <c r="AM200">
+        <v>2.1</v>
+      </c>
+      <c r="AN200">
+        <v>1.91</v>
+      </c>
+      <c r="AO200">
+        <v>1.82</v>
+      </c>
+      <c r="AP200">
+        <v>2</v>
+      </c>
+      <c r="AQ200">
+        <v>1.67</v>
+      </c>
+      <c r="AR200">
+        <v>1.78</v>
+      </c>
+      <c r="AS200">
+        <v>1.43</v>
+      </c>
+      <c r="AT200">
+        <v>3.21</v>
+      </c>
+      <c r="AU200">
+        <v>9</v>
+      </c>
+      <c r="AV200">
+        <v>2</v>
+      </c>
+      <c r="AW200">
+        <v>7</v>
+      </c>
+      <c r="AX200">
+        <v>10</v>
+      </c>
+      <c r="AY200">
+        <v>18</v>
+      </c>
+      <c r="AZ200">
+        <v>13</v>
+      </c>
+      <c r="BA200">
+        <v>12</v>
+      </c>
+      <c r="BB200">
+        <v>2</v>
+      </c>
+      <c r="BC200">
+        <v>14</v>
+      </c>
+      <c r="BD200">
+        <v>1.49</v>
+      </c>
+      <c r="BE200">
+        <v>6.75</v>
+      </c>
+      <c r="BF200">
+        <v>2.9</v>
+      </c>
+      <c r="BG200">
+        <v>1.32</v>
+      </c>
+      <c r="BH200">
+        <v>3.05</v>
+      </c>
+      <c r="BI200">
+        <v>1.54</v>
+      </c>
+      <c r="BJ200">
+        <v>2.28</v>
+      </c>
+      <c r="BK200">
+        <v>1.89</v>
+      </c>
+      <c r="BL200">
+        <v>1.8</v>
+      </c>
+      <c r="BM200">
+        <v>2.35</v>
+      </c>
+      <c r="BN200">
+        <v>1.5</v>
+      </c>
+      <c r="BO200">
+        <v>3.05</v>
+      </c>
+      <c r="BP200">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7491694</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45709.60416666666</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>73</v>
+      </c>
+      <c r="H201" t="s">
+        <v>81</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201" t="s">
+        <v>92</v>
+      </c>
+      <c r="P201" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q201">
+        <v>2.5</v>
+      </c>
+      <c r="R201">
+        <v>2.43</v>
+      </c>
+      <c r="S201">
+        <v>3.6</v>
+      </c>
+      <c r="T201">
+        <v>1.27</v>
+      </c>
+      <c r="U201">
+        <v>3.45</v>
+      </c>
+      <c r="V201">
+        <v>2.22</v>
+      </c>
+      <c r="W201">
+        <v>1.6</v>
+      </c>
+      <c r="X201">
+        <v>4.75</v>
+      </c>
+      <c r="Y201">
+        <v>1.15</v>
+      </c>
+      <c r="Z201">
+        <v>2.04</v>
+      </c>
+      <c r="AA201">
+        <v>3.89</v>
+      </c>
+      <c r="AB201">
+        <v>3.47</v>
+      </c>
+      <c r="AC201">
+        <v>1.01</v>
+      </c>
+      <c r="AD201">
+        <v>13</v>
+      </c>
+      <c r="AE201">
+        <v>1.16</v>
+      </c>
+      <c r="AF201">
+        <v>4.8</v>
+      </c>
+      <c r="AG201">
+        <v>1.54</v>
+      </c>
+      <c r="AH201">
+        <v>2.37</v>
+      </c>
+      <c r="AI201">
+        <v>1.48</v>
+      </c>
+      <c r="AJ201">
+        <v>2.48</v>
+      </c>
+      <c r="AK201">
+        <v>1.33</v>
+      </c>
+      <c r="AL201">
+        <v>1.25</v>
+      </c>
+      <c r="AM201">
+        <v>1.71</v>
+      </c>
+      <c r="AN201">
+        <v>0.7</v>
+      </c>
+      <c r="AO201">
+        <v>1</v>
+      </c>
+      <c r="AP201">
+        <v>0.73</v>
+      </c>
+      <c r="AQ201">
+        <v>1</v>
+      </c>
+      <c r="AR201">
+        <v>1.48</v>
+      </c>
+      <c r="AS201">
+        <v>1.49</v>
+      </c>
+      <c r="AT201">
+        <v>2.97</v>
+      </c>
+      <c r="AU201">
+        <v>4</v>
+      </c>
+      <c r="AV201">
+        <v>5</v>
+      </c>
+      <c r="AW201">
+        <v>13</v>
+      </c>
+      <c r="AX201">
+        <v>0</v>
+      </c>
+      <c r="AY201">
+        <v>21</v>
+      </c>
+      <c r="AZ201">
+        <v>5</v>
+      </c>
+      <c r="BA201">
+        <v>6</v>
+      </c>
+      <c r="BB201">
+        <v>4</v>
+      </c>
+      <c r="BC201">
+        <v>10</v>
+      </c>
+      <c r="BD201">
+        <v>1.77</v>
+      </c>
+      <c r="BE201">
+        <v>6.75</v>
+      </c>
+      <c r="BF201">
+        <v>2.25</v>
+      </c>
+      <c r="BG201">
+        <v>1.24</v>
+      </c>
+      <c r="BH201">
+        <v>3.55</v>
+      </c>
+      <c r="BI201">
+        <v>1.43</v>
+      </c>
+      <c r="BJ201">
+        <v>2.6</v>
+      </c>
+      <c r="BK201">
+        <v>1.68</v>
+      </c>
+      <c r="BL201">
+        <v>2.02</v>
+      </c>
+      <c r="BM201">
+        <v>2.08</v>
+      </c>
+      <c r="BN201">
+        <v>1.65</v>
+      </c>
+      <c r="BO201">
+        <v>2.65</v>
+      </c>
+      <c r="BP201">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="348">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,12 @@
     <t>['42', '65', '78']</t>
   </si>
   <si>
+    <t>['45+3', '48', '69']</t>
+  </si>
+  <si>
+    <t>['42', '69']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1046,6 +1052,12 @@
   </si>
   <si>
     <t>['13']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['89']</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1663,7 +1675,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1869,7 +1881,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1947,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2153,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ4">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2281,7 +2293,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2362,7 +2374,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ5">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2568,7 +2580,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2693,7 +2705,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2899,7 +2911,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3105,7 +3117,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3311,7 +3323,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3389,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
         <v>1.67</v>
@@ -3723,7 +3735,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4135,7 +4147,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4547,7 +4559,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4753,7 +4765,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4959,7 +4971,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5040,7 +5052,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ18">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5243,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
         <v>0.91</v>
@@ -5371,7 +5383,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5449,10 +5461,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR20">
         <v>1.6</v>
@@ -5655,7 +5667,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ21">
         <v>1.64</v>
@@ -5783,7 +5795,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -5861,7 +5873,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22">
         <v>1.67</v>
@@ -6070,7 +6082,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ23">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR23">
         <v>2.28</v>
@@ -6276,7 +6288,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ24">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6607,7 +6619,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6685,7 +6697,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ26">
         <v>2.1</v>
@@ -6813,7 +6825,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7019,7 +7031,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7431,7 +7443,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7637,7 +7649,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8049,7 +8061,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8130,7 +8142,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ33">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR33">
         <v>1.09</v>
@@ -8255,7 +8267,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8667,7 +8679,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8873,7 +8885,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9079,7 +9091,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9157,10 +9169,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ38">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR38">
         <v>1.52</v>
@@ -9363,7 +9375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39">
         <v>1.18</v>
@@ -9491,7 +9503,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9569,7 +9581,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ40">
         <v>1.67</v>
@@ -9697,7 +9709,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9775,7 +9787,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9903,7 +9915,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10109,7 +10121,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10190,7 +10202,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR43">
         <v>2.41</v>
@@ -10396,7 +10408,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR44">
         <v>1.68</v>
@@ -10521,7 +10533,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10808,7 +10820,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR46">
         <v>1.28</v>
@@ -10933,7 +10945,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11139,7 +11151,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11345,7 +11357,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11551,7 +11563,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11963,7 +11975,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12169,7 +12181,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12375,7 +12387,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12581,7 +12593,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12787,7 +12799,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12865,7 +12877,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ56">
         <v>0.55</v>
@@ -12993,7 +13005,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13199,7 +13211,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13280,7 +13292,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13611,7 +13623,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13692,7 +13704,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ60">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13817,7 +13829,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13895,7 +13907,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ61">
         <v>1.18</v>
@@ -14101,7 +14113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14229,7 +14241,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14310,7 +14322,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR63">
         <v>1.36</v>
@@ -14435,7 +14447,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14722,7 +14734,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ65">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR65">
         <v>1.43</v>
@@ -14847,7 +14859,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14925,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66">
         <v>1.09</v>
@@ -15465,7 +15477,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15671,7 +15683,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15877,7 +15889,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16289,7 +16301,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16907,7 +16919,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16985,10 +16997,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ76">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -17113,7 +17125,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17397,7 +17409,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78">
         <v>1.18</v>
@@ -17606,7 +17618,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR79">
         <v>1.72</v>
@@ -17809,7 +17821,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ80">
         <v>1.33</v>
@@ -17937,7 +17949,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18224,7 +18236,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR82">
         <v>1.62</v>
@@ -18349,7 +18361,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18430,7 +18442,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ83">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR83">
         <v>2.13</v>
@@ -18555,7 +18567,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18636,7 +18648,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ84">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR84">
         <v>1.18</v>
@@ -18761,7 +18773,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18839,7 +18851,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ85">
         <v>1.5</v>
@@ -18967,7 +18979,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19173,7 +19185,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19379,7 +19391,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19585,7 +19597,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19791,7 +19803,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20281,7 +20293,7 @@
         <v>3</v>
       </c>
       <c r="AP92">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ92">
         <v>2.1</v>
@@ -20487,7 +20499,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ93">
         <v>1.18</v>
@@ -20696,7 +20708,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR94">
         <v>1.29</v>
@@ -20821,7 +20833,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21105,7 +21117,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ96">
         <v>1.33</v>
@@ -21233,7 +21245,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21439,7 +21451,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21520,7 +21532,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ98">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR98">
         <v>1.68</v>
@@ -22057,7 +22069,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22675,7 +22687,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23087,7 +23099,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23168,7 +23180,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ106">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR106">
         <v>1.62</v>
@@ -23293,7 +23305,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23371,7 +23383,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ107">
         <v>0.91</v>
@@ -23580,7 +23592,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ108">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR108">
         <v>1.53</v>
@@ -23705,7 +23717,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23911,7 +23923,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24195,7 +24207,7 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ111">
         <v>1.82</v>
@@ -24323,7 +24335,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24529,7 +24541,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24735,7 +24747,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24816,7 +24828,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR114">
         <v>1.54</v>
@@ -24941,7 +24953,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25019,7 +25031,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ115">
         <v>1.09</v>
@@ -25147,7 +25159,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25353,7 +25365,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25559,7 +25571,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25640,7 +25652,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ118">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR118">
         <v>1.21</v>
@@ -25765,7 +25777,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25971,7 +25983,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26177,7 +26189,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26383,7 +26395,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26464,7 +26476,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR122">
         <v>1.56</v>
@@ -26670,7 +26682,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ123">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -27001,7 +27013,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27079,7 +27091,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ125">
         <v>1.64</v>
@@ -27207,7 +27219,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27491,7 +27503,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ127">
         <v>1.09</v>
@@ -27825,7 +27837,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28031,7 +28043,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28443,7 +28455,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28521,7 +28533,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ132">
         <v>0.67</v>
@@ -28649,7 +28661,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28727,10 +28739,10 @@
         <v>2.29</v>
       </c>
       <c r="AP133">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR133">
         <v>1.17</v>
@@ -28855,7 +28867,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29267,7 +29279,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29473,7 +29485,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29551,10 +29563,10 @@
         <v>0.14</v>
       </c>
       <c r="AP137">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ137">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR137">
         <v>1.55</v>
@@ -29679,7 +29691,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30091,7 +30103,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30172,7 +30184,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ140">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR140">
         <v>1.64</v>
@@ -30375,7 +30387,7 @@
         <v>1.43</v>
       </c>
       <c r="AP141">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ141">
         <v>1.64</v>
@@ -30503,7 +30515,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31121,7 +31133,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31202,7 +31214,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ145">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR145">
         <v>1.36</v>
@@ -31327,7 +31339,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31533,7 +31545,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31614,7 +31626,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -32023,7 +32035,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ149">
         <v>0.67</v>
@@ -32151,7 +32163,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32563,7 +32575,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32847,7 +32859,7 @@
         <v>1.75</v>
       </c>
       <c r="AP153">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ153">
         <v>1.5</v>
@@ -32975,7 +32987,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33181,7 +33193,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -34083,7 +34095,7 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ159">
         <v>1.09</v>
@@ -34417,7 +34429,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34623,7 +34635,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34704,7 +34716,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR162">
         <v>1.5</v>
@@ -34829,7 +34841,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35035,7 +35047,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35241,7 +35253,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35528,7 +35540,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ166">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR166">
         <v>1.82</v>
@@ -35653,7 +35665,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35731,7 +35743,7 @@
         <v>2.13</v>
       </c>
       <c r="AP167">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ167">
         <v>2.1</v>
@@ -35859,7 +35871,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36065,7 +36077,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36271,7 +36283,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36349,10 +36361,10 @@
         <v>0.13</v>
       </c>
       <c r="AP170">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ170">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR170">
         <v>1.46</v>
@@ -36558,7 +36570,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ171">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -36683,7 +36695,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36761,7 +36773,7 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ172">
         <v>0.91</v>
@@ -37095,7 +37107,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37507,7 +37519,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37713,7 +37725,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37919,7 +37931,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38000,7 +38012,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ178">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR178">
         <v>1.59</v>
@@ -38125,7 +38137,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38331,7 +38343,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38537,7 +38549,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38743,7 +38755,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38821,7 +38833,7 @@
         <v>1.56</v>
       </c>
       <c r="AP182">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ182">
         <v>1.64</v>
@@ -39030,7 +39042,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ183">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR183">
         <v>1.4</v>
@@ -39155,7 +39167,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39236,7 +39248,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ184">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR184">
         <v>1.56</v>
@@ -39361,7 +39373,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39567,7 +39579,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39645,10 +39657,10 @@
         <v>1.7</v>
       </c>
       <c r="AP186">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ186">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR186">
         <v>1.53</v>
@@ -40185,7 +40197,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40263,7 +40275,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ189">
         <v>0.55</v>
@@ -40469,7 +40481,7 @@
         <v>2.22</v>
       </c>
       <c r="AP190">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ190">
         <v>2.1</v>
@@ -41627,7 +41639,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42814,6 +42826,830 @@
       </c>
       <c r="BP201">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7491691</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>71</v>
+      </c>
+      <c r="H202" t="s">
+        <v>74</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202">
+        <v>3</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>4</v>
+      </c>
+      <c r="O202" t="s">
+        <v>229</v>
+      </c>
+      <c r="P202" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q202">
+        <v>3.1</v>
+      </c>
+      <c r="R202">
+        <v>2.25</v>
+      </c>
+      <c r="S202">
+        <v>2.75</v>
+      </c>
+      <c r="T202">
+        <v>1.26</v>
+      </c>
+      <c r="U202">
+        <v>3.5</v>
+      </c>
+      <c r="V202">
+        <v>2.1</v>
+      </c>
+      <c r="W202">
+        <v>1.65</v>
+      </c>
+      <c r="X202">
+        <v>4.6</v>
+      </c>
+      <c r="Y202">
+        <v>1.17</v>
+      </c>
+      <c r="Z202">
+        <v>2.74</v>
+      </c>
+      <c r="AA202">
+        <v>3.7</v>
+      </c>
+      <c r="AB202">
+        <v>2.5</v>
+      </c>
+      <c r="AC202">
+        <v>1.01</v>
+      </c>
+      <c r="AD202">
+        <v>13</v>
+      </c>
+      <c r="AE202">
+        <v>1.14</v>
+      </c>
+      <c r="AF202">
+        <v>5.2</v>
+      </c>
+      <c r="AG202">
+        <v>1.43</v>
+      </c>
+      <c r="AH202">
+        <v>2.7</v>
+      </c>
+      <c r="AI202">
+        <v>1.42</v>
+      </c>
+      <c r="AJ202">
+        <v>2.65</v>
+      </c>
+      <c r="AK202">
+        <v>1.57</v>
+      </c>
+      <c r="AL202">
+        <v>1.28</v>
+      </c>
+      <c r="AM202">
+        <v>1.42</v>
+      </c>
+      <c r="AN202">
+        <v>1.4</v>
+      </c>
+      <c r="AO202">
+        <v>2.55</v>
+      </c>
+      <c r="AP202">
+        <v>1.55</v>
+      </c>
+      <c r="AQ202">
+        <v>2.33</v>
+      </c>
+      <c r="AR202">
+        <v>1.71</v>
+      </c>
+      <c r="AS202">
+        <v>1.51</v>
+      </c>
+      <c r="AT202">
+        <v>3.22</v>
+      </c>
+      <c r="AU202">
+        <v>5</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>3</v>
+      </c>
+      <c r="AX202">
+        <v>10</v>
+      </c>
+      <c r="AY202">
+        <v>8</v>
+      </c>
+      <c r="AZ202">
+        <v>19</v>
+      </c>
+      <c r="BA202">
+        <v>3</v>
+      </c>
+      <c r="BB202">
+        <v>6</v>
+      </c>
+      <c r="BC202">
+        <v>9</v>
+      </c>
+      <c r="BD202">
+        <v>2.12</v>
+      </c>
+      <c r="BE202">
+        <v>6.5</v>
+      </c>
+      <c r="BF202">
+        <v>1.86</v>
+      </c>
+      <c r="BG202">
+        <v>1.28</v>
+      </c>
+      <c r="BH202">
+        <v>3.25</v>
+      </c>
+      <c r="BI202">
+        <v>1.49</v>
+      </c>
+      <c r="BJ202">
+        <v>2.4</v>
+      </c>
+      <c r="BK202">
+        <v>1.8</v>
+      </c>
+      <c r="BL202">
+        <v>1.88</v>
+      </c>
+      <c r="BM202">
+        <v>2.23</v>
+      </c>
+      <c r="BN202">
+        <v>1.56</v>
+      </c>
+      <c r="BO202">
+        <v>2.9</v>
+      </c>
+      <c r="BP202">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7491695</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>78</v>
+      </c>
+      <c r="H203" t="s">
+        <v>82</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203" t="s">
+        <v>92</v>
+      </c>
+      <c r="P203" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q203">
+        <v>3.5</v>
+      </c>
+      <c r="R203">
+        <v>2.23</v>
+      </c>
+      <c r="S203">
+        <v>2.9</v>
+      </c>
+      <c r="T203">
+        <v>1.36</v>
+      </c>
+      <c r="U203">
+        <v>2.9</v>
+      </c>
+      <c r="V203">
+        <v>2.55</v>
+      </c>
+      <c r="W203">
+        <v>1.45</v>
+      </c>
+      <c r="X203">
+        <v>6.1</v>
+      </c>
+      <c r="Y203">
+        <v>1.1</v>
+      </c>
+      <c r="Z203">
+        <v>2.91</v>
+      </c>
+      <c r="AA203">
+        <v>3.45</v>
+      </c>
+      <c r="AB203">
+        <v>2.49</v>
+      </c>
+      <c r="AC203">
+        <v>1.05</v>
+      </c>
+      <c r="AD203">
+        <v>9</v>
+      </c>
+      <c r="AE203">
+        <v>1.25</v>
+      </c>
+      <c r="AF203">
+        <v>3.6</v>
+      </c>
+      <c r="AG203">
+        <v>1.81</v>
+      </c>
+      <c r="AH203">
+        <v>2.01</v>
+      </c>
+      <c r="AI203">
+        <v>1.63</v>
+      </c>
+      <c r="AJ203">
+        <v>2.15</v>
+      </c>
+      <c r="AK203">
+        <v>1.56</v>
+      </c>
+      <c r="AL203">
+        <v>1.3</v>
+      </c>
+      <c r="AM203">
+        <v>1.38</v>
+      </c>
+      <c r="AN203">
+        <v>0.9</v>
+      </c>
+      <c r="AO203">
+        <v>1.5</v>
+      </c>
+      <c r="AP203">
+        <v>0.91</v>
+      </c>
+      <c r="AQ203">
+        <v>1.45</v>
+      </c>
+      <c r="AR203">
+        <v>1.48</v>
+      </c>
+      <c r="AS203">
+        <v>1.41</v>
+      </c>
+      <c r="AT203">
+        <v>2.89</v>
+      </c>
+      <c r="AU203">
+        <v>4</v>
+      </c>
+      <c r="AV203">
+        <v>5</v>
+      </c>
+      <c r="AW203">
+        <v>12</v>
+      </c>
+      <c r="AX203">
+        <v>7</v>
+      </c>
+      <c r="AY203">
+        <v>16</v>
+      </c>
+      <c r="AZ203">
+        <v>15</v>
+      </c>
+      <c r="BA203">
+        <v>5</v>
+      </c>
+      <c r="BB203">
+        <v>4</v>
+      </c>
+      <c r="BC203">
+        <v>9</v>
+      </c>
+      <c r="BD203">
+        <v>2.17</v>
+      </c>
+      <c r="BE203">
+        <v>6.4</v>
+      </c>
+      <c r="BF203">
+        <v>1.84</v>
+      </c>
+      <c r="BG203">
+        <v>1.29</v>
+      </c>
+      <c r="BH203">
+        <v>3.15</v>
+      </c>
+      <c r="BI203">
+        <v>1.5</v>
+      </c>
+      <c r="BJ203">
+        <v>2.33</v>
+      </c>
+      <c r="BK203">
+        <v>1.84</v>
+      </c>
+      <c r="BL203">
+        <v>1.84</v>
+      </c>
+      <c r="BM203">
+        <v>2.3</v>
+      </c>
+      <c r="BN203">
+        <v>1.53</v>
+      </c>
+      <c r="BO203">
+        <v>2.9</v>
+      </c>
+      <c r="BP203">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7491696</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>87</v>
+      </c>
+      <c r="H204" t="s">
+        <v>79</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>2</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>230</v>
+      </c>
+      <c r="P204" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q204">
+        <v>2.4</v>
+      </c>
+      <c r="R204">
+        <v>2.15</v>
+      </c>
+      <c r="S204">
+        <v>4.2</v>
+      </c>
+      <c r="T204">
+        <v>1.37</v>
+      </c>
+      <c r="U204">
+        <v>2.8</v>
+      </c>
+      <c r="V204">
+        <v>2.7</v>
+      </c>
+      <c r="W204">
+        <v>1.41</v>
+      </c>
+      <c r="X204">
+        <v>6.75</v>
+      </c>
+      <c r="Y204">
+        <v>1.09</v>
+      </c>
+      <c r="Z204">
+        <v>1.86</v>
+      </c>
+      <c r="AA204">
+        <v>3.72</v>
+      </c>
+      <c r="AB204">
+        <v>4.4</v>
+      </c>
+      <c r="AC204">
+        <v>1.05</v>
+      </c>
+      <c r="AD204">
+        <v>9</v>
+      </c>
+      <c r="AE204">
+        <v>1.29</v>
+      </c>
+      <c r="AF204">
+        <v>3.3</v>
+      </c>
+      <c r="AG204">
+        <v>1.92</v>
+      </c>
+      <c r="AH204">
+        <v>1.82</v>
+      </c>
+      <c r="AI204">
+        <v>1.8</v>
+      </c>
+      <c r="AJ204">
+        <v>1.88</v>
+      </c>
+      <c r="AK204">
+        <v>1.23</v>
+      </c>
+      <c r="AL204">
+        <v>1.28</v>
+      </c>
+      <c r="AM204">
+        <v>1.9</v>
+      </c>
+      <c r="AN204">
+        <v>0.91</v>
+      </c>
+      <c r="AO204">
+        <v>0.1</v>
+      </c>
+      <c r="AP204">
+        <v>1.08</v>
+      </c>
+      <c r="AQ204">
+        <v>0.09</v>
+      </c>
+      <c r="AR204">
+        <v>1.2</v>
+      </c>
+      <c r="AS204">
+        <v>1.15</v>
+      </c>
+      <c r="AT204">
+        <v>2.35</v>
+      </c>
+      <c r="AU204">
+        <v>6</v>
+      </c>
+      <c r="AV204">
+        <v>3</v>
+      </c>
+      <c r="AW204">
+        <v>9</v>
+      </c>
+      <c r="AX204">
+        <v>6</v>
+      </c>
+      <c r="AY204">
+        <v>16</v>
+      </c>
+      <c r="AZ204">
+        <v>11</v>
+      </c>
+      <c r="BA204">
+        <v>4</v>
+      </c>
+      <c r="BB204">
+        <v>3</v>
+      </c>
+      <c r="BC204">
+        <v>7</v>
+      </c>
+      <c r="BD204">
+        <v>1.55</v>
+      </c>
+      <c r="BE204">
+        <v>6.5</v>
+      </c>
+      <c r="BF204">
+        <v>2.7</v>
+      </c>
+      <c r="BG204">
+        <v>1.26</v>
+      </c>
+      <c r="BH204">
+        <v>3.4</v>
+      </c>
+      <c r="BI204">
+        <v>1.47</v>
+      </c>
+      <c r="BJ204">
+        <v>2.48</v>
+      </c>
+      <c r="BK204">
+        <v>1.74</v>
+      </c>
+      <c r="BL204">
+        <v>1.96</v>
+      </c>
+      <c r="BM204">
+        <v>2.15</v>
+      </c>
+      <c r="BN204">
+        <v>1.61</v>
+      </c>
+      <c r="BO204">
+        <v>2.7</v>
+      </c>
+      <c r="BP204">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7491692</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45710.6875</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>72</v>
+      </c>
+      <c r="H205" t="s">
+        <v>85</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>146</v>
+      </c>
+      <c r="P205" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q205">
+        <v>2.75</v>
+      </c>
+      <c r="R205">
+        <v>2.35</v>
+      </c>
+      <c r="S205">
+        <v>3.77</v>
+      </c>
+      <c r="T205">
+        <v>1.36</v>
+      </c>
+      <c r="U205">
+        <v>3.17</v>
+      </c>
+      <c r="V205">
+        <v>2.6</v>
+      </c>
+      <c r="W205">
+        <v>1.5</v>
+      </c>
+      <c r="X205">
+        <v>6</v>
+      </c>
+      <c r="Y205">
+        <v>1.11</v>
+      </c>
+      <c r="Z205">
+        <v>2.22</v>
+      </c>
+      <c r="AA205">
+        <v>3.57</v>
+      </c>
+      <c r="AB205">
+        <v>3.27</v>
+      </c>
+      <c r="AC205">
+        <v>1.05</v>
+      </c>
+      <c r="AD205">
+        <v>9.5</v>
+      </c>
+      <c r="AE205">
+        <v>1.22</v>
+      </c>
+      <c r="AF205">
+        <v>3.9</v>
+      </c>
+      <c r="AG205">
+        <v>1.82</v>
+      </c>
+      <c r="AH205">
+        <v>2</v>
+      </c>
+      <c r="AI205">
+        <v>1.6</v>
+      </c>
+      <c r="AJ205">
+        <v>2.2</v>
+      </c>
+      <c r="AK205">
+        <v>1.36</v>
+      </c>
+      <c r="AL205">
+        <v>1.28</v>
+      </c>
+      <c r="AM205">
+        <v>1.65</v>
+      </c>
+      <c r="AN205">
+        <v>2.18</v>
+      </c>
+      <c r="AO205">
+        <v>1.82</v>
+      </c>
+      <c r="AP205">
+        <v>2.08</v>
+      </c>
+      <c r="AQ205">
+        <v>1.75</v>
+      </c>
+      <c r="AR205">
+        <v>1.73</v>
+      </c>
+      <c r="AS205">
+        <v>1.4</v>
+      </c>
+      <c r="AT205">
+        <v>3.13</v>
+      </c>
+      <c r="AU205">
+        <v>2</v>
+      </c>
+      <c r="AV205">
+        <v>7</v>
+      </c>
+      <c r="AW205">
+        <v>6</v>
+      </c>
+      <c r="AX205">
+        <v>10</v>
+      </c>
+      <c r="AY205">
+        <v>8</v>
+      </c>
+      <c r="AZ205">
+        <v>19</v>
+      </c>
+      <c r="BA205">
+        <v>4</v>
+      </c>
+      <c r="BB205">
+        <v>6</v>
+      </c>
+      <c r="BC205">
+        <v>10</v>
+      </c>
+      <c r="BD205">
+        <v>1.76</v>
+      </c>
+      <c r="BE205">
+        <v>6.75</v>
+      </c>
+      <c r="BF205">
+        <v>2.28</v>
+      </c>
+      <c r="BG205">
+        <v>1.29</v>
+      </c>
+      <c r="BH205">
+        <v>3.2</v>
+      </c>
+      <c r="BI205">
+        <v>1.49</v>
+      </c>
+      <c r="BJ205">
+        <v>2.4</v>
+      </c>
+      <c r="BK205">
+        <v>1.79</v>
+      </c>
+      <c r="BL205">
+        <v>1.9</v>
+      </c>
+      <c r="BM205">
+        <v>2.23</v>
+      </c>
+      <c r="BN205">
+        <v>1.56</v>
+      </c>
+      <c r="BO205">
+        <v>2.9</v>
+      </c>
+      <c r="BP205">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -707,6 +707,12 @@
   </si>
   <si>
     <t>['42', '69']</t>
+  </si>
+  <si>
+    <t>['3', '5']</t>
+  </si>
+  <si>
+    <t>['10', '88', '90+8']</t>
   </si>
   <si>
     <t>['5', '35']</t>
@@ -1419,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1675,7 +1681,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1753,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2">
         <v>1.64</v>
@@ -1881,7 +1887,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2293,7 +2299,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2705,7 +2711,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2786,7 +2792,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2911,7 +2917,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2989,10 +2995,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3117,7 +3123,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3195,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9">
         <v>0.91</v>
@@ -3323,7 +3329,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3735,7 +3741,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4022,7 +4028,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ13">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4147,7 +4153,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4559,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4765,7 +4771,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4971,7 +4977,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5383,7 +5389,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5795,7 +5801,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6079,7 +6085,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ23">
         <v>1.75</v>
@@ -6491,10 +6497,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>2.21</v>
@@ -6619,7 +6625,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6700,7 +6706,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR26">
         <v>1.22</v>
@@ -6825,7 +6831,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6903,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7031,7 +7037,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7112,7 +7118,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ28">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR28">
         <v>1.96</v>
@@ -7443,7 +7449,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7649,7 +7655,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8061,7 +8067,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8267,7 +8273,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8679,7 +8685,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8885,7 +8891,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9091,7 +9097,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9378,7 +9384,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ39">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR39">
         <v>1.65</v>
@@ -9503,7 +9509,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9709,7 +9715,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9915,7 +9921,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -9993,10 +9999,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.72</v>
@@ -10121,7 +10127,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10199,7 +10205,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
         <v>2.33</v>
@@ -10405,7 +10411,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44">
         <v>1.45</v>
@@ -10533,7 +10539,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10614,7 +10620,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ45">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.24</v>
@@ -10945,7 +10951,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11151,7 +11157,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11357,7 +11363,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11563,7 +11569,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11975,7 +11981,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12181,7 +12187,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12387,7 +12393,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12593,7 +12599,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12799,7 +12805,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12880,7 +12886,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ56">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -13005,7 +13011,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13083,10 +13089,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ57">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13211,7 +13217,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13623,7 +13629,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13701,7 +13707,7 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ60">
         <v>2.33</v>
@@ -13829,7 +13835,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13910,7 +13916,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
         <v>1.4</v>
@@ -14241,7 +14247,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14447,7 +14453,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14525,7 +14531,7 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ64">
         <v>1.33</v>
@@ -14859,7 +14865,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15143,7 +15149,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ67">
         <v>0.67</v>
@@ -15477,7 +15483,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15683,7 +15689,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15889,7 +15895,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16301,7 +16307,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16585,7 +16591,7 @@
         <v>1.67</v>
       </c>
       <c r="AP74">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>1.82</v>
@@ -16794,7 +16800,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ75">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16919,7 +16925,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17125,7 +17131,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17206,7 +17212,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR77">
         <v>1.26</v>
@@ -17412,7 +17418,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ78">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17949,7 +17955,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18027,7 +18033,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18361,7 +18367,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18439,7 +18445,7 @@
         <v>1.2</v>
       </c>
       <c r="AP83">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ83">
         <v>1.75</v>
@@ -18567,7 +18573,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18773,7 +18779,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18979,7 +18985,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19185,7 +19191,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19391,7 +19397,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19597,7 +19603,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19675,7 +19681,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ89">
         <v>0.67</v>
@@ -19803,7 +19809,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20296,7 +20302,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR92">
         <v>1.28</v>
@@ -20502,7 +20508,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ93">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR93">
         <v>1.52</v>
@@ -20833,7 +20839,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20911,7 +20917,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ95">
         <v>1.09</v>
@@ -21245,7 +21251,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21451,7 +21457,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21738,7 +21744,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ99">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR99">
         <v>1.63</v>
@@ -22069,7 +22075,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22559,7 +22565,7 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ103">
         <v>1.09</v>
@@ -22687,7 +22693,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22765,7 +22771,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ104">
         <v>1.5</v>
@@ -23099,7 +23105,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23305,7 +23311,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23717,7 +23723,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23923,7 +23929,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24335,7 +24341,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24413,7 +24419,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ112">
         <v>1.33</v>
@@ -24541,7 +24547,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24747,7 +24753,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24953,7 +24959,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25159,7 +25165,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25240,7 +25246,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25365,7 +25371,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25446,7 +25452,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ117">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
         <v>1.79</v>
@@ -25571,7 +25577,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25777,7 +25783,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25983,7 +25989,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26189,7 +26195,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26267,7 +26273,7 @@
         <v>0.67</v>
       </c>
       <c r="AP121">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ121">
         <v>0.91</v>
@@ -26395,7 +26401,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26885,7 +26891,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124">
         <v>0.91</v>
@@ -27013,7 +27019,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27219,7 +27225,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27300,7 +27306,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ126">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27837,7 +27843,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27918,7 +27924,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ129">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR129">
         <v>1.5</v>
@@ -28043,7 +28049,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28327,7 +28333,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ131">
         <v>1.5</v>
@@ -28455,7 +28461,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28661,7 +28667,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28867,7 +28873,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29154,7 +29160,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ135">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR135">
         <v>1.54</v>
@@ -29279,7 +29285,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29485,7 +29491,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29691,7 +29697,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29978,7 +29984,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ139">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR139">
         <v>1.49</v>
@@ -30103,7 +30109,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30515,7 +30521,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30593,7 +30599,7 @@
         <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ142">
         <v>1.67</v>
@@ -30799,7 +30805,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -31005,7 +31011,7 @@
         <v>0.71</v>
       </c>
       <c r="AP144">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ144">
         <v>0.91</v>
@@ -31133,7 +31139,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31339,7 +31345,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31420,7 +31426,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ146">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR146">
         <v>1.51</v>
@@ -31545,7 +31551,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32163,7 +32169,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32450,7 +32456,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ151">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR151">
         <v>1.49</v>
@@ -32575,7 +32581,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32987,7 +32993,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33193,7 +33199,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33892,7 +33898,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ158">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR158">
         <v>1.3</v>
@@ -34429,7 +34435,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34635,7 +34641,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34841,7 +34847,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35047,7 +35053,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35128,7 +35134,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ164">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR164">
         <v>1.62</v>
@@ -35253,7 +35259,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35331,7 +35337,7 @@
         <v>1.56</v>
       </c>
       <c r="AP165">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ165">
         <v>1.67</v>
@@ -35537,7 +35543,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ166">
         <v>1.45</v>
@@ -35665,7 +35671,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35746,7 +35752,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ167">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR167">
         <v>1.61</v>
@@ -35871,7 +35877,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36077,7 +36083,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36283,7 +36289,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36567,7 +36573,7 @@
         <v>1.56</v>
       </c>
       <c r="AP171">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ171">
         <v>1.75</v>
@@ -36695,7 +36701,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37107,7 +37113,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37519,7 +37525,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37725,7 +37731,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37931,7 +37937,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38137,7 +38143,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38343,7 +38349,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38549,7 +38555,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38755,7 +38761,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39039,7 +39045,7 @@
         <v>0.11</v>
       </c>
       <c r="AP183">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ183">
         <v>0.09</v>
@@ -39167,7 +39173,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39245,7 +39251,7 @@
         <v>1.33</v>
       </c>
       <c r="AP184">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ184">
         <v>1.45</v>
@@ -39373,7 +39379,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39579,7 +39585,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40069,10 +40075,10 @@
         <v>1.3</v>
       </c>
       <c r="AP188">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ188">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR188">
         <v>1.83</v>
@@ -40197,7 +40203,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40278,7 +40284,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ189">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR189">
         <v>1.59</v>
@@ -40484,7 +40490,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ190">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR190">
         <v>1.76</v>
@@ -41639,7 +41645,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42875,7 +42881,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43493,7 +43499,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43650,6 +43656,624 @@
       </c>
       <c r="BP205">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7491688</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45711.39583333334</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>70</v>
+      </c>
+      <c r="H206" t="s">
+        <v>83</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>102</v>
+      </c>
+      <c r="P206" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q206">
+        <v>2.4</v>
+      </c>
+      <c r="R206">
+        <v>2.3</v>
+      </c>
+      <c r="S206">
+        <v>4.33</v>
+      </c>
+      <c r="T206">
+        <v>1.33</v>
+      </c>
+      <c r="U206">
+        <v>3.25</v>
+      </c>
+      <c r="V206">
+        <v>2.5</v>
+      </c>
+      <c r="W206">
+        <v>1.5</v>
+      </c>
+      <c r="X206">
+        <v>6.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.11</v>
+      </c>
+      <c r="Z206">
+        <v>1.86</v>
+      </c>
+      <c r="AA206">
+        <v>3.86</v>
+      </c>
+      <c r="AB206">
+        <v>4.2</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>10</v>
+      </c>
+      <c r="AE206">
+        <v>1.21</v>
+      </c>
+      <c r="AF206">
+        <v>4</v>
+      </c>
+      <c r="AG206">
+        <v>1.67</v>
+      </c>
+      <c r="AH206">
+        <v>2</v>
+      </c>
+      <c r="AI206">
+        <v>1.62</v>
+      </c>
+      <c r="AJ206">
+        <v>2.2</v>
+      </c>
+      <c r="AK206">
+        <v>1.24</v>
+      </c>
+      <c r="AL206">
+        <v>1.26</v>
+      </c>
+      <c r="AM206">
+        <v>1.93</v>
+      </c>
+      <c r="AN206">
+        <v>1.82</v>
+      </c>
+      <c r="AO206">
+        <v>2.1</v>
+      </c>
+      <c r="AP206">
+        <v>1.75</v>
+      </c>
+      <c r="AQ206">
+        <v>2</v>
+      </c>
+      <c r="AR206">
+        <v>1.8</v>
+      </c>
+      <c r="AS206">
+        <v>1.32</v>
+      </c>
+      <c r="AT206">
+        <v>3.12</v>
+      </c>
+      <c r="AU206">
+        <v>5</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>11</v>
+      </c>
+      <c r="AX206">
+        <v>9</v>
+      </c>
+      <c r="AY206">
+        <v>18</v>
+      </c>
+      <c r="AZ206">
+        <v>16</v>
+      </c>
+      <c r="BA206">
+        <v>7</v>
+      </c>
+      <c r="BB206">
+        <v>0</v>
+      </c>
+      <c r="BC206">
+        <v>7</v>
+      </c>
+      <c r="BD206">
+        <v>1.6</v>
+      </c>
+      <c r="BE206">
+        <v>6.75</v>
+      </c>
+      <c r="BF206">
+        <v>2.55</v>
+      </c>
+      <c r="BG206">
+        <v>1.21</v>
+      </c>
+      <c r="BH206">
+        <v>3.8</v>
+      </c>
+      <c r="BI206">
+        <v>1.38</v>
+      </c>
+      <c r="BJ206">
+        <v>2.7</v>
+      </c>
+      <c r="BK206">
+        <v>1.64</v>
+      </c>
+      <c r="BL206">
+        <v>2.1</v>
+      </c>
+      <c r="BM206">
+        <v>1.98</v>
+      </c>
+      <c r="BN206">
+        <v>1.72</v>
+      </c>
+      <c r="BO206">
+        <v>2.5</v>
+      </c>
+      <c r="BP206">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7491689</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45711.39583333334</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>76</v>
+      </c>
+      <c r="H207" t="s">
+        <v>75</v>
+      </c>
+      <c r="I207">
+        <v>2</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>2</v>
+      </c>
+      <c r="L207">
+        <v>2</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>231</v>
+      </c>
+      <c r="P207" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q207">
+        <v>3</v>
+      </c>
+      <c r="R207">
+        <v>2.3</v>
+      </c>
+      <c r="S207">
+        <v>3.2</v>
+      </c>
+      <c r="T207">
+        <v>1.3</v>
+      </c>
+      <c r="U207">
+        <v>3.4</v>
+      </c>
+      <c r="V207">
+        <v>2.5</v>
+      </c>
+      <c r="W207">
+        <v>1.5</v>
+      </c>
+      <c r="X207">
+        <v>6</v>
+      </c>
+      <c r="Y207">
+        <v>1.13</v>
+      </c>
+      <c r="Z207">
+        <v>2.35</v>
+      </c>
+      <c r="AA207">
+        <v>3.86</v>
+      </c>
+      <c r="AB207">
+        <v>2.85</v>
+      </c>
+      <c r="AC207">
+        <v>1.04</v>
+      </c>
+      <c r="AD207">
+        <v>10</v>
+      </c>
+      <c r="AE207">
+        <v>1.19</v>
+      </c>
+      <c r="AF207">
+        <v>4.3</v>
+      </c>
+      <c r="AG207">
+        <v>1.57</v>
+      </c>
+      <c r="AH207">
+        <v>2.15</v>
+      </c>
+      <c r="AI207">
+        <v>1.53</v>
+      </c>
+      <c r="AJ207">
+        <v>2.38</v>
+      </c>
+      <c r="AK207">
+        <v>1.46</v>
+      </c>
+      <c r="AL207">
+        <v>1.27</v>
+      </c>
+      <c r="AM207">
+        <v>1.53</v>
+      </c>
+      <c r="AN207">
+        <v>1.18</v>
+      </c>
+      <c r="AO207">
+        <v>1.18</v>
+      </c>
+      <c r="AP207">
+        <v>1.33</v>
+      </c>
+      <c r="AQ207">
+        <v>1.08</v>
+      </c>
+      <c r="AR207">
+        <v>1.55</v>
+      </c>
+      <c r="AS207">
+        <v>1.39</v>
+      </c>
+      <c r="AT207">
+        <v>2.94</v>
+      </c>
+      <c r="AU207">
+        <v>4</v>
+      </c>
+      <c r="AV207">
+        <v>3</v>
+      </c>
+      <c r="AW207">
+        <v>10</v>
+      </c>
+      <c r="AX207">
+        <v>4</v>
+      </c>
+      <c r="AY207">
+        <v>16</v>
+      </c>
+      <c r="AZ207">
+        <v>8</v>
+      </c>
+      <c r="BA207">
+        <v>3</v>
+      </c>
+      <c r="BB207">
+        <v>11</v>
+      </c>
+      <c r="BC207">
+        <v>14</v>
+      </c>
+      <c r="BD207">
+        <v>1.95</v>
+      </c>
+      <c r="BE207">
+        <v>6.25</v>
+      </c>
+      <c r="BF207">
+        <v>2.07</v>
+      </c>
+      <c r="BG207">
+        <v>1.41</v>
+      </c>
+      <c r="BH207">
+        <v>2.65</v>
+      </c>
+      <c r="BI207">
+        <v>1.71</v>
+      </c>
+      <c r="BJ207">
+        <v>2</v>
+      </c>
+      <c r="BK207">
+        <v>2.12</v>
+      </c>
+      <c r="BL207">
+        <v>1.63</v>
+      </c>
+      <c r="BM207">
+        <v>2.7</v>
+      </c>
+      <c r="BN207">
+        <v>1.38</v>
+      </c>
+      <c r="BO207">
+        <v>3.65</v>
+      </c>
+      <c r="BP207">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7491693</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45711.39583333334</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>77</v>
+      </c>
+      <c r="H208" t="s">
+        <v>86</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>3</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>3</v>
+      </c>
+      <c r="O208" t="s">
+        <v>232</v>
+      </c>
+      <c r="P208" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q208">
+        <v>2.75</v>
+      </c>
+      <c r="R208">
+        <v>2.25</v>
+      </c>
+      <c r="S208">
+        <v>3.75</v>
+      </c>
+      <c r="T208">
+        <v>1.36</v>
+      </c>
+      <c r="U208">
+        <v>3</v>
+      </c>
+      <c r="V208">
+        <v>2.63</v>
+      </c>
+      <c r="W208">
+        <v>1.44</v>
+      </c>
+      <c r="X208">
+        <v>7</v>
+      </c>
+      <c r="Y208">
+        <v>1.1</v>
+      </c>
+      <c r="Z208">
+        <v>2.12</v>
+      </c>
+      <c r="AA208">
+        <v>3.7</v>
+      </c>
+      <c r="AB208">
+        <v>3.41</v>
+      </c>
+      <c r="AC208">
+        <v>1.05</v>
+      </c>
+      <c r="AD208">
+        <v>9.5</v>
+      </c>
+      <c r="AE208">
+        <v>1.23</v>
+      </c>
+      <c r="AF208">
+        <v>3.75</v>
+      </c>
+      <c r="AG208">
+        <v>1.8</v>
+      </c>
+      <c r="AH208">
+        <v>2.02</v>
+      </c>
+      <c r="AI208">
+        <v>1.62</v>
+      </c>
+      <c r="AJ208">
+        <v>2.2</v>
+      </c>
+      <c r="AK208">
+        <v>1.33</v>
+      </c>
+      <c r="AL208">
+        <v>1.29</v>
+      </c>
+      <c r="AM208">
+        <v>1.68</v>
+      </c>
+      <c r="AN208">
+        <v>1.27</v>
+      </c>
+      <c r="AO208">
+        <v>0.55</v>
+      </c>
+      <c r="AP208">
+        <v>1.42</v>
+      </c>
+      <c r="AQ208">
+        <v>0.5</v>
+      </c>
+      <c r="AR208">
+        <v>1.46</v>
+      </c>
+      <c r="AS208">
+        <v>1.15</v>
+      </c>
+      <c r="AT208">
+        <v>2.61</v>
+      </c>
+      <c r="AU208">
+        <v>8</v>
+      </c>
+      <c r="AV208">
+        <v>4</v>
+      </c>
+      <c r="AW208">
+        <v>13</v>
+      </c>
+      <c r="AX208">
+        <v>6</v>
+      </c>
+      <c r="AY208">
+        <v>24</v>
+      </c>
+      <c r="AZ208">
+        <v>11</v>
+      </c>
+      <c r="BA208">
+        <v>3</v>
+      </c>
+      <c r="BB208">
+        <v>5</v>
+      </c>
+      <c r="BC208">
+        <v>8</v>
+      </c>
+      <c r="BD208">
+        <v>1.73</v>
+      </c>
+      <c r="BE208">
+        <v>7</v>
+      </c>
+      <c r="BF208">
+        <v>2.3</v>
+      </c>
+      <c r="BG208">
+        <v>1.23</v>
+      </c>
+      <c r="BH208">
+        <v>3.65</v>
+      </c>
+      <c r="BI208">
+        <v>1.4</v>
+      </c>
+      <c r="BJ208">
+        <v>2.65</v>
+      </c>
+      <c r="BK208">
+        <v>1.65</v>
+      </c>
+      <c r="BL208">
+        <v>2.07</v>
+      </c>
+      <c r="BM208">
+        <v>2.04</v>
+      </c>
+      <c r="BN208">
+        <v>1.68</v>
+      </c>
+      <c r="BO208">
+        <v>2.55</v>
+      </c>
+      <c r="BP208">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -44231,10 +44231,10 @@
         <v>3</v>
       </c>
       <c r="BB208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC208">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD208">
         <v>1.73</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,12 @@
     <t>['10', '88', '90+8']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -740,9 +746,6 @@
   </si>
   <si>
     <t>['21', '84']</t>
-  </si>
-  <si>
-    <t>['86']</t>
   </si>
   <si>
     <t>['7']</t>
@@ -1064,6 +1067,9 @@
   </si>
   <si>
     <t>['89']</t>
+  </si>
+  <si>
+    <t>['9', '75']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1681,7 +1687,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1887,7 +1893,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2299,7 +2305,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2711,7 +2717,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2789,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2917,7 +2923,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3123,7 +3129,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3204,7 +3210,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ9">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3329,7 +3335,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3741,7 +3747,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3822,7 +3828,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4153,7 +4159,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4437,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15">
         <v>1.33</v>
@@ -4565,7 +4571,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4771,7 +4777,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4977,7 +4983,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5389,7 +5395,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5801,7 +5807,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -6625,7 +6631,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6831,7 +6837,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7037,7 +7043,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7321,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ29">
         <v>0.91</v>
@@ -7449,7 +7455,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7530,7 +7536,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ30">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR30">
         <v>0.79</v>
@@ -7655,7 +7661,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7736,7 +7742,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR31">
         <v>1.09</v>
@@ -8067,7 +8073,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8273,7 +8279,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8685,7 +8691,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8763,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ36">
         <v>1.82</v>
@@ -8891,7 +8897,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9097,7 +9103,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9509,7 +9515,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9715,7 +9721,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9921,7 +9927,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -10127,7 +10133,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10539,7 +10545,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10951,7 +10957,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11157,7 +11163,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11235,7 +11241,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ48">
         <v>1.09</v>
@@ -11363,7 +11369,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11441,7 +11447,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ49">
         <v>1.82</v>
@@ -11569,7 +11575,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11856,7 +11862,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -11981,7 +11987,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12187,7 +12193,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12393,7 +12399,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12599,7 +12605,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12680,7 +12686,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ55">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12805,7 +12811,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13011,7 +13017,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13217,7 +13223,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13629,7 +13635,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13835,7 +13841,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14247,7 +14253,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14453,7 +14459,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14865,7 +14871,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15483,7 +15489,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15564,7 +15570,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ69">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR69">
         <v>0.99</v>
@@ -15689,7 +15695,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15767,7 +15773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ70">
         <v>1.5</v>
@@ -15895,7 +15901,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15976,7 +15982,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ71">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16307,7 +16313,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16385,7 +16391,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ73">
         <v>1.64</v>
@@ -16925,7 +16931,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17131,7 +17137,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17955,7 +17961,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18367,7 +18373,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18573,7 +18579,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18779,7 +18785,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18985,7 +18991,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19063,10 +19069,10 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ86">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR86">
         <v>1.49</v>
@@ -19191,7 +19197,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19397,7 +19403,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19475,7 +19481,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ88">
         <v>1.67</v>
@@ -19603,7 +19609,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19809,7 +19815,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20096,7 +20102,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ91">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR91">
         <v>1.66</v>
@@ -20839,7 +20845,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21251,7 +21257,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21457,7 +21463,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22075,7 +22081,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22568,7 +22574,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ103">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR103">
         <v>1.96</v>
@@ -22693,7 +22699,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23105,7 +23111,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23183,7 +23189,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ106">
         <v>1.75</v>
@@ -23311,7 +23317,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23392,7 +23398,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ107">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23595,7 +23601,7 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ108">
         <v>0.09</v>
@@ -23723,7 +23729,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23929,7 +23935,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24341,7 +24347,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24547,7 +24553,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24753,7 +24759,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24831,7 +24837,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ114">
         <v>1.45</v>
@@ -24959,7 +24965,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25165,7 +25171,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25371,7 +25377,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25577,7 +25583,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25783,7 +25789,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25989,7 +25995,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26067,7 +26073,7 @@
         <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ120">
         <v>1.67</v>
@@ -26195,7 +26201,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26401,7 +26407,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26894,7 +26900,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ124">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR124">
         <v>1.46</v>
@@ -27019,7 +27025,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27225,7 +27231,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27512,7 +27518,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ127">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27843,7 +27849,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28049,7 +28055,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28461,7 +28467,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28667,7 +28673,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28873,7 +28879,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29157,7 +29163,7 @@
         <v>0.29</v>
       </c>
       <c r="AP135">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ135">
         <v>0.5</v>
@@ -29285,7 +29291,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29491,7 +29497,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29697,7 +29703,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29778,7 +29784,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ138">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR138">
         <v>1.37</v>
@@ -29981,7 +29987,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ139">
         <v>2</v>
@@ -30109,7 +30115,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30521,7 +30527,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31139,7 +31145,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31345,7 +31351,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31551,7 +31557,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31629,7 +31635,7 @@
         <v>2.38</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ147">
         <v>2.33</v>
@@ -31838,7 +31844,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR148">
         <v>1.74</v>
@@ -32169,7 +32175,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32581,7 +32587,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32993,7 +32999,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33199,7 +33205,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33277,7 +33283,7 @@
         <v>1.38</v>
       </c>
       <c r="AP155">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ155">
         <v>1.09</v>
@@ -34104,7 +34110,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ159">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR159">
         <v>1.15</v>
@@ -34435,7 +34441,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34641,7 +34647,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34847,7 +34853,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35053,7 +35059,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35259,7 +35265,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35671,7 +35677,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35877,7 +35883,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -35955,7 +35961,7 @@
         <v>0.89</v>
       </c>
       <c r="AP168">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ168">
         <v>1</v>
@@ -36083,7 +36089,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36289,7 +36295,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36701,7 +36707,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36782,7 +36788,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ172">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR172">
         <v>1.67</v>
@@ -37113,7 +37119,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37525,7 +37531,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37731,7 +37737,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37809,7 +37815,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ177">
         <v>0.67</v>
@@ -37937,7 +37943,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38015,7 +38021,7 @@
         <v>2.5</v>
       </c>
       <c r="AP178">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ178">
         <v>2.33</v>
@@ -38143,7 +38149,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38224,7 +38230,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ179">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR179">
         <v>1.64</v>
@@ -38349,7 +38355,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38430,7 +38436,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ180">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR180">
         <v>1.74</v>
@@ -38555,7 +38561,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38761,7 +38767,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39173,7 +39179,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39379,7 +39385,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39585,7 +39591,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40203,7 +40209,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40902,7 +40908,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ192">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR192">
         <v>1.67</v>
@@ -41108,7 +41114,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ193">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR193">
         <v>1.5</v>
@@ -41645,7 +41651,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -41723,7 +41729,7 @@
         <v>1.64</v>
       </c>
       <c r="AP196">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ196">
         <v>1.5</v>
@@ -42135,7 +42141,7 @@
         <v>1.45</v>
       </c>
       <c r="AP198">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ198">
         <v>1.33</v>
@@ -42881,7 +42887,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43499,7 +43505,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -44274,6 +44280,418 @@
       </c>
       <c r="BP208">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7491697</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45716.60416666666</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>83</v>
+      </c>
+      <c r="H209" t="s">
+        <v>77</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>2</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>233</v>
+      </c>
+      <c r="P209" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q209">
+        <v>2.25</v>
+      </c>
+      <c r="R209">
+        <v>2.3</v>
+      </c>
+      <c r="S209">
+        <v>4</v>
+      </c>
+      <c r="T209">
+        <v>1.28</v>
+      </c>
+      <c r="U209">
+        <v>3.3</v>
+      </c>
+      <c r="V209">
+        <v>2.3</v>
+      </c>
+      <c r="W209">
+        <v>1.55</v>
+      </c>
+      <c r="X209">
+        <v>5.25</v>
+      </c>
+      <c r="Y209">
+        <v>1.14</v>
+      </c>
+      <c r="Z209">
+        <v>1.74</v>
+      </c>
+      <c r="AA209">
+        <v>4.2</v>
+      </c>
+      <c r="AB209">
+        <v>4.4</v>
+      </c>
+      <c r="AC209">
+        <v>1.04</v>
+      </c>
+      <c r="AD209">
+        <v>10</v>
+      </c>
+      <c r="AE209">
+        <v>1.18</v>
+      </c>
+      <c r="AF209">
+        <v>4.4</v>
+      </c>
+      <c r="AG209">
+        <v>1.55</v>
+      </c>
+      <c r="AH209">
+        <v>2.2</v>
+      </c>
+      <c r="AI209">
+        <v>1.58</v>
+      </c>
+      <c r="AJ209">
+        <v>2.2</v>
+      </c>
+      <c r="AK209">
+        <v>1.24</v>
+      </c>
+      <c r="AL209">
+        <v>1.24</v>
+      </c>
+      <c r="AM209">
+        <v>1.98</v>
+      </c>
+      <c r="AN209">
+        <v>1.33</v>
+      </c>
+      <c r="AO209">
+        <v>1.09</v>
+      </c>
+      <c r="AP209">
+        <v>1.23</v>
+      </c>
+      <c r="AQ209">
+        <v>1.25</v>
+      </c>
+      <c r="AR209">
+        <v>1.52</v>
+      </c>
+      <c r="AS209">
+        <v>1.28</v>
+      </c>
+      <c r="AT209">
+        <v>2.8</v>
+      </c>
+      <c r="AU209">
+        <v>5</v>
+      </c>
+      <c r="AV209">
+        <v>5</v>
+      </c>
+      <c r="AW209">
+        <v>5</v>
+      </c>
+      <c r="AX209">
+        <v>6</v>
+      </c>
+      <c r="AY209">
+        <v>12</v>
+      </c>
+      <c r="AZ209">
+        <v>14</v>
+      </c>
+      <c r="BA209">
+        <v>6</v>
+      </c>
+      <c r="BB209">
+        <v>4</v>
+      </c>
+      <c r="BC209">
+        <v>10</v>
+      </c>
+      <c r="BD209">
+        <v>1.63</v>
+      </c>
+      <c r="BE209">
+        <v>6.5</v>
+      </c>
+      <c r="BF209">
+        <v>2.55</v>
+      </c>
+      <c r="BG209">
+        <v>1.33</v>
+      </c>
+      <c r="BH209">
+        <v>2.95</v>
+      </c>
+      <c r="BI209">
+        <v>1.56</v>
+      </c>
+      <c r="BJ209">
+        <v>2.23</v>
+      </c>
+      <c r="BK209">
+        <v>1.92</v>
+      </c>
+      <c r="BL209">
+        <v>1.77</v>
+      </c>
+      <c r="BM209">
+        <v>2.43</v>
+      </c>
+      <c r="BN209">
+        <v>1.48</v>
+      </c>
+      <c r="BO209">
+        <v>3.15</v>
+      </c>
+      <c r="BP209">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7491700</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45716.60416666666</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>75</v>
+      </c>
+      <c r="H210" t="s">
+        <v>87</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>1</v>
+      </c>
+      <c r="O210" t="s">
+        <v>234</v>
+      </c>
+      <c r="P210" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q210">
+        <v>2.3</v>
+      </c>
+      <c r="R210">
+        <v>2.2</v>
+      </c>
+      <c r="S210">
+        <v>4.2</v>
+      </c>
+      <c r="T210">
+        <v>1.33</v>
+      </c>
+      <c r="U210">
+        <v>3</v>
+      </c>
+      <c r="V210">
+        <v>2.5</v>
+      </c>
+      <c r="W210">
+        <v>1.46</v>
+      </c>
+      <c r="X210">
+        <v>6</v>
+      </c>
+      <c r="Y210">
+        <v>1.11</v>
+      </c>
+      <c r="Z210">
+        <v>1.81</v>
+      </c>
+      <c r="AA210">
+        <v>3.94</v>
+      </c>
+      <c r="AB210">
+        <v>4.33</v>
+      </c>
+      <c r="AC210">
+        <v>1.04</v>
+      </c>
+      <c r="AD210">
+        <v>10</v>
+      </c>
+      <c r="AE210">
+        <v>1.22</v>
+      </c>
+      <c r="AF210">
+        <v>3.85</v>
+      </c>
+      <c r="AG210">
+        <v>1.67</v>
+      </c>
+      <c r="AH210">
+        <v>2</v>
+      </c>
+      <c r="AI210">
+        <v>1.68</v>
+      </c>
+      <c r="AJ210">
+        <v>2.05</v>
+      </c>
+      <c r="AK210">
+        <v>1.22</v>
+      </c>
+      <c r="AL210">
+        <v>1.25</v>
+      </c>
+      <c r="AM210">
+        <v>1.98</v>
+      </c>
+      <c r="AN210">
+        <v>1.27</v>
+      </c>
+      <c r="AO210">
+        <v>0.91</v>
+      </c>
+      <c r="AP210">
+        <v>1.42</v>
+      </c>
+      <c r="AQ210">
+        <v>0.83</v>
+      </c>
+      <c r="AR210">
+        <v>1.67</v>
+      </c>
+      <c r="AS210">
+        <v>1.29</v>
+      </c>
+      <c r="AT210">
+        <v>2.96</v>
+      </c>
+      <c r="AU210">
+        <v>7</v>
+      </c>
+      <c r="AV210">
+        <v>7</v>
+      </c>
+      <c r="AW210">
+        <v>9</v>
+      </c>
+      <c r="AX210">
+        <v>8</v>
+      </c>
+      <c r="AY210">
+        <v>16</v>
+      </c>
+      <c r="AZ210">
+        <v>17</v>
+      </c>
+      <c r="BA210">
+        <v>10</v>
+      </c>
+      <c r="BB210">
+        <v>7</v>
+      </c>
+      <c r="BC210">
+        <v>17</v>
+      </c>
+      <c r="BD210">
+        <v>1.64</v>
+      </c>
+      <c r="BE210">
+        <v>6.5</v>
+      </c>
+      <c r="BF210">
+        <v>2.5</v>
+      </c>
+      <c r="BG210">
+        <v>1.36</v>
+      </c>
+      <c r="BH210">
+        <v>2.8</v>
+      </c>
+      <c r="BI210">
+        <v>1.64</v>
+      </c>
+      <c r="BJ210">
+        <v>2.1</v>
+      </c>
+      <c r="BK210">
+        <v>2</v>
+      </c>
+      <c r="BL210">
+        <v>1.7</v>
+      </c>
+      <c r="BM210">
+        <v>2.55</v>
+      </c>
+      <c r="BN210">
+        <v>1.44</v>
+      </c>
+      <c r="BO210">
+        <v>3.3</v>
+      </c>
+      <c r="BP210">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="355">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -721,6 +721,12 @@
     <t>['86']</t>
   </si>
   <si>
+    <t>['47', '51', '70']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1070,6 +1076,9 @@
   </si>
   <si>
     <t>['9', '75']</t>
+  </si>
+  <si>
+    <t>['42', '57']</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1687,7 +1696,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1893,7 +1902,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1971,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2180,7 +2189,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ4">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2305,7 +2314,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2717,7 +2726,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2923,7 +2932,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3129,7 +3138,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3335,7 +3344,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3622,7 +3631,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3747,7 +3756,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3825,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ12">
         <v>1.25</v>
@@ -4031,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -4159,7 +4168,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4240,7 +4249,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4777,7 +4786,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4983,7 +4992,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5061,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
         <v>2.33</v>
@@ -5270,7 +5279,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ19">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5395,7 +5404,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5473,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>1.45</v>
@@ -6300,7 +6309,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ24">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6631,7 +6640,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6837,7 +6846,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7043,7 +7052,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7330,7 +7339,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ29">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7455,7 +7464,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7661,7 +7670,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8073,7 +8082,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8151,7 +8160,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ33">
         <v>2.33</v>
@@ -8279,7 +8288,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8357,7 +8366,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ34">
         <v>1.5</v>
@@ -8566,7 +8575,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ35">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR35">
         <v>1.49</v>
@@ -8691,7 +8700,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8772,7 +8781,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8897,7 +8906,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8975,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9103,7 +9112,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9387,7 +9396,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
         <v>1.08</v>
@@ -9515,7 +9524,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9721,7 +9730,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10133,7 +10142,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10545,7 +10554,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10832,7 +10841,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR46">
         <v>1.28</v>
@@ -10957,7 +10966,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11038,7 +11047,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ47">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -11163,7 +11172,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11369,7 +11378,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11450,7 +11459,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ49">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11575,7 +11584,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11653,7 +11662,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ50">
         <v>1.5</v>
@@ -11859,7 +11868,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51">
         <v>1.25</v>
@@ -11987,7 +11996,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12065,7 +12074,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ52">
         <v>1.64</v>
@@ -12193,7 +12202,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12274,7 +12283,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12399,7 +12408,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12605,7 +12614,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12811,7 +12820,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13017,7 +13026,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13223,7 +13232,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13635,7 +13644,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13841,7 +13850,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14253,7 +14262,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14459,7 +14468,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14746,7 +14755,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ65">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR65">
         <v>1.43</v>
@@ -14871,7 +14880,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14949,7 +14958,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ66">
         <v>1.09</v>
@@ -15158,7 +15167,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR67">
         <v>2.27</v>
@@ -15489,7 +15498,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15567,7 +15576,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>0.83</v>
@@ -15695,7 +15704,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15901,7 +15910,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16185,10 +16194,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16313,7 +16322,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16600,7 +16609,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16931,7 +16940,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17137,7 +17146,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17627,7 +17636,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ79">
         <v>1.75</v>
@@ -17961,7 +17970,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18373,7 +18382,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18579,7 +18588,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18657,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ84">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR84">
         <v>1.18</v>
@@ -18785,7 +18794,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18863,7 +18872,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ85">
         <v>1.5</v>
@@ -18991,7 +19000,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19197,7 +19206,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19403,7 +19412,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19609,7 +19618,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19690,7 +19699,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19815,7 +19824,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19896,7 +19905,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ90">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.7</v>
@@ -20099,7 +20108,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91">
         <v>0.83</v>
@@ -20845,7 +20854,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21257,7 +21266,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21338,7 +21347,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ97">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21463,7 +21472,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21541,7 +21550,7 @@
         <v>2.4</v>
       </c>
       <c r="AP98">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ98">
         <v>2.33</v>
@@ -22081,7 +22090,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22159,7 +22168,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ101">
         <v>1.64</v>
@@ -22365,7 +22374,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ102">
         <v>1.67</v>
@@ -22699,7 +22708,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22986,7 +22995,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ105">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR105">
         <v>1.68</v>
@@ -23111,7 +23120,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23317,7 +23326,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23395,7 +23404,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ107">
         <v>0.83</v>
@@ -23604,7 +23613,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ108">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR108">
         <v>1.53</v>
@@ -23729,7 +23738,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23810,7 +23819,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ109">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -23935,7 +23944,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24222,7 +24231,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR111">
         <v>1.23</v>
@@ -24347,7 +24356,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24553,7 +24562,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24634,7 +24643,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ113">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR113">
         <v>1.37</v>
@@ -24759,7 +24768,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24965,7 +24974,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25171,7 +25180,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25377,7 +25386,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25455,7 +25464,7 @@
         <v>0.33</v>
       </c>
       <c r="AP117">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ117">
         <v>0.5</v>
@@ -25583,7 +25592,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25789,7 +25798,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25995,7 +26004,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26201,7 +26210,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26282,7 +26291,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ121">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -26407,7 +26416,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26691,10 +26700,10 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ123">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -27025,7 +27034,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27103,7 +27112,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ125">
         <v>1.64</v>
@@ -27231,7 +27240,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27309,7 +27318,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ126">
         <v>2</v>
@@ -27849,7 +27858,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28055,7 +28064,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28133,7 +28142,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ130">
         <v>1.33</v>
@@ -28467,7 +28476,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28548,7 +28557,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ132">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR132">
         <v>1.64</v>
@@ -28673,7 +28682,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28879,7 +28888,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29291,7 +29300,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29372,7 +29381,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ136">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29497,7 +29506,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29575,10 +29584,10 @@
         <v>0.14</v>
       </c>
       <c r="AP137">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ137">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR137">
         <v>1.55</v>
@@ -29703,7 +29712,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30115,7 +30124,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30527,7 +30536,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31020,7 +31029,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ144">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31145,7 +31154,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31223,7 +31232,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ145">
         <v>1.45</v>
@@ -31351,7 +31360,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31557,7 +31566,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32050,7 +32059,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ149">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR149">
         <v>1.2</v>
@@ -32175,7 +32184,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32459,7 +32468,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ151">
         <v>0.5</v>
@@ -32587,7 +32596,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32999,7 +33008,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33077,10 +33086,10 @@
         <v>2</v>
       </c>
       <c r="AP154">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ154">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR154">
         <v>1.69</v>
@@ -33205,7 +33214,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33492,7 +33501,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ156">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
         <v>1.25</v>
@@ -33695,10 +33704,10 @@
         <v>0.89</v>
       </c>
       <c r="AP157">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ157">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR157">
         <v>1.65</v>
@@ -33901,7 +33910,7 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ158">
         <v>1.08</v>
@@ -34316,7 +34325,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR160">
         <v>1.75</v>
@@ -34441,7 +34450,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34647,7 +34656,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34853,7 +34862,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34931,7 +34940,7 @@
         <v>1.67</v>
       </c>
       <c r="AP163">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ163">
         <v>1.33</v>
@@ -35059,7 +35068,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35265,7 +35274,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35677,7 +35686,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35755,7 +35764,7 @@
         <v>2.13</v>
       </c>
       <c r="AP167">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ167">
         <v>2</v>
@@ -35883,7 +35892,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36089,7 +36098,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36295,7 +36304,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36376,7 +36385,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ170">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR170">
         <v>1.46</v>
@@ -36707,7 +36716,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36991,7 +37000,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ173">
         <v>1.09</v>
@@ -37119,7 +37128,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37531,7 +37540,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37609,10 +37618,10 @@
         <v>1.89</v>
       </c>
       <c r="AP176">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ176">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37737,7 +37746,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37818,7 +37827,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ177">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR177">
         <v>1.61</v>
@@ -37943,7 +37952,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38149,7 +38158,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38355,7 +38364,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38433,7 +38442,7 @@
         <v>1.11</v>
       </c>
       <c r="AP180">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ180">
         <v>0.83</v>
@@ -38561,7 +38570,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38642,7 +38651,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR181">
         <v>1.76</v>
@@ -38767,7 +38776,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39054,7 +39063,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ183">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR183">
         <v>1.4</v>
@@ -39179,7 +39188,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39385,7 +39394,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39591,7 +39600,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40209,7 +40218,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40287,7 +40296,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ189">
         <v>0.5</v>
@@ -40702,7 +40711,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ191">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR191">
         <v>1.77</v>
@@ -41317,10 +41326,10 @@
         <v>0.9</v>
       </c>
       <c r="AP194">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ194">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR194">
         <v>1.74</v>
@@ -41523,7 +41532,7 @@
         <v>1.2</v>
       </c>
       <c r="AP195">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ195">
         <v>1.09</v>
@@ -41651,7 +41660,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42347,10 +42356,10 @@
         <v>0.73</v>
       </c>
       <c r="AP199">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ199">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR199">
         <v>1.58</v>
@@ -42887,7 +42896,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -42965,7 +42974,7 @@
         <v>2.55</v>
       </c>
       <c r="AP202">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ202">
         <v>2.33</v>
@@ -43380,7 +43389,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ204">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR204">
         <v>1.2</v>
@@ -43505,7 +43514,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -44329,7 +44338,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -44692,6 +44701,830 @@
       </c>
       <c r="BP210">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7491705</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45717.375</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>86</v>
+      </c>
+      <c r="H211" t="s">
+        <v>78</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>2</v>
+      </c>
+      <c r="O211" t="s">
+        <v>208</v>
+      </c>
+      <c r="P211" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q211">
+        <v>3</v>
+      </c>
+      <c r="R211">
+        <v>2</v>
+      </c>
+      <c r="S211">
+        <v>3.4</v>
+      </c>
+      <c r="T211">
+        <v>1.42</v>
+      </c>
+      <c r="U211">
+        <v>2.65</v>
+      </c>
+      <c r="V211">
+        <v>2.87</v>
+      </c>
+      <c r="W211">
+        <v>1.36</v>
+      </c>
+      <c r="X211">
+        <v>7.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.07</v>
+      </c>
+      <c r="Z211">
+        <v>2.55</v>
+      </c>
+      <c r="AA211">
+        <v>3.63</v>
+      </c>
+      <c r="AB211">
+        <v>2.72</v>
+      </c>
+      <c r="AC211">
+        <v>1.06</v>
+      </c>
+      <c r="AD211">
+        <v>8.5</v>
+      </c>
+      <c r="AE211">
+        <v>1.33</v>
+      </c>
+      <c r="AF211">
+        <v>3</v>
+      </c>
+      <c r="AG211">
+        <v>1.92</v>
+      </c>
+      <c r="AH211">
+        <v>1.89</v>
+      </c>
+      <c r="AI211">
+        <v>1.78</v>
+      </c>
+      <c r="AJ211">
+        <v>1.9</v>
+      </c>
+      <c r="AK211">
+        <v>1.4</v>
+      </c>
+      <c r="AL211">
+        <v>1.32</v>
+      </c>
+      <c r="AM211">
+        <v>1.53</v>
+      </c>
+      <c r="AN211">
+        <v>1.36</v>
+      </c>
+      <c r="AO211">
+        <v>0.67</v>
+      </c>
+      <c r="AP211">
+        <v>1.33</v>
+      </c>
+      <c r="AQ211">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR211">
+        <v>1.31</v>
+      </c>
+      <c r="AS211">
+        <v>1.2</v>
+      </c>
+      <c r="AT211">
+        <v>2.51</v>
+      </c>
+      <c r="AU211">
+        <v>4</v>
+      </c>
+      <c r="AV211">
+        <v>5</v>
+      </c>
+      <c r="AW211">
+        <v>16</v>
+      </c>
+      <c r="AX211">
+        <v>7</v>
+      </c>
+      <c r="AY211">
+        <v>26</v>
+      </c>
+      <c r="AZ211">
+        <v>15</v>
+      </c>
+      <c r="BA211">
+        <v>8</v>
+      </c>
+      <c r="BB211">
+        <v>4</v>
+      </c>
+      <c r="BC211">
+        <v>12</v>
+      </c>
+      <c r="BD211">
+        <v>1.89</v>
+      </c>
+      <c r="BE211">
+        <v>6.1</v>
+      </c>
+      <c r="BF211">
+        <v>2.15</v>
+      </c>
+      <c r="BG211">
+        <v>1.44</v>
+      </c>
+      <c r="BH211">
+        <v>2.55</v>
+      </c>
+      <c r="BI211">
+        <v>1.73</v>
+      </c>
+      <c r="BJ211">
+        <v>1.96</v>
+      </c>
+      <c r="BK211">
+        <v>2.18</v>
+      </c>
+      <c r="BL211">
+        <v>1.58</v>
+      </c>
+      <c r="BM211">
+        <v>2.8</v>
+      </c>
+      <c r="BN211">
+        <v>1.36</v>
+      </c>
+      <c r="BO211">
+        <v>3.8</v>
+      </c>
+      <c r="BP211">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7491703</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45717.375</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>80</v>
+      </c>
+      <c r="H212" t="s">
+        <v>79</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>3</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212" t="s">
+        <v>235</v>
+      </c>
+      <c r="P212" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q212">
+        <v>2.2</v>
+      </c>
+      <c r="R212">
+        <v>2.25</v>
+      </c>
+      <c r="S212">
+        <v>4.5</v>
+      </c>
+      <c r="T212">
+        <v>1.31</v>
+      </c>
+      <c r="U212">
+        <v>3.1</v>
+      </c>
+      <c r="V212">
+        <v>2.4</v>
+      </c>
+      <c r="W212">
+        <v>1.5</v>
+      </c>
+      <c r="X212">
+        <v>5.75</v>
+      </c>
+      <c r="Y212">
+        <v>1.12</v>
+      </c>
+      <c r="Z212">
+        <v>1.61</v>
+      </c>
+      <c r="AA212">
+        <v>4.4</v>
+      </c>
+      <c r="AB212">
+        <v>5.4</v>
+      </c>
+      <c r="AC212">
+        <v>1.04</v>
+      </c>
+      <c r="AD212">
+        <v>10</v>
+      </c>
+      <c r="AE212">
+        <v>1.21</v>
+      </c>
+      <c r="AF212">
+        <v>4.1</v>
+      </c>
+      <c r="AG212">
+        <v>1.61</v>
+      </c>
+      <c r="AH212">
+        <v>2.1</v>
+      </c>
+      <c r="AI212">
+        <v>1.66</v>
+      </c>
+      <c r="AJ212">
+        <v>2.05</v>
+      </c>
+      <c r="AK212">
+        <v>1.19</v>
+      </c>
+      <c r="AL212">
+        <v>1.24</v>
+      </c>
+      <c r="AM212">
+        <v>2.15</v>
+      </c>
+      <c r="AN212">
+        <v>1.73</v>
+      </c>
+      <c r="AO212">
+        <v>0.09</v>
+      </c>
+      <c r="AP212">
+        <v>1.83</v>
+      </c>
+      <c r="AQ212">
+        <v>0.08</v>
+      </c>
+      <c r="AR212">
+        <v>1.77</v>
+      </c>
+      <c r="AS212">
+        <v>1.15</v>
+      </c>
+      <c r="AT212">
+        <v>2.92</v>
+      </c>
+      <c r="AU212">
+        <v>14</v>
+      </c>
+      <c r="AV212">
+        <v>7</v>
+      </c>
+      <c r="AW212">
+        <v>3</v>
+      </c>
+      <c r="AX212">
+        <v>14</v>
+      </c>
+      <c r="AY212">
+        <v>21</v>
+      </c>
+      <c r="AZ212">
+        <v>24</v>
+      </c>
+      <c r="BA212">
+        <v>7</v>
+      </c>
+      <c r="BB212">
+        <v>7</v>
+      </c>
+      <c r="BC212">
+        <v>14</v>
+      </c>
+      <c r="BD212">
+        <v>1.5</v>
+      </c>
+      <c r="BE212">
+        <v>6.5</v>
+      </c>
+      <c r="BF212">
+        <v>2.8</v>
+      </c>
+      <c r="BG212">
+        <v>1.36</v>
+      </c>
+      <c r="BH212">
+        <v>2.8</v>
+      </c>
+      <c r="BI212">
+        <v>1.61</v>
+      </c>
+      <c r="BJ212">
+        <v>2.15</v>
+      </c>
+      <c r="BK212">
+        <v>1.98</v>
+      </c>
+      <c r="BL212">
+        <v>1.72</v>
+      </c>
+      <c r="BM212">
+        <v>2.55</v>
+      </c>
+      <c r="BN212">
+        <v>1.44</v>
+      </c>
+      <c r="BO212">
+        <v>3.3</v>
+      </c>
+      <c r="BP212">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7491702</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45717.375</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>81</v>
+      </c>
+      <c r="H213" t="s">
+        <v>72</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>2</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="M213">
+        <v>2</v>
+      </c>
+      <c r="N213">
+        <v>3</v>
+      </c>
+      <c r="O213" t="s">
+        <v>175</v>
+      </c>
+      <c r="P213" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q213">
+        <v>3.1</v>
+      </c>
+      <c r="R213">
+        <v>2.1</v>
+      </c>
+      <c r="S213">
+        <v>3</v>
+      </c>
+      <c r="T213">
+        <v>1.35</v>
+      </c>
+      <c r="U213">
+        <v>2.95</v>
+      </c>
+      <c r="V213">
+        <v>2.55</v>
+      </c>
+      <c r="W213">
+        <v>1.44</v>
+      </c>
+      <c r="X213">
+        <v>6.25</v>
+      </c>
+      <c r="Y213">
+        <v>1.1</v>
+      </c>
+      <c r="Z213">
+        <v>2.71</v>
+      </c>
+      <c r="AA213">
+        <v>3.47</v>
+      </c>
+      <c r="AB213">
+        <v>2.64</v>
+      </c>
+      <c r="AC213">
+        <v>1.02</v>
+      </c>
+      <c r="AD213">
+        <v>10</v>
+      </c>
+      <c r="AE213">
+        <v>1.24</v>
+      </c>
+      <c r="AF213">
+        <v>3.7</v>
+      </c>
+      <c r="AG213">
+        <v>1.76</v>
+      </c>
+      <c r="AH213">
+        <v>2.02</v>
+      </c>
+      <c r="AI213">
+        <v>1.63</v>
+      </c>
+      <c r="AJ213">
+        <v>2.1</v>
+      </c>
+      <c r="AK213">
+        <v>1.49</v>
+      </c>
+      <c r="AL213">
+        <v>1.3</v>
+      </c>
+      <c r="AM213">
+        <v>1.46</v>
+      </c>
+      <c r="AN213">
+        <v>2.09</v>
+      </c>
+      <c r="AO213">
+        <v>0.91</v>
+      </c>
+      <c r="AP213">
+        <v>1.92</v>
+      </c>
+      <c r="AQ213">
+        <v>1.08</v>
+      </c>
+      <c r="AR213">
+        <v>1.64</v>
+      </c>
+      <c r="AS213">
+        <v>1.38</v>
+      </c>
+      <c r="AT213">
+        <v>3.02</v>
+      </c>
+      <c r="AU213">
+        <v>3</v>
+      </c>
+      <c r="AV213">
+        <v>8</v>
+      </c>
+      <c r="AW213">
+        <v>8</v>
+      </c>
+      <c r="AX213">
+        <v>9</v>
+      </c>
+      <c r="AY213">
+        <v>13</v>
+      </c>
+      <c r="AZ213">
+        <v>18</v>
+      </c>
+      <c r="BA213">
+        <v>4</v>
+      </c>
+      <c r="BB213">
+        <v>2</v>
+      </c>
+      <c r="BC213">
+        <v>6</v>
+      </c>
+      <c r="BD213">
+        <v>2.05</v>
+      </c>
+      <c r="BE213">
+        <v>6.4</v>
+      </c>
+      <c r="BF213">
+        <v>1.94</v>
+      </c>
+      <c r="BG213">
+        <v>1.35</v>
+      </c>
+      <c r="BH213">
+        <v>2.88</v>
+      </c>
+      <c r="BI213">
+        <v>1.6</v>
+      </c>
+      <c r="BJ213">
+        <v>2.17</v>
+      </c>
+      <c r="BK213">
+        <v>1.96</v>
+      </c>
+      <c r="BL213">
+        <v>1.73</v>
+      </c>
+      <c r="BM213">
+        <v>2.48</v>
+      </c>
+      <c r="BN213">
+        <v>1.46</v>
+      </c>
+      <c r="BO213">
+        <v>3.3</v>
+      </c>
+      <c r="BP213">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7491698</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45717.6875</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>71</v>
+      </c>
+      <c r="H214" t="s">
+        <v>70</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>236</v>
+      </c>
+      <c r="P214" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q214">
+        <v>3.4</v>
+      </c>
+      <c r="R214">
+        <v>2.2</v>
+      </c>
+      <c r="S214">
+        <v>2.65</v>
+      </c>
+      <c r="T214">
+        <v>1.3</v>
+      </c>
+      <c r="U214">
+        <v>3.2</v>
+      </c>
+      <c r="V214">
+        <v>2.3</v>
+      </c>
+      <c r="W214">
+        <v>1.53</v>
+      </c>
+      <c r="X214">
+        <v>5.5</v>
+      </c>
+      <c r="Y214">
+        <v>1.13</v>
+      </c>
+      <c r="Z214">
+        <v>3.15</v>
+      </c>
+      <c r="AA214">
+        <v>3.71</v>
+      </c>
+      <c r="AB214">
+        <v>2.23</v>
+      </c>
+      <c r="AC214">
+        <v>1.04</v>
+      </c>
+      <c r="AD214">
+        <v>10</v>
+      </c>
+      <c r="AE214">
+        <v>1.18</v>
+      </c>
+      <c r="AF214">
+        <v>4.4</v>
+      </c>
+      <c r="AG214">
+        <v>1.57</v>
+      </c>
+      <c r="AH214">
+        <v>2.15</v>
+      </c>
+      <c r="AI214">
+        <v>1.53</v>
+      </c>
+      <c r="AJ214">
+        <v>2.3</v>
+      </c>
+      <c r="AK214">
+        <v>1.65</v>
+      </c>
+      <c r="AL214">
+        <v>1.28</v>
+      </c>
+      <c r="AM214">
+        <v>1.36</v>
+      </c>
+      <c r="AN214">
+        <v>1.55</v>
+      </c>
+      <c r="AO214">
+        <v>1.82</v>
+      </c>
+      <c r="AP214">
+        <v>1.67</v>
+      </c>
+      <c r="AQ214">
+        <v>1.67</v>
+      </c>
+      <c r="AR214">
+        <v>1.66</v>
+      </c>
+      <c r="AS214">
+        <v>1.55</v>
+      </c>
+      <c r="AT214">
+        <v>3.21</v>
+      </c>
+      <c r="AU214">
+        <v>3</v>
+      </c>
+      <c r="AV214">
+        <v>6</v>
+      </c>
+      <c r="AW214">
+        <v>5</v>
+      </c>
+      <c r="AX214">
+        <v>6</v>
+      </c>
+      <c r="AY214">
+        <v>9</v>
+      </c>
+      <c r="AZ214">
+        <v>16</v>
+      </c>
+      <c r="BA214">
+        <v>3</v>
+      </c>
+      <c r="BB214">
+        <v>2</v>
+      </c>
+      <c r="BC214">
+        <v>5</v>
+      </c>
+      <c r="BD214">
+        <v>2.3</v>
+      </c>
+      <c r="BE214">
+        <v>6.4</v>
+      </c>
+      <c r="BF214">
+        <v>1.76</v>
+      </c>
+      <c r="BG214">
+        <v>1.33</v>
+      </c>
+      <c r="BH214">
+        <v>2.95</v>
+      </c>
+      <c r="BI214">
+        <v>1.56</v>
+      </c>
+      <c r="BJ214">
+        <v>2.23</v>
+      </c>
+      <c r="BK214">
+        <v>1.91</v>
+      </c>
+      <c r="BL214">
+        <v>1.77</v>
+      </c>
+      <c r="BM214">
+        <v>2.4</v>
+      </c>
+      <c r="BN214">
+        <v>1.49</v>
+      </c>
+      <c r="BO214">
+        <v>3.15</v>
+      </c>
+      <c r="BP214">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="358">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,12 @@
     <t>['52']</t>
   </si>
   <si>
+    <t>['56', '73', '78', '81']</t>
+  </si>
+  <si>
+    <t>['11', '29', '37', '45+3']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1079,6 +1085,9 @@
   </si>
   <si>
     <t>['42', '57']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1696,7 +1705,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1777,7 +1786,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ2">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1902,7 +1911,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2314,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2598,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ6">
         <v>1.45</v>
@@ -2726,7 +2735,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2932,7 +2941,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3138,7 +3147,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3344,7 +3353,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3756,7 +3765,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4168,7 +4177,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4246,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ14">
         <v>1.67</v>
@@ -4661,7 +4670,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4786,7 +4795,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4864,10 +4873,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4992,7 +5001,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5404,7 +5413,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5691,7 +5700,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ21">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -6640,7 +6649,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6846,7 +6855,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7052,7 +7061,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7130,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ28">
         <v>1.08</v>
@@ -7464,7 +7473,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7670,7 +7679,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7954,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>0.9399999999999999</v>
@@ -8082,7 +8091,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8288,7 +8297,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8369,7 +8378,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ34">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR34">
         <v>1.8</v>
@@ -8572,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35">
         <v>0.6899999999999999</v>
@@ -8700,7 +8709,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8906,7 +8915,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9112,7 +9121,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9524,7 +9533,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9730,7 +9739,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10142,7 +10151,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10554,7 +10563,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10966,7 +10975,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11044,7 +11053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ47">
         <v>1.08</v>
@@ -11172,7 +11181,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11253,7 +11262,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ48">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.7</v>
@@ -11378,7 +11387,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11584,7 +11593,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11665,7 +11674,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ50">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR50">
         <v>0.97</v>
@@ -11996,7 +12005,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12077,7 +12086,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ52">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>1.99</v>
@@ -12202,7 +12211,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12280,7 +12289,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ53">
         <v>0.6899999999999999</v>
@@ -12408,7 +12417,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12486,7 +12495,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12614,7 +12623,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12820,7 +12829,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13026,7 +13035,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13232,7 +13241,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13644,7 +13653,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13850,7 +13859,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14262,7 +14271,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14468,7 +14477,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14752,7 +14761,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65">
         <v>0.08</v>
@@ -14880,7 +14889,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14961,7 +14970,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.63</v>
@@ -15370,7 +15379,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ68">
         <v>1.67</v>
@@ -15498,7 +15507,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15704,7 +15713,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15785,7 +15794,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR70">
         <v>1.66</v>
@@ -15910,7 +15919,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15988,7 +15997,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ71">
         <v>1.25</v>
@@ -16322,7 +16331,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16403,7 +16412,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ73">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>1.59</v>
@@ -16940,7 +16949,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17146,7 +17155,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17970,7 +17979,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18382,7 +18391,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18588,7 +18597,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18794,7 +18803,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18875,7 +18884,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR85">
         <v>1.57</v>
@@ -19000,7 +19009,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19206,7 +19215,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19284,10 +19293,10 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ87">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR87">
         <v>1.33</v>
@@ -19412,7 +19421,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19618,7 +19627,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19824,7 +19833,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19902,7 +19911,7 @@
         <v>0.25</v>
       </c>
       <c r="AP90">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -20854,7 +20863,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20935,7 +20944,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ95">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -21266,7 +21275,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21472,7 +21481,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21756,7 +21765,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
         <v>0.5</v>
@@ -22090,7 +22099,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22171,7 +22180,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ101">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
         <v>1.49</v>
@@ -22708,7 +22717,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22789,7 +22798,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -22992,7 +23001,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ105">
         <v>0.6899999999999999</v>
@@ -23120,7 +23129,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23326,7 +23335,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23738,7 +23747,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23816,7 +23825,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>1.08</v>
@@ -23944,7 +23953,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24022,7 +24031,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24356,7 +24365,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24562,7 +24571,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24768,7 +24777,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24974,7 +24983,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25055,7 +25064,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ115">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.64</v>
@@ -25180,7 +25189,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25386,7 +25395,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25592,7 +25601,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25798,7 +25807,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25876,10 +25885,10 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ119">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR119">
         <v>1.77</v>
@@ -26004,7 +26013,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26210,7 +26219,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26416,7 +26425,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26494,7 +26503,7 @@
         <v>1.43</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ122">
         <v>1.75</v>
@@ -27034,7 +27043,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27115,7 +27124,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ125">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.52</v>
@@ -27240,7 +27249,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27730,7 +27739,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27858,7 +27867,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27936,7 +27945,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129">
         <v>1.08</v>
@@ -28064,7 +28073,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28351,7 +28360,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.46</v>
@@ -28476,7 +28485,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28682,7 +28691,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28888,7 +28897,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28969,7 +28978,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>1.67</v>
@@ -29300,7 +29309,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29506,7 +29515,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29712,7 +29721,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30124,7 +30133,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30202,7 +30211,7 @@
         <v>1.63</v>
       </c>
       <c r="AP140">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ140">
         <v>1.75</v>
@@ -30411,7 +30420,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ141">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR141">
         <v>1.46</v>
@@ -30536,7 +30545,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31154,7 +31163,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31360,7 +31369,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31438,7 +31447,7 @@
         <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ146">
         <v>1.08</v>
@@ -31566,7 +31575,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32184,7 +32193,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32262,7 +32271,7 @@
         <v>1.5</v>
       </c>
       <c r="AP150">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ150">
         <v>1.33</v>
@@ -32596,7 +32605,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32677,7 +32686,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ152">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.2</v>
@@ -32883,7 +32892,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ153">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR153">
         <v>1.76</v>
@@ -33008,7 +33017,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33214,7 +33223,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33295,7 +33304,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ155">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.57</v>
@@ -34450,7 +34459,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34528,10 +34537,10 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34656,7 +34665,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34734,7 +34743,7 @@
         <v>2.44</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ162">
         <v>2.33</v>
@@ -34862,7 +34871,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35068,7 +35077,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35146,7 +35155,7 @@
         <v>0.22</v>
       </c>
       <c r="AP164">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ164">
         <v>0.5</v>
@@ -35274,7 +35283,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35686,7 +35695,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35892,7 +35901,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36098,7 +36107,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36179,7 +36188,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ169">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36304,7 +36313,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36716,7 +36725,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37003,7 +37012,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ173">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.57</v>
@@ -37128,7 +37137,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37206,7 +37215,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ174">
         <v>1.33</v>
@@ -37415,7 +37424,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ175">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR175">
         <v>1.23</v>
@@ -37540,7 +37549,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37746,7 +37755,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37952,7 +37961,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38158,7 +38167,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38236,7 +38245,7 @@
         <v>1</v>
       </c>
       <c r="AP179">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179">
         <v>1.25</v>
@@ -38364,7 +38373,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38570,7 +38579,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38776,7 +38785,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -38857,7 +38866,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ182">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR182">
         <v>1.22</v>
@@ -39188,7 +39197,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39394,7 +39403,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39472,7 +39481,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39600,7 +39609,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40218,7 +40227,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40708,7 +40717,7 @@
         <v>2</v>
       </c>
       <c r="AP191">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ191">
         <v>1.67</v>
@@ -40914,7 +40923,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ192">
         <v>0.83</v>
@@ -41120,7 +41129,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ193">
         <v>1.25</v>
@@ -41535,7 +41544,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ195">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR195">
         <v>1.27</v>
@@ -41660,7 +41669,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -41741,7 +41750,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ196">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.57</v>
@@ -41947,7 +41956,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ197">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR197">
         <v>1.21</v>
@@ -42896,7 +42905,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43514,7 +43523,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -44338,7 +44347,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -45162,7 +45171,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45525,6 +45534,624 @@
       </c>
       <c r="BP214">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7491704</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45718.39583333334</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>74</v>
+      </c>
+      <c r="H215" t="s">
+        <v>76</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>4</v>
+      </c>
+      <c r="M215">
+        <v>1</v>
+      </c>
+      <c r="N215">
+        <v>5</v>
+      </c>
+      <c r="O215" t="s">
+        <v>237</v>
+      </c>
+      <c r="P215" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q215">
+        <v>2.5</v>
+      </c>
+      <c r="R215">
+        <v>2.4</v>
+      </c>
+      <c r="S215">
+        <v>3.75</v>
+      </c>
+      <c r="T215">
+        <v>1.29</v>
+      </c>
+      <c r="U215">
+        <v>3.5</v>
+      </c>
+      <c r="V215">
+        <v>2.25</v>
+      </c>
+      <c r="W215">
+        <v>1.57</v>
+      </c>
+      <c r="X215">
+        <v>5.5</v>
+      </c>
+      <c r="Y215">
+        <v>1.14</v>
+      </c>
+      <c r="Z215">
+        <v>1.95</v>
+      </c>
+      <c r="AA215">
+        <v>4</v>
+      </c>
+      <c r="AB215">
+        <v>3.66</v>
+      </c>
+      <c r="AC215">
+        <v>1.03</v>
+      </c>
+      <c r="AD215">
+        <v>11</v>
+      </c>
+      <c r="AE215">
+        <v>1.17</v>
+      </c>
+      <c r="AF215">
+        <v>4.6</v>
+      </c>
+      <c r="AG215">
+        <v>1.53</v>
+      </c>
+      <c r="AH215">
+        <v>2.25</v>
+      </c>
+      <c r="AI215">
+        <v>1.5</v>
+      </c>
+      <c r="AJ215">
+        <v>2.5</v>
+      </c>
+      <c r="AK215">
+        <v>1.28</v>
+      </c>
+      <c r="AL215">
+        <v>1.26</v>
+      </c>
+      <c r="AM215">
+        <v>1.82</v>
+      </c>
+      <c r="AN215">
+        <v>0.91</v>
+      </c>
+      <c r="AO215">
+        <v>1.09</v>
+      </c>
+      <c r="AP215">
+        <v>1.08</v>
+      </c>
+      <c r="AQ215">
+        <v>1</v>
+      </c>
+      <c r="AR215">
+        <v>1.76</v>
+      </c>
+      <c r="AS215">
+        <v>1.67</v>
+      </c>
+      <c r="AT215">
+        <v>3.43</v>
+      </c>
+      <c r="AU215">
+        <v>11</v>
+      </c>
+      <c r="AV215">
+        <v>7</v>
+      </c>
+      <c r="AW215">
+        <v>6</v>
+      </c>
+      <c r="AX215">
+        <v>8</v>
+      </c>
+      <c r="AY215">
+        <v>19</v>
+      </c>
+      <c r="AZ215">
+        <v>17</v>
+      </c>
+      <c r="BA215">
+        <v>12</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>16</v>
+      </c>
+      <c r="BD215">
+        <v>1.68</v>
+      </c>
+      <c r="BE215">
+        <v>6.75</v>
+      </c>
+      <c r="BF215">
+        <v>2.4</v>
+      </c>
+      <c r="BG215">
+        <v>1.19</v>
+      </c>
+      <c r="BH215">
+        <v>4.1</v>
+      </c>
+      <c r="BI215">
+        <v>1.34</v>
+      </c>
+      <c r="BJ215">
+        <v>2.9</v>
+      </c>
+      <c r="BK215">
+        <v>1.56</v>
+      </c>
+      <c r="BL215">
+        <v>2.23</v>
+      </c>
+      <c r="BM215">
+        <v>1.88</v>
+      </c>
+      <c r="BN215">
+        <v>1.8</v>
+      </c>
+      <c r="BO215">
+        <v>2.33</v>
+      </c>
+      <c r="BP215">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7491701</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45718.39583333334</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>82</v>
+      </c>
+      <c r="H216" t="s">
+        <v>73</v>
+      </c>
+      <c r="I216">
+        <v>4</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>4</v>
+      </c>
+      <c r="L216">
+        <v>4</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>4</v>
+      </c>
+      <c r="O216" t="s">
+        <v>238</v>
+      </c>
+      <c r="P216" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q216">
+        <v>3</v>
+      </c>
+      <c r="R216">
+        <v>2.38</v>
+      </c>
+      <c r="S216">
+        <v>3.2</v>
+      </c>
+      <c r="T216">
+        <v>1.3</v>
+      </c>
+      <c r="U216">
+        <v>3.4</v>
+      </c>
+      <c r="V216">
+        <v>2.38</v>
+      </c>
+      <c r="W216">
+        <v>1.53</v>
+      </c>
+      <c r="X216">
+        <v>6</v>
+      </c>
+      <c r="Y216">
+        <v>1.13</v>
+      </c>
+      <c r="Z216">
+        <v>2.43</v>
+      </c>
+      <c r="AA216">
+        <v>3.86</v>
+      </c>
+      <c r="AB216">
+        <v>2.74</v>
+      </c>
+      <c r="AC216">
+        <v>1.04</v>
+      </c>
+      <c r="AD216">
+        <v>10</v>
+      </c>
+      <c r="AE216">
+        <v>1.17</v>
+      </c>
+      <c r="AF216">
+        <v>4.5</v>
+      </c>
+      <c r="AG216">
+        <v>1.63</v>
+      </c>
+      <c r="AH216">
+        <v>2.29</v>
+      </c>
+      <c r="AI216">
+        <v>1.5</v>
+      </c>
+      <c r="AJ216">
+        <v>2.5</v>
+      </c>
+      <c r="AK216">
+        <v>1.44</v>
+      </c>
+      <c r="AL216">
+        <v>1.27</v>
+      </c>
+      <c r="AM216">
+        <v>1.55</v>
+      </c>
+      <c r="AN216">
+        <v>1.67</v>
+      </c>
+      <c r="AO216">
+        <v>1.5</v>
+      </c>
+      <c r="AP216">
+        <v>1.77</v>
+      </c>
+      <c r="AQ216">
+        <v>1.38</v>
+      </c>
+      <c r="AR216">
+        <v>1.49</v>
+      </c>
+      <c r="AS216">
+        <v>1.53</v>
+      </c>
+      <c r="AT216">
+        <v>3.02</v>
+      </c>
+      <c r="AU216">
+        <v>6</v>
+      </c>
+      <c r="AV216">
+        <v>3</v>
+      </c>
+      <c r="AW216">
+        <v>7</v>
+      </c>
+      <c r="AX216">
+        <v>6</v>
+      </c>
+      <c r="AY216">
+        <v>16</v>
+      </c>
+      <c r="AZ216">
+        <v>10</v>
+      </c>
+      <c r="BA216">
+        <v>7</v>
+      </c>
+      <c r="BB216">
+        <v>6</v>
+      </c>
+      <c r="BC216">
+        <v>13</v>
+      </c>
+      <c r="BD216">
+        <v>1.93</v>
+      </c>
+      <c r="BE216">
+        <v>6.75</v>
+      </c>
+      <c r="BF216">
+        <v>2.02</v>
+      </c>
+      <c r="BG216">
+        <v>1.15</v>
+      </c>
+      <c r="BH216">
+        <v>4.6</v>
+      </c>
+      <c r="BI216">
+        <v>1.27</v>
+      </c>
+      <c r="BJ216">
+        <v>3.3</v>
+      </c>
+      <c r="BK216">
+        <v>1.44</v>
+      </c>
+      <c r="BL216">
+        <v>2.55</v>
+      </c>
+      <c r="BM216">
+        <v>1.72</v>
+      </c>
+      <c r="BN216">
+        <v>1.98</v>
+      </c>
+      <c r="BO216">
+        <v>2.07</v>
+      </c>
+      <c r="BP216">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7491699</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45718.39583333334</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>85</v>
+      </c>
+      <c r="H217" t="s">
+        <v>84</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>176</v>
+      </c>
+      <c r="P217" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q217">
+        <v>3.1</v>
+      </c>
+      <c r="R217">
+        <v>2.3</v>
+      </c>
+      <c r="S217">
+        <v>3.1</v>
+      </c>
+      <c r="T217">
+        <v>1.3</v>
+      </c>
+      <c r="U217">
+        <v>3.4</v>
+      </c>
+      <c r="V217">
+        <v>2.5</v>
+      </c>
+      <c r="W217">
+        <v>1.5</v>
+      </c>
+      <c r="X217">
+        <v>6</v>
+      </c>
+      <c r="Y217">
+        <v>1.13</v>
+      </c>
+      <c r="Z217">
+        <v>2.54</v>
+      </c>
+      <c r="AA217">
+        <v>3.59</v>
+      </c>
+      <c r="AB217">
+        <v>2.76</v>
+      </c>
+      <c r="AC217">
+        <v>1.04</v>
+      </c>
+      <c r="AD217">
+        <v>10</v>
+      </c>
+      <c r="AE217">
+        <v>1.19</v>
+      </c>
+      <c r="AF217">
+        <v>4.3</v>
+      </c>
+      <c r="AG217">
+        <v>1.6</v>
+      </c>
+      <c r="AH217">
+        <v>2.1</v>
+      </c>
+      <c r="AI217">
+        <v>1.53</v>
+      </c>
+      <c r="AJ217">
+        <v>2.38</v>
+      </c>
+      <c r="AK217">
+        <v>1.47</v>
+      </c>
+      <c r="AL217">
+        <v>1.29</v>
+      </c>
+      <c r="AM217">
+        <v>1.5</v>
+      </c>
+      <c r="AN217">
+        <v>1.55</v>
+      </c>
+      <c r="AO217">
+        <v>1.64</v>
+      </c>
+      <c r="AP217">
+        <v>1.67</v>
+      </c>
+      <c r="AQ217">
+        <v>1.5</v>
+      </c>
+      <c r="AR217">
+        <v>1.68</v>
+      </c>
+      <c r="AS217">
+        <v>1.5</v>
+      </c>
+      <c r="AT217">
+        <v>3.18</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>6</v>
+      </c>
+      <c r="AW217">
+        <v>11</v>
+      </c>
+      <c r="AX217">
+        <v>10</v>
+      </c>
+      <c r="AY217">
+        <v>19</v>
+      </c>
+      <c r="AZ217">
+        <v>20</v>
+      </c>
+      <c r="BA217">
+        <v>9</v>
+      </c>
+      <c r="BB217">
+        <v>3</v>
+      </c>
+      <c r="BC217">
+        <v>12</v>
+      </c>
+      <c r="BD217">
+        <v>1.92</v>
+      </c>
+      <c r="BE217">
+        <v>6.75</v>
+      </c>
+      <c r="BF217">
+        <v>2.05</v>
+      </c>
+      <c r="BG217">
+        <v>1.17</v>
+      </c>
+      <c r="BH217">
+        <v>4.35</v>
+      </c>
+      <c r="BI217">
+        <v>1.3</v>
+      </c>
+      <c r="BJ217">
+        <v>3.05</v>
+      </c>
+      <c r="BK217">
+        <v>1.52</v>
+      </c>
+      <c r="BL217">
+        <v>2.33</v>
+      </c>
+      <c r="BM217">
+        <v>1.81</v>
+      </c>
+      <c r="BN217">
+        <v>1.88</v>
+      </c>
+      <c r="BO217">
+        <v>2.23</v>
+      </c>
+      <c r="BP217">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="362">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,18 @@
     <t>['11', '29', '37', '45+3']</t>
   </si>
   <si>
+    <t>['10', '73', '79']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['7', '39', '66', '90+4']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -746,9 +758,6 @@
   </si>
   <si>
     <t>['55', '86']</t>
-  </si>
-  <si>
-    <t>['41']</t>
   </si>
   <si>
     <t>['77', '83']</t>
@@ -1027,9 +1036,6 @@
     <t>['47', '81', '90+3']</t>
   </si>
   <si>
-    <t>['17']</t>
-  </si>
-  <si>
     <t>['23', '61', '84']</t>
   </si>
   <si>
@@ -1088,6 +1094,12 @@
   </si>
   <si>
     <t>['29']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['26', '55']</t>
   </si>
 </sst>
 </file>
@@ -1449,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1705,7 +1717,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1911,7 +1923,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2323,7 +2335,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2401,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ5">
         <v>1.75</v>
@@ -2610,7 +2622,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ6">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2735,7 +2747,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2941,7 +2953,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3019,10 +3031,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3147,7 +3159,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3225,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
         <v>0.83</v>
@@ -3353,7 +3365,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3431,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ10">
         <v>1.67</v>
@@ -3765,7 +3777,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3843,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ12">
         <v>1.25</v>
@@ -4052,7 +4064,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ13">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4177,7 +4189,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4258,7 +4270,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ14">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4464,7 +4476,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4667,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
         <v>1.38</v>
@@ -4795,7 +4807,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5001,7 +5013,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5082,7 +5094,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5413,7 +5425,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5494,7 +5506,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR20">
         <v>1.6</v>
@@ -6109,7 +6121,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23">
         <v>1.75</v>
@@ -6315,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ24">
         <v>0.08</v>
@@ -6649,7 +6661,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6727,10 +6739,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR26">
         <v>1.22</v>
@@ -6855,7 +6867,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6933,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7061,7 +7073,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7142,7 +7154,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR28">
         <v>1.96</v>
@@ -7473,7 +7485,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7679,7 +7691,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7757,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ31">
         <v>0.83</v>
@@ -8091,7 +8103,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8172,7 +8184,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ33">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR33">
         <v>1.09</v>
@@ -8297,7 +8309,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8375,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ34">
         <v>1.38</v>
@@ -8709,7 +8721,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8790,7 +8802,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8915,7 +8927,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8996,7 +9008,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR37">
         <v>2.14</v>
@@ -9121,7 +9133,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9408,7 +9420,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR39">
         <v>1.65</v>
@@ -9533,7 +9545,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9739,7 +9751,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9817,7 +9829,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10023,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ42">
         <v>0.5</v>
@@ -10151,7 +10163,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10232,7 +10244,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR43">
         <v>2.41</v>
@@ -10435,10 +10447,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
+        <v>1.38</v>
+      </c>
+      <c r="AQ44">
         <v>1.42</v>
-      </c>
-      <c r="AQ44">
-        <v>1.45</v>
       </c>
       <c r="AR44">
         <v>1.68</v>
@@ -10563,7 +10575,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10641,10 +10653,10 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR45">
         <v>1.24</v>
@@ -10847,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
         <v>0.08</v>
@@ -10975,7 +10987,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11181,7 +11193,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11387,7 +11399,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11468,7 +11480,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ49">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11593,7 +11605,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12005,7 +12017,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12083,7 +12095,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ52">
         <v>1.5</v>
@@ -12211,7 +12223,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12417,7 +12429,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12498,7 +12510,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR54">
         <v>1.87</v>
@@ -12623,7 +12635,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12829,7 +12841,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12907,7 +12919,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ56">
         <v>0.5</v>
@@ -13035,7 +13047,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13113,10 +13125,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13241,7 +13253,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13319,7 +13331,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ58">
         <v>1.75</v>
@@ -13653,7 +13665,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13731,10 +13743,10 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ60">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13859,7 +13871,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13940,7 +13952,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ61">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR61">
         <v>1.4</v>
@@ -14271,7 +14283,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14349,10 +14361,10 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ63">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR63">
         <v>1.36</v>
@@ -14477,7 +14489,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14558,7 +14570,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR64">
         <v>2.51</v>
@@ -14889,7 +14901,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15507,7 +15519,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15713,7 +15725,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15919,7 +15931,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16331,7 +16343,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16615,10 +16627,10 @@
         <v>1.67</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16821,7 +16833,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -16949,7 +16961,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17030,7 +17042,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -17155,7 +17167,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17236,7 +17248,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR77">
         <v>1.26</v>
@@ -17442,7 +17454,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ78">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17645,7 +17657,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ79">
         <v>1.75</v>
@@ -17851,10 +17863,10 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR80">
         <v>1.52</v>
@@ -17979,7 +17991,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18057,7 +18069,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18263,10 +18275,10 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ82">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR82">
         <v>1.62</v>
@@ -18391,7 +18403,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18597,7 +18609,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18803,7 +18815,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -19009,7 +19021,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19215,7 +19227,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19421,7 +19433,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19627,7 +19639,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19705,7 +19717,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ89">
         <v>0.6899999999999999</v>
@@ -19833,7 +19845,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20326,7 +20338,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR92">
         <v>1.28</v>
@@ -20529,10 +20541,10 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ93">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR93">
         <v>1.52</v>
@@ -20738,7 +20750,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ94">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR94">
         <v>1.29</v>
@@ -20863,7 +20875,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20941,7 +20953,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -21150,7 +21162,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ96">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR96">
         <v>1.59</v>
@@ -21275,7 +21287,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21353,10 +21365,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ97">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21481,7 +21493,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21559,10 +21571,10 @@
         <v>2.4</v>
       </c>
       <c r="AP98">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ98">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR98">
         <v>1.68</v>
@@ -21971,7 +21983,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -22099,7 +22111,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22717,7 +22729,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22795,7 +22807,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ104">
         <v>1.38</v>
@@ -23129,7 +23141,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23335,7 +23347,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23747,7 +23759,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23953,7 +23965,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24240,7 +24252,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR111">
         <v>1.23</v>
@@ -24365,7 +24377,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24443,10 +24455,10 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ112">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24571,7 +24583,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24649,7 +24661,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ113">
         <v>0.6899999999999999</v>
@@ -24777,7 +24789,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24858,7 +24870,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ114">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR114">
         <v>1.54</v>
@@ -24983,7 +24995,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25189,7 +25201,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25267,10 +25279,10 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ116">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25395,7 +25407,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25473,7 +25485,7 @@
         <v>0.33</v>
       </c>
       <c r="AP117">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ117">
         <v>0.5</v>
@@ -25601,7 +25613,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25682,7 +25694,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ118">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR118">
         <v>1.21</v>
@@ -25807,7 +25819,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -26013,7 +26025,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26219,7 +26231,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26425,7 +26437,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26915,7 +26927,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ124">
         <v>0.83</v>
@@ -27043,7 +27055,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27249,7 +27261,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27330,7 +27342,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ126">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27533,7 +27545,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ127">
         <v>1.25</v>
@@ -27867,7 +27879,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27948,7 +27960,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ129">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR129">
         <v>1.5</v>
@@ -28073,7 +28085,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28151,10 +28163,10 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ130">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR130">
         <v>1.78</v>
@@ -28357,7 +28369,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28485,7 +28497,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28691,7 +28703,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28772,7 +28784,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR133">
         <v>1.17</v>
@@ -28897,7 +28909,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28975,7 +28987,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29309,7 +29321,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29390,7 +29402,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ136">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29515,7 +29527,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29721,7 +29733,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29799,7 +29811,7 @@
         <v>0.86</v>
       </c>
       <c r="AP138">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ138">
         <v>0.83</v>
@@ -30008,7 +30020,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ139">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR139">
         <v>1.49</v>
@@ -30133,7 +30145,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30417,7 +30429,7 @@
         <v>1.43</v>
       </c>
       <c r="AP141">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ141">
         <v>1.5</v>
@@ -30545,7 +30557,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30623,7 +30635,7 @@
         <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ142">
         <v>1.67</v>
@@ -31035,7 +31047,7 @@
         <v>0.71</v>
       </c>
       <c r="AP144">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ144">
         <v>1.08</v>
@@ -31163,7 +31175,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31244,7 +31256,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ145">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR145">
         <v>1.36</v>
@@ -31369,7 +31381,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31450,7 +31462,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ146">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR146">
         <v>1.51</v>
@@ -31575,7 +31587,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31656,7 +31668,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ147">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -31859,7 +31871,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ148">
         <v>1.25</v>
@@ -32193,7 +32205,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32274,7 +32286,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ150">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32605,7 +32617,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33017,7 +33029,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33095,10 +33107,10 @@
         <v>2</v>
       </c>
       <c r="AP154">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ154">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR154">
         <v>1.69</v>
@@ -33223,7 +33235,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33713,7 +33725,7 @@
         <v>0.89</v>
       </c>
       <c r="AP157">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ157">
         <v>0.6899999999999999</v>
@@ -33922,7 +33934,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ158">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR158">
         <v>1.3</v>
@@ -34331,10 +34343,10 @@
         <v>2.13</v>
       </c>
       <c r="AP160">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ160">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR160">
         <v>1.75</v>
@@ -34459,7 +34471,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34665,7 +34677,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34746,7 +34758,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ162">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR162">
         <v>1.5</v>
@@ -34871,7 +34883,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34952,7 +34964,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ163">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35077,7 +35089,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35283,7 +35295,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35361,7 +35373,7 @@
         <v>1.56</v>
       </c>
       <c r="AP165">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ165">
         <v>1.67</v>
@@ -35570,7 +35582,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ166">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR166">
         <v>1.82</v>
@@ -35695,7 +35707,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35776,7 +35788,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ167">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR167">
         <v>1.61</v>
@@ -35901,7 +35913,7 @@
         <v>204</v>
       </c>
       <c r="P168" t="s">
-        <v>337</v>
+        <v>241</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -36107,7 +36119,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36185,7 +36197,7 @@
         <v>1.38</v>
       </c>
       <c r="AP169">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ169">
         <v>1.5</v>
@@ -36313,7 +36325,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36391,7 +36403,7 @@
         <v>0.13</v>
       </c>
       <c r="AP170">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ170">
         <v>0.08</v>
@@ -36597,7 +36609,7 @@
         <v>1.56</v>
       </c>
       <c r="AP171">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ171">
         <v>1.75</v>
@@ -36725,7 +36737,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37137,7 +37149,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37218,7 +37230,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ174">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR174">
         <v>1.47</v>
@@ -37549,7 +37561,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37630,7 +37642,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ176">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37755,7 +37767,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37961,7 +37973,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38042,7 +38054,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ178">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR178">
         <v>1.59</v>
@@ -38167,7 +38179,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38373,7 +38385,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38451,7 +38463,7 @@
         <v>1.11</v>
       </c>
       <c r="AP180">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ180">
         <v>0.83</v>
@@ -38579,7 +38591,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38657,7 +38669,7 @@
         <v>0.89</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ181">
         <v>1.08</v>
@@ -38785,7 +38797,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39069,7 +39081,7 @@
         <v>0.11</v>
       </c>
       <c r="AP183">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ183">
         <v>0.08</v>
@@ -39197,7 +39209,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39275,10 +39287,10 @@
         <v>1.33</v>
       </c>
       <c r="AP184">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ184">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR184">
         <v>1.56</v>
@@ -39403,7 +39415,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39609,7 +39621,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39687,7 +39699,7 @@
         <v>1.7</v>
       </c>
       <c r="AP186">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ186">
         <v>1.75</v>
@@ -39893,7 +39905,7 @@
         <v>1.7</v>
       </c>
       <c r="AP187">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ187">
         <v>1.67</v>
@@ -40102,7 +40114,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ188">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR188">
         <v>1.83</v>
@@ -40227,7 +40239,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40514,7 +40526,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ190">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR190">
         <v>1.76</v>
@@ -40720,7 +40732,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ191">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR191">
         <v>1.77</v>
@@ -41335,7 +41347,7 @@
         <v>0.9</v>
       </c>
       <c r="AP194">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ194">
         <v>1.08</v>
@@ -41669,7 +41681,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42162,7 +42174,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ198">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR198">
         <v>1.64</v>
@@ -42571,7 +42583,7 @@
         <v>1.82</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ200">
         <v>1.67</v>
@@ -42777,7 +42789,7 @@
         <v>1</v>
       </c>
       <c r="AP201">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ201">
         <v>1</v>
@@ -42905,7 +42917,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -42986,7 +42998,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ202">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AR202">
         <v>1.71</v>
@@ -43189,10 +43201,10 @@
         <v>1.5</v>
       </c>
       <c r="AP203">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ203">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR203">
         <v>1.48</v>
@@ -43523,7 +43535,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43810,7 +43822,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ206">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR206">
         <v>1.8</v>
@@ -44013,10 +44025,10 @@
         <v>1.18</v>
       </c>
       <c r="AP207">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ207">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR207">
         <v>1.55</v>
@@ -44219,7 +44231,7 @@
         <v>0.55</v>
       </c>
       <c r="AP208">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ208">
         <v>0.5</v>
@@ -44347,7 +44359,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -45043,7 +45055,7 @@
         <v>0.09</v>
       </c>
       <c r="AP212">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ212">
         <v>0.08</v>
@@ -45171,7 +45183,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45458,7 +45470,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR214">
         <v>1.66</v>
@@ -45583,7 +45595,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -46152,6 +46164,1242 @@
       </c>
       <c r="BP217">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7491706</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45723.60416666666</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>76</v>
+      </c>
+      <c r="H218" t="s">
+        <v>71</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>3</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>3</v>
+      </c>
+      <c r="O218" t="s">
+        <v>239</v>
+      </c>
+      <c r="P218" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q218">
+        <v>2.38</v>
+      </c>
+      <c r="R218">
+        <v>2.2</v>
+      </c>
+      <c r="S218">
+        <v>4</v>
+      </c>
+      <c r="T218">
+        <v>1.33</v>
+      </c>
+      <c r="U218">
+        <v>3.1</v>
+      </c>
+      <c r="V218">
+        <v>2.4</v>
+      </c>
+      <c r="W218">
+        <v>1.5</v>
+      </c>
+      <c r="X218">
+        <v>6.1</v>
+      </c>
+      <c r="Y218">
+        <v>1.06</v>
+      </c>
+      <c r="Z218">
+        <v>2.04</v>
+      </c>
+      <c r="AA218">
+        <v>3.87</v>
+      </c>
+      <c r="AB218">
+        <v>3.5</v>
+      </c>
+      <c r="AC218">
+        <v>1.04</v>
+      </c>
+      <c r="AD218">
+        <v>10</v>
+      </c>
+      <c r="AE218">
+        <v>1.22</v>
+      </c>
+      <c r="AF218">
+        <v>4.2</v>
+      </c>
+      <c r="AG218">
+        <v>1.55</v>
+      </c>
+      <c r="AH218">
+        <v>2.2</v>
+      </c>
+      <c r="AI218">
+        <v>1.55</v>
+      </c>
+      <c r="AJ218">
+        <v>2.25</v>
+      </c>
+      <c r="AK218">
+        <v>1.25</v>
+      </c>
+      <c r="AL218">
+        <v>1.22</v>
+      </c>
+      <c r="AM218">
+        <v>1.85</v>
+      </c>
+      <c r="AN218">
+        <v>1.33</v>
+      </c>
+      <c r="AO218">
+        <v>1.33</v>
+      </c>
+      <c r="AP218">
+        <v>1.46</v>
+      </c>
+      <c r="AQ218">
+        <v>1.23</v>
+      </c>
+      <c r="AR218">
+        <v>1.53</v>
+      </c>
+      <c r="AS218">
+        <v>1.25</v>
+      </c>
+      <c r="AT218">
+        <v>2.78</v>
+      </c>
+      <c r="AU218">
+        <v>13</v>
+      </c>
+      <c r="AV218">
+        <v>4</v>
+      </c>
+      <c r="AW218">
+        <v>11</v>
+      </c>
+      <c r="AX218">
+        <v>5</v>
+      </c>
+      <c r="AY218">
+        <v>30</v>
+      </c>
+      <c r="AZ218">
+        <v>10</v>
+      </c>
+      <c r="BA218">
+        <v>2</v>
+      </c>
+      <c r="BB218">
+        <v>3</v>
+      </c>
+      <c r="BC218">
+        <v>5</v>
+      </c>
+      <c r="BD218">
+        <v>1.67</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2.48</v>
+      </c>
+      <c r="BG218">
+        <v>1.35</v>
+      </c>
+      <c r="BH218">
+        <v>2.9</v>
+      </c>
+      <c r="BI218">
+        <v>1.58</v>
+      </c>
+      <c r="BJ218">
+        <v>2.18</v>
+      </c>
+      <c r="BK218">
+        <v>1.96</v>
+      </c>
+      <c r="BL218">
+        <v>1.74</v>
+      </c>
+      <c r="BM218">
+        <v>2.48</v>
+      </c>
+      <c r="BN218">
+        <v>1.47</v>
+      </c>
+      <c r="BO218">
+        <v>3.2</v>
+      </c>
+      <c r="BP218">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7491711</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45723.60416666666</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>80</v>
+      </c>
+      <c r="H219" t="s">
+        <v>82</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>2</v>
+      </c>
+      <c r="O219" t="s">
+        <v>240</v>
+      </c>
+      <c r="P219" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q219">
+        <v>2.85</v>
+      </c>
+      <c r="R219">
+        <v>2.25</v>
+      </c>
+      <c r="S219">
+        <v>3.1</v>
+      </c>
+      <c r="T219">
+        <v>1.28</v>
+      </c>
+      <c r="U219">
+        <v>3.3</v>
+      </c>
+      <c r="V219">
+        <v>2.25</v>
+      </c>
+      <c r="W219">
+        <v>1.55</v>
+      </c>
+      <c r="X219">
+        <v>5.25</v>
+      </c>
+      <c r="Y219">
+        <v>1.14</v>
+      </c>
+      <c r="Z219">
+        <v>2.1</v>
+      </c>
+      <c r="AA219">
+        <v>3.81</v>
+      </c>
+      <c r="AB219">
+        <v>3.37</v>
+      </c>
+      <c r="AC219">
+        <v>1.04</v>
+      </c>
+      <c r="AD219">
+        <v>10</v>
+      </c>
+      <c r="AE219">
+        <v>1.2</v>
+      </c>
+      <c r="AF219">
+        <v>4.33</v>
+      </c>
+      <c r="AG219">
+        <v>1.55</v>
+      </c>
+      <c r="AH219">
+        <v>2.2</v>
+      </c>
+      <c r="AI219">
+        <v>1.5</v>
+      </c>
+      <c r="AJ219">
+        <v>2.37</v>
+      </c>
+      <c r="AK219">
+        <v>1.44</v>
+      </c>
+      <c r="AL219">
+        <v>1.28</v>
+      </c>
+      <c r="AM219">
+        <v>1.53</v>
+      </c>
+      <c r="AN219">
+        <v>1.83</v>
+      </c>
+      <c r="AO219">
+        <v>1.45</v>
+      </c>
+      <c r="AP219">
+        <v>1.77</v>
+      </c>
+      <c r="AQ219">
+        <v>1.42</v>
+      </c>
+      <c r="AR219">
+        <v>1.83</v>
+      </c>
+      <c r="AS219">
+        <v>1.4</v>
+      </c>
+      <c r="AT219">
+        <v>3.23</v>
+      </c>
+      <c r="AU219">
+        <v>2</v>
+      </c>
+      <c r="AV219">
+        <v>3</v>
+      </c>
+      <c r="AW219">
+        <v>5</v>
+      </c>
+      <c r="AX219">
+        <v>2</v>
+      </c>
+      <c r="AY219">
+        <v>10</v>
+      </c>
+      <c r="AZ219">
+        <v>8</v>
+      </c>
+      <c r="BA219">
+        <v>7</v>
+      </c>
+      <c r="BB219">
+        <v>3</v>
+      </c>
+      <c r="BC219">
+        <v>10</v>
+      </c>
+      <c r="BD219">
+        <v>1.95</v>
+      </c>
+      <c r="BE219">
+        <v>6.4</v>
+      </c>
+      <c r="BF219">
+        <v>2.05</v>
+      </c>
+      <c r="BG219">
+        <v>1.3</v>
+      </c>
+      <c r="BH219">
+        <v>3.05</v>
+      </c>
+      <c r="BI219">
+        <v>1.53</v>
+      </c>
+      <c r="BJ219">
+        <v>2.32</v>
+      </c>
+      <c r="BK219">
+        <v>1.86</v>
+      </c>
+      <c r="BL219">
+        <v>1.82</v>
+      </c>
+      <c r="BM219">
+        <v>2.33</v>
+      </c>
+      <c r="BN219">
+        <v>1.5</v>
+      </c>
+      <c r="BO219">
+        <v>3.05</v>
+      </c>
+      <c r="BP219">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7491709</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45724.375</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>77</v>
+      </c>
+      <c r="H220" t="s">
+        <v>74</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>2</v>
+      </c>
+      <c r="O220" t="s">
+        <v>241</v>
+      </c>
+      <c r="P220" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q220">
+        <v>3.2</v>
+      </c>
+      <c r="R220">
+        <v>2.3</v>
+      </c>
+      <c r="S220">
+        <v>2.65</v>
+      </c>
+      <c r="T220">
+        <v>1.27</v>
+      </c>
+      <c r="U220">
+        <v>3.4</v>
+      </c>
+      <c r="V220">
+        <v>2.25</v>
+      </c>
+      <c r="W220">
+        <v>1.57</v>
+      </c>
+      <c r="X220">
+        <v>5</v>
+      </c>
+      <c r="Y220">
+        <v>1.14</v>
+      </c>
+      <c r="Z220">
+        <v>2.86</v>
+      </c>
+      <c r="AA220">
+        <v>3.76</v>
+      </c>
+      <c r="AB220">
+        <v>2.39</v>
+      </c>
+      <c r="AC220">
+        <v>1.04</v>
+      </c>
+      <c r="AD220">
+        <v>10</v>
+      </c>
+      <c r="AE220">
+        <v>1.18</v>
+      </c>
+      <c r="AF220">
+        <v>4.75</v>
+      </c>
+      <c r="AG220">
+        <v>1.55</v>
+      </c>
+      <c r="AH220">
+        <v>2.2</v>
+      </c>
+      <c r="AI220">
+        <v>1.49</v>
+      </c>
+      <c r="AJ220">
+        <v>2.4</v>
+      </c>
+      <c r="AK220">
+        <v>1.62</v>
+      </c>
+      <c r="AL220">
+        <v>1.26</v>
+      </c>
+      <c r="AM220">
+        <v>1.4</v>
+      </c>
+      <c r="AN220">
+        <v>1.42</v>
+      </c>
+      <c r="AO220">
+        <v>2.33</v>
+      </c>
+      <c r="AP220">
+        <v>1.38</v>
+      </c>
+      <c r="AQ220">
+        <v>2.23</v>
+      </c>
+      <c r="AR220">
+        <v>1.53</v>
+      </c>
+      <c r="AS220">
+        <v>1.52</v>
+      </c>
+      <c r="AT220">
+        <v>3.05</v>
+      </c>
+      <c r="AU220">
+        <v>3</v>
+      </c>
+      <c r="AV220">
+        <v>4</v>
+      </c>
+      <c r="AW220">
+        <v>7</v>
+      </c>
+      <c r="AX220">
+        <v>9</v>
+      </c>
+      <c r="AY220">
+        <v>10</v>
+      </c>
+      <c r="AZ220">
+        <v>14</v>
+      </c>
+      <c r="BA220">
+        <v>1</v>
+      </c>
+      <c r="BB220">
+        <v>9</v>
+      </c>
+      <c r="BC220">
+        <v>10</v>
+      </c>
+      <c r="BD220">
+        <v>0</v>
+      </c>
+      <c r="BE220">
+        <v>0</v>
+      </c>
+      <c r="BF220">
+        <v>0</v>
+      </c>
+      <c r="BG220">
+        <v>0</v>
+      </c>
+      <c r="BH220">
+        <v>0</v>
+      </c>
+      <c r="BI220">
+        <v>0</v>
+      </c>
+      <c r="BJ220">
+        <v>0</v>
+      </c>
+      <c r="BK220">
+        <v>0</v>
+      </c>
+      <c r="BL220">
+        <v>0</v>
+      </c>
+      <c r="BM220">
+        <v>0</v>
+      </c>
+      <c r="BN220">
+        <v>0</v>
+      </c>
+      <c r="BO220">
+        <v>0</v>
+      </c>
+      <c r="BP220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7491710</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45724.375</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>73</v>
+      </c>
+      <c r="H221" t="s">
+        <v>75</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>1</v>
+      </c>
+      <c r="M221">
+        <v>2</v>
+      </c>
+      <c r="N221">
+        <v>3</v>
+      </c>
+      <c r="O221" t="s">
+        <v>119</v>
+      </c>
+      <c r="P221" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q221">
+        <v>2.5</v>
+      </c>
+      <c r="R221">
+        <v>2.25</v>
+      </c>
+      <c r="S221">
+        <v>3.6</v>
+      </c>
+      <c r="T221">
+        <v>1.3</v>
+      </c>
+      <c r="U221">
+        <v>3.25</v>
+      </c>
+      <c r="V221">
+        <v>2.3</v>
+      </c>
+      <c r="W221">
+        <v>1.53</v>
+      </c>
+      <c r="X221">
+        <v>5.25</v>
+      </c>
+      <c r="Y221">
+        <v>1.13</v>
+      </c>
+      <c r="Z221">
+        <v>2</v>
+      </c>
+      <c r="AA221">
+        <v>3.87</v>
+      </c>
+      <c r="AB221">
+        <v>3.62</v>
+      </c>
+      <c r="AC221">
+        <v>1.04</v>
+      </c>
+      <c r="AD221">
+        <v>10</v>
+      </c>
+      <c r="AE221">
+        <v>1.2</v>
+      </c>
+      <c r="AF221">
+        <v>4.33</v>
+      </c>
+      <c r="AG221">
+        <v>1.55</v>
+      </c>
+      <c r="AH221">
+        <v>2.2</v>
+      </c>
+      <c r="AI221">
+        <v>1.53</v>
+      </c>
+      <c r="AJ221">
+        <v>2.3</v>
+      </c>
+      <c r="AK221">
+        <v>1.31</v>
+      </c>
+      <c r="AL221">
+        <v>1.27</v>
+      </c>
+      <c r="AM221">
+        <v>1.73</v>
+      </c>
+      <c r="AN221">
+        <v>0.73</v>
+      </c>
+      <c r="AO221">
+        <v>1.08</v>
+      </c>
+      <c r="AP221">
+        <v>0.67</v>
+      </c>
+      <c r="AQ221">
+        <v>1.23</v>
+      </c>
+      <c r="AR221">
+        <v>1.51</v>
+      </c>
+      <c r="AS221">
+        <v>1.36</v>
+      </c>
+      <c r="AT221">
+        <v>2.87</v>
+      </c>
+      <c r="AU221">
+        <v>6</v>
+      </c>
+      <c r="AV221">
+        <v>5</v>
+      </c>
+      <c r="AW221">
+        <v>9</v>
+      </c>
+      <c r="AX221">
+        <v>4</v>
+      </c>
+      <c r="AY221">
+        <v>18</v>
+      </c>
+      <c r="AZ221">
+        <v>12</v>
+      </c>
+      <c r="BA221">
+        <v>3</v>
+      </c>
+      <c r="BB221">
+        <v>5</v>
+      </c>
+      <c r="BC221">
+        <v>8</v>
+      </c>
+      <c r="BD221">
+        <v>0</v>
+      </c>
+      <c r="BE221">
+        <v>0</v>
+      </c>
+      <c r="BF221">
+        <v>0</v>
+      </c>
+      <c r="BG221">
+        <v>0</v>
+      </c>
+      <c r="BH221">
+        <v>0</v>
+      </c>
+      <c r="BI221">
+        <v>0</v>
+      </c>
+      <c r="BJ221">
+        <v>0</v>
+      </c>
+      <c r="BK221">
+        <v>0</v>
+      </c>
+      <c r="BL221">
+        <v>0</v>
+      </c>
+      <c r="BM221">
+        <v>0</v>
+      </c>
+      <c r="BN221">
+        <v>0</v>
+      </c>
+      <c r="BO221">
+        <v>0</v>
+      </c>
+      <c r="BP221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7491712</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45724.375</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>78</v>
+      </c>
+      <c r="H222" t="s">
+        <v>70</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>92</v>
+      </c>
+      <c r="P222" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q222">
+        <v>4</v>
+      </c>
+      <c r="R222">
+        <v>2.05</v>
+      </c>
+      <c r="S222">
+        <v>2.55</v>
+      </c>
+      <c r="T222">
+        <v>1.4</v>
+      </c>
+      <c r="U222">
+        <v>2.7</v>
+      </c>
+      <c r="V222">
+        <v>2.85</v>
+      </c>
+      <c r="W222">
+        <v>1.37</v>
+      </c>
+      <c r="X222">
+        <v>7.5</v>
+      </c>
+      <c r="Y222">
+        <v>1.08</v>
+      </c>
+      <c r="Z222">
+        <v>3.97</v>
+      </c>
+      <c r="AA222">
+        <v>3.45</v>
+      </c>
+      <c r="AB222">
+        <v>2.02</v>
+      </c>
+      <c r="AC222">
+        <v>1.07</v>
+      </c>
+      <c r="AD222">
+        <v>8</v>
+      </c>
+      <c r="AE222">
+        <v>1.36</v>
+      </c>
+      <c r="AF222">
+        <v>3.1</v>
+      </c>
+      <c r="AG222">
+        <v>2.01</v>
+      </c>
+      <c r="AH222">
+        <v>1.81</v>
+      </c>
+      <c r="AI222">
+        <v>1.85</v>
+      </c>
+      <c r="AJ222">
+        <v>1.83</v>
+      </c>
+      <c r="AK222">
+        <v>1.78</v>
+      </c>
+      <c r="AL222">
+        <v>1.3</v>
+      </c>
+      <c r="AM222">
+        <v>1.26</v>
+      </c>
+      <c r="AN222">
+        <v>0.91</v>
+      </c>
+      <c r="AO222">
+        <v>1.67</v>
+      </c>
+      <c r="AP222">
+        <v>0.83</v>
+      </c>
+      <c r="AQ222">
+        <v>1.77</v>
+      </c>
+      <c r="AR222">
+        <v>1.49</v>
+      </c>
+      <c r="AS222">
+        <v>1.55</v>
+      </c>
+      <c r="AT222">
+        <v>3.04</v>
+      </c>
+      <c r="AU222">
+        <v>2</v>
+      </c>
+      <c r="AV222">
+        <v>3</v>
+      </c>
+      <c r="AW222">
+        <v>12</v>
+      </c>
+      <c r="AX222">
+        <v>9</v>
+      </c>
+      <c r="AY222">
+        <v>17</v>
+      </c>
+      <c r="AZ222">
+        <v>14</v>
+      </c>
+      <c r="BA222">
+        <v>3</v>
+      </c>
+      <c r="BB222">
+        <v>7</v>
+      </c>
+      <c r="BC222">
+        <v>10</v>
+      </c>
+      <c r="BD222">
+        <v>0</v>
+      </c>
+      <c r="BE222">
+        <v>0</v>
+      </c>
+      <c r="BF222">
+        <v>0</v>
+      </c>
+      <c r="BG222">
+        <v>0</v>
+      </c>
+      <c r="BH222">
+        <v>0</v>
+      </c>
+      <c r="BI222">
+        <v>0</v>
+      </c>
+      <c r="BJ222">
+        <v>0</v>
+      </c>
+      <c r="BK222">
+        <v>0</v>
+      </c>
+      <c r="BL222">
+        <v>0</v>
+      </c>
+      <c r="BM222">
+        <v>0</v>
+      </c>
+      <c r="BN222">
+        <v>0</v>
+      </c>
+      <c r="BO222">
+        <v>0</v>
+      </c>
+      <c r="BP222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7491707</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45724.6875</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>84</v>
+      </c>
+      <c r="H223" t="s">
+        <v>83</v>
+      </c>
+      <c r="I223">
+        <v>2</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>3</v>
+      </c>
+      <c r="L223">
+        <v>4</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>5</v>
+      </c>
+      <c r="O223" t="s">
+        <v>242</v>
+      </c>
+      <c r="P223" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q223">
+        <v>2.2</v>
+      </c>
+      <c r="R223">
+        <v>2.37</v>
+      </c>
+      <c r="S223">
+        <v>4.1</v>
+      </c>
+      <c r="T223">
+        <v>1.26</v>
+      </c>
+      <c r="U223">
+        <v>3.5</v>
+      </c>
+      <c r="V223">
+        <v>2.2</v>
+      </c>
+      <c r="W223">
+        <v>1.58</v>
+      </c>
+      <c r="X223">
+        <v>5</v>
+      </c>
+      <c r="Y223">
+        <v>1.15</v>
+      </c>
+      <c r="Z223">
+        <v>1.82</v>
+      </c>
+      <c r="AA223">
+        <v>4.2</v>
+      </c>
+      <c r="AB223">
+        <v>4</v>
+      </c>
+      <c r="AC223">
+        <v>1.01</v>
+      </c>
+      <c r="AD223">
+        <v>13</v>
+      </c>
+      <c r="AE223">
+        <v>1.18</v>
+      </c>
+      <c r="AF223">
+        <v>4.75</v>
+      </c>
+      <c r="AG223">
+        <v>1.51</v>
+      </c>
+      <c r="AH223">
+        <v>2.46</v>
+      </c>
+      <c r="AI223">
+        <v>1.55</v>
+      </c>
+      <c r="AJ223">
+        <v>2.3</v>
+      </c>
+      <c r="AK223">
+        <v>1.22</v>
+      </c>
+      <c r="AL223">
+        <v>1.23</v>
+      </c>
+      <c r="AM223">
+        <v>2.05</v>
+      </c>
+      <c r="AN223">
+        <v>2</v>
+      </c>
+      <c r="AO223">
+        <v>2</v>
+      </c>
+      <c r="AP223">
+        <v>2.08</v>
+      </c>
+      <c r="AQ223">
+        <v>1.83</v>
+      </c>
+      <c r="AR223">
+        <v>1.8</v>
+      </c>
+      <c r="AS223">
+        <v>1.3</v>
+      </c>
+      <c r="AT223">
+        <v>3.1</v>
+      </c>
+      <c r="AU223">
+        <v>10</v>
+      </c>
+      <c r="AV223">
+        <v>2</v>
+      </c>
+      <c r="AW223">
+        <v>11</v>
+      </c>
+      <c r="AX223">
+        <v>9</v>
+      </c>
+      <c r="AY223">
+        <v>25</v>
+      </c>
+      <c r="AZ223">
+        <v>14</v>
+      </c>
+      <c r="BA223">
+        <v>8</v>
+      </c>
+      <c r="BB223">
+        <v>2</v>
+      </c>
+      <c r="BC223">
+        <v>10</v>
+      </c>
+      <c r="BD223">
+        <v>0</v>
+      </c>
+      <c r="BE223">
+        <v>0</v>
+      </c>
+      <c r="BF223">
+        <v>0</v>
+      </c>
+      <c r="BG223">
+        <v>0</v>
+      </c>
+      <c r="BH223">
+        <v>0</v>
+      </c>
+      <c r="BI223">
+        <v>0</v>
+      </c>
+      <c r="BJ223">
+        <v>0</v>
+      </c>
+      <c r="BK223">
+        <v>0</v>
+      </c>
+      <c r="BL223">
+        <v>0</v>
+      </c>
+      <c r="BM223">
+        <v>0</v>
+      </c>
+      <c r="BN223">
+        <v>0</v>
+      </c>
+      <c r="BO223">
+        <v>0</v>
+      </c>
+      <c r="BP223">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="364">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -745,6 +745,9 @@
     <t>['7', '39', '66', '90+4']</t>
   </si>
   <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1015,9 +1018,6 @@
     <t>['16', '34']</t>
   </si>
   <si>
-    <t>['90+3']</t>
-  </si>
-  <si>
     <t>['69', '72']</t>
   </si>
   <si>
@@ -1100,6 +1100,12 @@
   </si>
   <si>
     <t>['26', '55']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['82']</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1717,7 +1723,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1923,7 +1929,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2004,7 +2010,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2207,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.08</v>
@@ -2335,7 +2341,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2416,7 +2422,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ5">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2747,7 +2753,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2828,7 +2834,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2953,7 +2959,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3365,7 +3371,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3649,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ11">
         <v>0.6899999999999999</v>
@@ -3777,7 +3783,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4189,7 +4195,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4807,7 +4813,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5013,7 +5019,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5297,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>1.08</v>
@@ -5425,7 +5431,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5709,7 +5715,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5915,7 +5921,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1.67</v>
@@ -6124,7 +6130,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ23">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR23">
         <v>2.28</v>
@@ -6536,7 +6542,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR25">
         <v>2.21</v>
@@ -6661,7 +6667,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6867,7 +6873,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6948,7 +6954,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR27">
         <v>1.43</v>
@@ -7073,7 +7079,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7485,7 +7491,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7563,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ30">
         <v>1.25</v>
@@ -7691,7 +7697,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8103,7 +8109,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8309,7 +8315,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8721,7 +8727,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8927,7 +8933,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9133,7 +9139,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9211,10 +9217,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR38">
         <v>1.52</v>
@@ -9545,7 +9551,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9623,7 +9629,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>1.67</v>
@@ -9751,7 +9757,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9832,7 +9838,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.64</v>
@@ -10038,7 +10044,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR42">
         <v>1.72</v>
@@ -10163,7 +10169,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10575,7 +10581,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10987,7 +10993,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11193,7 +11199,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11399,7 +11405,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11605,7 +11611,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12017,7 +12023,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12223,7 +12229,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12429,7 +12435,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12635,7 +12641,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12713,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ55">
         <v>0.83</v>
@@ -12841,7 +12847,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12922,7 +12928,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -13047,7 +13053,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13253,7 +13259,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13334,7 +13340,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ58">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13537,7 +13543,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ59">
         <v>1.67</v>
@@ -13665,7 +13671,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13871,7 +13877,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13949,7 +13955,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
         <v>1.23</v>
@@ -14155,10 +14161,10 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR62">
         <v>1.64</v>
@@ -14283,7 +14289,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14489,7 +14495,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14901,7 +14907,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15519,7 +15525,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15725,7 +15731,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15931,7 +15937,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16343,7 +16349,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16836,7 +16842,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16961,7 +16967,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17039,7 +17045,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.42</v>
@@ -17167,7 +17173,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17245,7 +17251,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ77">
         <v>1.83</v>
@@ -17451,7 +17457,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>1.23</v>
@@ -17660,7 +17666,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ79">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR79">
         <v>1.72</v>
@@ -17991,7 +17997,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18072,7 +18078,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR81">
         <v>1.41</v>
@@ -18403,7 +18409,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18484,7 +18490,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ83">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR83">
         <v>2.13</v>
@@ -18609,7 +18615,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18815,7 +18821,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -19021,7 +19027,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19227,7 +19233,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19433,7 +19439,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19639,7 +19645,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19845,7 +19851,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20335,7 +20341,7 @@
         <v>3</v>
       </c>
       <c r="AP92">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ92">
         <v>1.83</v>
@@ -20747,7 +20753,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ94">
         <v>1.42</v>
@@ -20875,7 +20881,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21159,7 +21165,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1.23</v>
@@ -21287,7 +21293,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21493,7 +21499,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21780,7 +21786,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR99">
         <v>1.63</v>
@@ -21986,7 +21992,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR100">
         <v>1.62</v>
@@ -22111,7 +22117,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22729,7 +22735,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23141,7 +23147,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23222,7 +23228,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ106">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR106">
         <v>1.62</v>
@@ -23347,7 +23353,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23759,7 +23765,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23965,7 +23971,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24046,7 +24052,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR110">
         <v>1.5</v>
@@ -24249,7 +24255,7 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
         <v>1.77</v>
@@ -24377,7 +24383,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24583,7 +24589,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24789,7 +24795,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24995,7 +25001,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25073,7 +25079,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25201,7 +25207,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25407,7 +25413,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25488,7 +25494,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR117">
         <v>1.79</v>
@@ -25613,7 +25619,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25691,7 +25697,7 @@
         <v>2.17</v>
       </c>
       <c r="AP118">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ118">
         <v>2.23</v>
@@ -25819,7 +25825,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -26025,7 +26031,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26231,7 +26237,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26437,7 +26443,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26518,7 +26524,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR122">
         <v>1.56</v>
@@ -27055,7 +27061,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27261,7 +27267,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27754,7 +27760,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -27879,7 +27885,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28085,7 +28091,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28497,7 +28503,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28575,7 +28581,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
         <v>0.6899999999999999</v>
@@ -28703,7 +28709,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28781,7 +28787,7 @@
         <v>2.29</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ133">
         <v>2.23</v>
@@ -28909,7 +28915,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29196,7 +29202,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ135">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR135">
         <v>1.54</v>
@@ -29321,7 +29327,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29399,7 +29405,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ136">
         <v>1.77</v>
@@ -29527,7 +29533,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29733,7 +29739,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30145,7 +30151,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30226,7 +30232,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ140">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR140">
         <v>1.64</v>
@@ -30557,7 +30563,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30844,7 +30850,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR143">
         <v>1.88</v>
@@ -31175,7 +31181,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31381,7 +31387,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31587,7 +31593,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32077,7 +32083,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
         <v>0.6899999999999999</v>
@@ -32205,7 +32211,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32492,7 +32498,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ151">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR151">
         <v>1.49</v>
@@ -32617,7 +32623,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32695,7 +32701,7 @@
         <v>1.57</v>
       </c>
       <c r="AP152">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -32901,7 +32907,7 @@
         <v>1.75</v>
       </c>
       <c r="AP153">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
         <v>1.38</v>
@@ -33029,7 +33035,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33519,7 +33525,7 @@
         <v>0.63</v>
       </c>
       <c r="AP156">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ156">
         <v>1.08</v>
@@ -34137,7 +34143,7 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ159">
         <v>1.25</v>
@@ -35089,7 +35095,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35170,7 +35176,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR164">
         <v>1.62</v>
@@ -35994,7 +36000,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36325,7 +36331,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36612,7 +36618,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ171">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -36815,7 +36821,7 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
         <v>0.83</v>
@@ -37433,7 +37439,7 @@
         <v>1.8</v>
       </c>
       <c r="AP175">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ175">
         <v>1.38</v>
@@ -38875,7 +38881,7 @@
         <v>1.56</v>
       </c>
       <c r="AP182">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ182">
         <v>1.5</v>
@@ -39496,7 +39502,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR185">
         <v>1.66</v>
@@ -39702,7 +39708,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ186">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR186">
         <v>1.53</v>
@@ -40320,7 +40326,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ189">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
         <v>1.59</v>
@@ -40523,7 +40529,7 @@
         <v>2.22</v>
       </c>
       <c r="AP190">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
         <v>1.83</v>
@@ -41965,7 +41971,7 @@
         <v>1.7</v>
       </c>
       <c r="AP197">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ197">
         <v>1.5</v>
@@ -42792,7 +42798,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ201">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR201">
         <v>1.48</v>
@@ -43407,7 +43413,7 @@
         <v>0.1</v>
       </c>
       <c r="AP204">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ204">
         <v>0.08</v>
@@ -43613,10 +43619,10 @@
         <v>1.82</v>
       </c>
       <c r="AP205">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR205">
         <v>1.73</v>
@@ -44234,7 +44240,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ208">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -47243,7 +47249,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47400,6 +47406,624 @@
       </c>
       <c r="BP223">
         <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7491708</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45725.39583333334</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>72</v>
+      </c>
+      <c r="H224" t="s">
+        <v>86</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>2</v>
+      </c>
+      <c r="O224" t="s">
+        <v>243</v>
+      </c>
+      <c r="P224" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q224">
+        <v>2.2</v>
+      </c>
+      <c r="R224">
+        <v>2.3</v>
+      </c>
+      <c r="S224">
+        <v>5</v>
+      </c>
+      <c r="T224">
+        <v>1.33</v>
+      </c>
+      <c r="U224">
+        <v>3.25</v>
+      </c>
+      <c r="V224">
+        <v>2.63</v>
+      </c>
+      <c r="W224">
+        <v>1.44</v>
+      </c>
+      <c r="X224">
+        <v>7</v>
+      </c>
+      <c r="Y224">
+        <v>1.1</v>
+      </c>
+      <c r="Z224">
+        <v>1.66</v>
+      </c>
+      <c r="AA224">
+        <v>4.2</v>
+      </c>
+      <c r="AB224">
+        <v>5.1</v>
+      </c>
+      <c r="AC224">
+        <v>1.04</v>
+      </c>
+      <c r="AD224">
+        <v>10</v>
+      </c>
+      <c r="AE224">
+        <v>1.22</v>
+      </c>
+      <c r="AF224">
+        <v>4.2</v>
+      </c>
+      <c r="AG224">
+        <v>1.79</v>
+      </c>
+      <c r="AH224">
+        <v>2.03</v>
+      </c>
+      <c r="AI224">
+        <v>1.8</v>
+      </c>
+      <c r="AJ224">
+        <v>1.91</v>
+      </c>
+      <c r="AK224">
+        <v>1.16</v>
+      </c>
+      <c r="AL224">
+        <v>1.21</v>
+      </c>
+      <c r="AM224">
+        <v>2.3</v>
+      </c>
+      <c r="AN224">
+        <v>2.08</v>
+      </c>
+      <c r="AO224">
+        <v>0.5</v>
+      </c>
+      <c r="AP224">
+        <v>2</v>
+      </c>
+      <c r="AQ224">
+        <v>0.54</v>
+      </c>
+      <c r="AR224">
+        <v>1.65</v>
+      </c>
+      <c r="AS224">
+        <v>1.15</v>
+      </c>
+      <c r="AT224">
+        <v>2.8</v>
+      </c>
+      <c r="AU224">
+        <v>4</v>
+      </c>
+      <c r="AV224">
+        <v>10</v>
+      </c>
+      <c r="AW224">
+        <v>12</v>
+      </c>
+      <c r="AX224">
+        <v>7</v>
+      </c>
+      <c r="AY224">
+        <v>16</v>
+      </c>
+      <c r="AZ224">
+        <v>17</v>
+      </c>
+      <c r="BA224">
+        <v>5</v>
+      </c>
+      <c r="BB224">
+        <v>10</v>
+      </c>
+      <c r="BC224">
+        <v>15</v>
+      </c>
+      <c r="BD224">
+        <v>1.36</v>
+      </c>
+      <c r="BE224">
+        <v>10</v>
+      </c>
+      <c r="BF224">
+        <v>3.4</v>
+      </c>
+      <c r="BG224">
+        <v>1.19</v>
+      </c>
+      <c r="BH224">
+        <v>4.1</v>
+      </c>
+      <c r="BI224">
+        <v>1.36</v>
+      </c>
+      <c r="BJ224">
+        <v>2.8</v>
+      </c>
+      <c r="BK224">
+        <v>1.63</v>
+      </c>
+      <c r="BL224">
+        <v>2.05</v>
+      </c>
+      <c r="BM224">
+        <v>2.1</v>
+      </c>
+      <c r="BN224">
+        <v>1.62</v>
+      </c>
+      <c r="BO224">
+        <v>2.8</v>
+      </c>
+      <c r="BP224">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7491713</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45725.39583333334</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>87</v>
+      </c>
+      <c r="H225" t="s">
+        <v>81</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>1</v>
+      </c>
+      <c r="O225" t="s">
+        <v>92</v>
+      </c>
+      <c r="P225" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q225">
+        <v>3.4</v>
+      </c>
+      <c r="R225">
+        <v>2.2</v>
+      </c>
+      <c r="S225">
+        <v>3.2</v>
+      </c>
+      <c r="T225">
+        <v>1.4</v>
+      </c>
+      <c r="U225">
+        <v>2.75</v>
+      </c>
+      <c r="V225">
+        <v>2.75</v>
+      </c>
+      <c r="W225">
+        <v>1.4</v>
+      </c>
+      <c r="X225">
+        <v>8</v>
+      </c>
+      <c r="Y225">
+        <v>1.08</v>
+      </c>
+      <c r="Z225">
+        <v>2.77</v>
+      </c>
+      <c r="AA225">
+        <v>3.47</v>
+      </c>
+      <c r="AB225">
+        <v>2.59</v>
+      </c>
+      <c r="AC225">
+        <v>1.06</v>
+      </c>
+      <c r="AD225">
+        <v>8.5</v>
+      </c>
+      <c r="AE225">
+        <v>1.3</v>
+      </c>
+      <c r="AF225">
+        <v>3.4</v>
+      </c>
+      <c r="AG225">
+        <v>1.87</v>
+      </c>
+      <c r="AH225">
+        <v>1.83</v>
+      </c>
+      <c r="AI225">
+        <v>1.73</v>
+      </c>
+      <c r="AJ225">
+        <v>2</v>
+      </c>
+      <c r="AK225">
+        <v>1.46</v>
+      </c>
+      <c r="AL225">
+        <v>1.3</v>
+      </c>
+      <c r="AM225">
+        <v>1.49</v>
+      </c>
+      <c r="AN225">
+        <v>1.08</v>
+      </c>
+      <c r="AO225">
+        <v>1</v>
+      </c>
+      <c r="AP225">
+        <v>1</v>
+      </c>
+      <c r="AQ225">
+        <v>1.15</v>
+      </c>
+      <c r="AR225">
+        <v>1.24</v>
+      </c>
+      <c r="AS225">
+        <v>1.44</v>
+      </c>
+      <c r="AT225">
+        <v>2.68</v>
+      </c>
+      <c r="AU225">
+        <v>5</v>
+      </c>
+      <c r="AV225">
+        <v>7</v>
+      </c>
+      <c r="AW225">
+        <v>13</v>
+      </c>
+      <c r="AX225">
+        <v>8</v>
+      </c>
+      <c r="AY225">
+        <v>19</v>
+      </c>
+      <c r="AZ225">
+        <v>15</v>
+      </c>
+      <c r="BA225">
+        <v>5</v>
+      </c>
+      <c r="BB225">
+        <v>3</v>
+      </c>
+      <c r="BC225">
+        <v>8</v>
+      </c>
+      <c r="BD225">
+        <v>2.15</v>
+      </c>
+      <c r="BE225">
+        <v>8.5</v>
+      </c>
+      <c r="BF225">
+        <v>1.85</v>
+      </c>
+      <c r="BG225">
+        <v>1.15</v>
+      </c>
+      <c r="BH225">
+        <v>4.2</v>
+      </c>
+      <c r="BI225">
+        <v>1.32</v>
+      </c>
+      <c r="BJ225">
+        <v>3</v>
+      </c>
+      <c r="BK225">
+        <v>1.57</v>
+      </c>
+      <c r="BL225">
+        <v>2.15</v>
+      </c>
+      <c r="BM225">
+        <v>1.98</v>
+      </c>
+      <c r="BN225">
+        <v>1.68</v>
+      </c>
+      <c r="BO225">
+        <v>2.65</v>
+      </c>
+      <c r="BP225">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7491714</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45725.39583333334</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>79</v>
+      </c>
+      <c r="H226" t="s">
+        <v>85</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226" t="s">
+        <v>92</v>
+      </c>
+      <c r="P226" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q226">
+        <v>5</v>
+      </c>
+      <c r="R226">
+        <v>2.25</v>
+      </c>
+      <c r="S226">
+        <v>2.3</v>
+      </c>
+      <c r="T226">
+        <v>1.36</v>
+      </c>
+      <c r="U226">
+        <v>3</v>
+      </c>
+      <c r="V226">
+        <v>2.75</v>
+      </c>
+      <c r="W226">
+        <v>1.4</v>
+      </c>
+      <c r="X226">
+        <v>7</v>
+      </c>
+      <c r="Y226">
+        <v>1.1</v>
+      </c>
+      <c r="Z226">
+        <v>4.5</v>
+      </c>
+      <c r="AA226">
+        <v>3.79</v>
+      </c>
+      <c r="AB226">
+        <v>1.82</v>
+      </c>
+      <c r="AC226">
+        <v>1.05</v>
+      </c>
+      <c r="AD226">
+        <v>9.5</v>
+      </c>
+      <c r="AE226">
+        <v>1.28</v>
+      </c>
+      <c r="AF226">
+        <v>3.55</v>
+      </c>
+      <c r="AG226">
+        <v>1.94</v>
+      </c>
+      <c r="AH226">
+        <v>1.87</v>
+      </c>
+      <c r="AI226">
+        <v>1.8</v>
+      </c>
+      <c r="AJ226">
+        <v>1.91</v>
+      </c>
+      <c r="AK226">
+        <v>2</v>
+      </c>
+      <c r="AL226">
+        <v>1.26</v>
+      </c>
+      <c r="AM226">
+        <v>1.2</v>
+      </c>
+      <c r="AN226">
+        <v>1.17</v>
+      </c>
+      <c r="AO226">
+        <v>1.75</v>
+      </c>
+      <c r="AP226">
+        <v>1.15</v>
+      </c>
+      <c r="AQ226">
+        <v>1.69</v>
+      </c>
+      <c r="AR226">
+        <v>1.26</v>
+      </c>
+      <c r="AS226">
+        <v>1.44</v>
+      </c>
+      <c r="AT226">
+        <v>2.7</v>
+      </c>
+      <c r="AU226">
+        <v>0</v>
+      </c>
+      <c r="AV226">
+        <v>4</v>
+      </c>
+      <c r="AW226">
+        <v>7</v>
+      </c>
+      <c r="AX226">
+        <v>11</v>
+      </c>
+      <c r="AY226">
+        <v>7</v>
+      </c>
+      <c r="AZ226">
+        <v>18</v>
+      </c>
+      <c r="BA226">
+        <v>3</v>
+      </c>
+      <c r="BB226">
+        <v>9</v>
+      </c>
+      <c r="BC226">
+        <v>12</v>
+      </c>
+      <c r="BD226">
+        <v>2.8</v>
+      </c>
+      <c r="BE226">
+        <v>9</v>
+      </c>
+      <c r="BF226">
+        <v>1.53</v>
+      </c>
+      <c r="BG226">
+        <v>1.14</v>
+      </c>
+      <c r="BH226">
+        <v>4.4</v>
+      </c>
+      <c r="BI226">
+        <v>1.31</v>
+      </c>
+      <c r="BJ226">
+        <v>3.1</v>
+      </c>
+      <c r="BK226">
+        <v>1.55</v>
+      </c>
+      <c r="BL226">
+        <v>2.2</v>
+      </c>
+      <c r="BM226">
+        <v>1.95</v>
+      </c>
+      <c r="BN226">
+        <v>1.7</v>
+      </c>
+      <c r="BO226">
+        <v>2.6</v>
+      </c>
+      <c r="BP226">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -47363,10 +47363,10 @@
         <v>8</v>
       </c>
       <c r="BB223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC223">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD223">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -47981,10 +47981,10 @@
         <v>3</v>
       </c>
       <c r="BB226">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC226">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD226">
         <v>2.8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="366">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1107,6 +1107,12 @@
   <si>
     <t>['82']</t>
   </si>
+  <si>
+    <t>['87', '88']</t>
+  </si>
+  <si>
+    <t>['9', '15', '53']</t>
+  </si>
 </sst>
 </file>
 
@@ -1467,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1804,7 +1810,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2625,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
         <v>1.42</v>
@@ -2831,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ7">
         <v>0.54</v>
@@ -5306,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5718,7 +5724,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -7157,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1.23</v>
@@ -7366,7 +7372,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ29">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -8805,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ36">
         <v>1.77</v>
@@ -11074,7 +11080,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -11277,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -12104,7 +12110,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR52">
         <v>1.99</v>
@@ -12513,7 +12519,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
         <v>1.23</v>
@@ -15809,7 +15815,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ70">
         <v>1.38</v>
@@ -16015,7 +16021,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>1.25</v>
@@ -16224,7 +16230,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16430,7 +16436,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR73">
         <v>1.59</v>
@@ -19105,7 +19111,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ86">
         <v>1.25</v>
@@ -19314,7 +19320,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ87">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR87">
         <v>1.33</v>
@@ -19929,10 +19935,10 @@
         <v>0.25</v>
       </c>
       <c r="AP90">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR90">
         <v>1.7</v>
@@ -22198,7 +22204,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR101">
         <v>1.49</v>
@@ -23019,7 +23025,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
         <v>0.6899999999999999</v>
@@ -23637,7 +23643,7 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ108">
         <v>0.08</v>
@@ -23846,7 +23852,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ109">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -25903,7 +25909,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ119">
         <v>1.38</v>
@@ -26109,7 +26115,7 @@
         <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ120">
         <v>1.67</v>
@@ -26318,7 +26324,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -27142,7 +27148,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ125">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR125">
         <v>1.52</v>
@@ -30023,7 +30029,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ139">
         <v>1.83</v>
@@ -30229,7 +30235,7 @@
         <v>1.63</v>
       </c>
       <c r="AP140">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ140">
         <v>1.69</v>
@@ -30438,7 +30444,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ141">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR141">
         <v>1.46</v>
@@ -31056,7 +31062,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ144">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -33528,7 +33534,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ156">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR156">
         <v>1.25</v>
@@ -35173,7 +35179,7 @@
         <v>0.22</v>
       </c>
       <c r="AP164">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
         <v>0.54</v>
@@ -35997,7 +36003,7 @@
         <v>0.89</v>
       </c>
       <c r="AP168">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ168">
         <v>1.15</v>
@@ -36206,7 +36212,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ169">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -38057,7 +38063,7 @@
         <v>2.5</v>
       </c>
       <c r="AP178">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ178">
         <v>2.23</v>
@@ -38678,7 +38684,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ181">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR181">
         <v>1.76</v>
@@ -38884,7 +38890,7 @@
         <v>1</v>
       </c>
       <c r="AQ182">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR182">
         <v>1.22</v>
@@ -39499,7 +39505,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ185">
         <v>1.15</v>
@@ -40735,7 +40741,7 @@
         <v>2</v>
       </c>
       <c r="AP191">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ191">
         <v>1.77</v>
@@ -41356,7 +41362,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ194">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR194">
         <v>1.74</v>
@@ -41974,7 +41980,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ197">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR197">
         <v>1.21</v>
@@ -42177,7 +42183,7 @@
         <v>1.45</v>
       </c>
       <c r="AP198">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ198">
         <v>1.23</v>
@@ -44649,7 +44655,7 @@
         <v>0.91</v>
       </c>
       <c r="AP210">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ210">
         <v>0.83</v>
@@ -45270,7 +45276,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ213">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR213">
         <v>1.64</v>
@@ -45679,7 +45685,7 @@
         <v>1.09</v>
       </c>
       <c r="AP215">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ215">
         <v>1</v>
@@ -46094,7 +46100,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ217">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR217">
         <v>1.68</v>
@@ -48024,6 +48030,418 @@
       </c>
       <c r="BP226">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7491719</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45730.60416666666</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>75</v>
+      </c>
+      <c r="H227" t="s">
+        <v>72</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>2</v>
+      </c>
+      <c r="N227">
+        <v>3</v>
+      </c>
+      <c r="O227" t="s">
+        <v>174</v>
+      </c>
+      <c r="P227" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q227">
+        <v>3.1</v>
+      </c>
+      <c r="R227">
+        <v>2.25</v>
+      </c>
+      <c r="S227">
+        <v>3.2</v>
+      </c>
+      <c r="T227">
+        <v>1.33</v>
+      </c>
+      <c r="U227">
+        <v>3.25</v>
+      </c>
+      <c r="V227">
+        <v>2.63</v>
+      </c>
+      <c r="W227">
+        <v>1.44</v>
+      </c>
+      <c r="X227">
+        <v>6.5</v>
+      </c>
+      <c r="Y227">
+        <v>1.11</v>
+      </c>
+      <c r="Z227">
+        <v>2.45</v>
+      </c>
+      <c r="AA227">
+        <v>3.53</v>
+      </c>
+      <c r="AB227">
+        <v>2.91</v>
+      </c>
+      <c r="AC227">
+        <v>1</v>
+      </c>
+      <c r="AD227">
+        <v>12.9</v>
+      </c>
+      <c r="AE227">
+        <v>1.22</v>
+      </c>
+      <c r="AF227">
+        <v>4.31</v>
+      </c>
+      <c r="AG227">
+        <v>1.65</v>
+      </c>
+      <c r="AH227">
+        <v>2</v>
+      </c>
+      <c r="AI227">
+        <v>1.57</v>
+      </c>
+      <c r="AJ227">
+        <v>2.25</v>
+      </c>
+      <c r="AK227">
+        <v>1.46</v>
+      </c>
+      <c r="AL227">
+        <v>1.29</v>
+      </c>
+      <c r="AM227">
+        <v>1.51</v>
+      </c>
+      <c r="AN227">
+        <v>1.42</v>
+      </c>
+      <c r="AO227">
+        <v>1.08</v>
+      </c>
+      <c r="AP227">
+        <v>1.31</v>
+      </c>
+      <c r="AQ227">
+        <v>1.23</v>
+      </c>
+      <c r="AR227">
+        <v>1.68</v>
+      </c>
+      <c r="AS227">
+        <v>1.43</v>
+      </c>
+      <c r="AT227">
+        <v>3.11</v>
+      </c>
+      <c r="AU227">
+        <v>5</v>
+      </c>
+      <c r="AV227">
+        <v>5</v>
+      </c>
+      <c r="AW227">
+        <v>6</v>
+      </c>
+      <c r="AX227">
+        <v>8</v>
+      </c>
+      <c r="AY227">
+        <v>11</v>
+      </c>
+      <c r="AZ227">
+        <v>15</v>
+      </c>
+      <c r="BA227">
+        <v>5</v>
+      </c>
+      <c r="BB227">
+        <v>7</v>
+      </c>
+      <c r="BC227">
+        <v>12</v>
+      </c>
+      <c r="BD227">
+        <v>1.94</v>
+      </c>
+      <c r="BE227">
+        <v>6.5</v>
+      </c>
+      <c r="BF227">
+        <v>2.05</v>
+      </c>
+      <c r="BG227">
+        <v>1.33</v>
+      </c>
+      <c r="BH227">
+        <v>2.95</v>
+      </c>
+      <c r="BI227">
+        <v>1.57</v>
+      </c>
+      <c r="BJ227">
+        <v>2.23</v>
+      </c>
+      <c r="BK227">
+        <v>1.95</v>
+      </c>
+      <c r="BL227">
+        <v>1.75</v>
+      </c>
+      <c r="BM227">
+        <v>2.45</v>
+      </c>
+      <c r="BN227">
+        <v>1.48</v>
+      </c>
+      <c r="BO227">
+        <v>3.2</v>
+      </c>
+      <c r="BP227">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7491722</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45730.60416666666</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>74</v>
+      </c>
+      <c r="H228" t="s">
+        <v>84</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>2</v>
+      </c>
+      <c r="K228">
+        <v>2</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>3</v>
+      </c>
+      <c r="N228">
+        <v>3</v>
+      </c>
+      <c r="O228" t="s">
+        <v>92</v>
+      </c>
+      <c r="P228" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q228">
+        <v>2.88</v>
+      </c>
+      <c r="R228">
+        <v>2.5</v>
+      </c>
+      <c r="S228">
+        <v>3</v>
+      </c>
+      <c r="T228">
+        <v>1.25</v>
+      </c>
+      <c r="U228">
+        <v>3.75</v>
+      </c>
+      <c r="V228">
+        <v>2.2</v>
+      </c>
+      <c r="W228">
+        <v>1.62</v>
+      </c>
+      <c r="X228">
+        <v>5</v>
+      </c>
+      <c r="Y228">
+        <v>1.17</v>
+      </c>
+      <c r="Z228">
+        <v>2.45</v>
+      </c>
+      <c r="AA228">
+        <v>3.74</v>
+      </c>
+      <c r="AB228">
+        <v>2.78</v>
+      </c>
+      <c r="AC228">
+        <v>1.02</v>
+      </c>
+      <c r="AD228">
+        <v>20</v>
+      </c>
+      <c r="AE228">
+        <v>1.14</v>
+      </c>
+      <c r="AF228">
+        <v>5.95</v>
+      </c>
+      <c r="AG228">
+        <v>1.48</v>
+      </c>
+      <c r="AH228">
+        <v>2.55</v>
+      </c>
+      <c r="AI228">
+        <v>1.4</v>
+      </c>
+      <c r="AJ228">
+        <v>2.75</v>
+      </c>
+      <c r="AK228">
+        <v>1.51</v>
+      </c>
+      <c r="AL228">
+        <v>1.25</v>
+      </c>
+      <c r="AM228">
+        <v>1.5</v>
+      </c>
+      <c r="AN228">
+        <v>1.08</v>
+      </c>
+      <c r="AO228">
+        <v>1.5</v>
+      </c>
+      <c r="AP228">
+        <v>1</v>
+      </c>
+      <c r="AQ228">
+        <v>1.62</v>
+      </c>
+      <c r="AR228">
+        <v>1.81</v>
+      </c>
+      <c r="AS228">
+        <v>1.53</v>
+      </c>
+      <c r="AT228">
+        <v>3.34</v>
+      </c>
+      <c r="AU228">
+        <v>11</v>
+      </c>
+      <c r="AV228">
+        <v>8</v>
+      </c>
+      <c r="AW228">
+        <v>4</v>
+      </c>
+      <c r="AX228">
+        <v>8</v>
+      </c>
+      <c r="AY228">
+        <v>21</v>
+      </c>
+      <c r="AZ228">
+        <v>17</v>
+      </c>
+      <c r="BA228">
+        <v>3</v>
+      </c>
+      <c r="BB228">
+        <v>3</v>
+      </c>
+      <c r="BC228">
+        <v>6</v>
+      </c>
+      <c r="BD228">
+        <v>2.05</v>
+      </c>
+      <c r="BE228">
+        <v>6.5</v>
+      </c>
+      <c r="BF228">
+        <v>1.94</v>
+      </c>
+      <c r="BG228">
+        <v>1.28</v>
+      </c>
+      <c r="BH228">
+        <v>3.3</v>
+      </c>
+      <c r="BI228">
+        <v>1.48</v>
+      </c>
+      <c r="BJ228">
+        <v>2.43</v>
+      </c>
+      <c r="BK228">
+        <v>1.78</v>
+      </c>
+      <c r="BL228">
+        <v>1.91</v>
+      </c>
+      <c r="BM228">
+        <v>2.2</v>
+      </c>
+      <c r="BN228">
+        <v>1.58</v>
+      </c>
+      <c r="BO228">
+        <v>2.8</v>
+      </c>
+      <c r="BP228">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="370">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,6 +748,12 @@
     <t>['90+3']</t>
   </si>
   <si>
+    <t>['2', '8', '15', '72', '90+5']</t>
+  </si>
+  <si>
+    <t>['1', '80']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1113,6 +1119,12 @@
   <si>
     <t>['9', '15', '53']</t>
   </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['45+1', '45+8', '61']</t>
+  </si>
 </sst>
 </file>
 
@@ -1473,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP228"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1729,7 +1741,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1807,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ2">
         <v>1.62</v>
@@ -1935,7 +1947,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2347,7 +2359,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2759,7 +2771,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2965,7 +2977,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3252,7 +3264,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3377,7 +3389,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3458,7 +3470,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ10">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3789,7 +3801,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4201,7 +4213,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4279,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ14">
         <v>1.77</v>
@@ -4485,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15">
         <v>1.23</v>
@@ -4819,7 +4831,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4897,10 +4909,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5025,7 +5037,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5437,7 +5449,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5930,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -6545,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ25">
         <v>0.54</v>
@@ -6673,7 +6685,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6879,7 +6891,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7085,7 +7097,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7369,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ29">
         <v>1.23</v>
@@ -7497,7 +7509,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7703,7 +7715,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7784,7 +7796,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ31">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.09</v>
@@ -7987,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
         <v>0.9399999999999999</v>
@@ -8115,7 +8127,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8321,7 +8333,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8605,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ35">
         <v>0.6899999999999999</v>
@@ -8733,7 +8745,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8939,7 +8951,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9145,7 +9157,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9557,7 +9569,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9638,7 +9650,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR40">
         <v>1.31</v>
@@ -9763,7 +9775,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10175,7 +10187,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10253,7 +10265,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
         <v>2.23</v>
@@ -10587,7 +10599,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10999,7 +11011,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11077,7 +11089,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ47">
         <v>1.23</v>
@@ -11205,7 +11217,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11286,7 +11298,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR48">
         <v>1.7</v>
@@ -11411,7 +11423,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11489,7 +11501,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49">
         <v>1.77</v>
@@ -11617,7 +11629,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12029,7 +12041,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12235,7 +12247,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12313,7 +12325,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ53">
         <v>0.6899999999999999</v>
@@ -12441,7 +12453,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12647,7 +12659,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12728,7 +12740,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ55">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12853,7 +12865,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13059,7 +13071,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13265,7 +13277,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13552,7 +13564,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ59">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13677,7 +13689,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13883,7 +13895,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14295,7 +14307,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14501,7 +14513,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14579,7 +14591,7 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ64">
         <v>1.23</v>
@@ -14785,7 +14797,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ65">
         <v>0.08</v>
@@ -14913,7 +14925,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14994,7 +15006,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR66">
         <v>1.63</v>
@@ -15197,7 +15209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ67">
         <v>0.6899999999999999</v>
@@ -15403,10 +15415,10 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ68">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15531,7 +15543,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15612,7 +15624,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ69">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>0.99</v>
@@ -15737,7 +15749,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15943,7 +15955,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16355,7 +16367,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16433,7 +16445,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ73">
         <v>1.62</v>
@@ -16973,7 +16985,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17179,7 +17191,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -18003,7 +18015,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18415,7 +18427,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18493,7 +18505,7 @@
         <v>1.2</v>
       </c>
       <c r="AP83">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ83">
         <v>1.69</v>
@@ -18621,7 +18633,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18827,7 +18839,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -19033,7 +19045,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19239,7 +19251,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19317,7 +19329,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ87">
         <v>1.62</v>
@@ -19445,7 +19457,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19523,10 +19535,10 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR88">
         <v>1.59</v>
@@ -19651,7 +19663,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19857,7 +19869,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20144,7 +20156,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ91">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.66</v>
@@ -20887,7 +20899,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20968,7 +20980,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -21299,7 +21311,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21505,7 +21517,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21789,7 +21801,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ99">
         <v>0.54</v>
@@ -22123,7 +22135,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22410,7 +22422,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ102">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR102">
         <v>1.42</v>
@@ -22613,7 +22625,7 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ103">
         <v>1.25</v>
@@ -22741,7 +22753,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23153,7 +23165,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23231,7 +23243,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ106">
         <v>1.69</v>
@@ -23359,7 +23371,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23440,7 +23452,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ107">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23771,7 +23783,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23849,7 +23861,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ109">
         <v>1.23</v>
@@ -23977,7 +23989,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24055,7 +24067,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ110">
         <v>1.15</v>
@@ -24389,7 +24401,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24595,7 +24607,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24801,7 +24813,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24879,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ114">
         <v>1.42</v>
@@ -25007,7 +25019,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25088,7 +25100,7 @@
         <v>2</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR115">
         <v>1.64</v>
@@ -25213,7 +25225,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25419,7 +25431,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25625,7 +25637,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25831,7 +25843,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -26037,7 +26049,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26118,7 +26130,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ120">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26243,7 +26255,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26321,7 +26333,7 @@
         <v>0.67</v>
       </c>
       <c r="AP121">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ121">
         <v>1.23</v>
@@ -26449,7 +26461,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26527,7 +26539,7 @@
         <v>1.43</v>
       </c>
       <c r="AP122">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ122">
         <v>1.69</v>
@@ -26942,7 +26954,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ124">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.46</v>
@@ -27067,7 +27079,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27273,7 +27285,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27763,7 +27775,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ128">
         <v>1.15</v>
@@ -27891,7 +27903,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27969,7 +27981,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ129">
         <v>1.23</v>
@@ -28097,7 +28109,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28509,7 +28521,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28715,7 +28727,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28921,7 +28933,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29002,7 +29014,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR134">
         <v>1.67</v>
@@ -29205,7 +29217,7 @@
         <v>0.29</v>
       </c>
       <c r="AP135">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ135">
         <v>0.54</v>
@@ -29333,7 +29345,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29539,7 +29551,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29745,7 +29757,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29826,7 +29838,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ138">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.37</v>
@@ -30157,7 +30169,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30569,7 +30581,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30650,7 +30662,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ142">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR142">
         <v>1.45</v>
@@ -30853,7 +30865,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ143">
         <v>1.15</v>
@@ -31187,7 +31199,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31393,7 +31405,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31471,7 +31483,7 @@
         <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146">
         <v>1.23</v>
@@ -31599,7 +31611,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31677,7 +31689,7 @@
         <v>2.38</v>
       </c>
       <c r="AP147">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ147">
         <v>2.23</v>
@@ -32217,7 +32229,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32295,7 +32307,7 @@
         <v>1.5</v>
       </c>
       <c r="AP150">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ150">
         <v>1.23</v>
@@ -32710,7 +32722,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR152">
         <v>1.2</v>
@@ -33041,7 +33053,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33247,7 +33259,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33325,10 +33337,10 @@
         <v>1.38</v>
       </c>
       <c r="AP155">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR155">
         <v>1.57</v>
@@ -34483,7 +34495,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34561,7 +34573,7 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ161">
         <v>1.38</v>
@@ -34689,7 +34701,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34767,7 +34779,7 @@
         <v>2.44</v>
       </c>
       <c r="AP162">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ162">
         <v>2.23</v>
@@ -34895,7 +34907,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35101,7 +35113,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35307,7 +35319,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35388,7 +35400,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ165">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -35591,7 +35603,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ166">
         <v>1.42</v>
@@ -35719,7 +35731,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36131,7 +36143,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36337,7 +36349,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36749,7 +36761,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36830,7 +36842,7 @@
         <v>2</v>
       </c>
       <c r="AQ172">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR172">
         <v>1.67</v>
@@ -37036,7 +37048,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ173">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR173">
         <v>1.57</v>
@@ -37161,7 +37173,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37239,7 +37251,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ174">
         <v>1.23</v>
@@ -37573,7 +37585,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37779,7 +37791,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37857,7 +37869,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ177">
         <v>0.6899999999999999</v>
@@ -37985,7 +37997,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38191,7 +38203,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38269,7 +38281,7 @@
         <v>1</v>
       </c>
       <c r="AP179">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ179">
         <v>1.25</v>
@@ -38397,7 +38409,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38478,7 +38490,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ180">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR180">
         <v>1.74</v>
@@ -38603,7 +38615,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38809,7 +38821,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39221,7 +39233,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39427,7 +39439,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39633,7 +39645,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39920,7 +39932,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ187">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR187">
         <v>1.44</v>
@@ -40123,7 +40135,7 @@
         <v>1.3</v>
       </c>
       <c r="AP188">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ188">
         <v>1.23</v>
@@ -40251,7 +40263,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40947,10 +40959,10 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ192">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR192">
         <v>1.67</v>
@@ -41153,7 +41165,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ193">
         <v>1.25</v>
@@ -41568,7 +41580,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ195">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR195">
         <v>1.27</v>
@@ -41693,7 +41705,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -41771,7 +41783,7 @@
         <v>1.64</v>
       </c>
       <c r="AP196">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ196">
         <v>1.38</v>
@@ -42598,7 +42610,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ200">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR200">
         <v>1.78</v>
@@ -42929,7 +42941,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43547,7 +43559,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43831,7 +43843,7 @@
         <v>2.1</v>
       </c>
       <c r="AP206">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ206">
         <v>1.83</v>
@@ -44371,7 +44383,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -44449,7 +44461,7 @@
         <v>1.09</v>
       </c>
       <c r="AP209">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ209">
         <v>1.25</v>
@@ -44658,7 +44670,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ210">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR210">
         <v>1.67</v>
@@ -45195,7 +45207,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45607,7 +45619,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -45688,7 +45700,7 @@
         <v>1</v>
       </c>
       <c r="AQ215">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR215">
         <v>1.76</v>
@@ -45891,7 +45903,7 @@
         <v>1.5</v>
       </c>
       <c r="AP216">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ216">
         <v>1.38</v>
@@ -46097,7 +46109,7 @@
         <v>1.64</v>
       </c>
       <c r="AP217">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ217">
         <v>1.62</v>
@@ -46431,7 +46443,7 @@
         <v>240</v>
       </c>
       <c r="P219" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q219">
         <v>2.85</v>
@@ -46843,7 +46855,7 @@
         <v>119</v>
       </c>
       <c r="P221" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47255,7 +47267,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47461,7 +47473,7 @@
         <v>243</v>
       </c>
       <c r="P224" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q224">
         <v>2.2</v>
@@ -47667,7 +47679,7 @@
         <v>92</v>
       </c>
       <c r="P225" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q225">
         <v>3.4</v>
@@ -48079,7 +48091,7 @@
         <v>174</v>
       </c>
       <c r="P227" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q227">
         <v>3.1</v>
@@ -48285,7 +48297,7 @@
         <v>92</v>
       </c>
       <c r="P228" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48442,6 +48454,830 @@
       </c>
       <c r="BP228">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7491720</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45731.375</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>82</v>
+      </c>
+      <c r="H229" t="s">
+        <v>87</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
+        <v>92</v>
+      </c>
+      <c r="P229" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q229">
+        <v>2.25</v>
+      </c>
+      <c r="R229">
+        <v>2.25</v>
+      </c>
+      <c r="S229">
+        <v>5</v>
+      </c>
+      <c r="T229">
+        <v>1.36</v>
+      </c>
+      <c r="U229">
+        <v>3</v>
+      </c>
+      <c r="V229">
+        <v>2.63</v>
+      </c>
+      <c r="W229">
+        <v>1.44</v>
+      </c>
+      <c r="X229">
+        <v>7</v>
+      </c>
+      <c r="Y229">
+        <v>1.1</v>
+      </c>
+      <c r="Z229">
+        <v>1.75</v>
+      </c>
+      <c r="AA229">
+        <v>4.1</v>
+      </c>
+      <c r="AB229">
+        <v>4.6</v>
+      </c>
+      <c r="AC229">
+        <v>0</v>
+      </c>
+      <c r="AD229">
+        <v>0</v>
+      </c>
+      <c r="AE229">
+        <v>2.08</v>
+      </c>
+      <c r="AF229">
+        <v>1.79</v>
+      </c>
+      <c r="AG229">
+        <v>1.85</v>
+      </c>
+      <c r="AH229">
+        <v>1.96</v>
+      </c>
+      <c r="AI229">
+        <v>1.8</v>
+      </c>
+      <c r="AJ229">
+        <v>1.91</v>
+      </c>
+      <c r="AK229">
+        <v>1.2</v>
+      </c>
+      <c r="AL229">
+        <v>1.26</v>
+      </c>
+      <c r="AM229">
+        <v>2.18</v>
+      </c>
+      <c r="AN229">
+        <v>1.77</v>
+      </c>
+      <c r="AO229">
+        <v>0.83</v>
+      </c>
+      <c r="AP229">
+        <v>1.64</v>
+      </c>
+      <c r="AQ229">
+        <v>1</v>
+      </c>
+      <c r="AR229">
+        <v>1.5</v>
+      </c>
+      <c r="AS229">
+        <v>1.32</v>
+      </c>
+      <c r="AT229">
+        <v>2.82</v>
+      </c>
+      <c r="AU229">
+        <v>5</v>
+      </c>
+      <c r="AV229">
+        <v>2</v>
+      </c>
+      <c r="AW229">
+        <v>12</v>
+      </c>
+      <c r="AX229">
+        <v>5</v>
+      </c>
+      <c r="AY229">
+        <v>23</v>
+      </c>
+      <c r="AZ229">
+        <v>8</v>
+      </c>
+      <c r="BA229">
+        <v>4</v>
+      </c>
+      <c r="BB229">
+        <v>2</v>
+      </c>
+      <c r="BC229">
+        <v>6</v>
+      </c>
+      <c r="BD229">
+        <v>0</v>
+      </c>
+      <c r="BE229">
+        <v>0</v>
+      </c>
+      <c r="BF229">
+        <v>0</v>
+      </c>
+      <c r="BG229">
+        <v>0</v>
+      </c>
+      <c r="BH229">
+        <v>0</v>
+      </c>
+      <c r="BI229">
+        <v>0</v>
+      </c>
+      <c r="BJ229">
+        <v>0</v>
+      </c>
+      <c r="BK229">
+        <v>1.73</v>
+      </c>
+      <c r="BL229">
+        <v>2.06</v>
+      </c>
+      <c r="BM229">
+        <v>2.12</v>
+      </c>
+      <c r="BN229">
+        <v>1.7</v>
+      </c>
+      <c r="BO229">
+        <v>2.34</v>
+      </c>
+      <c r="BP229">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7491718</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45731.375</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>85</v>
+      </c>
+      <c r="H230" t="s">
+        <v>80</v>
+      </c>
+      <c r="I230">
+        <v>3</v>
+      </c>
+      <c r="J230">
+        <v>2</v>
+      </c>
+      <c r="K230">
+        <v>5</v>
+      </c>
+      <c r="L230">
+        <v>5</v>
+      </c>
+      <c r="M230">
+        <v>3</v>
+      </c>
+      <c r="N230">
+        <v>8</v>
+      </c>
+      <c r="O230" t="s">
+        <v>244</v>
+      </c>
+      <c r="P230" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q230">
+        <v>2.4</v>
+      </c>
+      <c r="R230">
+        <v>2.38</v>
+      </c>
+      <c r="S230">
+        <v>4</v>
+      </c>
+      <c r="T230">
+        <v>1.3</v>
+      </c>
+      <c r="U230">
+        <v>3.4</v>
+      </c>
+      <c r="V230">
+        <v>2.38</v>
+      </c>
+      <c r="W230">
+        <v>1.53</v>
+      </c>
+      <c r="X230">
+        <v>6</v>
+      </c>
+      <c r="Y230">
+        <v>1.13</v>
+      </c>
+      <c r="Z230">
+        <v>2.03</v>
+      </c>
+      <c r="AA230">
+        <v>3.45</v>
+      </c>
+      <c r="AB230">
+        <v>3.97</v>
+      </c>
+      <c r="AC230">
+        <v>0</v>
+      </c>
+      <c r="AD230">
+        <v>0</v>
+      </c>
+      <c r="AE230">
+        <v>1.14</v>
+      </c>
+      <c r="AF230">
+        <v>4.55</v>
+      </c>
+      <c r="AG230">
+        <v>1.6</v>
+      </c>
+      <c r="AH230">
+        <v>2.1</v>
+      </c>
+      <c r="AI230">
+        <v>1.57</v>
+      </c>
+      <c r="AJ230">
+        <v>2.25</v>
+      </c>
+      <c r="AK230">
+        <v>1.21</v>
+      </c>
+      <c r="AL230">
+        <v>1.28</v>
+      </c>
+      <c r="AM230">
+        <v>2.02</v>
+      </c>
+      <c r="AN230">
+        <v>1.67</v>
+      </c>
+      <c r="AO230">
+        <v>1.67</v>
+      </c>
+      <c r="AP230">
+        <v>1.77</v>
+      </c>
+      <c r="AQ230">
+        <v>1.54</v>
+      </c>
+      <c r="AR230">
+        <v>1.69</v>
+      </c>
+      <c r="AS230">
+        <v>1.4</v>
+      </c>
+      <c r="AT230">
+        <v>3.09</v>
+      </c>
+      <c r="AU230">
+        <v>9</v>
+      </c>
+      <c r="AV230">
+        <v>5</v>
+      </c>
+      <c r="AW230">
+        <v>4</v>
+      </c>
+      <c r="AX230">
+        <v>5</v>
+      </c>
+      <c r="AY230">
+        <v>14</v>
+      </c>
+      <c r="AZ230">
+        <v>14</v>
+      </c>
+      <c r="BA230">
+        <v>4</v>
+      </c>
+      <c r="BB230">
+        <v>5</v>
+      </c>
+      <c r="BC230">
+        <v>9</v>
+      </c>
+      <c r="BD230">
+        <v>1.42</v>
+      </c>
+      <c r="BE230">
+        <v>7.7</v>
+      </c>
+      <c r="BF230">
+        <v>3.86</v>
+      </c>
+      <c r="BG230">
+        <v>1.14</v>
+      </c>
+      <c r="BH230">
+        <v>4.4</v>
+      </c>
+      <c r="BI230">
+        <v>1.3</v>
+      </c>
+      <c r="BJ230">
+        <v>2.97</v>
+      </c>
+      <c r="BK230">
+        <v>1.55</v>
+      </c>
+      <c r="BL230">
+        <v>2.23</v>
+      </c>
+      <c r="BM230">
+        <v>1.94</v>
+      </c>
+      <c r="BN230">
+        <v>1.77</v>
+      </c>
+      <c r="BO230">
+        <v>2.48</v>
+      </c>
+      <c r="BP230">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7491716</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45731.375</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>83</v>
+      </c>
+      <c r="H231" t="s">
+        <v>79</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="L231">
+        <v>1</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>1</v>
+      </c>
+      <c r="O231" t="s">
+        <v>240</v>
+      </c>
+      <c r="P231" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q231">
+        <v>2.2</v>
+      </c>
+      <c r="R231">
+        <v>2.38</v>
+      </c>
+      <c r="S231">
+        <v>5</v>
+      </c>
+      <c r="T231">
+        <v>1.33</v>
+      </c>
+      <c r="U231">
+        <v>3.25</v>
+      </c>
+      <c r="V231">
+        <v>2.63</v>
+      </c>
+      <c r="W231">
+        <v>1.44</v>
+      </c>
+      <c r="X231">
+        <v>6.5</v>
+      </c>
+      <c r="Y231">
+        <v>1.11</v>
+      </c>
+      <c r="Z231">
+        <v>1.65</v>
+      </c>
+      <c r="AA231">
+        <v>4.75</v>
+      </c>
+      <c r="AB231">
+        <v>4.6</v>
+      </c>
+      <c r="AC231">
+        <v>0</v>
+      </c>
+      <c r="AD231">
+        <v>0</v>
+      </c>
+      <c r="AE231">
+        <v>2.88</v>
+      </c>
+      <c r="AF231">
+        <v>1.45</v>
+      </c>
+      <c r="AG231">
+        <v>1.67</v>
+      </c>
+      <c r="AH231">
+        <v>2.17</v>
+      </c>
+      <c r="AI231">
+        <v>1.8</v>
+      </c>
+      <c r="AJ231">
+        <v>1.91</v>
+      </c>
+      <c r="AK231">
+        <v>1.22</v>
+      </c>
+      <c r="AL231">
+        <v>1.21</v>
+      </c>
+      <c r="AM231">
+        <v>2.32</v>
+      </c>
+      <c r="AN231">
+        <v>1.23</v>
+      </c>
+      <c r="AO231">
+        <v>0.08</v>
+      </c>
+      <c r="AP231">
+        <v>1.36</v>
+      </c>
+      <c r="AQ231">
+        <v>0.08</v>
+      </c>
+      <c r="AR231">
+        <v>1.5</v>
+      </c>
+      <c r="AS231">
+        <v>1.24</v>
+      </c>
+      <c r="AT231">
+        <v>2.74</v>
+      </c>
+      <c r="AU231">
+        <v>10</v>
+      </c>
+      <c r="AV231">
+        <v>2</v>
+      </c>
+      <c r="AW231">
+        <v>7</v>
+      </c>
+      <c r="AX231">
+        <v>9</v>
+      </c>
+      <c r="AY231">
+        <v>18</v>
+      </c>
+      <c r="AZ231">
+        <v>13</v>
+      </c>
+      <c r="BA231">
+        <v>5</v>
+      </c>
+      <c r="BB231">
+        <v>4</v>
+      </c>
+      <c r="BC231">
+        <v>9</v>
+      </c>
+      <c r="BD231">
+        <v>0</v>
+      </c>
+      <c r="BE231">
+        <v>0</v>
+      </c>
+      <c r="BF231">
+        <v>0</v>
+      </c>
+      <c r="BG231">
+        <v>0</v>
+      </c>
+      <c r="BH231">
+        <v>0</v>
+      </c>
+      <c r="BI231">
+        <v>0</v>
+      </c>
+      <c r="BJ231">
+        <v>0</v>
+      </c>
+      <c r="BK231">
+        <v>1.5</v>
+      </c>
+      <c r="BL231">
+        <v>2.45</v>
+      </c>
+      <c r="BM231">
+        <v>1.86</v>
+      </c>
+      <c r="BN231">
+        <v>1.93</v>
+      </c>
+      <c r="BO231">
+        <v>2.29</v>
+      </c>
+      <c r="BP231">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7491715</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45731.6875</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>70</v>
+      </c>
+      <c r="H232" t="s">
+        <v>76</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>2</v>
+      </c>
+      <c r="L232">
+        <v>2</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>3</v>
+      </c>
+      <c r="O232" t="s">
+        <v>245</v>
+      </c>
+      <c r="P232" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q232">
+        <v>2.5</v>
+      </c>
+      <c r="R232">
+        <v>2.2</v>
+      </c>
+      <c r="S232">
+        <v>4.33</v>
+      </c>
+      <c r="T232">
+        <v>1.36</v>
+      </c>
+      <c r="U232">
+        <v>3</v>
+      </c>
+      <c r="V232">
+        <v>2.75</v>
+      </c>
+      <c r="W232">
+        <v>1.4</v>
+      </c>
+      <c r="X232">
+        <v>8</v>
+      </c>
+      <c r="Y232">
+        <v>1.08</v>
+      </c>
+      <c r="Z232">
+        <v>1.88</v>
+      </c>
+      <c r="AA232">
+        <v>3.73</v>
+      </c>
+      <c r="AB232">
+        <v>4.2</v>
+      </c>
+      <c r="AC232">
+        <v>1.05</v>
+      </c>
+      <c r="AD232">
+        <v>9</v>
+      </c>
+      <c r="AE232">
+        <v>1.24</v>
+      </c>
+      <c r="AF232">
+        <v>3.48</v>
+      </c>
+      <c r="AG232">
+        <v>1.87</v>
+      </c>
+      <c r="AH232">
+        <v>1.94</v>
+      </c>
+      <c r="AI232">
+        <v>1.73</v>
+      </c>
+      <c r="AJ232">
+        <v>2</v>
+      </c>
+      <c r="AK232">
+        <v>1.28</v>
+      </c>
+      <c r="AL232">
+        <v>1.3</v>
+      </c>
+      <c r="AM232">
+        <v>1.82</v>
+      </c>
+      <c r="AN232">
+        <v>1.75</v>
+      </c>
+      <c r="AO232">
+        <v>1</v>
+      </c>
+      <c r="AP232">
+        <v>1.85</v>
+      </c>
+      <c r="AQ232">
+        <v>0.92</v>
+      </c>
+      <c r="AR232">
+        <v>1.81</v>
+      </c>
+      <c r="AS232">
+        <v>1.67</v>
+      </c>
+      <c r="AT232">
+        <v>3.48</v>
+      </c>
+      <c r="AU232">
+        <v>6</v>
+      </c>
+      <c r="AV232">
+        <v>5</v>
+      </c>
+      <c r="AW232">
+        <v>13</v>
+      </c>
+      <c r="AX232">
+        <v>2</v>
+      </c>
+      <c r="AY232">
+        <v>23</v>
+      </c>
+      <c r="AZ232">
+        <v>7</v>
+      </c>
+      <c r="BA232">
+        <v>6</v>
+      </c>
+      <c r="BB232">
+        <v>3</v>
+      </c>
+      <c r="BC232">
+        <v>9</v>
+      </c>
+      <c r="BD232">
+        <v>1.37</v>
+      </c>
+      <c r="BE232">
+        <v>7.8</v>
+      </c>
+      <c r="BF232">
+        <v>4.25</v>
+      </c>
+      <c r="BG232">
+        <v>1.14</v>
+      </c>
+      <c r="BH232">
+        <v>4.4</v>
+      </c>
+      <c r="BI232">
+        <v>1.3</v>
+      </c>
+      <c r="BJ232">
+        <v>2.97</v>
+      </c>
+      <c r="BK232">
+        <v>1.56</v>
+      </c>
+      <c r="BL232">
+        <v>2.21</v>
+      </c>
+      <c r="BM232">
+        <v>1.95</v>
+      </c>
+      <c r="BN232">
+        <v>1.76</v>
+      </c>
+      <c r="BO232">
+        <v>2.51</v>
+      </c>
+      <c r="BP232">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="372">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,12 @@
     <t>['1', '80']</t>
   </si>
   <si>
+    <t>['4', '39', '45+4']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -940,9 +946,6 @@
     <t>['90+2']</t>
   </si>
   <si>
-    <t>['90+1']</t>
-  </si>
-  <si>
     <t>['8', '51']</t>
   </si>
   <si>
@@ -1124,6 +1127,9 @@
   </si>
   <si>
     <t>['45+1', '45+8', '61']</t>
+  </si>
+  <si>
+    <t>['7', '42', '44', '69', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1741,7 +1747,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1947,7 +1953,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2025,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ3">
         <v>1.15</v>
@@ -2359,7 +2365,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2771,7 +2777,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2977,7 +2983,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3389,7 +3395,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3676,7 +3682,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ11">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3801,7 +3807,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3882,7 +3888,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ12">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4085,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.23</v>
@@ -4213,7 +4219,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4706,7 +4712,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ16">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4831,7 +4837,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5037,7 +5043,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5115,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ18">
         <v>2.23</v>
@@ -5449,7 +5455,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5527,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ20">
         <v>1.42</v>
@@ -6685,7 +6691,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6891,7 +6897,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7097,7 +7103,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7509,7 +7515,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7590,7 +7596,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ30">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR30">
         <v>0.79</v>
@@ -7715,7 +7721,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8127,7 +8133,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8205,7 +8211,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>2.23</v>
@@ -8333,7 +8339,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8414,7 +8420,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ34">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR34">
         <v>1.8</v>
@@ -8620,7 +8626,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ35">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR35">
         <v>1.49</v>
@@ -8745,7 +8751,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8951,7 +8957,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9029,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ37">
         <v>1.23</v>
@@ -9157,7 +9163,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9441,7 +9447,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ39">
         <v>1.23</v>
@@ -9569,7 +9575,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9775,7 +9781,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10187,7 +10193,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10599,7 +10605,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -11011,7 +11017,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11217,7 +11223,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11423,7 +11429,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11629,7 +11635,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11707,10 +11713,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR50">
         <v>0.97</v>
@@ -11913,10 +11919,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ51">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -12041,7 +12047,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12247,7 +12253,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12328,7 +12334,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ53">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12453,7 +12459,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12659,7 +12665,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12865,7 +12871,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13071,7 +13077,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13277,7 +13283,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13689,7 +13695,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13895,7 +13901,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14307,7 +14313,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14513,7 +14519,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14925,7 +14931,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15003,7 +15009,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ66">
         <v>0.92</v>
@@ -15212,7 +15218,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ67">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR67">
         <v>2.27</v>
@@ -15543,7 +15549,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15621,7 +15627,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -15749,7 +15755,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15830,7 +15836,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ70">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.66</v>
@@ -15955,7 +15961,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16036,7 +16042,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16239,7 +16245,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ72">
         <v>1.23</v>
@@ -16367,7 +16373,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16985,7 +16991,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17191,7 +17197,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -18015,7 +18021,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18427,7 +18433,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18633,7 +18639,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18711,7 +18717,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>0.08</v>
@@ -18839,7 +18845,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18917,10 +18923,10 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ85">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
         <v>1.57</v>
@@ -19045,7 +19051,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19126,7 +19132,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR86">
         <v>1.49</v>
@@ -19251,7 +19257,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19457,7 +19463,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19663,7 +19669,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19744,7 +19750,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ89">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19869,7 +19875,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20153,7 +20159,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -20899,7 +20905,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21311,7 +21317,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21517,7 +21523,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22135,7 +22141,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22213,7 +22219,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ101">
         <v>1.62</v>
@@ -22419,7 +22425,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ102">
         <v>1.54</v>
@@ -22628,7 +22634,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ103">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR103">
         <v>1.96</v>
@@ -22753,7 +22759,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22834,7 +22840,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ104">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -23040,7 +23046,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR105">
         <v>1.68</v>
@@ -23165,7 +23171,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23371,7 +23377,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23449,7 +23455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23783,7 +23789,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23989,7 +23995,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24401,7 +24407,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24607,7 +24613,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24688,7 +24694,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ113">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR113">
         <v>1.37</v>
@@ -24813,7 +24819,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -25019,7 +25025,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25225,7 +25231,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25431,7 +25437,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25637,7 +25643,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25843,7 +25849,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25924,7 +25930,7 @@
         <v>1</v>
       </c>
       <c r="AQ119">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR119">
         <v>1.77</v>
@@ -26049,7 +26055,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26255,7 +26261,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26461,7 +26467,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26745,7 +26751,7 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ123">
         <v>0.08</v>
@@ -27079,7 +27085,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27157,7 +27163,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ125">
         <v>1.62</v>
@@ -27285,7 +27291,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27363,7 +27369,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ126">
         <v>1.83</v>
@@ -27572,7 +27578,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ127">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27903,7 +27909,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28109,7 +28115,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28396,7 +28402,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.46</v>
@@ -28521,7 +28527,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28602,7 +28608,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR132">
         <v>1.64</v>
@@ -28727,7 +28733,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28933,7 +28939,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29345,7 +29351,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29551,7 +29557,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29629,7 +29635,7 @@
         <v>0.14</v>
       </c>
       <c r="AP137">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ137">
         <v>0.08</v>
@@ -29757,7 +29763,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30169,7 +30175,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30581,7 +30587,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31199,7 +31205,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31277,7 +31283,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ145">
         <v>1.42</v>
@@ -31405,7 +31411,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31611,7 +31617,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31898,7 +31904,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ148">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR148">
         <v>1.74</v>
@@ -32104,7 +32110,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR149">
         <v>1.2</v>
@@ -32229,7 +32235,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32513,7 +32519,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>0.54</v>
@@ -32928,7 +32934,7 @@
         <v>2</v>
       </c>
       <c r="AQ153">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR153">
         <v>1.76</v>
@@ -33053,7 +33059,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33259,7 +33265,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33752,7 +33758,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ157">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR157">
         <v>1.65</v>
@@ -33955,7 +33961,7 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ158">
         <v>1.23</v>
@@ -34164,7 +34170,7 @@
         <v>1</v>
       </c>
       <c r="AQ159">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR159">
         <v>1.15</v>
@@ -34495,7 +34501,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34576,7 +34582,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ161">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34701,7 +34707,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34907,7 +34913,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34985,7 +34991,7 @@
         <v>1.67</v>
       </c>
       <c r="AP163">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ163">
         <v>1.23</v>
@@ -35113,7 +35119,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35319,7 +35325,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35731,7 +35737,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35809,7 +35815,7 @@
         <v>2.13</v>
       </c>
       <c r="AP167">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ167">
         <v>1.83</v>
@@ -36143,7 +36149,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36349,7 +36355,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36761,7 +36767,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37045,7 +37051,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ173">
         <v>0.92</v>
@@ -37173,7 +37179,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37460,7 +37466,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ175">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR175">
         <v>1.23</v>
@@ -37585,7 +37591,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37663,7 +37669,7 @@
         <v>1.89</v>
       </c>
       <c r="AP176">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ176">
         <v>1.77</v>
@@ -37791,7 +37797,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37872,7 +37878,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ177">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR177">
         <v>1.61</v>
@@ -37997,7 +38003,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38203,7 +38209,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38284,7 +38290,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ179">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR179">
         <v>1.64</v>
@@ -38409,7 +38415,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38615,7 +38621,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38821,7 +38827,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39233,7 +39239,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39439,7 +39445,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39645,7 +39651,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -40263,7 +40269,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40341,7 +40347,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ189">
         <v>0.54</v>
@@ -41168,7 +41174,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ193">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR193">
         <v>1.5</v>
@@ -41577,7 +41583,7 @@
         <v>1.2</v>
       </c>
       <c r="AP195">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ195">
         <v>0.92</v>
@@ -41705,7 +41711,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -41786,7 +41792,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ196">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR196">
         <v>1.57</v>
@@ -42401,10 +42407,10 @@
         <v>0.73</v>
       </c>
       <c r="AP199">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ199">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR199">
         <v>1.58</v>
@@ -42941,7 +42947,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43019,7 +43025,7 @@
         <v>2.55</v>
       </c>
       <c r="AP202">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ202">
         <v>2.23</v>
@@ -43559,7 +43565,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -44383,7 +44389,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -44464,7 +44470,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ209">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -44873,10 +44879,10 @@
         <v>0.67</v>
       </c>
       <c r="AP211">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ211">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR211">
         <v>1.31</v>
@@ -45207,7 +45213,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45285,7 +45291,7 @@
         <v>0.91</v>
       </c>
       <c r="AP213">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ213">
         <v>1.23</v>
@@ -45491,7 +45497,7 @@
         <v>1.82</v>
       </c>
       <c r="AP214">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ214">
         <v>1.77</v>
@@ -45619,7 +45625,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -45906,7 +45912,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ216">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR216">
         <v>1.49</v>
@@ -46443,7 +46449,7 @@
         <v>240</v>
       </c>
       <c r="P219" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q219">
         <v>2.85</v>
@@ -46855,7 +46861,7 @@
         <v>119</v>
       </c>
       <c r="P221" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47267,7 +47273,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47473,7 +47479,7 @@
         <v>243</v>
       </c>
       <c r="P224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q224">
         <v>2.2</v>
@@ -47679,7 +47685,7 @@
         <v>92</v>
       </c>
       <c r="P225" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q225">
         <v>3.4</v>
@@ -48091,7 +48097,7 @@
         <v>174</v>
       </c>
       <c r="P227" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q227">
         <v>3.1</v>
@@ -48297,7 +48303,7 @@
         <v>92</v>
       </c>
       <c r="P228" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48503,7 +48509,7 @@
         <v>92</v>
       </c>
       <c r="P229" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q229">
         <v>2.25</v>
@@ -48709,7 +48715,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q230">
         <v>2.4</v>
@@ -49278,6 +49284,624 @@
       </c>
       <c r="BP232">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7491721</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>81</v>
+      </c>
+      <c r="H233" t="s">
+        <v>77</v>
+      </c>
+      <c r="I233">
+        <v>3</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>3</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>3</v>
+      </c>
+      <c r="O233" t="s">
+        <v>246</v>
+      </c>
+      <c r="P233" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q233">
+        <v>2.6</v>
+      </c>
+      <c r="R233">
+        <v>2.3</v>
+      </c>
+      <c r="S233">
+        <v>4</v>
+      </c>
+      <c r="T233">
+        <v>1.33</v>
+      </c>
+      <c r="U233">
+        <v>3.25</v>
+      </c>
+      <c r="V233">
+        <v>2.63</v>
+      </c>
+      <c r="W233">
+        <v>1.44</v>
+      </c>
+      <c r="X233">
+        <v>6.5</v>
+      </c>
+      <c r="Y233">
+        <v>1.11</v>
+      </c>
+      <c r="Z233">
+        <v>2</v>
+      </c>
+      <c r="AA233">
+        <v>3.7</v>
+      </c>
+      <c r="AB233">
+        <v>3.77</v>
+      </c>
+      <c r="AC233">
+        <v>1.05</v>
+      </c>
+      <c r="AD233">
+        <v>9.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.22</v>
+      </c>
+      <c r="AF233">
+        <v>4</v>
+      </c>
+      <c r="AG233">
+        <v>1.65</v>
+      </c>
+      <c r="AH233">
+        <v>2</v>
+      </c>
+      <c r="AI233">
+        <v>1.62</v>
+      </c>
+      <c r="AJ233">
+        <v>2.2</v>
+      </c>
+      <c r="AK233">
+        <v>1.34</v>
+      </c>
+      <c r="AL233">
+        <v>1.31</v>
+      </c>
+      <c r="AM233">
+        <v>1.72</v>
+      </c>
+      <c r="AN233">
+        <v>1.92</v>
+      </c>
+      <c r="AO233">
+        <v>1.25</v>
+      </c>
+      <c r="AP233">
+        <v>2</v>
+      </c>
+      <c r="AQ233">
+        <v>1.15</v>
+      </c>
+      <c r="AR233">
+        <v>1.6</v>
+      </c>
+      <c r="AS233">
+        <v>1.28</v>
+      </c>
+      <c r="AT233">
+        <v>2.88</v>
+      </c>
+      <c r="AU233">
+        <v>4</v>
+      </c>
+      <c r="AV233">
+        <v>3</v>
+      </c>
+      <c r="AW233">
+        <v>1</v>
+      </c>
+      <c r="AX233">
+        <v>5</v>
+      </c>
+      <c r="AY233">
+        <v>6</v>
+      </c>
+      <c r="AZ233">
+        <v>9</v>
+      </c>
+      <c r="BA233">
+        <v>1</v>
+      </c>
+      <c r="BB233">
+        <v>6</v>
+      </c>
+      <c r="BC233">
+        <v>7</v>
+      </c>
+      <c r="BD233">
+        <v>1.57</v>
+      </c>
+      <c r="BE233">
+        <v>9</v>
+      </c>
+      <c r="BF233">
+        <v>2.62</v>
+      </c>
+      <c r="BG233">
+        <v>1.18</v>
+      </c>
+      <c r="BH233">
+        <v>4.1</v>
+      </c>
+      <c r="BI233">
+        <v>1.35</v>
+      </c>
+      <c r="BJ233">
+        <v>2.8</v>
+      </c>
+      <c r="BK233">
+        <v>1.64</v>
+      </c>
+      <c r="BL233">
+        <v>2.24</v>
+      </c>
+      <c r="BM233">
+        <v>2.02</v>
+      </c>
+      <c r="BN233">
+        <v>1.78</v>
+      </c>
+      <c r="BO233">
+        <v>2.8</v>
+      </c>
+      <c r="BP233">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7491717</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>71</v>
+      </c>
+      <c r="H234" t="s">
+        <v>78</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234" t="s">
+        <v>92</v>
+      </c>
+      <c r="P234" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q234">
+        <v>2.75</v>
+      </c>
+      <c r="R234">
+        <v>2.2</v>
+      </c>
+      <c r="S234">
+        <v>3.75</v>
+      </c>
+      <c r="T234">
+        <v>1.4</v>
+      </c>
+      <c r="U234">
+        <v>2.75</v>
+      </c>
+      <c r="V234">
+        <v>2.75</v>
+      </c>
+      <c r="W234">
+        <v>1.4</v>
+      </c>
+      <c r="X234">
+        <v>8</v>
+      </c>
+      <c r="Y234">
+        <v>1.08</v>
+      </c>
+      <c r="Z234">
+        <v>2.08</v>
+      </c>
+      <c r="AA234">
+        <v>3.79</v>
+      </c>
+      <c r="AB234">
+        <v>3.45</v>
+      </c>
+      <c r="AC234">
+        <v>1.05</v>
+      </c>
+      <c r="AD234">
+        <v>9.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.24</v>
+      </c>
+      <c r="AF234">
+        <v>3.48</v>
+      </c>
+      <c r="AG234">
+        <v>1.92</v>
+      </c>
+      <c r="AH234">
+        <v>1.89</v>
+      </c>
+      <c r="AI234">
+        <v>1.73</v>
+      </c>
+      <c r="AJ234">
+        <v>2</v>
+      </c>
+      <c r="AK234">
+        <v>1.34</v>
+      </c>
+      <c r="AL234">
+        <v>1.29</v>
+      </c>
+      <c r="AM234">
+        <v>1.72</v>
+      </c>
+      <c r="AN234">
+        <v>1.67</v>
+      </c>
+      <c r="AO234">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP234">
+        <v>1.62</v>
+      </c>
+      <c r="AQ234">
+        <v>0.71</v>
+      </c>
+      <c r="AR234">
+        <v>1.6</v>
+      </c>
+      <c r="AS234">
+        <v>1.21</v>
+      </c>
+      <c r="AT234">
+        <v>2.81</v>
+      </c>
+      <c r="AU234">
+        <v>6</v>
+      </c>
+      <c r="AV234">
+        <v>6</v>
+      </c>
+      <c r="AW234">
+        <v>11</v>
+      </c>
+      <c r="AX234">
+        <v>9</v>
+      </c>
+      <c r="AY234">
+        <v>22</v>
+      </c>
+      <c r="AZ234">
+        <v>18</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>6</v>
+      </c>
+      <c r="BD234">
+        <v>1.83</v>
+      </c>
+      <c r="BE234">
+        <v>6.75</v>
+      </c>
+      <c r="BF234">
+        <v>2.51</v>
+      </c>
+      <c r="BG234">
+        <v>1.15</v>
+      </c>
+      <c r="BH234">
+        <v>4.2</v>
+      </c>
+      <c r="BI234">
+        <v>1.32</v>
+      </c>
+      <c r="BJ234">
+        <v>2.88</v>
+      </c>
+      <c r="BK234">
+        <v>1.59</v>
+      </c>
+      <c r="BL234">
+        <v>2.16</v>
+      </c>
+      <c r="BM234">
+        <v>2</v>
+      </c>
+      <c r="BN234">
+        <v>1.72</v>
+      </c>
+      <c r="BO234">
+        <v>2.57</v>
+      </c>
+      <c r="BP234">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7491723</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>86</v>
+      </c>
+      <c r="H235" t="s">
+        <v>73</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>3</v>
+      </c>
+      <c r="K235">
+        <v>3</v>
+      </c>
+      <c r="L235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>5</v>
+      </c>
+      <c r="N235">
+        <v>6</v>
+      </c>
+      <c r="O235" t="s">
+        <v>247</v>
+      </c>
+      <c r="P235" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q235">
+        <v>3.6</v>
+      </c>
+      <c r="R235">
+        <v>2.25</v>
+      </c>
+      <c r="S235">
+        <v>2.75</v>
+      </c>
+      <c r="T235">
+        <v>1.33</v>
+      </c>
+      <c r="U235">
+        <v>3.25</v>
+      </c>
+      <c r="V235">
+        <v>2.63</v>
+      </c>
+      <c r="W235">
+        <v>1.44</v>
+      </c>
+      <c r="X235">
+        <v>6.5</v>
+      </c>
+      <c r="Y235">
+        <v>1.11</v>
+      </c>
+      <c r="Z235">
+        <v>3.28</v>
+      </c>
+      <c r="AA235">
+        <v>3.57</v>
+      </c>
+      <c r="AB235">
+        <v>2.22</v>
+      </c>
+      <c r="AC235">
+        <v>1.05</v>
+      </c>
+      <c r="AD235">
+        <v>9.5</v>
+      </c>
+      <c r="AE235">
+        <v>1.2</v>
+      </c>
+      <c r="AF235">
+        <v>3.82</v>
+      </c>
+      <c r="AG235">
+        <v>1.81</v>
+      </c>
+      <c r="AH235">
+        <v>2.01</v>
+      </c>
+      <c r="AI235">
+        <v>1.62</v>
+      </c>
+      <c r="AJ235">
+        <v>2.2</v>
+      </c>
+      <c r="AK235">
+        <v>1.68</v>
+      </c>
+      <c r="AL235">
+        <v>1.28</v>
+      </c>
+      <c r="AM235">
+        <v>1.36</v>
+      </c>
+      <c r="AN235">
+        <v>1.33</v>
+      </c>
+      <c r="AO235">
+        <v>1.38</v>
+      </c>
+      <c r="AP235">
+        <v>1.23</v>
+      </c>
+      <c r="AQ235">
+        <v>1.5</v>
+      </c>
+      <c r="AR235">
+        <v>1.38</v>
+      </c>
+      <c r="AS235">
+        <v>1.49</v>
+      </c>
+      <c r="AT235">
+        <v>2.87</v>
+      </c>
+      <c r="AU235">
+        <v>5</v>
+      </c>
+      <c r="AV235">
+        <v>14</v>
+      </c>
+      <c r="AW235">
+        <v>8</v>
+      </c>
+      <c r="AX235">
+        <v>3</v>
+      </c>
+      <c r="AY235">
+        <v>18</v>
+      </c>
+      <c r="AZ235">
+        <v>18</v>
+      </c>
+      <c r="BA235">
+        <v>4</v>
+      </c>
+      <c r="BB235">
+        <v>3</v>
+      </c>
+      <c r="BC235">
+        <v>7</v>
+      </c>
+      <c r="BD235">
+        <v>2.23</v>
+      </c>
+      <c r="BE235">
+        <v>6.65</v>
+      </c>
+      <c r="BF235">
+        <v>2.02</v>
+      </c>
+      <c r="BG235">
+        <v>1.15</v>
+      </c>
+      <c r="BH235">
+        <v>4.25</v>
+      </c>
+      <c r="BI235">
+        <v>1.32</v>
+      </c>
+      <c r="BJ235">
+        <v>2.88</v>
+      </c>
+      <c r="BK235">
+        <v>1.59</v>
+      </c>
+      <c r="BL235">
+        <v>2.16</v>
+      </c>
+      <c r="BM235">
+        <v>2</v>
+      </c>
+      <c r="BN235">
+        <v>1.72</v>
+      </c>
+      <c r="BO235">
+        <v>2.57</v>
+      </c>
+      <c r="BP235">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="373">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,9 @@
     <t>['90+1']</t>
   </si>
   <si>
+    <t>['50', '57']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1491,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1747,7 +1750,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1953,7 +1956,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2365,7 +2368,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2652,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2777,7 +2780,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2983,7 +2986,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3395,7 +3398,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3473,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>1.54</v>
@@ -3807,7 +3810,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4219,7 +4222,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4709,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -4837,7 +4840,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4918,7 +4921,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ17">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5043,7 +5046,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5455,7 +5458,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5536,7 +5539,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ20">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR20">
         <v>1.6</v>
@@ -6691,7 +6694,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6769,7 +6772,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>1.83</v>
@@ -6897,7 +6900,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7103,7 +7106,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7515,7 +7518,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7721,7 +7724,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7799,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -8008,7 +8011,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR32">
         <v>0.9399999999999999</v>
@@ -8133,7 +8136,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8339,7 +8342,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8751,7 +8754,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8957,7 +8960,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9163,7 +9166,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9575,7 +9578,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9781,7 +9784,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9859,7 +9862,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.15</v>
@@ -10193,7 +10196,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10480,7 +10483,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR44">
         <v>1.68</v>
@@ -10605,7 +10608,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10889,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.08</v>
@@ -11017,7 +11020,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11223,7 +11226,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11304,7 +11307,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ48">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>1.7</v>
@@ -11429,7 +11432,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11635,7 +11638,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12047,7 +12050,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12253,7 +12256,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12459,7 +12462,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12665,7 +12668,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12871,7 +12874,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12949,7 +12952,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>0.54</v>
@@ -13077,7 +13080,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13283,7 +13286,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13361,7 +13364,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>1.69</v>
@@ -13695,7 +13698,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13901,7 +13904,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14313,7 +14316,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14394,7 +14397,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ63">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR63">
         <v>1.36</v>
@@ -14519,7 +14522,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14931,7 +14934,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15012,7 +15015,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ66">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.63</v>
@@ -15549,7 +15552,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15755,7 +15758,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15961,7 +15964,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16373,7 +16376,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16991,7 +16994,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17072,7 +17075,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -17197,7 +17200,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17893,7 +17896,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>1.23</v>
@@ -18021,7 +18024,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18305,7 +18308,7 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>2.23</v>
@@ -18433,7 +18436,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18639,7 +18642,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18845,7 +18848,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -19051,7 +19054,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19257,7 +19260,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19463,7 +19466,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19669,7 +19672,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19875,7 +19878,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20571,7 +20574,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
         <v>1.23</v>
@@ -20780,7 +20783,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ94">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
         <v>1.29</v>
@@ -20905,7 +20908,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20986,7 +20989,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ95">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -21317,7 +21320,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21523,7 +21526,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22013,7 +22016,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1.15</v>
@@ -22141,7 +22144,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22759,7 +22762,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23171,7 +23174,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23377,7 +23380,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23995,7 +23998,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24407,7 +24410,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24613,7 +24616,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24819,7 +24822,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24900,7 +24903,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR114">
         <v>1.54</v>
@@ -25025,7 +25028,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25106,7 +25109,7 @@
         <v>2</v>
       </c>
       <c r="AQ115">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR115">
         <v>1.64</v>
@@ -25231,7 +25234,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25309,7 +25312,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>1.23</v>
@@ -25437,7 +25440,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25643,7 +25646,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25849,7 +25852,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -26055,7 +26058,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26261,7 +26264,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26467,7 +26470,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -27085,7 +27088,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27291,7 +27294,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27575,7 +27578,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
         <v>1.15</v>
@@ -27909,7 +27912,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28115,7 +28118,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28527,7 +28530,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28733,7 +28736,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28939,7 +28942,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29017,10 +29020,10 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR134">
         <v>1.67</v>
@@ -29351,7 +29354,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29557,7 +29560,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29763,7 +29766,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30175,7 +30178,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30459,7 +30462,7 @@
         <v>1.43</v>
       </c>
       <c r="AP141">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
         <v>1.62</v>
@@ -30587,7 +30590,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31205,7 +31208,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31286,7 +31289,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ145">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR145">
         <v>1.36</v>
@@ -31411,7 +31414,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31617,7 +31620,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31901,7 +31904,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
         <v>1.15</v>
@@ -32235,7 +32238,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32728,7 +32731,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ152">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR152">
         <v>1.2</v>
@@ -33059,7 +33062,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33265,7 +33268,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33346,7 +33349,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ155">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR155">
         <v>1.57</v>
@@ -34373,7 +34376,7 @@
         <v>2.13</v>
       </c>
       <c r="AP160">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ160">
         <v>1.77</v>
@@ -34501,7 +34504,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34707,7 +34710,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34913,7 +34916,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35119,7 +35122,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35325,7 +35328,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35612,7 +35615,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ166">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR166">
         <v>1.82</v>
@@ -35737,7 +35740,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36149,7 +36152,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36355,7 +36358,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36433,7 +36436,7 @@
         <v>0.13</v>
       </c>
       <c r="AP170">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
         <v>0.08</v>
@@ -36767,7 +36770,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37054,7 +37057,7 @@
         <v>2</v>
       </c>
       <c r="AQ173">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR173">
         <v>1.57</v>
@@ -37179,7 +37182,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37591,7 +37594,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37797,7 +37800,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -38003,7 +38006,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38209,7 +38212,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38415,7 +38418,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38621,7 +38624,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38699,7 +38702,7 @@
         <v>0.89</v>
       </c>
       <c r="AP181">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.23</v>
@@ -38827,7 +38830,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39239,7 +39242,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39320,7 +39323,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ184">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR184">
         <v>1.56</v>
@@ -39445,7 +39448,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39651,7 +39654,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39729,7 +39732,7 @@
         <v>1.7</v>
       </c>
       <c r="AP186">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ186">
         <v>1.69</v>
@@ -40269,7 +40272,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -41586,7 +41589,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ195">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR195">
         <v>1.27</v>
@@ -41711,7 +41714,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42613,7 +42616,7 @@
         <v>1.82</v>
       </c>
       <c r="AP200">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
         <v>1.54</v>
@@ -42947,7 +42950,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43231,10 +43234,10 @@
         <v>1.5</v>
       </c>
       <c r="AP203">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ203">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR203">
         <v>1.48</v>
@@ -43565,7 +43568,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -44389,7 +44392,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -45213,7 +45216,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45625,7 +45628,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -45706,7 +45709,7 @@
         <v>1</v>
       </c>
       <c r="AQ215">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR215">
         <v>1.76</v>
@@ -46449,7 +46452,7 @@
         <v>240</v>
       </c>
       <c r="P219" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q219">
         <v>2.85</v>
@@ -46530,7 +46533,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ219">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR219">
         <v>1.83</v>
@@ -46861,7 +46864,7 @@
         <v>119</v>
       </c>
       <c r="P221" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47145,7 +47148,7 @@
         <v>1.67</v>
       </c>
       <c r="AP222">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ222">
         <v>1.77</v>
@@ -47273,7 +47276,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47351,7 +47354,7 @@
         <v>2</v>
       </c>
       <c r="AP223">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ223">
         <v>1.83</v>
@@ -47479,7 +47482,7 @@
         <v>243</v>
       </c>
       <c r="P224" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q224">
         <v>2.2</v>
@@ -47685,7 +47688,7 @@
         <v>92</v>
       </c>
       <c r="P225" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q225">
         <v>3.4</v>
@@ -48097,7 +48100,7 @@
         <v>174</v>
       </c>
       <c r="P227" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q227">
         <v>3.1</v>
@@ -48303,7 +48306,7 @@
         <v>92</v>
       </c>
       <c r="P228" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48509,7 +48512,7 @@
         <v>92</v>
       </c>
       <c r="P229" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q229">
         <v>2.25</v>
@@ -48715,7 +48718,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q230">
         <v>2.4</v>
@@ -49208,7 +49211,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ232">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR232">
         <v>1.81</v>
@@ -49745,7 +49748,7 @@
         <v>247</v>
       </c>
       <c r="P235" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q235">
         <v>3.6</v>
@@ -49902,6 +49905,418 @@
       </c>
       <c r="BP235">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7491724</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45744.60416666666</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>84</v>
+      </c>
+      <c r="H236" t="s">
+        <v>82</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236" t="s">
+        <v>92</v>
+      </c>
+      <c r="P236" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q236">
+        <v>2.25</v>
+      </c>
+      <c r="R236">
+        <v>2.4</v>
+      </c>
+      <c r="S236">
+        <v>4.5</v>
+      </c>
+      <c r="T236">
+        <v>1.29</v>
+      </c>
+      <c r="U236">
+        <v>3.5</v>
+      </c>
+      <c r="V236">
+        <v>2.38</v>
+      </c>
+      <c r="W236">
+        <v>1.53</v>
+      </c>
+      <c r="X236">
+        <v>5.5</v>
+      </c>
+      <c r="Y236">
+        <v>1.14</v>
+      </c>
+      <c r="Z236">
+        <v>1.72</v>
+      </c>
+      <c r="AA236">
+        <v>4.2</v>
+      </c>
+      <c r="AB236">
+        <v>4.6</v>
+      </c>
+      <c r="AC236">
+        <v>1.04</v>
+      </c>
+      <c r="AD236">
+        <v>10</v>
+      </c>
+      <c r="AE236">
+        <v>1.18</v>
+      </c>
+      <c r="AF236">
+        <v>4.75</v>
+      </c>
+      <c r="AG236">
+        <v>1.53</v>
+      </c>
+      <c r="AH236">
+        <v>2.25</v>
+      </c>
+      <c r="AI236">
+        <v>1.57</v>
+      </c>
+      <c r="AJ236">
+        <v>2.25</v>
+      </c>
+      <c r="AK236">
+        <v>1.22</v>
+      </c>
+      <c r="AL236">
+        <v>1.23</v>
+      </c>
+      <c r="AM236">
+        <v>2.05</v>
+      </c>
+      <c r="AN236">
+        <v>2.08</v>
+      </c>
+      <c r="AO236">
+        <v>1.42</v>
+      </c>
+      <c r="AP236">
+        <v>2</v>
+      </c>
+      <c r="AQ236">
+        <v>1.38</v>
+      </c>
+      <c r="AR236">
+        <v>1.85</v>
+      </c>
+      <c r="AS236">
+        <v>1.35</v>
+      </c>
+      <c r="AT236">
+        <v>3.2</v>
+      </c>
+      <c r="AU236">
+        <v>3</v>
+      </c>
+      <c r="AV236">
+        <v>4</v>
+      </c>
+      <c r="AW236">
+        <v>12</v>
+      </c>
+      <c r="AX236">
+        <v>12</v>
+      </c>
+      <c r="AY236">
+        <v>18</v>
+      </c>
+      <c r="AZ236">
+        <v>19</v>
+      </c>
+      <c r="BA236">
+        <v>8</v>
+      </c>
+      <c r="BB236">
+        <v>4</v>
+      </c>
+      <c r="BC236">
+        <v>12</v>
+      </c>
+      <c r="BD236">
+        <v>1.58</v>
+      </c>
+      <c r="BE236">
+        <v>7.1</v>
+      </c>
+      <c r="BF236">
+        <v>3.12</v>
+      </c>
+      <c r="BG236">
+        <v>1.1</v>
+      </c>
+      <c r="BH236">
+        <v>5</v>
+      </c>
+      <c r="BI236">
+        <v>1.24</v>
+      </c>
+      <c r="BJ236">
+        <v>3.34</v>
+      </c>
+      <c r="BK236">
+        <v>1.46</v>
+      </c>
+      <c r="BL236">
+        <v>2.45</v>
+      </c>
+      <c r="BM236">
+        <v>1.79</v>
+      </c>
+      <c r="BN236">
+        <v>1.92</v>
+      </c>
+      <c r="BO236">
+        <v>2.23</v>
+      </c>
+      <c r="BP236">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7491730</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45744.60416666666</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>78</v>
+      </c>
+      <c r="H237" t="s">
+        <v>76</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>2</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>3</v>
+      </c>
+      <c r="O237" t="s">
+        <v>248</v>
+      </c>
+      <c r="P237" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q237">
+        <v>3.4</v>
+      </c>
+      <c r="R237">
+        <v>2.1</v>
+      </c>
+      <c r="S237">
+        <v>3.2</v>
+      </c>
+      <c r="T237">
+        <v>1.4</v>
+      </c>
+      <c r="U237">
+        <v>2.75</v>
+      </c>
+      <c r="V237">
+        <v>3</v>
+      </c>
+      <c r="W237">
+        <v>1.36</v>
+      </c>
+      <c r="X237">
+        <v>8</v>
+      </c>
+      <c r="Y237">
+        <v>1.08</v>
+      </c>
+      <c r="Z237">
+        <v>2.81</v>
+      </c>
+      <c r="AA237">
+        <v>3.45</v>
+      </c>
+      <c r="AB237">
+        <v>2.57</v>
+      </c>
+      <c r="AC237">
+        <v>1.06</v>
+      </c>
+      <c r="AD237">
+        <v>8.5</v>
+      </c>
+      <c r="AE237">
+        <v>1.33</v>
+      </c>
+      <c r="AF237">
+        <v>3.25</v>
+      </c>
+      <c r="AG237">
+        <v>1.94</v>
+      </c>
+      <c r="AH237">
+        <v>1.87</v>
+      </c>
+      <c r="AI237">
+        <v>1.73</v>
+      </c>
+      <c r="AJ237">
+        <v>2</v>
+      </c>
+      <c r="AK237">
+        <v>1.5</v>
+      </c>
+      <c r="AL237">
+        <v>1.31</v>
+      </c>
+      <c r="AM237">
+        <v>1.44</v>
+      </c>
+      <c r="AN237">
+        <v>0.83</v>
+      </c>
+      <c r="AO237">
+        <v>0.92</v>
+      </c>
+      <c r="AP237">
+        <v>1</v>
+      </c>
+      <c r="AQ237">
+        <v>0.86</v>
+      </c>
+      <c r="AR237">
+        <v>1.48</v>
+      </c>
+      <c r="AS237">
+        <v>1.62</v>
+      </c>
+      <c r="AT237">
+        <v>3.1</v>
+      </c>
+      <c r="AU237">
+        <v>5</v>
+      </c>
+      <c r="AV237">
+        <v>7</v>
+      </c>
+      <c r="AW237">
+        <v>7</v>
+      </c>
+      <c r="AX237">
+        <v>15</v>
+      </c>
+      <c r="AY237">
+        <v>15</v>
+      </c>
+      <c r="AZ237">
+        <v>26</v>
+      </c>
+      <c r="BA237">
+        <v>5</v>
+      </c>
+      <c r="BB237">
+        <v>4</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
+        <v>1.89</v>
+      </c>
+      <c r="BE237">
+        <v>6.7</v>
+      </c>
+      <c r="BF237">
+        <v>2.41</v>
+      </c>
+      <c r="BG237">
+        <v>1.17</v>
+      </c>
+      <c r="BH237">
+        <v>4.05</v>
+      </c>
+      <c r="BI237">
+        <v>1.34</v>
+      </c>
+      <c r="BJ237">
+        <v>2.78</v>
+      </c>
+      <c r="BK237">
+        <v>1.63</v>
+      </c>
+      <c r="BL237">
+        <v>2.09</v>
+      </c>
+      <c r="BM237">
+        <v>2.07</v>
+      </c>
+      <c r="BN237">
+        <v>1.67</v>
+      </c>
+      <c r="BO237">
+        <v>2.67</v>
+      </c>
+      <c r="BP237">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -763,6 +763,18 @@
     <t>['50', '57']</t>
   </si>
   <si>
+    <t>['16', '47', '89']</t>
+  </si>
+  <si>
+    <t>['14', '73', '90+3']</t>
+  </si>
+  <si>
+    <t>['11', '26', '54']</t>
+  </si>
+  <si>
+    <t>['47', '55']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1134,6 +1146,15 @@
   <si>
     <t>['7', '42', '44', '69', '90+3']</t>
   </si>
+  <si>
+    <t>['42', '61']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['9', '84', '90+5']</t>
+  </si>
 </sst>
 </file>
 
@@ -1494,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP237"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1750,7 +1771,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1956,7 +1977,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2037,7 +2058,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2240,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ4">
         <v>0.08</v>
@@ -2368,7 +2389,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2446,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ5">
         <v>1.69</v>
@@ -2780,7 +2801,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2861,7 +2882,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ7">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2986,7 +3007,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3067,7 +3088,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ8">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3270,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3398,7 +3419,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3682,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11">
         <v>0.71</v>
@@ -3810,7 +3831,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3888,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12">
         <v>1.15</v>
@@ -4097,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4222,7 +4243,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4303,7 +4324,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ14">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4509,7 +4530,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ15">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4840,7 +4861,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4918,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ17">
         <v>0.86</v>
@@ -5046,7 +5067,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5127,7 +5148,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ18">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5458,7 +5479,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5742,7 +5763,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21">
         <v>1.62</v>
@@ -6154,7 +6175,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ23">
         <v>1.69</v>
@@ -6360,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ24">
         <v>0.08</v>
@@ -6569,7 +6590,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ25">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR25">
         <v>2.21</v>
@@ -6694,7 +6715,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6775,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR26">
         <v>1.22</v>
@@ -6900,7 +6921,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6981,7 +7002,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ27">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR27">
         <v>1.43</v>
@@ -7106,7 +7127,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7187,7 +7208,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR28">
         <v>1.96</v>
@@ -7518,7 +7539,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7596,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30">
         <v>1.15</v>
@@ -7724,7 +7745,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8136,7 +8157,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8217,7 +8238,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR33">
         <v>1.09</v>
@@ -8342,7 +8363,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8420,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ34">
         <v>1.5</v>
@@ -8626,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ35">
         <v>0.71</v>
@@ -8754,7 +8775,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8835,7 +8856,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ36">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8960,7 +8981,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9041,7 +9062,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ37">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR37">
         <v>2.14</v>
@@ -9166,7 +9187,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9453,7 +9474,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ39">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR39">
         <v>1.65</v>
@@ -9578,7 +9599,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9656,7 +9677,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ40">
         <v>1.54</v>
@@ -9784,7 +9805,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9865,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.64</v>
@@ -10071,7 +10092,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ42">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR42">
         <v>1.72</v>
@@ -10196,7 +10217,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10277,7 +10298,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ43">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR43">
         <v>2.41</v>
@@ -10480,7 +10501,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44">
         <v>1.38</v>
@@ -10608,7 +10629,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10686,10 +10707,10 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ45">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR45">
         <v>1.24</v>
@@ -11020,7 +11041,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11098,7 +11119,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
         <v>1.23</v>
@@ -11226,7 +11247,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11432,7 +11453,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11513,7 +11534,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ49">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11638,7 +11659,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12050,7 +12071,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12128,7 +12149,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
         <v>1.62</v>
@@ -12256,7 +12277,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12462,7 +12483,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12543,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR54">
         <v>1.87</v>
@@ -12668,7 +12689,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12746,7 +12767,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12874,7 +12895,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12955,7 +12976,7 @@
         <v>1</v>
       </c>
       <c r="AQ56">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -13080,7 +13101,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13158,10 +13179,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13286,7 +13307,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13570,7 +13591,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ59">
         <v>1.54</v>
@@ -13698,7 +13719,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13779,7 +13800,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ60">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13904,7 +13925,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13985,7 +14006,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR61">
         <v>1.4</v>
@@ -14188,10 +14209,10 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ62">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR62">
         <v>1.64</v>
@@ -14316,7 +14337,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14394,7 +14415,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ63">
         <v>1.38</v>
@@ -14522,7 +14543,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14603,7 +14624,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ64">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR64">
         <v>2.51</v>
@@ -14806,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
         <v>0.08</v>
@@ -14934,7 +14955,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15552,7 +15573,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15758,7 +15779,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15964,7 +15985,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16376,7 +16397,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16663,7 +16684,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16866,10 +16887,10 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ75">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16994,7 +17015,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17200,7 +17221,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17278,10 +17299,10 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR77">
         <v>1.26</v>
@@ -17484,10 +17505,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ78">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17690,7 +17711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ79">
         <v>1.69</v>
@@ -17899,7 +17920,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR80">
         <v>1.52</v>
@@ -18024,7 +18045,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18102,10 +18123,10 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ81">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR81">
         <v>1.41</v>
@@ -18311,7 +18332,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR82">
         <v>1.62</v>
@@ -18436,7 +18457,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18642,7 +18663,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18848,7 +18869,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -19054,7 +19075,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19260,7 +19281,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19466,7 +19487,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19672,7 +19693,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19878,7 +19899,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20371,7 +20392,7 @@
         <v>1</v>
       </c>
       <c r="AQ92">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR92">
         <v>1.28</v>
@@ -20577,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR93">
         <v>1.52</v>
@@ -20780,7 +20801,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ94">
         <v>1.38</v>
@@ -20908,7 +20929,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20986,7 +21007,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
         <v>0.86</v>
@@ -21192,10 +21213,10 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ96">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR96">
         <v>1.59</v>
@@ -21320,7 +21341,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21398,10 +21419,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ97">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21526,7 +21547,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21604,10 +21625,10 @@
         <v>2.4</v>
       </c>
       <c r="AP98">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR98">
         <v>1.68</v>
@@ -21810,10 +21831,10 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ99">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR99">
         <v>1.63</v>
@@ -22019,7 +22040,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR100">
         <v>1.62</v>
@@ -22144,7 +22165,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22762,7 +22783,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23174,7 +23195,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23380,7 +23401,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23998,7 +24019,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24076,10 +24097,10 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ110">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR110">
         <v>1.5</v>
@@ -24285,7 +24306,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR111">
         <v>1.23</v>
@@ -24410,7 +24431,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24488,10 +24509,10 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ112">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24616,7 +24637,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24694,7 +24715,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ113">
         <v>0.71</v>
@@ -24822,7 +24843,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -25028,7 +25049,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25106,7 +25127,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ115">
         <v>0.86</v>
@@ -25234,7 +25255,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25315,7 +25336,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25440,7 +25461,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25518,10 +25539,10 @@
         <v>0.33</v>
       </c>
       <c r="AP117">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ117">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR117">
         <v>1.79</v>
@@ -25646,7 +25667,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25724,10 +25745,10 @@
         <v>2.17</v>
       </c>
       <c r="AP118">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ118">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR118">
         <v>1.21</v>
@@ -25852,7 +25873,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -26058,7 +26079,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26264,7 +26285,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26470,7 +26491,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -27088,7 +27109,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27294,7 +27315,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27375,7 +27396,7 @@
         <v>2</v>
       </c>
       <c r="AQ126">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27787,7 +27808,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ128">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -27912,7 +27933,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27990,10 +28011,10 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ129">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>1.5</v>
@@ -28118,7 +28139,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28196,10 +28217,10 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ130">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR130">
         <v>1.78</v>
@@ -28402,7 +28423,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ131">
         <v>1.5</v>
@@ -28530,7 +28551,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28608,7 +28629,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ132">
         <v>0.71</v>
@@ -28736,7 +28757,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28817,7 +28838,7 @@
         <v>1</v>
       </c>
       <c r="AQ133">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR133">
         <v>1.17</v>
@@ -28942,7 +28963,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29229,7 +29250,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ135">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR135">
         <v>1.54</v>
@@ -29354,7 +29375,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29432,10 +29453,10 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ136">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29560,7 +29581,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29766,7 +29787,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29844,7 +29865,7 @@
         <v>0.86</v>
       </c>
       <c r="AP138">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30053,7 +30074,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ139">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR139">
         <v>1.49</v>
@@ -30178,7 +30199,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30590,7 +30611,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30877,7 +30898,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ143">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR143">
         <v>1.88</v>
@@ -31080,7 +31101,7 @@
         <v>0.71</v>
       </c>
       <c r="AP144">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ144">
         <v>1.23</v>
@@ -31208,7 +31229,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31414,7 +31435,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31495,7 +31516,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ146">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR146">
         <v>1.51</v>
@@ -31620,7 +31641,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31701,7 +31722,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ147">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -32238,7 +32259,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32316,10 +32337,10 @@
         <v>1.5</v>
       </c>
       <c r="AP150">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ150">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32525,7 +32546,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR151">
         <v>1.49</v>
@@ -32728,7 +32749,7 @@
         <v>1.57</v>
       </c>
       <c r="AP152">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ152">
         <v>0.86</v>
@@ -32934,7 +32955,7 @@
         <v>1.75</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ153">
         <v>1.5</v>
@@ -33062,7 +33083,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33140,10 +33161,10 @@
         <v>2</v>
       </c>
       <c r="AP154">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ154">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR154">
         <v>1.69</v>
@@ -33268,7 +33289,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33552,7 +33573,7 @@
         <v>0.63</v>
       </c>
       <c r="AP156">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ156">
         <v>1.23</v>
@@ -33758,7 +33779,7 @@
         <v>0.89</v>
       </c>
       <c r="AP157">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ157">
         <v>0.71</v>
@@ -33967,7 +33988,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ158">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR158">
         <v>1.3</v>
@@ -34379,7 +34400,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR160">
         <v>1.75</v>
@@ -34504,7 +34525,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34582,7 +34603,7 @@
         <v>1.67</v>
       </c>
       <c r="AP161">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ161">
         <v>1.5</v>
@@ -34710,7 +34731,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34791,7 +34812,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ162">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR162">
         <v>1.5</v>
@@ -34916,7 +34937,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34997,7 +35018,7 @@
         <v>2</v>
       </c>
       <c r="AQ163">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35122,7 +35143,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35203,7 +35224,7 @@
         <v>1</v>
       </c>
       <c r="AQ164">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR164">
         <v>1.62</v>
@@ -35328,7 +35349,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35406,7 +35427,7 @@
         <v>1.56</v>
       </c>
       <c r="AP165">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ165">
         <v>1.54</v>
@@ -35740,7 +35761,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35821,7 +35842,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ167">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR167">
         <v>1.61</v>
@@ -36027,7 +36048,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ168">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR168">
         <v>1.59</v>
@@ -36152,7 +36173,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36230,7 +36251,7 @@
         <v>1.38</v>
       </c>
       <c r="AP169">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ169">
         <v>1.62</v>
@@ -36358,7 +36379,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36770,7 +36791,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36848,7 +36869,7 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37182,7 +37203,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37263,7 +37284,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ174">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR174">
         <v>1.47</v>
@@ -37466,7 +37487,7 @@
         <v>1.8</v>
       </c>
       <c r="AP175">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ175">
         <v>1.5</v>
@@ -37594,7 +37615,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37675,7 +37696,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ176">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37800,7 +37821,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -38006,7 +38027,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38087,7 +38108,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ178">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR178">
         <v>1.59</v>
@@ -38212,7 +38233,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38290,7 +38311,7 @@
         <v>1</v>
       </c>
       <c r="AP179">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ179">
         <v>1.15</v>
@@ -38418,7 +38439,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38496,7 +38517,7 @@
         <v>1.11</v>
       </c>
       <c r="AP180">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -38624,7 +38645,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38830,7 +38851,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39114,7 +39135,7 @@
         <v>0.11</v>
       </c>
       <c r="AP183">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ183">
         <v>0.08</v>
@@ -39242,7 +39263,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39448,7 +39469,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39529,7 +39550,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR185">
         <v>1.66</v>
@@ -39654,7 +39675,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39938,7 +39959,7 @@
         <v>1.7</v>
       </c>
       <c r="AP187">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ187">
         <v>1.54</v>
@@ -40147,7 +40168,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ188">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR188">
         <v>1.83</v>
@@ -40272,7 +40293,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40353,7 +40374,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR189">
         <v>1.59</v>
@@ -40556,10 +40577,10 @@
         <v>2.22</v>
       </c>
       <c r="AP190">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ190">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR190">
         <v>1.76</v>
@@ -40765,7 +40786,7 @@
         <v>1</v>
       </c>
       <c r="AQ191">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR191">
         <v>1.77</v>
@@ -40968,7 +40989,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ192">
         <v>1</v>
@@ -41380,7 +41401,7 @@
         <v>0.9</v>
       </c>
       <c r="AP194">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ194">
         <v>1.23</v>
@@ -41714,7 +41735,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -41998,7 +42019,7 @@
         <v>1.7</v>
       </c>
       <c r="AP197">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ197">
         <v>1.62</v>
@@ -42207,7 +42228,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ198">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR198">
         <v>1.64</v>
@@ -42822,10 +42843,10 @@
         <v>1</v>
       </c>
       <c r="AP201">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ201">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR201">
         <v>1.48</v>
@@ -42950,7 +42971,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43031,7 +43052,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ202">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR202">
         <v>1.71</v>
@@ -43568,7 +43589,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43646,7 +43667,7 @@
         <v>1.82</v>
       </c>
       <c r="AP205">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ205">
         <v>1.69</v>
@@ -43855,7 +43876,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ206">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR206">
         <v>1.8</v>
@@ -44061,7 +44082,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ207">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR207">
         <v>1.55</v>
@@ -44264,10 +44285,10 @@
         <v>0.55</v>
       </c>
       <c r="AP208">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ208">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44392,7 +44413,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -45088,7 +45109,7 @@
         <v>0.09</v>
       </c>
       <c r="AP212">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ212">
         <v>0.08</v>
@@ -45216,7 +45237,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45503,7 +45524,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ214">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR214">
         <v>1.66</v>
@@ -45628,7 +45649,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -46118,7 +46139,7 @@
         <v>1.64</v>
       </c>
       <c r="AP217">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ217">
         <v>1.62</v>
@@ -46327,7 +46348,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ218">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR218">
         <v>1.53</v>
@@ -46452,7 +46473,7 @@
         <v>240</v>
       </c>
       <c r="P219" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q219">
         <v>2.85</v>
@@ -46530,7 +46551,7 @@
         <v>1.45</v>
       </c>
       <c r="AP219">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ219">
         <v>1.38</v>
@@ -46736,10 +46757,10 @@
         <v>2.33</v>
       </c>
       <c r="AP220">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ220">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR220">
         <v>1.53</v>
@@ -46864,7 +46885,7 @@
         <v>119</v>
       </c>
       <c r="P221" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -46942,10 +46963,10 @@
         <v>1.08</v>
       </c>
       <c r="AP221">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ221">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR221">
         <v>1.51</v>
@@ -47151,7 +47172,7 @@
         <v>1</v>
       </c>
       <c r="AQ222">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR222">
         <v>1.49</v>
@@ -47276,7 +47297,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47357,7 +47378,7 @@
         <v>2</v>
       </c>
       <c r="AQ223">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR223">
         <v>1.8</v>
@@ -47482,7 +47503,7 @@
         <v>243</v>
       </c>
       <c r="P224" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q224">
         <v>2.2</v>
@@ -47560,10 +47581,10 @@
         <v>0.5</v>
       </c>
       <c r="AP224">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ224">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR224">
         <v>1.65</v>
@@ -47688,7 +47709,7 @@
         <v>92</v>
       </c>
       <c r="P225" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q225">
         <v>3.4</v>
@@ -47769,7 +47790,7 @@
         <v>1</v>
       </c>
       <c r="AQ225">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR225">
         <v>1.24</v>
@@ -47972,7 +47993,7 @@
         <v>1.75</v>
       </c>
       <c r="AP226">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ226">
         <v>1.69</v>
@@ -48100,7 +48121,7 @@
         <v>174</v>
       </c>
       <c r="P227" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q227">
         <v>3.1</v>
@@ -48306,7 +48327,7 @@
         <v>92</v>
       </c>
       <c r="P228" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48512,7 +48533,7 @@
         <v>92</v>
       </c>
       <c r="P229" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q229">
         <v>2.25</v>
@@ -48718,7 +48739,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q230">
         <v>2.4</v>
@@ -48796,7 +48817,7 @@
         <v>1.67</v>
       </c>
       <c r="AP230">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ230">
         <v>1.54</v>
@@ -49748,7 +49769,7 @@
         <v>247</v>
       </c>
       <c r="P235" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q235">
         <v>3.6</v>
@@ -50317,6 +50338,1448 @@
       </c>
       <c r="BP237">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7491725</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45745.375</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>72</v>
+      </c>
+      <c r="H238" t="s">
+        <v>74</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238" t="s">
+        <v>92</v>
+      </c>
+      <c r="P238" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q238">
+        <v>2.88</v>
+      </c>
+      <c r="R238">
+        <v>2.38</v>
+      </c>
+      <c r="S238">
+        <v>3.25</v>
+      </c>
+      <c r="T238">
+        <v>1.3</v>
+      </c>
+      <c r="U238">
+        <v>3.4</v>
+      </c>
+      <c r="V238">
+        <v>2.38</v>
+      </c>
+      <c r="W238">
+        <v>1.53</v>
+      </c>
+      <c r="X238">
+        <v>6</v>
+      </c>
+      <c r="Y238">
+        <v>1.13</v>
+      </c>
+      <c r="Z238">
+        <v>2.3</v>
+      </c>
+      <c r="AA238">
+        <v>3.75</v>
+      </c>
+      <c r="AB238">
+        <v>2.99</v>
+      </c>
+      <c r="AC238">
+        <v>1.04</v>
+      </c>
+      <c r="AD238">
+        <v>10</v>
+      </c>
+      <c r="AE238">
+        <v>1.2</v>
+      </c>
+      <c r="AF238">
+        <v>4.33</v>
+      </c>
+      <c r="AG238">
+        <v>1.55</v>
+      </c>
+      <c r="AH238">
+        <v>2.2</v>
+      </c>
+      <c r="AI238">
+        <v>1.5</v>
+      </c>
+      <c r="AJ238">
+        <v>2.5</v>
+      </c>
+      <c r="AK238">
+        <v>1.42</v>
+      </c>
+      <c r="AL238">
+        <v>1.26</v>
+      </c>
+      <c r="AM238">
+        <v>1.58</v>
+      </c>
+      <c r="AN238">
+        <v>2</v>
+      </c>
+      <c r="AO238">
+        <v>2.23</v>
+      </c>
+      <c r="AP238">
+        <v>1.93</v>
+      </c>
+      <c r="AQ238">
+        <v>2.14</v>
+      </c>
+      <c r="AR238">
+        <v>1.65</v>
+      </c>
+      <c r="AS238">
+        <v>1.53</v>
+      </c>
+      <c r="AT238">
+        <v>3.18</v>
+      </c>
+      <c r="AU238">
+        <v>3</v>
+      </c>
+      <c r="AV238">
+        <v>4</v>
+      </c>
+      <c r="AW238">
+        <v>12</v>
+      </c>
+      <c r="AX238">
+        <v>10</v>
+      </c>
+      <c r="AY238">
+        <v>19</v>
+      </c>
+      <c r="AZ238">
+        <v>17</v>
+      </c>
+      <c r="BA238">
+        <v>12</v>
+      </c>
+      <c r="BB238">
+        <v>5</v>
+      </c>
+      <c r="BC238">
+        <v>17</v>
+      </c>
+      <c r="BD238">
+        <v>1.74</v>
+      </c>
+      <c r="BE238">
+        <v>6.8</v>
+      </c>
+      <c r="BF238">
+        <v>2.69</v>
+      </c>
+      <c r="BG238">
+        <v>1.14</v>
+      </c>
+      <c r="BH238">
+        <v>4.45</v>
+      </c>
+      <c r="BI238">
+        <v>1.29</v>
+      </c>
+      <c r="BJ238">
+        <v>3.04</v>
+      </c>
+      <c r="BK238">
+        <v>1.54</v>
+      </c>
+      <c r="BL238">
+        <v>2.25</v>
+      </c>
+      <c r="BM238">
+        <v>1.93</v>
+      </c>
+      <c r="BN238">
+        <v>1.78</v>
+      </c>
+      <c r="BO238">
+        <v>2.45</v>
+      </c>
+      <c r="BP238">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7491726</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45745.375</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>85</v>
+      </c>
+      <c r="H239" t="s">
+        <v>70</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>2</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>96</v>
+      </c>
+      <c r="P239" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q239">
+        <v>3</v>
+      </c>
+      <c r="R239">
+        <v>2.1</v>
+      </c>
+      <c r="S239">
+        <v>3.6</v>
+      </c>
+      <c r="T239">
+        <v>1.4</v>
+      </c>
+      <c r="U239">
+        <v>2.75</v>
+      </c>
+      <c r="V239">
+        <v>3</v>
+      </c>
+      <c r="W239">
+        <v>1.36</v>
+      </c>
+      <c r="X239">
+        <v>8</v>
+      </c>
+      <c r="Y239">
+        <v>1.08</v>
+      </c>
+      <c r="Z239">
+        <v>2.32</v>
+      </c>
+      <c r="AA239">
+        <v>3.59</v>
+      </c>
+      <c r="AB239">
+        <v>3.08</v>
+      </c>
+      <c r="AC239">
+        <v>1.05</v>
+      </c>
+      <c r="AD239">
+        <v>9</v>
+      </c>
+      <c r="AE239">
+        <v>1.3</v>
+      </c>
+      <c r="AF239">
+        <v>3.4</v>
+      </c>
+      <c r="AG239">
+        <v>1.94</v>
+      </c>
+      <c r="AH239">
+        <v>1.87</v>
+      </c>
+      <c r="AI239">
+        <v>1.73</v>
+      </c>
+      <c r="AJ239">
+        <v>2</v>
+      </c>
+      <c r="AK239">
+        <v>1.38</v>
+      </c>
+      <c r="AL239">
+        <v>1.3</v>
+      </c>
+      <c r="AM239">
+        <v>1.58</v>
+      </c>
+      <c r="AN239">
+        <v>1.77</v>
+      </c>
+      <c r="AO239">
+        <v>1.77</v>
+      </c>
+      <c r="AP239">
+        <v>1.64</v>
+      </c>
+      <c r="AQ239">
+        <v>1.86</v>
+      </c>
+      <c r="AR239">
+        <v>1.7</v>
+      </c>
+      <c r="AS239">
+        <v>1.53</v>
+      </c>
+      <c r="AT239">
+        <v>3.23</v>
+      </c>
+      <c r="AU239">
+        <v>9</v>
+      </c>
+      <c r="AV239">
+        <v>7</v>
+      </c>
+      <c r="AW239">
+        <v>14</v>
+      </c>
+      <c r="AX239">
+        <v>11</v>
+      </c>
+      <c r="AY239">
+        <v>28</v>
+      </c>
+      <c r="AZ239">
+        <v>20</v>
+      </c>
+      <c r="BA239">
+        <v>6</v>
+      </c>
+      <c r="BB239">
+        <v>6</v>
+      </c>
+      <c r="BC239">
+        <v>12</v>
+      </c>
+      <c r="BD239">
+        <v>1.69</v>
+      </c>
+      <c r="BE239">
+        <v>7.1</v>
+      </c>
+      <c r="BF239">
+        <v>2.77</v>
+      </c>
+      <c r="BG239">
+        <v>1.09</v>
+      </c>
+      <c r="BH239">
+        <v>5.3</v>
+      </c>
+      <c r="BI239">
+        <v>1.21</v>
+      </c>
+      <c r="BJ239">
+        <v>3.58</v>
+      </c>
+      <c r="BK239">
+        <v>1.42</v>
+      </c>
+      <c r="BL239">
+        <v>2.57</v>
+      </c>
+      <c r="BM239">
+        <v>1.73</v>
+      </c>
+      <c r="BN239">
+        <v>1.99</v>
+      </c>
+      <c r="BO239">
+        <v>2.14</v>
+      </c>
+      <c r="BP239">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7491728</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45745.375</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>73</v>
+      </c>
+      <c r="H240" t="s">
+        <v>71</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>3</v>
+      </c>
+      <c r="M240">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>4</v>
+      </c>
+      <c r="O240" t="s">
+        <v>249</v>
+      </c>
+      <c r="P240" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q240">
+        <v>2.3</v>
+      </c>
+      <c r="R240">
+        <v>2.4</v>
+      </c>
+      <c r="S240">
+        <v>4.33</v>
+      </c>
+      <c r="T240">
+        <v>1.29</v>
+      </c>
+      <c r="U240">
+        <v>3.5</v>
+      </c>
+      <c r="V240">
+        <v>2.38</v>
+      </c>
+      <c r="W240">
+        <v>1.53</v>
+      </c>
+      <c r="X240">
+        <v>5.5</v>
+      </c>
+      <c r="Y240">
+        <v>1.14</v>
+      </c>
+      <c r="Z240">
+        <v>1.78</v>
+      </c>
+      <c r="AA240">
+        <v>4</v>
+      </c>
+      <c r="AB240">
+        <v>4.5</v>
+      </c>
+      <c r="AC240">
+        <v>1.03</v>
+      </c>
+      <c r="AD240">
+        <v>11</v>
+      </c>
+      <c r="AE240">
+        <v>1.18</v>
+      </c>
+      <c r="AF240">
+        <v>4.75</v>
+      </c>
+      <c r="AG240">
+        <v>1.58</v>
+      </c>
+      <c r="AH240">
+        <v>2.38</v>
+      </c>
+      <c r="AI240">
+        <v>1.57</v>
+      </c>
+      <c r="AJ240">
+        <v>2.25</v>
+      </c>
+      <c r="AK240">
+        <v>1.23</v>
+      </c>
+      <c r="AL240">
+        <v>1.23</v>
+      </c>
+      <c r="AM240">
+        <v>2</v>
+      </c>
+      <c r="AN240">
+        <v>0.67</v>
+      </c>
+      <c r="AO240">
+        <v>1.23</v>
+      </c>
+      <c r="AP240">
+        <v>0.85</v>
+      </c>
+      <c r="AQ240">
+        <v>1.14</v>
+      </c>
+      <c r="AR240">
+        <v>1.53</v>
+      </c>
+      <c r="AS240">
+        <v>1.24</v>
+      </c>
+      <c r="AT240">
+        <v>2.77</v>
+      </c>
+      <c r="AU240">
+        <v>5</v>
+      </c>
+      <c r="AV240">
+        <v>4</v>
+      </c>
+      <c r="AW240">
+        <v>12</v>
+      </c>
+      <c r="AX240">
+        <v>10</v>
+      </c>
+      <c r="AY240">
+        <v>21</v>
+      </c>
+      <c r="AZ240">
+        <v>18</v>
+      </c>
+      <c r="BA240">
+        <v>4</v>
+      </c>
+      <c r="BB240">
+        <v>5</v>
+      </c>
+      <c r="BC240">
+        <v>9</v>
+      </c>
+      <c r="BD240">
+        <v>1.63</v>
+      </c>
+      <c r="BE240">
+        <v>9.1</v>
+      </c>
+      <c r="BF240">
+        <v>2.7</v>
+      </c>
+      <c r="BG240">
+        <v>1.13</v>
+      </c>
+      <c r="BH240">
+        <v>4.5</v>
+      </c>
+      <c r="BI240">
+        <v>1.28</v>
+      </c>
+      <c r="BJ240">
+        <v>3.05</v>
+      </c>
+      <c r="BK240">
+        <v>1.54</v>
+      </c>
+      <c r="BL240">
+        <v>2.25</v>
+      </c>
+      <c r="BM240">
+        <v>1.92</v>
+      </c>
+      <c r="BN240">
+        <v>1.79</v>
+      </c>
+      <c r="BO240">
+        <v>2.45</v>
+      </c>
+      <c r="BP240">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7491729</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45745.6875</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>80</v>
+      </c>
+      <c r="H241" t="s">
+        <v>83</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>3</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>4</v>
+      </c>
+      <c r="O241" t="s">
+        <v>250</v>
+      </c>
+      <c r="P241" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q241">
+        <v>2.75</v>
+      </c>
+      <c r="R241">
+        <v>2.3</v>
+      </c>
+      <c r="S241">
+        <v>3.5</v>
+      </c>
+      <c r="T241">
+        <v>1.3</v>
+      </c>
+      <c r="U241">
+        <v>3.4</v>
+      </c>
+      <c r="V241">
+        <v>2.5</v>
+      </c>
+      <c r="W241">
+        <v>1.5</v>
+      </c>
+      <c r="X241">
+        <v>6</v>
+      </c>
+      <c r="Y241">
+        <v>1.13</v>
+      </c>
+      <c r="Z241">
+        <v>2.32</v>
+      </c>
+      <c r="AA241">
+        <v>3.79</v>
+      </c>
+      <c r="AB241">
+        <v>2.94</v>
+      </c>
+      <c r="AC241">
+        <v>1.04</v>
+      </c>
+      <c r="AD241">
+        <v>10</v>
+      </c>
+      <c r="AE241">
+        <v>1.22</v>
+      </c>
+      <c r="AF241">
+        <v>4.2</v>
+      </c>
+      <c r="AG241">
+        <v>1.6</v>
+      </c>
+      <c r="AH241">
+        <v>2.1</v>
+      </c>
+      <c r="AI241">
+        <v>1.53</v>
+      </c>
+      <c r="AJ241">
+        <v>2.38</v>
+      </c>
+      <c r="AK241">
+        <v>1.4</v>
+      </c>
+      <c r="AL241">
+        <v>1.26</v>
+      </c>
+      <c r="AM241">
+        <v>1.62</v>
+      </c>
+      <c r="AN241">
+        <v>1.77</v>
+      </c>
+      <c r="AO241">
+        <v>1.83</v>
+      </c>
+      <c r="AP241">
+        <v>1.86</v>
+      </c>
+      <c r="AQ241">
+        <v>1.69</v>
+      </c>
+      <c r="AR241">
+        <v>1.78</v>
+      </c>
+      <c r="AS241">
+        <v>1.28</v>
+      </c>
+      <c r="AT241">
+        <v>3.06</v>
+      </c>
+      <c r="AU241">
+        <v>8</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>7</v>
+      </c>
+      <c r="AX241">
+        <v>4</v>
+      </c>
+      <c r="AY241">
+        <v>17</v>
+      </c>
+      <c r="AZ241">
+        <v>11</v>
+      </c>
+      <c r="BA241">
+        <v>5</v>
+      </c>
+      <c r="BB241">
+        <v>5</v>
+      </c>
+      <c r="BC241">
+        <v>10</v>
+      </c>
+      <c r="BD241">
+        <v>1.76</v>
+      </c>
+      <c r="BE241">
+        <v>6.9</v>
+      </c>
+      <c r="BF241">
+        <v>2.63</v>
+      </c>
+      <c r="BG241">
+        <v>1.11</v>
+      </c>
+      <c r="BH241">
+        <v>4.85</v>
+      </c>
+      <c r="BI241">
+        <v>1.25</v>
+      </c>
+      <c r="BJ241">
+        <v>3.28</v>
+      </c>
+      <c r="BK241">
+        <v>1.48</v>
+      </c>
+      <c r="BL241">
+        <v>2.4</v>
+      </c>
+      <c r="BM241">
+        <v>1.83</v>
+      </c>
+      <c r="BN241">
+        <v>1.87</v>
+      </c>
+      <c r="BO241">
+        <v>2.3</v>
+      </c>
+      <c r="BP241">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7491727</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45746.35416666666</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>77</v>
+      </c>
+      <c r="H242" t="s">
+        <v>75</v>
+      </c>
+      <c r="I242">
+        <v>2</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>3</v>
+      </c>
+      <c r="L242">
+        <v>3</v>
+      </c>
+      <c r="M242">
+        <v>3</v>
+      </c>
+      <c r="N242">
+        <v>6</v>
+      </c>
+      <c r="O242" t="s">
+        <v>251</v>
+      </c>
+      <c r="P242" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q242">
+        <v>3.1</v>
+      </c>
+      <c r="R242">
+        <v>2.25</v>
+      </c>
+      <c r="S242">
+        <v>3.2</v>
+      </c>
+      <c r="T242">
+        <v>1.36</v>
+      </c>
+      <c r="U242">
+        <v>3</v>
+      </c>
+      <c r="V242">
+        <v>2.63</v>
+      </c>
+      <c r="W242">
+        <v>1.44</v>
+      </c>
+      <c r="X242">
+        <v>7</v>
+      </c>
+      <c r="Y242">
+        <v>1.1</v>
+      </c>
+      <c r="Z242">
+        <v>2.62</v>
+      </c>
+      <c r="AA242">
+        <v>3.41</v>
+      </c>
+      <c r="AB242">
+        <v>2.77</v>
+      </c>
+      <c r="AC242">
+        <v>1.05</v>
+      </c>
+      <c r="AD242">
+        <v>9.5</v>
+      </c>
+      <c r="AE242">
+        <v>1.25</v>
+      </c>
+      <c r="AF242">
+        <v>3.8</v>
+      </c>
+      <c r="AG242">
+        <v>1.65</v>
+      </c>
+      <c r="AH242">
+        <v>2</v>
+      </c>
+      <c r="AI242">
+        <v>1.62</v>
+      </c>
+      <c r="AJ242">
+        <v>2.2</v>
+      </c>
+      <c r="AK242">
+        <v>1.46</v>
+      </c>
+      <c r="AL242">
+        <v>1.28</v>
+      </c>
+      <c r="AM242">
+        <v>1.52</v>
+      </c>
+      <c r="AN242">
+        <v>1.38</v>
+      </c>
+      <c r="AO242">
+        <v>1.23</v>
+      </c>
+      <c r="AP242">
+        <v>1.36</v>
+      </c>
+      <c r="AQ242">
+        <v>1.21</v>
+      </c>
+      <c r="AR242">
+        <v>1.48</v>
+      </c>
+      <c r="AS242">
+        <v>1.35</v>
+      </c>
+      <c r="AT242">
+        <v>2.83</v>
+      </c>
+      <c r="AU242">
+        <v>8</v>
+      </c>
+      <c r="AV242">
+        <v>7</v>
+      </c>
+      <c r="AW242">
+        <v>5</v>
+      </c>
+      <c r="AX242">
+        <v>7</v>
+      </c>
+      <c r="AY242">
+        <v>13</v>
+      </c>
+      <c r="AZ242">
+        <v>16</v>
+      </c>
+      <c r="BA242">
+        <v>4</v>
+      </c>
+      <c r="BB242">
+        <v>6</v>
+      </c>
+      <c r="BC242">
+        <v>10</v>
+      </c>
+      <c r="BD242">
+        <v>2.1</v>
+      </c>
+      <c r="BE242">
+        <v>6.55</v>
+      </c>
+      <c r="BF242">
+        <v>2.15</v>
+      </c>
+      <c r="BG242">
+        <v>1.2</v>
+      </c>
+      <c r="BH242">
+        <v>3.72</v>
+      </c>
+      <c r="BI242">
+        <v>1.41</v>
+      </c>
+      <c r="BJ242">
+        <v>2.6</v>
+      </c>
+      <c r="BK242">
+        <v>1.73</v>
+      </c>
+      <c r="BL242">
+        <v>1.99</v>
+      </c>
+      <c r="BM242">
+        <v>2.17</v>
+      </c>
+      <c r="BN242">
+        <v>1.58</v>
+      </c>
+      <c r="BO242">
+        <v>2.88</v>
+      </c>
+      <c r="BP242">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7491731</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45746.35416666666</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>87</v>
+      </c>
+      <c r="H243" t="s">
+        <v>86</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>1</v>
+      </c>
+      <c r="K243">
+        <v>2</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>1</v>
+      </c>
+      <c r="N243">
+        <v>2</v>
+      </c>
+      <c r="O243" t="s">
+        <v>146</v>
+      </c>
+      <c r="P243" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q243">
+        <v>3</v>
+      </c>
+      <c r="R243">
+        <v>2.05</v>
+      </c>
+      <c r="S243">
+        <v>3.75</v>
+      </c>
+      <c r="T243">
+        <v>1.44</v>
+      </c>
+      <c r="U243">
+        <v>2.63</v>
+      </c>
+      <c r="V243">
+        <v>3.25</v>
+      </c>
+      <c r="W243">
+        <v>1.33</v>
+      </c>
+      <c r="X243">
+        <v>9</v>
+      </c>
+      <c r="Y243">
+        <v>1.07</v>
+      </c>
+      <c r="Z243">
+        <v>2.2</v>
+      </c>
+      <c r="AA243">
+        <v>3.35</v>
+      </c>
+      <c r="AB243">
+        <v>3.55</v>
+      </c>
+      <c r="AC243">
+        <v>1.07</v>
+      </c>
+      <c r="AD243">
+        <v>8</v>
+      </c>
+      <c r="AE243">
+        <v>1.36</v>
+      </c>
+      <c r="AF243">
+        <v>3.1</v>
+      </c>
+      <c r="AG243">
+        <v>1.91</v>
+      </c>
+      <c r="AH243">
+        <v>1.75</v>
+      </c>
+      <c r="AI243">
+        <v>1.83</v>
+      </c>
+      <c r="AJ243">
+        <v>1.83</v>
+      </c>
+      <c r="AK243">
+        <v>1.32</v>
+      </c>
+      <c r="AL243">
+        <v>1.31</v>
+      </c>
+      <c r="AM243">
+        <v>1.65</v>
+      </c>
+      <c r="AN243">
+        <v>1</v>
+      </c>
+      <c r="AO243">
+        <v>0.54</v>
+      </c>
+      <c r="AP243">
+        <v>1</v>
+      </c>
+      <c r="AQ243">
+        <v>0.57</v>
+      </c>
+      <c r="AR243">
+        <v>1.29</v>
+      </c>
+      <c r="AS243">
+        <v>1.22</v>
+      </c>
+      <c r="AT243">
+        <v>2.51</v>
+      </c>
+      <c r="AU243">
+        <v>4</v>
+      </c>
+      <c r="AV243">
+        <v>3</v>
+      </c>
+      <c r="AW243">
+        <v>12</v>
+      </c>
+      <c r="AX243">
+        <v>7</v>
+      </c>
+      <c r="AY243">
+        <v>18</v>
+      </c>
+      <c r="AZ243">
+        <v>14</v>
+      </c>
+      <c r="BA243">
+        <v>4</v>
+      </c>
+      <c r="BB243">
+        <v>3</v>
+      </c>
+      <c r="BC243">
+        <v>7</v>
+      </c>
+      <c r="BD243">
+        <v>1.94</v>
+      </c>
+      <c r="BE243">
+        <v>6.7</v>
+      </c>
+      <c r="BF243">
+        <v>2.33</v>
+      </c>
+      <c r="BG243">
+        <v>1.14</v>
+      </c>
+      <c r="BH243">
+        <v>4.45</v>
+      </c>
+      <c r="BI243">
+        <v>1.29</v>
+      </c>
+      <c r="BJ243">
+        <v>3.04</v>
+      </c>
+      <c r="BK243">
+        <v>1.55</v>
+      </c>
+      <c r="BL243">
+        <v>2.23</v>
+      </c>
+      <c r="BM243">
+        <v>1.94</v>
+      </c>
+      <c r="BN243">
+        <v>1.77</v>
+      </c>
+      <c r="BO243">
+        <v>2.48</v>
+      </c>
+      <c r="BP243">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7491732</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45746.35416666666</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>79</v>
+      </c>
+      <c r="H244" t="s">
+        <v>81</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244">
+        <v>1</v>
+      </c>
+      <c r="L244">
+        <v>2</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>3</v>
+      </c>
+      <c r="O244" t="s">
+        <v>252</v>
+      </c>
+      <c r="P244" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q244">
+        <v>4</v>
+      </c>
+      <c r="R244">
+        <v>2.2</v>
+      </c>
+      <c r="S244">
+        <v>2.75</v>
+      </c>
+      <c r="T244">
+        <v>1.4</v>
+      </c>
+      <c r="U244">
+        <v>2.75</v>
+      </c>
+      <c r="V244">
+        <v>2.75</v>
+      </c>
+      <c r="W244">
+        <v>1.4</v>
+      </c>
+      <c r="X244">
+        <v>8</v>
+      </c>
+      <c r="Y244">
+        <v>1.08</v>
+      </c>
+      <c r="Z244">
+        <v>3.39</v>
+      </c>
+      <c r="AA244">
+        <v>3.68</v>
+      </c>
+      <c r="AB244">
+        <v>2.14</v>
+      </c>
+      <c r="AC244">
+        <v>1.05</v>
+      </c>
+      <c r="AD244">
+        <v>9.5</v>
+      </c>
+      <c r="AE244">
+        <v>1.28</v>
+      </c>
+      <c r="AF244">
+        <v>3.55</v>
+      </c>
+      <c r="AG244">
+        <v>1.93</v>
+      </c>
+      <c r="AH244">
+        <v>1.88</v>
+      </c>
+      <c r="AI244">
+        <v>1.73</v>
+      </c>
+      <c r="AJ244">
+        <v>2</v>
+      </c>
+      <c r="AK244">
+        <v>1.71</v>
+      </c>
+      <c r="AL244">
+        <v>1.28</v>
+      </c>
+      <c r="AM244">
+        <v>1.32</v>
+      </c>
+      <c r="AN244">
+        <v>1.15</v>
+      </c>
+      <c r="AO244">
+        <v>1.15</v>
+      </c>
+      <c r="AP244">
+        <v>1.29</v>
+      </c>
+      <c r="AQ244">
+        <v>1.07</v>
+      </c>
+      <c r="AR244">
+        <v>1.22</v>
+      </c>
+      <c r="AS244">
+        <v>1.45</v>
+      </c>
+      <c r="AT244">
+        <v>2.67</v>
+      </c>
+      <c r="AU244">
+        <v>5</v>
+      </c>
+      <c r="AV244">
+        <v>5</v>
+      </c>
+      <c r="AW244">
+        <v>6</v>
+      </c>
+      <c r="AX244">
+        <v>11</v>
+      </c>
+      <c r="AY244">
+        <v>12</v>
+      </c>
+      <c r="AZ244">
+        <v>20</v>
+      </c>
+      <c r="BA244">
+        <v>3</v>
+      </c>
+      <c r="BB244">
+        <v>6</v>
+      </c>
+      <c r="BC244">
+        <v>9</v>
+      </c>
+      <c r="BD244">
+        <v>2.64</v>
+      </c>
+      <c r="BE244">
+        <v>7</v>
+      </c>
+      <c r="BF244">
+        <v>1.75</v>
+      </c>
+      <c r="BG244">
+        <v>1.1</v>
+      </c>
+      <c r="BH244">
+        <v>5.1</v>
+      </c>
+      <c r="BI244">
+        <v>1.23</v>
+      </c>
+      <c r="BJ244">
+        <v>3.42</v>
+      </c>
+      <c r="BK244">
+        <v>1.44</v>
+      </c>
+      <c r="BL244">
+        <v>2.5</v>
+      </c>
+      <c r="BM244">
+        <v>1.78</v>
+      </c>
+      <c r="BN244">
+        <v>1.93</v>
+      </c>
+      <c r="BO244">
+        <v>2.21</v>
+      </c>
+      <c r="BP244">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="383">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,12 @@
     <t>['47', '55']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['44', '71', '78']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1155,6 +1161,9 @@
   <si>
     <t>['9', '84', '90+5']</t>
   </si>
+  <si>
+    <t>['25', '47']</t>
+  </si>
 </sst>
 </file>
 
@@ -1515,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1771,7 +1780,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1977,7 +1986,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2055,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3">
         <v>1.07</v>
@@ -2389,7 +2398,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2470,7 +2479,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ5">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2801,7 +2810,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3007,7 +3016,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3419,7 +3428,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3831,7 +3840,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4243,7 +4252,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4861,7 +4870,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5067,7 +5076,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5145,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18">
         <v>2.14</v>
@@ -5354,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5479,7 +5488,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5557,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ20">
         <v>1.38</v>
@@ -6178,7 +6187,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ23">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR23">
         <v>2.28</v>
@@ -6715,7 +6724,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6921,7 +6930,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7127,7 +7136,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7414,7 +7423,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ29">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7539,7 +7548,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7745,7 +7754,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8157,7 +8166,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8363,7 +8372,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8775,7 +8784,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8981,7 +8990,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9059,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
         <v>1.14</v>
@@ -9187,7 +9196,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9268,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR38">
         <v>1.52</v>
@@ -9471,7 +9480,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ39">
         <v>1.21</v>
@@ -9599,7 +9608,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9805,7 +9814,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10217,7 +10226,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10629,7 +10638,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -11041,7 +11050,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11122,7 +11131,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -11247,7 +11256,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11453,7 +11462,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11659,7 +11668,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11943,7 +11952,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51">
         <v>1.15</v>
@@ -12071,7 +12080,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12277,7 +12286,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12483,7 +12492,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12689,7 +12698,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12895,7 +12904,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13101,7 +13110,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13307,7 +13316,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13388,7 +13397,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13719,7 +13728,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13925,7 +13934,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14337,7 +14346,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14543,7 +14552,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14955,7 +14964,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15033,7 +15042,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ66">
         <v>0.86</v>
@@ -15573,7 +15582,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15779,7 +15788,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15985,7 +15994,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16269,10 +16278,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16397,7 +16406,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -17015,7 +17024,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17221,7 +17230,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17714,7 +17723,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ79">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR79">
         <v>1.72</v>
@@ -18045,7 +18054,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18457,7 +18466,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18538,7 +18547,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ83">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR83">
         <v>2.13</v>
@@ -18663,7 +18672,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18869,7 +18878,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18947,7 +18956,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ85">
         <v>1.5</v>
@@ -19075,7 +19084,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19281,7 +19290,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19487,7 +19496,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19693,7 +19702,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19899,7 +19908,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19980,7 +19989,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR90">
         <v>1.7</v>
@@ -20183,7 +20192,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -20929,7 +20938,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21341,7 +21350,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21547,7 +21556,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22165,7 +22174,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22243,7 +22252,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ101">
         <v>1.62</v>
@@ -22783,7 +22792,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23195,7 +23204,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23276,7 +23285,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ106">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR106">
         <v>1.62</v>
@@ -23401,7 +23410,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23479,7 +23488,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23894,7 +23903,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ109">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -24019,7 +24028,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24431,7 +24440,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24637,7 +24646,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24843,7 +24852,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -25049,7 +25058,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25255,7 +25264,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25461,7 +25470,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25667,7 +25676,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25873,7 +25882,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -26079,7 +26088,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26285,7 +26294,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26366,7 +26375,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ121">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -26491,7 +26500,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26572,7 +26581,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ122">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR122">
         <v>1.56</v>
@@ -26775,7 +26784,7 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
         <v>0.08</v>
@@ -27109,7 +27118,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27187,7 +27196,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ125">
         <v>1.62</v>
@@ -27315,7 +27324,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27933,7 +27942,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28139,7 +28148,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28551,7 +28560,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28757,7 +28766,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28963,7 +28972,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29375,7 +29384,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29581,7 +29590,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29659,7 +29668,7 @@
         <v>0.14</v>
       </c>
       <c r="AP137">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ137">
         <v>0.08</v>
@@ -29787,7 +29796,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30199,7 +30208,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30280,7 +30289,7 @@
         <v>1</v>
       </c>
       <c r="AQ140">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR140">
         <v>1.64</v>
@@ -30611,7 +30620,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -31104,7 +31113,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ144">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -31229,7 +31238,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31307,7 +31316,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ145">
         <v>1.38</v>
@@ -31435,7 +31444,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31641,7 +31650,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32259,7 +32268,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -33083,7 +33092,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33289,7 +33298,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33576,7 +33585,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ156">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR156">
         <v>1.25</v>
@@ -33985,7 +33994,7 @@
         <v>1.33</v>
       </c>
       <c r="AP158">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ158">
         <v>1.21</v>
@@ -34525,7 +34534,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34731,7 +34740,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34937,7 +34946,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35143,7 +35152,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35349,7 +35358,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35761,7 +35770,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35839,7 +35848,7 @@
         <v>2.13</v>
       </c>
       <c r="AP167">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ167">
         <v>1.69</v>
@@ -36173,7 +36182,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36379,7 +36388,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36666,7 +36675,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ171">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -36791,7 +36800,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37203,7 +37212,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37615,7 +37624,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37693,7 +37702,7 @@
         <v>1.89</v>
       </c>
       <c r="AP176">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ176">
         <v>1.86</v>
@@ -37821,7 +37830,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -38027,7 +38036,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38233,7 +38242,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38439,7 +38448,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38645,7 +38654,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38726,7 +38735,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR181">
         <v>1.76</v>
@@ -38851,7 +38860,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39263,7 +39272,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39469,7 +39478,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39675,7 +39684,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39756,7 +39765,7 @@
         <v>1</v>
       </c>
       <c r="AQ186">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR186">
         <v>1.53</v>
@@ -40293,7 +40302,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40371,7 +40380,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ189">
         <v>0.57</v>
@@ -41404,7 +41413,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ194">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR194">
         <v>1.74</v>
@@ -41607,7 +41616,7 @@
         <v>1.2</v>
       </c>
       <c r="AP195">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ195">
         <v>0.86</v>
@@ -41735,7 +41744,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42971,7 +42980,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43049,7 +43058,7 @@
         <v>2.55</v>
       </c>
       <c r="AP202">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ202">
         <v>2.14</v>
@@ -43589,7 +43598,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43670,7 +43679,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ205">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR205">
         <v>1.73</v>
@@ -44413,7 +44422,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -44903,7 +44912,7 @@
         <v>0.67</v>
       </c>
       <c r="AP211">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ211">
         <v>0.71</v>
@@ -45237,7 +45246,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45318,7 +45327,7 @@
         <v>2</v>
       </c>
       <c r="AQ213">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR213">
         <v>1.64</v>
@@ -45521,7 +45530,7 @@
         <v>1.82</v>
       </c>
       <c r="AP214">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ214">
         <v>1.86</v>
@@ -45649,7 +45658,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -46473,7 +46482,7 @@
         <v>240</v>
       </c>
       <c r="P219" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q219">
         <v>2.85</v>
@@ -46885,7 +46894,7 @@
         <v>119</v>
       </c>
       <c r="P221" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47297,7 +47306,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47503,7 +47512,7 @@
         <v>243</v>
       </c>
       <c r="P224" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q224">
         <v>2.2</v>
@@ -47709,7 +47718,7 @@
         <v>92</v>
       </c>
       <c r="P225" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q225">
         <v>3.4</v>
@@ -47996,7 +48005,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ226">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR226">
         <v>1.26</v>
@@ -48121,7 +48130,7 @@
         <v>174</v>
       </c>
       <c r="P227" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q227">
         <v>3.1</v>
@@ -48202,7 +48211,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ227">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR227">
         <v>1.68</v>
@@ -48327,7 +48336,7 @@
         <v>92</v>
       </c>
       <c r="P228" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48533,7 +48542,7 @@
         <v>92</v>
       </c>
       <c r="P229" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q229">
         <v>2.25</v>
@@ -48739,7 +48748,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q230">
         <v>2.4</v>
@@ -49641,7 +49650,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP234">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ234">
         <v>0.71</v>
@@ -49769,7 +49778,7 @@
         <v>247</v>
       </c>
       <c r="P235" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q235">
         <v>3.6</v>
@@ -49847,7 +49856,7 @@
         <v>1.38</v>
       </c>
       <c r="AP235">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ235">
         <v>1.5</v>
@@ -50593,7 +50602,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50799,7 +50808,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q240">
         <v>2.3</v>
@@ -51211,7 +51220,7 @@
         <v>251</v>
       </c>
       <c r="P242" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51780,6 +51789,418 @@
       </c>
       <c r="BP244">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7491736</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45751.5625</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>71</v>
+      </c>
+      <c r="H245" t="s">
+        <v>72</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>1</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>1</v>
+      </c>
+      <c r="O245" t="s">
+        <v>253</v>
+      </c>
+      <c r="P245" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q245">
+        <v>3.25</v>
+      </c>
+      <c r="R245">
+        <v>2.25</v>
+      </c>
+      <c r="S245">
+        <v>3</v>
+      </c>
+      <c r="T245">
+        <v>1.33</v>
+      </c>
+      <c r="U245">
+        <v>3.25</v>
+      </c>
+      <c r="V245">
+        <v>2.63</v>
+      </c>
+      <c r="W245">
+        <v>1.44</v>
+      </c>
+      <c r="X245">
+        <v>6.5</v>
+      </c>
+      <c r="Y245">
+        <v>1.11</v>
+      </c>
+      <c r="Z245">
+        <v>2.72</v>
+      </c>
+      <c r="AA245">
+        <v>3.52</v>
+      </c>
+      <c r="AB245">
+        <v>2.61</v>
+      </c>
+      <c r="AC245">
+        <v>1.05</v>
+      </c>
+      <c r="AD245">
+        <v>9.5</v>
+      </c>
+      <c r="AE245">
+        <v>1.22</v>
+      </c>
+      <c r="AF245">
+        <v>4.2</v>
+      </c>
+      <c r="AG245">
+        <v>1.65</v>
+      </c>
+      <c r="AH245">
+        <v>2.05</v>
+      </c>
+      <c r="AI245">
+        <v>1.57</v>
+      </c>
+      <c r="AJ245">
+        <v>2.25</v>
+      </c>
+      <c r="AK245">
+        <v>1.5</v>
+      </c>
+      <c r="AL245">
+        <v>1.29</v>
+      </c>
+      <c r="AM245">
+        <v>1.46</v>
+      </c>
+      <c r="AN245">
+        <v>1.62</v>
+      </c>
+      <c r="AO245">
+        <v>1.23</v>
+      </c>
+      <c r="AP245">
+        <v>1.71</v>
+      </c>
+      <c r="AQ245">
+        <v>1.14</v>
+      </c>
+      <c r="AR245">
+        <v>1.63</v>
+      </c>
+      <c r="AS245">
+        <v>1.44</v>
+      </c>
+      <c r="AT245">
+        <v>3.07</v>
+      </c>
+      <c r="AU245">
+        <v>5</v>
+      </c>
+      <c r="AV245">
+        <v>3</v>
+      </c>
+      <c r="AW245">
+        <v>8</v>
+      </c>
+      <c r="AX245">
+        <v>15</v>
+      </c>
+      <c r="AY245">
+        <v>17</v>
+      </c>
+      <c r="AZ245">
+        <v>24</v>
+      </c>
+      <c r="BA245">
+        <v>5</v>
+      </c>
+      <c r="BB245">
+        <v>6</v>
+      </c>
+      <c r="BC245">
+        <v>11</v>
+      </c>
+      <c r="BD245">
+        <v>2.05</v>
+      </c>
+      <c r="BE245">
+        <v>6.5</v>
+      </c>
+      <c r="BF245">
+        <v>1.95</v>
+      </c>
+      <c r="BG245">
+        <v>1.23</v>
+      </c>
+      <c r="BH245">
+        <v>3.65</v>
+      </c>
+      <c r="BI245">
+        <v>1.4</v>
+      </c>
+      <c r="BJ245">
+        <v>2.65</v>
+      </c>
+      <c r="BK245">
+        <v>1.65</v>
+      </c>
+      <c r="BL245">
+        <v>2.08</v>
+      </c>
+      <c r="BM245">
+        <v>2</v>
+      </c>
+      <c r="BN245">
+        <v>1.71</v>
+      </c>
+      <c r="BO245">
+        <v>2.5</v>
+      </c>
+      <c r="BP245">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7491741</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45751.5625</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>86</v>
+      </c>
+      <c r="H246" t="s">
+        <v>85</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>2</v>
+      </c>
+      <c r="L246">
+        <v>3</v>
+      </c>
+      <c r="M246">
+        <v>2</v>
+      </c>
+      <c r="N246">
+        <v>5</v>
+      </c>
+      <c r="O246" t="s">
+        <v>254</v>
+      </c>
+      <c r="P246" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q246">
+        <v>4.33</v>
+      </c>
+      <c r="R246">
+        <v>2.2</v>
+      </c>
+      <c r="S246">
+        <v>2.6</v>
+      </c>
+      <c r="T246">
+        <v>1.36</v>
+      </c>
+      <c r="U246">
+        <v>3</v>
+      </c>
+      <c r="V246">
+        <v>2.75</v>
+      </c>
+      <c r="W246">
+        <v>1.4</v>
+      </c>
+      <c r="X246">
+        <v>8</v>
+      </c>
+      <c r="Y246">
+        <v>1.08</v>
+      </c>
+      <c r="Z246">
+        <v>3.61</v>
+      </c>
+      <c r="AA246">
+        <v>3.67</v>
+      </c>
+      <c r="AB246">
+        <v>2.06</v>
+      </c>
+      <c r="AC246">
+        <v>1.05</v>
+      </c>
+      <c r="AD246">
+        <v>9</v>
+      </c>
+      <c r="AE246">
+        <v>1.28</v>
+      </c>
+      <c r="AF246">
+        <v>3.55</v>
+      </c>
+      <c r="AG246">
+        <v>1.89</v>
+      </c>
+      <c r="AH246">
+        <v>1.92</v>
+      </c>
+      <c r="AI246">
+        <v>1.73</v>
+      </c>
+      <c r="AJ246">
+        <v>2</v>
+      </c>
+      <c r="AK246">
+        <v>1.75</v>
+      </c>
+      <c r="AL246">
+        <v>1.28</v>
+      </c>
+      <c r="AM246">
+        <v>1.29</v>
+      </c>
+      <c r="AN246">
+        <v>1.23</v>
+      </c>
+      <c r="AO246">
+        <v>1.69</v>
+      </c>
+      <c r="AP246">
+        <v>1.36</v>
+      </c>
+      <c r="AQ246">
+        <v>1.57</v>
+      </c>
+      <c r="AR246">
+        <v>1.42</v>
+      </c>
+      <c r="AS246">
+        <v>1.46</v>
+      </c>
+      <c r="AT246">
+        <v>2.88</v>
+      </c>
+      <c r="AU246">
+        <v>6</v>
+      </c>
+      <c r="AV246">
+        <v>6</v>
+      </c>
+      <c r="AW246">
+        <v>4</v>
+      </c>
+      <c r="AX246">
+        <v>14</v>
+      </c>
+      <c r="AY246">
+        <v>12</v>
+      </c>
+      <c r="AZ246">
+        <v>24</v>
+      </c>
+      <c r="BA246">
+        <v>0</v>
+      </c>
+      <c r="BB246">
+        <v>4</v>
+      </c>
+      <c r="BC246">
+        <v>4</v>
+      </c>
+      <c r="BD246">
+        <v>2.43</v>
+      </c>
+      <c r="BE246">
+        <v>6.75</v>
+      </c>
+      <c r="BF246">
+        <v>1.67</v>
+      </c>
+      <c r="BG246">
+        <v>1.24</v>
+      </c>
+      <c r="BH246">
+        <v>3.55</v>
+      </c>
+      <c r="BI246">
+        <v>1.43</v>
+      </c>
+      <c r="BJ246">
+        <v>2.6</v>
+      </c>
+      <c r="BK246">
+        <v>1.68</v>
+      </c>
+      <c r="BL246">
+        <v>2.02</v>
+      </c>
+      <c r="BM246">
+        <v>2.07</v>
+      </c>
+      <c r="BN246">
+        <v>1.66</v>
+      </c>
+      <c r="BO246">
+        <v>2.55</v>
+      </c>
+      <c r="BP246">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="385">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,9 @@
     <t>['44', '71', '78']</t>
   </si>
   <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1087,9 +1090,6 @@
     <t>['21', '50']</t>
   </si>
   <si>
-    <t>['79']</t>
-  </si>
-  <si>
     <t>['52', '79']</t>
   </si>
   <si>
@@ -1163,6 +1163,12 @@
   </si>
   <si>
     <t>['25', '47']</t>
+  </si>
+  <si>
+    <t>['8', '37', '84']</t>
+  </si>
+  <si>
+    <t>['46']</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP246"/>
+  <dimension ref="A1:BP250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1780,7 +1786,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1858,10 +1864,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ2">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1986,7 +1992,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2398,7 +2404,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2810,7 +2816,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3016,7 +3022,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3094,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
         <v>1.69</v>
@@ -3303,7 +3309,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3428,7 +3434,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3840,7 +3846,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3921,7 +3927,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4124,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ13">
         <v>1.21</v>
@@ -4252,7 +4258,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4536,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ15">
         <v>1.14</v>
@@ -4745,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4870,7 +4876,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5076,7 +5082,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5488,7 +5494,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5775,7 +5781,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ21">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -6596,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ25">
         <v>0.57</v>
@@ -6724,7 +6730,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6930,7 +6936,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7008,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ27">
         <v>1.07</v>
@@ -7136,7 +7142,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7420,7 +7426,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ29">
         <v>1.14</v>
@@ -7548,7 +7554,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7629,7 +7635,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR30">
         <v>0.79</v>
@@ -7754,7 +7760,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7835,7 +7841,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR31">
         <v>1.09</v>
@@ -8166,7 +8172,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8244,7 +8250,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ33">
         <v>2.14</v>
@@ -8372,7 +8378,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8453,7 +8459,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ34">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR34">
         <v>1.8</v>
@@ -8784,7 +8790,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8990,7 +8996,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9196,7 +9202,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9608,7 +9614,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9814,7 +9820,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10098,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ42">
         <v>0.57</v>
@@ -10226,7 +10232,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10304,7 +10310,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ43">
         <v>2.14</v>
@@ -10638,7 +10644,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -11050,7 +11056,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11256,7 +11262,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11462,7 +11468,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11540,7 +11546,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ49">
         <v>1.86</v>
@@ -11668,7 +11674,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11746,10 +11752,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR50">
         <v>0.97</v>
@@ -11955,7 +11961,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -12080,7 +12086,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12161,7 +12167,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR52">
         <v>1.99</v>
@@ -12286,7 +12292,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12492,7 +12498,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12698,7 +12704,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12779,7 +12785,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12904,7 +12910,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13110,7 +13116,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13316,7 +13322,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13728,7 +13734,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13806,7 +13812,7 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ60">
         <v>2.14</v>
@@ -13934,7 +13940,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14346,7 +14352,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14552,7 +14558,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14630,7 +14636,7 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ64">
         <v>1.14</v>
@@ -14964,7 +14970,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15248,7 +15254,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ67">
         <v>0.71</v>
@@ -15582,7 +15588,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15660,10 +15666,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR69">
         <v>0.99</v>
@@ -15788,7 +15794,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15869,7 +15875,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR70">
         <v>1.66</v>
@@ -15994,7 +16000,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16075,7 +16081,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16406,7 +16412,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16484,10 +16490,10 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ73">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR73">
         <v>1.59</v>
@@ -16690,7 +16696,7 @@
         <v>1.67</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ74">
         <v>1.86</v>
@@ -17024,7 +17030,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17230,7 +17236,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -18054,7 +18060,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18466,7 +18472,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18544,7 +18550,7 @@
         <v>1.2</v>
       </c>
       <c r="AP83">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ83">
         <v>1.57</v>
@@ -18672,7 +18678,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18750,7 +18756,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ84">
         <v>0.08</v>
@@ -18878,7 +18884,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18959,7 +18965,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR85">
         <v>1.57</v>
@@ -19084,7 +19090,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19165,7 +19171,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR86">
         <v>1.49</v>
@@ -19290,7 +19296,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19371,7 +19377,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ87">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR87">
         <v>1.33</v>
@@ -19496,7 +19502,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19574,7 +19580,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ88">
         <v>1.54</v>
@@ -19702,7 +19708,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19780,7 +19786,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ89">
         <v>0.71</v>
@@ -19908,7 +19914,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20195,7 +20201,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR91">
         <v>1.66</v>
@@ -20938,7 +20944,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21350,7 +21356,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21556,7 +21562,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22174,7 +22180,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22255,7 +22261,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ101">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR101">
         <v>1.49</v>
@@ -22458,7 +22464,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ102">
         <v>1.54</v>
@@ -22664,10 +22670,10 @@
         <v>1.6</v>
       </c>
       <c r="AP103">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ103">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR103">
         <v>1.96</v>
@@ -22792,7 +22798,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22870,10 +22876,10 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ104">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -23204,7 +23210,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23282,7 +23288,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ106">
         <v>1.57</v>
@@ -23410,7 +23416,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23491,7 +23497,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -24028,7 +24034,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24440,7 +24446,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24646,7 +24652,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24852,7 +24858,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24930,7 +24936,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ114">
         <v>1.38</v>
@@ -25058,7 +25064,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25264,7 +25270,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25470,7 +25476,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25676,7 +25682,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25882,7 +25888,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25963,7 +25969,7 @@
         <v>1</v>
       </c>
       <c r="AQ119">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR119">
         <v>1.77</v>
@@ -26088,7 +26094,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26294,7 +26300,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26372,7 +26378,7 @@
         <v>0.67</v>
       </c>
       <c r="AP121">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ121">
         <v>1.14</v>
@@ -26500,7 +26506,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26990,10 +26996,10 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR124">
         <v>1.46</v>
@@ -27118,7 +27124,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27199,7 +27205,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ125">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR125">
         <v>1.52</v>
@@ -27324,7 +27330,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27402,7 +27408,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ126">
         <v>1.69</v>
@@ -27611,7 +27617,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27942,7 +27948,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28148,7 +28154,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28435,7 +28441,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR131">
         <v>1.46</v>
@@ -28560,7 +28566,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28766,7 +28772,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28972,7 +28978,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29256,7 +29262,7 @@
         <v>0.29</v>
       </c>
       <c r="AP135">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ135">
         <v>0.57</v>
@@ -29384,7 +29390,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29590,7 +29596,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29796,7 +29802,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29877,7 +29883,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR138">
         <v>1.37</v>
@@ -30208,7 +30214,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30495,7 +30501,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR141">
         <v>1.46</v>
@@ -30620,7 +30626,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30698,7 +30704,7 @@
         <v>1.75</v>
       </c>
       <c r="AP142">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ142">
         <v>1.54</v>
@@ -30904,7 +30910,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ143">
         <v>1.07</v>
@@ -31238,7 +31244,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31444,7 +31450,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31650,7 +31656,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31728,7 +31734,7 @@
         <v>2.38</v>
       </c>
       <c r="AP147">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ147">
         <v>2.14</v>
@@ -31937,7 +31943,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR148">
         <v>1.74</v>
@@ -32268,7 +32274,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32552,7 +32558,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ151">
         <v>0.57</v>
@@ -32967,7 +32973,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ153">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR153">
         <v>1.76</v>
@@ -33092,7 +33098,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33298,7 +33304,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33376,7 +33382,7 @@
         <v>1.38</v>
       </c>
       <c r="AP155">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ155">
         <v>0.86</v>
@@ -34203,7 +34209,7 @@
         <v>1</v>
       </c>
       <c r="AQ159">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR159">
         <v>1.15</v>
@@ -34534,7 +34540,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34615,7 +34621,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR161">
         <v>1.53</v>
@@ -34740,7 +34746,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34946,7 +34952,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35024,7 +35030,7 @@
         <v>1.67</v>
       </c>
       <c r="AP163">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ163">
         <v>1.14</v>
@@ -35152,7 +35158,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35358,7 +35364,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35642,7 +35648,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ166">
         <v>1.38</v>
@@ -35770,7 +35776,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36182,7 +36188,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36263,7 +36269,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ169">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36388,7 +36394,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36672,7 +36678,7 @@
         <v>1.56</v>
       </c>
       <c r="AP171">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ171">
         <v>1.57</v>
@@ -36800,7 +36806,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -36881,7 +36887,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ172">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR172">
         <v>1.67</v>
@@ -37084,7 +37090,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ173">
         <v>0.86</v>
@@ -37212,7 +37218,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37499,7 +37505,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ175">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR175">
         <v>1.23</v>
@@ -37624,7 +37630,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37830,7 +37836,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37908,7 +37914,7 @@
         <v>0.8</v>
       </c>
       <c r="AP177">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ177">
         <v>0.71</v>
@@ -38036,7 +38042,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38242,7 +38248,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38323,7 +38329,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ179">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR179">
         <v>1.64</v>
@@ -38448,7 +38454,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>357</v>
+        <v>255</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38529,7 +38535,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR180">
         <v>1.74</v>
@@ -38941,7 +38947,7 @@
         <v>1</v>
       </c>
       <c r="AQ182">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR182">
         <v>1.22</v>
@@ -39350,7 +39356,7 @@
         <v>1.33</v>
       </c>
       <c r="AP184">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ184">
         <v>1.38</v>
@@ -40174,7 +40180,7 @@
         <v>1.3</v>
       </c>
       <c r="AP188">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ188">
         <v>1.21</v>
@@ -41001,7 +41007,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ192">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR192">
         <v>1.67</v>
@@ -41207,7 +41213,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ193">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR193">
         <v>1.5</v>
@@ -41822,10 +41828,10 @@
         <v>1.64</v>
       </c>
       <c r="AP196">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ196">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR196">
         <v>1.57</v>
@@ -42031,7 +42037,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ197">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR197">
         <v>1.21</v>
@@ -42440,7 +42446,7 @@
         <v>0.73</v>
       </c>
       <c r="AP199">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ199">
         <v>0.71</v>
@@ -43882,7 +43888,7 @@
         <v>2.1</v>
       </c>
       <c r="AP206">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ206">
         <v>1.69</v>
@@ -44088,7 +44094,7 @@
         <v>1.18</v>
       </c>
       <c r="AP207">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ207">
         <v>1.21</v>
@@ -44500,10 +44506,10 @@
         <v>1.09</v>
       </c>
       <c r="AP209">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ209">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -44709,7 +44715,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR210">
         <v>1.67</v>
@@ -45324,7 +45330,7 @@
         <v>0.91</v>
       </c>
       <c r="AP213">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ213">
         <v>1.14</v>
@@ -45945,7 +45951,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ216">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR216">
         <v>1.49</v>
@@ -46151,7 +46157,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ217">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR217">
         <v>1.68</v>
@@ -46354,7 +46360,7 @@
         <v>1.33</v>
       </c>
       <c r="AP218">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ218">
         <v>1.14</v>
@@ -47306,7 +47312,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -48417,7 +48423,7 @@
         <v>1</v>
       </c>
       <c r="AQ228">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR228">
         <v>1.81</v>
@@ -48623,7 +48629,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ229">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR229">
         <v>1.5</v>
@@ -49032,7 +49038,7 @@
         <v>0.08</v>
       </c>
       <c r="AP231">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ231">
         <v>0.08</v>
@@ -49238,7 +49244,7 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ232">
         <v>0.86</v>
@@ -49444,10 +49450,10 @@
         <v>1.25</v>
       </c>
       <c r="AP233">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ233">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR233">
         <v>1.6</v>
@@ -49859,7 +49865,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ235">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR235">
         <v>1.38</v>
@@ -52201,6 +52207,830 @@
       </c>
       <c r="BP246">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7491734</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45752.33333333334</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>76</v>
+      </c>
+      <c r="H247" t="s">
+        <v>77</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>0</v>
+      </c>
+      <c r="L247">
+        <v>1</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>1</v>
+      </c>
+      <c r="O247" t="s">
+        <v>255</v>
+      </c>
+      <c r="P247" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q247">
+        <v>2.5</v>
+      </c>
+      <c r="R247">
+        <v>2.25</v>
+      </c>
+      <c r="S247">
+        <v>4.33</v>
+      </c>
+      <c r="T247">
+        <v>1.36</v>
+      </c>
+      <c r="U247">
+        <v>3</v>
+      </c>
+      <c r="V247">
+        <v>2.63</v>
+      </c>
+      <c r="W247">
+        <v>1.44</v>
+      </c>
+      <c r="X247">
+        <v>7</v>
+      </c>
+      <c r="Y247">
+        <v>1.1</v>
+      </c>
+      <c r="Z247">
+        <v>1.87</v>
+      </c>
+      <c r="AA247">
+        <v>3.9</v>
+      </c>
+      <c r="AB247">
+        <v>4.1</v>
+      </c>
+      <c r="AC247">
+        <v>0</v>
+      </c>
+      <c r="AD247">
+        <v>0</v>
+      </c>
+      <c r="AE247">
+        <v>1.22</v>
+      </c>
+      <c r="AF247">
+        <v>4.56</v>
+      </c>
+      <c r="AG247">
+        <v>1.65</v>
+      </c>
+      <c r="AH247">
+        <v>2.05</v>
+      </c>
+      <c r="AI247">
+        <v>1.67</v>
+      </c>
+      <c r="AJ247">
+        <v>2.1</v>
+      </c>
+      <c r="AK247">
+        <v>1.22</v>
+      </c>
+      <c r="AL247">
+        <v>1.29</v>
+      </c>
+      <c r="AM247">
+        <v>2.17</v>
+      </c>
+      <c r="AN247">
+        <v>1.46</v>
+      </c>
+      <c r="AO247">
+        <v>1.15</v>
+      </c>
+      <c r="AP247">
+        <v>1.57</v>
+      </c>
+      <c r="AQ247">
+        <v>1.07</v>
+      </c>
+      <c r="AR247">
+        <v>1.63</v>
+      </c>
+      <c r="AS247">
+        <v>1.28</v>
+      </c>
+      <c r="AT247">
+        <v>2.91</v>
+      </c>
+      <c r="AU247">
+        <v>5</v>
+      </c>
+      <c r="AV247">
+        <v>2</v>
+      </c>
+      <c r="AW247">
+        <v>10</v>
+      </c>
+      <c r="AX247">
+        <v>4</v>
+      </c>
+      <c r="AY247">
+        <v>18</v>
+      </c>
+      <c r="AZ247">
+        <v>7</v>
+      </c>
+      <c r="BA247">
+        <v>6</v>
+      </c>
+      <c r="BB247">
+        <v>3</v>
+      </c>
+      <c r="BC247">
+        <v>9</v>
+      </c>
+      <c r="BD247">
+        <v>1.68</v>
+      </c>
+      <c r="BE247">
+        <v>8.6</v>
+      </c>
+      <c r="BF247">
+        <v>2.62</v>
+      </c>
+      <c r="BG247">
+        <v>1.22</v>
+      </c>
+      <c r="BH247">
+        <v>3.5</v>
+      </c>
+      <c r="BI247">
+        <v>1.48</v>
+      </c>
+      <c r="BJ247">
+        <v>2.56</v>
+      </c>
+      <c r="BK247">
+        <v>1.84</v>
+      </c>
+      <c r="BL247">
+        <v>1.97</v>
+      </c>
+      <c r="BM247">
+        <v>2.28</v>
+      </c>
+      <c r="BN247">
+        <v>1.59</v>
+      </c>
+      <c r="BO247">
+        <v>3.04</v>
+      </c>
+      <c r="BP247">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7491735</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45752.33333333334</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>83</v>
+      </c>
+      <c r="H248" t="s">
+        <v>87</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>1</v>
+      </c>
+      <c r="O248" t="s">
+        <v>155</v>
+      </c>
+      <c r="P248" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q248">
+        <v>2.88</v>
+      </c>
+      <c r="R248">
+        <v>2.2</v>
+      </c>
+      <c r="S248">
+        <v>3.75</v>
+      </c>
+      <c r="T248">
+        <v>1.36</v>
+      </c>
+      <c r="U248">
+        <v>3</v>
+      </c>
+      <c r="V248">
+        <v>2.75</v>
+      </c>
+      <c r="W248">
+        <v>1.4</v>
+      </c>
+      <c r="X248">
+        <v>7</v>
+      </c>
+      <c r="Y248">
+        <v>1.1</v>
+      </c>
+      <c r="Z248">
+        <v>1.79</v>
+      </c>
+      <c r="AA248">
+        <v>4</v>
+      </c>
+      <c r="AB248">
+        <v>4.4</v>
+      </c>
+      <c r="AC248">
+        <v>0</v>
+      </c>
+      <c r="AD248">
+        <v>0</v>
+      </c>
+      <c r="AE248">
+        <v>1.19</v>
+      </c>
+      <c r="AF248">
+        <v>5.07</v>
+      </c>
+      <c r="AG248">
+        <v>1.81</v>
+      </c>
+      <c r="AH248">
+        <v>2.01</v>
+      </c>
+      <c r="AI248">
+        <v>1.67</v>
+      </c>
+      <c r="AJ248">
+        <v>2.1</v>
+      </c>
+      <c r="AK248">
+        <v>1.29</v>
+      </c>
+      <c r="AL248">
+        <v>1.31</v>
+      </c>
+      <c r="AM248">
+        <v>1.92</v>
+      </c>
+      <c r="AN248">
+        <v>1.36</v>
+      </c>
+      <c r="AO248">
+        <v>1</v>
+      </c>
+      <c r="AP248">
+        <v>1.47</v>
+      </c>
+      <c r="AQ248">
+        <v>0.93</v>
+      </c>
+      <c r="AR248">
+        <v>1.56</v>
+      </c>
+      <c r="AS248">
+        <v>1.28</v>
+      </c>
+      <c r="AT248">
+        <v>2.84</v>
+      </c>
+      <c r="AU248">
+        <v>5</v>
+      </c>
+      <c r="AV248">
+        <v>5</v>
+      </c>
+      <c r="AW248">
+        <v>7</v>
+      </c>
+      <c r="AX248">
+        <v>16</v>
+      </c>
+      <c r="AY248">
+        <v>14</v>
+      </c>
+      <c r="AZ248">
+        <v>24</v>
+      </c>
+      <c r="BA248">
+        <v>5</v>
+      </c>
+      <c r="BB248">
+        <v>7</v>
+      </c>
+      <c r="BC248">
+        <v>12</v>
+      </c>
+      <c r="BD248">
+        <v>1.65</v>
+      </c>
+      <c r="BE248">
+        <v>8.9</v>
+      </c>
+      <c r="BF248">
+        <v>2.67</v>
+      </c>
+      <c r="BG248">
+        <v>1.2</v>
+      </c>
+      <c r="BH248">
+        <v>3.72</v>
+      </c>
+      <c r="BI248">
+        <v>1.45</v>
+      </c>
+      <c r="BJ248">
+        <v>2.64</v>
+      </c>
+      <c r="BK248">
+        <v>1.81</v>
+      </c>
+      <c r="BL248">
+        <v>2.01</v>
+      </c>
+      <c r="BM248">
+        <v>2.25</v>
+      </c>
+      <c r="BN248">
+        <v>1.62</v>
+      </c>
+      <c r="BO248">
+        <v>2.91</v>
+      </c>
+      <c r="BP248">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7491739</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45752.33333333334</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>81</v>
+      </c>
+      <c r="H249" t="s">
+        <v>84</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>2</v>
+      </c>
+      <c r="K249">
+        <v>2</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>3</v>
+      </c>
+      <c r="N249">
+        <v>3</v>
+      </c>
+      <c r="O249" t="s">
+        <v>92</v>
+      </c>
+      <c r="P249" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q249">
+        <v>3.6</v>
+      </c>
+      <c r="R249">
+        <v>2.3</v>
+      </c>
+      <c r="S249">
+        <v>2.63</v>
+      </c>
+      <c r="T249">
+        <v>1.3</v>
+      </c>
+      <c r="U249">
+        <v>3.4</v>
+      </c>
+      <c r="V249">
+        <v>2.5</v>
+      </c>
+      <c r="W249">
+        <v>1.5</v>
+      </c>
+      <c r="X249">
+        <v>6</v>
+      </c>
+      <c r="Y249">
+        <v>1.13</v>
+      </c>
+      <c r="Z249">
+        <v>3.28</v>
+      </c>
+      <c r="AA249">
+        <v>4</v>
+      </c>
+      <c r="AB249">
+        <v>2.08</v>
+      </c>
+      <c r="AC249">
+        <v>0</v>
+      </c>
+      <c r="AD249">
+        <v>0</v>
+      </c>
+      <c r="AE249">
+        <v>1.16</v>
+      </c>
+      <c r="AF249">
+        <v>5.69</v>
+      </c>
+      <c r="AG249">
+        <v>1.55</v>
+      </c>
+      <c r="AH249">
+        <v>2.2</v>
+      </c>
+      <c r="AI249">
+        <v>1.53</v>
+      </c>
+      <c r="AJ249">
+        <v>2.38</v>
+      </c>
+      <c r="AK249">
+        <v>2.06</v>
+      </c>
+      <c r="AL249">
+        <v>1.28</v>
+      </c>
+      <c r="AM249">
+        <v>1.26</v>
+      </c>
+      <c r="AN249">
+        <v>2</v>
+      </c>
+      <c r="AO249">
+        <v>1.62</v>
+      </c>
+      <c r="AP249">
+        <v>1.86</v>
+      </c>
+      <c r="AQ249">
+        <v>1.71</v>
+      </c>
+      <c r="AR249">
+        <v>1.55</v>
+      </c>
+      <c r="AS249">
+        <v>1.55</v>
+      </c>
+      <c r="AT249">
+        <v>3.1</v>
+      </c>
+      <c r="AU249">
+        <v>5</v>
+      </c>
+      <c r="AV249">
+        <v>9</v>
+      </c>
+      <c r="AW249">
+        <v>4</v>
+      </c>
+      <c r="AX249">
+        <v>15</v>
+      </c>
+      <c r="AY249">
+        <v>10</v>
+      </c>
+      <c r="AZ249">
+        <v>27</v>
+      </c>
+      <c r="BA249">
+        <v>7</v>
+      </c>
+      <c r="BB249">
+        <v>7</v>
+      </c>
+      <c r="BC249">
+        <v>14</v>
+      </c>
+      <c r="BD249">
+        <v>2.22</v>
+      </c>
+      <c r="BE249">
+        <v>8.6</v>
+      </c>
+      <c r="BF249">
+        <v>1.9</v>
+      </c>
+      <c r="BG249">
+        <v>1.19</v>
+      </c>
+      <c r="BH249">
+        <v>3.76</v>
+      </c>
+      <c r="BI249">
+        <v>1.4</v>
+      </c>
+      <c r="BJ249">
+        <v>2.64</v>
+      </c>
+      <c r="BK249">
+        <v>1.75</v>
+      </c>
+      <c r="BL249">
+        <v>2.05</v>
+      </c>
+      <c r="BM249">
+        <v>2.13</v>
+      </c>
+      <c r="BN249">
+        <v>1.69</v>
+      </c>
+      <c r="BO249">
+        <v>2.83</v>
+      </c>
+      <c r="BP249">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7491733</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45752.64583333334</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>70</v>
+      </c>
+      <c r="H250" t="s">
+        <v>73</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>1</v>
+      </c>
+      <c r="O250" t="s">
+        <v>92</v>
+      </c>
+      <c r="P250" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q250">
+        <v>2.75</v>
+      </c>
+      <c r="R250">
+        <v>2.2</v>
+      </c>
+      <c r="S250">
+        <v>3.75</v>
+      </c>
+      <c r="T250">
+        <v>1.36</v>
+      </c>
+      <c r="U250">
+        <v>3</v>
+      </c>
+      <c r="V250">
+        <v>2.75</v>
+      </c>
+      <c r="W250">
+        <v>1.4</v>
+      </c>
+      <c r="X250">
+        <v>7</v>
+      </c>
+      <c r="Y250">
+        <v>1.1</v>
+      </c>
+      <c r="Z250">
+        <v>2.14</v>
+      </c>
+      <c r="AA250">
+        <v>3.82</v>
+      </c>
+      <c r="AB250">
+        <v>3.26</v>
+      </c>
+      <c r="AC250">
+        <v>1.02</v>
+      </c>
+      <c r="AD250">
+        <v>15</v>
+      </c>
+      <c r="AE250">
+        <v>1.21</v>
+      </c>
+      <c r="AF250">
+        <v>4.8</v>
+      </c>
+      <c r="AG250">
+        <v>1.81</v>
+      </c>
+      <c r="AH250">
+        <v>2.01</v>
+      </c>
+      <c r="AI250">
+        <v>1.67</v>
+      </c>
+      <c r="AJ250">
+        <v>2.1</v>
+      </c>
+      <c r="AK250">
+        <v>1.33</v>
+      </c>
+      <c r="AL250">
+        <v>1.3</v>
+      </c>
+      <c r="AM250">
+        <v>1.84</v>
+      </c>
+      <c r="AN250">
+        <v>1.85</v>
+      </c>
+      <c r="AO250">
+        <v>1.5</v>
+      </c>
+      <c r="AP250">
+        <v>1.71</v>
+      </c>
+      <c r="AQ250">
+        <v>1.6</v>
+      </c>
+      <c r="AR250">
+        <v>1.83</v>
+      </c>
+      <c r="AS250">
+        <v>1.57</v>
+      </c>
+      <c r="AT250">
+        <v>3.4</v>
+      </c>
+      <c r="AU250">
+        <v>5</v>
+      </c>
+      <c r="AV250">
+        <v>6</v>
+      </c>
+      <c r="AW250">
+        <v>11</v>
+      </c>
+      <c r="AX250">
+        <v>12</v>
+      </c>
+      <c r="AY250">
+        <v>16</v>
+      </c>
+      <c r="AZ250">
+        <v>18</v>
+      </c>
+      <c r="BA250">
+        <v>7</v>
+      </c>
+      <c r="BB250">
+        <v>5</v>
+      </c>
+      <c r="BC250">
+        <v>12</v>
+      </c>
+      <c r="BD250">
+        <v>1.6</v>
+      </c>
+      <c r="BE250">
+        <v>6.95</v>
+      </c>
+      <c r="BF250">
+        <v>3.08</v>
+      </c>
+      <c r="BG250">
+        <v>1.16</v>
+      </c>
+      <c r="BH250">
+        <v>4.1</v>
+      </c>
+      <c r="BI250">
+        <v>1.33</v>
+      </c>
+      <c r="BJ250">
+        <v>2.83</v>
+      </c>
+      <c r="BK250">
+        <v>1.68</v>
+      </c>
+      <c r="BL250">
+        <v>2.13</v>
+      </c>
+      <c r="BM250">
+        <v>2.04</v>
+      </c>
+      <c r="BN250">
+        <v>1.76</v>
+      </c>
+      <c r="BO250">
+        <v>2.64</v>
+      </c>
+      <c r="BP250">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="388">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,15 @@
     <t>['79']</t>
   </si>
   <si>
+    <t>['29', '43']</t>
+  </si>
+  <si>
+    <t>['59', '88']</t>
+  </si>
+  <si>
+    <t>['13', '36', '43', '57', '65', '87']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -1530,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP250"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1786,7 +1795,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1992,7 +2001,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2279,7 +2288,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ4">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2404,7 +2413,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2688,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
         <v>1.38</v>
@@ -2816,7 +2825,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2894,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7">
         <v>0.57</v>
@@ -3022,7 +3031,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3434,7 +3443,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3515,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3721,7 +3730,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ11">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3846,7 +3855,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4258,7 +4267,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4336,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ14">
         <v>1.86</v>
@@ -4876,7 +4885,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -5082,7 +5091,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5494,7 +5503,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5987,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -6399,7 +6408,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ24">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6730,7 +6739,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6936,7 +6945,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7142,7 +7151,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7220,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ28">
         <v>1.21</v>
@@ -7554,7 +7563,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7760,7 +7769,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -8044,7 +8053,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ32">
         <v>0.86</v>
@@ -8172,7 +8181,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8378,7 +8387,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8665,7 +8674,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ35">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR35">
         <v>1.49</v>
@@ -8790,7 +8799,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8868,7 +8877,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ36">
         <v>1.86</v>
@@ -8996,7 +9005,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -9202,7 +9211,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9614,7 +9623,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9695,7 +9704,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ40">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR40">
         <v>1.31</v>
@@ -9820,7 +9829,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10232,7 +10241,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10644,7 +10653,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10931,7 +10940,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR46">
         <v>1.28</v>
@@ -11056,7 +11065,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11262,7 +11271,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11340,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ48">
         <v>0.86</v>
@@ -11468,7 +11477,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11674,7 +11683,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12086,7 +12095,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12292,7 +12301,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12370,10 +12379,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ53">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12498,7 +12507,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12576,7 +12585,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ54">
         <v>1.14</v>
@@ -12704,7 +12713,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12910,7 +12919,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -13116,7 +13125,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13322,7 +13331,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13609,7 +13618,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ59">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13734,7 +13743,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13940,7 +13949,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14352,7 +14361,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14558,7 +14567,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14845,7 +14854,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR65">
         <v>1.43</v>
@@ -14970,7 +14979,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15257,7 +15266,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ67">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>2.27</v>
@@ -15460,10 +15469,10 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ68">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15588,7 +15597,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15794,7 +15803,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15872,7 +15881,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ70">
         <v>1.6</v>
@@ -16000,7 +16009,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16078,7 +16087,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ71">
         <v>1.07</v>
@@ -16412,7 +16421,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -17030,7 +17039,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17236,7 +17245,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -18060,7 +18069,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -18472,7 +18481,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18678,7 +18687,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18759,7 +18768,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ84">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR84">
         <v>1.18</v>
@@ -18884,7 +18893,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -19090,7 +19099,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19168,7 +19177,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
         <v>1.07</v>
@@ -19296,7 +19305,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19374,7 +19383,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ87">
         <v>1.71</v>
@@ -19502,7 +19511,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19583,7 +19592,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ88">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR88">
         <v>1.59</v>
@@ -19708,7 +19717,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19789,7 +19798,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ89">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19914,7 +19923,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19992,7 +20001,7 @@
         <v>0.25</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ90">
         <v>1.14</v>
@@ -20944,7 +20953,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -21356,7 +21365,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21562,7 +21571,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -22180,7 +22189,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22467,7 +22476,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ102">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR102">
         <v>1.42</v>
@@ -22798,7 +22807,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -23082,10 +23091,10 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ105">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR105">
         <v>1.68</v>
@@ -23210,7 +23219,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23416,7 +23425,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23700,10 +23709,10 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ108">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR108">
         <v>1.53</v>
@@ -23906,7 +23915,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ109">
         <v>1.14</v>
@@ -24034,7 +24043,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24446,7 +24455,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24652,7 +24661,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24733,7 +24742,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ113">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
         <v>1.37</v>
@@ -24858,7 +24867,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -25064,7 +25073,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25270,7 +25279,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25476,7 +25485,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25682,7 +25691,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25888,7 +25897,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25966,7 +25975,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ119">
         <v>1.6</v>
@@ -26094,7 +26103,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26172,10 +26181,10 @@
         <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26300,7 +26309,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26506,7 +26515,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26584,7 +26593,7 @@
         <v>1.43</v>
       </c>
       <c r="AP122">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ122">
         <v>1.57</v>
@@ -26793,7 +26802,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ123">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -27124,7 +27133,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27330,7 +27339,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27820,7 +27829,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ128">
         <v>1.07</v>
@@ -27948,7 +27957,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -28154,7 +28163,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28566,7 +28575,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28647,7 +28656,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ132">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR132">
         <v>1.64</v>
@@ -28772,7 +28781,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28978,7 +28987,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29390,7 +29399,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29596,7 +29605,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29677,7 +29686,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ137">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR137">
         <v>1.55</v>
@@ -29802,7 +29811,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -30086,7 +30095,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ139">
         <v>1.69</v>
@@ -30214,7 +30223,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30292,7 +30301,7 @@
         <v>1.63</v>
       </c>
       <c r="AP140">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ140">
         <v>1.57</v>
@@ -30626,7 +30635,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30707,7 +30716,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ142">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR142">
         <v>1.45</v>
@@ -31244,7 +31253,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31450,7 +31459,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31528,7 +31537,7 @@
         <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ146">
         <v>1.21</v>
@@ -31656,7 +31665,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32149,7 +32158,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR149">
         <v>1.2</v>
@@ -32274,7 +32283,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -33098,7 +33107,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33304,7 +33313,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33797,7 +33806,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ157">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR157">
         <v>1.65</v>
@@ -34540,7 +34549,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34746,7 +34755,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34824,7 +34833,7 @@
         <v>2.44</v>
       </c>
       <c r="AP162">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162">
         <v>2.14</v>
@@ -34952,7 +34961,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -35158,7 +35167,7 @@
         <v>200</v>
       </c>
       <c r="P164" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q164">
         <v>2.15</v>
@@ -35236,7 +35245,7 @@
         <v>0.22</v>
       </c>
       <c r="AP164">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ164">
         <v>0.57</v>
@@ -35364,7 +35373,7 @@
         <v>201</v>
       </c>
       <c r="P165" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q165">
         <v>2.85</v>
@@ -35445,7 +35454,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ165">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR165">
         <v>1.4</v>
@@ -35776,7 +35785,7 @@
         <v>203</v>
       </c>
       <c r="P167" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36060,7 +36069,7 @@
         <v>0.89</v>
       </c>
       <c r="AP168">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ168">
         <v>1.07</v>
@@ -36188,7 +36197,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q169">
         <v>2.95</v>
@@ -36394,7 +36403,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q170">
         <v>2.63</v>
@@ -36475,7 +36484,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR170">
         <v>1.46</v>
@@ -36806,7 +36815,7 @@
         <v>207</v>
       </c>
       <c r="P172" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q172">
         <v>2.25</v>
@@ -37218,7 +37227,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q174">
         <v>2.7</v>
@@ -37296,7 +37305,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ174">
         <v>1.14</v>
@@ -37630,7 +37639,7 @@
         <v>211</v>
       </c>
       <c r="P176" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q176">
         <v>4.33</v>
@@ -37836,7 +37845,7 @@
         <v>212</v>
       </c>
       <c r="P177" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q177">
         <v>2.2</v>
@@ -37917,7 +37926,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ177">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR177">
         <v>1.61</v>
@@ -38042,7 +38051,7 @@
         <v>213</v>
       </c>
       <c r="P178" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38120,7 +38129,7 @@
         <v>2.5</v>
       </c>
       <c r="AP178">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ178">
         <v>2.14</v>
@@ -38248,7 +38257,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q179">
         <v>2.2</v>
@@ -38660,7 +38669,7 @@
         <v>176</v>
       </c>
       <c r="P181" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q181">
         <v>2.5</v>
@@ -38866,7 +38875,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q182">
         <v>4</v>
@@ -39153,7 +39162,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ183">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR183">
         <v>1.4</v>
@@ -39278,7 +39287,7 @@
         <v>92</v>
       </c>
       <c r="P184" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q184">
         <v>2.63</v>
@@ -39484,7 +39493,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39562,7 +39571,7 @@
         <v>0.8</v>
       </c>
       <c r="AP185">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ185">
         <v>1.07</v>
@@ -39690,7 +39699,7 @@
         <v>92</v>
       </c>
       <c r="P186" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q186">
         <v>3.4</v>
@@ -39977,7 +39986,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ187">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR187">
         <v>1.44</v>
@@ -40308,7 +40317,7 @@
         <v>92</v>
       </c>
       <c r="P189" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q189">
         <v>2.38</v>
@@ -40798,7 +40807,7 @@
         <v>2</v>
       </c>
       <c r="AP191">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ191">
         <v>1.86</v>
@@ -41210,7 +41219,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ193">
         <v>1.07</v>
@@ -41750,7 +41759,7 @@
         <v>224</v>
       </c>
       <c r="P196" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q196">
         <v>2.65</v>
@@ -42240,7 +42249,7 @@
         <v>1.45</v>
       </c>
       <c r="AP198">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ198">
         <v>1.14</v>
@@ -42449,7 +42458,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ199">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR199">
         <v>1.58</v>
@@ -42655,7 +42664,7 @@
         <v>2</v>
       </c>
       <c r="AQ200">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR200">
         <v>1.78</v>
@@ -42986,7 +42995,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q202">
         <v>3.1</v>
@@ -43479,7 +43488,7 @@
         <v>1</v>
       </c>
       <c r="AQ204">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR204">
         <v>1.2</v>
@@ -43604,7 +43613,7 @@
         <v>146</v>
       </c>
       <c r="P205" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -44428,7 +44437,7 @@
         <v>233</v>
       </c>
       <c r="P209" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
@@ -44712,7 +44721,7 @@
         <v>0.91</v>
       </c>
       <c r="AP210">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ210">
         <v>0.93</v>
@@ -44921,7 +44930,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ211">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR211">
         <v>1.31</v>
@@ -45127,7 +45136,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ212">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR212">
         <v>1.77</v>
@@ -45252,7 +45261,7 @@
         <v>175</v>
       </c>
       <c r="P213" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q213">
         <v>3.1</v>
@@ -45664,7 +45673,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q215">
         <v>2.5</v>
@@ -45742,7 +45751,7 @@
         <v>1.09</v>
       </c>
       <c r="AP215">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ215">
         <v>0.86</v>
@@ -45948,7 +45957,7 @@
         <v>1.5</v>
       </c>
       <c r="AP216">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ216">
         <v>1.6</v>
@@ -46488,7 +46497,7 @@
         <v>240</v>
       </c>
       <c r="P219" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q219">
         <v>2.85</v>
@@ -46900,7 +46909,7 @@
         <v>119</v>
       </c>
       <c r="P221" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47312,7 +47321,7 @@
         <v>242</v>
       </c>
       <c r="P223" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q223">
         <v>2.2</v>
@@ -47518,7 +47527,7 @@
         <v>243</v>
       </c>
       <c r="P224" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q224">
         <v>2.2</v>
@@ -47724,7 +47733,7 @@
         <v>92</v>
       </c>
       <c r="P225" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q225">
         <v>3.4</v>
@@ -48136,7 +48145,7 @@
         <v>174</v>
       </c>
       <c r="P227" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q227">
         <v>3.1</v>
@@ -48214,7 +48223,7 @@
         <v>1.08</v>
       </c>
       <c r="AP227">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ227">
         <v>1.14</v>
@@ -48342,7 +48351,7 @@
         <v>92</v>
       </c>
       <c r="P228" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48420,7 +48429,7 @@
         <v>1.5</v>
       </c>
       <c r="AP228">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ228">
         <v>1.71</v>
@@ -48548,7 +48557,7 @@
         <v>92</v>
       </c>
       <c r="P229" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q229">
         <v>2.25</v>
@@ -48626,7 +48635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP229">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ229">
         <v>0.93</v>
@@ -48754,7 +48763,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q230">
         <v>2.4</v>
@@ -48835,7 +48844,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ230">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR230">
         <v>1.69</v>
@@ -49041,7 +49050,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ231">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR231">
         <v>1.5</v>
@@ -49659,7 +49668,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ234">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR234">
         <v>1.6</v>
@@ -49784,7 +49793,7 @@
         <v>247</v>
       </c>
       <c r="P235" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q235">
         <v>3.6</v>
@@ -50608,7 +50617,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50814,7 +50823,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q240">
         <v>2.3</v>
@@ -51226,7 +51235,7 @@
         <v>251</v>
       </c>
       <c r="P242" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -52050,7 +52059,7 @@
         <v>254</v>
       </c>
       <c r="P246" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q246">
         <v>4.33</v>
@@ -52668,7 +52677,7 @@
         <v>92</v>
       </c>
       <c r="P249" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q249">
         <v>3.6</v>
@@ -52874,7 +52883,7 @@
         <v>92</v>
       </c>
       <c r="P250" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53031,6 +53040,624 @@
       </c>
       <c r="BP250">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7491740</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45753.35416666666</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>74</v>
+      </c>
+      <c r="H251" t="s">
+        <v>80</v>
+      </c>
+      <c r="I251">
+        <v>2</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>2</v>
+      </c>
+      <c r="L251">
+        <v>2</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>2</v>
+      </c>
+      <c r="O251" t="s">
+        <v>256</v>
+      </c>
+      <c r="P251" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q251">
+        <v>2.4</v>
+      </c>
+      <c r="R251">
+        <v>2.5</v>
+      </c>
+      <c r="S251">
+        <v>3.75</v>
+      </c>
+      <c r="T251">
+        <v>1.25</v>
+      </c>
+      <c r="U251">
+        <v>3.75</v>
+      </c>
+      <c r="V251">
+        <v>2.2</v>
+      </c>
+      <c r="W251">
+        <v>1.62</v>
+      </c>
+      <c r="X251">
+        <v>5</v>
+      </c>
+      <c r="Y251">
+        <v>1.17</v>
+      </c>
+      <c r="Z251">
+        <v>1.92</v>
+      </c>
+      <c r="AA251">
+        <v>4.5</v>
+      </c>
+      <c r="AB251">
+        <v>3.47</v>
+      </c>
+      <c r="AC251">
+        <v>1.01</v>
+      </c>
+      <c r="AD251">
+        <v>13</v>
+      </c>
+      <c r="AE251">
+        <v>1.14</v>
+      </c>
+      <c r="AF251">
+        <v>5.5</v>
+      </c>
+      <c r="AG251">
+        <v>1.47</v>
+      </c>
+      <c r="AH251">
+        <v>2.57</v>
+      </c>
+      <c r="AI251">
+        <v>1.5</v>
+      </c>
+      <c r="AJ251">
+        <v>2.5</v>
+      </c>
+      <c r="AK251">
+        <v>1.3</v>
+      </c>
+      <c r="AL251">
+        <v>1.24</v>
+      </c>
+      <c r="AM251">
+        <v>1.82</v>
+      </c>
+      <c r="AN251">
+        <v>1</v>
+      </c>
+      <c r="AO251">
+        <v>1.54</v>
+      </c>
+      <c r="AP251">
+        <v>1.14</v>
+      </c>
+      <c r="AQ251">
+        <v>1.43</v>
+      </c>
+      <c r="AR251">
+        <v>1.84</v>
+      </c>
+      <c r="AS251">
+        <v>1.39</v>
+      </c>
+      <c r="AT251">
+        <v>3.23</v>
+      </c>
+      <c r="AU251">
+        <v>5</v>
+      </c>
+      <c r="AV251">
+        <v>3</v>
+      </c>
+      <c r="AW251">
+        <v>3</v>
+      </c>
+      <c r="AX251">
+        <v>16</v>
+      </c>
+      <c r="AY251">
+        <v>9</v>
+      </c>
+      <c r="AZ251">
+        <v>23</v>
+      </c>
+      <c r="BA251">
+        <v>3</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>8</v>
+      </c>
+      <c r="BD251">
+        <v>1.7</v>
+      </c>
+      <c r="BE251">
+        <v>6.75</v>
+      </c>
+      <c r="BF251">
+        <v>2.4</v>
+      </c>
+      <c r="BG251">
+        <v>1.2</v>
+      </c>
+      <c r="BH251">
+        <v>3.9</v>
+      </c>
+      <c r="BI251">
+        <v>1.36</v>
+      </c>
+      <c r="BJ251">
+        <v>2.8</v>
+      </c>
+      <c r="BK251">
+        <v>1.6</v>
+      </c>
+      <c r="BL251">
+        <v>2.17</v>
+      </c>
+      <c r="BM251">
+        <v>1.95</v>
+      </c>
+      <c r="BN251">
+        <v>1.74</v>
+      </c>
+      <c r="BO251">
+        <v>2.43</v>
+      </c>
+      <c r="BP251">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7491737</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45753.35416666666</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>75</v>
+      </c>
+      <c r="H252" t="s">
+        <v>78</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>3</v>
+      </c>
+      <c r="O252" t="s">
+        <v>257</v>
+      </c>
+      <c r="P252" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q252">
+        <v>2.5</v>
+      </c>
+      <c r="R252">
+        <v>2.2</v>
+      </c>
+      <c r="S252">
+        <v>4.33</v>
+      </c>
+      <c r="T252">
+        <v>1.36</v>
+      </c>
+      <c r="U252">
+        <v>3</v>
+      </c>
+      <c r="V252">
+        <v>2.75</v>
+      </c>
+      <c r="W252">
+        <v>1.4</v>
+      </c>
+      <c r="X252">
+        <v>8</v>
+      </c>
+      <c r="Y252">
+        <v>1.08</v>
+      </c>
+      <c r="Z252">
+        <v>1.91</v>
+      </c>
+      <c r="AA252">
+        <v>4.1</v>
+      </c>
+      <c r="AB252">
+        <v>3.75</v>
+      </c>
+      <c r="AC252">
+        <v>1.04</v>
+      </c>
+      <c r="AD252">
+        <v>10</v>
+      </c>
+      <c r="AE252">
+        <v>1.25</v>
+      </c>
+      <c r="AF252">
+        <v>3.8</v>
+      </c>
+      <c r="AG252">
+        <v>1.84</v>
+      </c>
+      <c r="AH252">
+        <v>1.97</v>
+      </c>
+      <c r="AI252">
+        <v>1.8</v>
+      </c>
+      <c r="AJ252">
+        <v>1.91</v>
+      </c>
+      <c r="AK252">
+        <v>1.25</v>
+      </c>
+      <c r="AL252">
+        <v>1.27</v>
+      </c>
+      <c r="AM252">
+        <v>1.85</v>
+      </c>
+      <c r="AN252">
+        <v>1.31</v>
+      </c>
+      <c r="AO252">
+        <v>0.71</v>
+      </c>
+      <c r="AP252">
+        <v>1.43</v>
+      </c>
+      <c r="AQ252">
+        <v>0.67</v>
+      </c>
+      <c r="AR252">
+        <v>1.66</v>
+      </c>
+      <c r="AS252">
+        <v>1.25</v>
+      </c>
+      <c r="AT252">
+        <v>2.91</v>
+      </c>
+      <c r="AU252">
+        <v>6</v>
+      </c>
+      <c r="AV252">
+        <v>6</v>
+      </c>
+      <c r="AW252">
+        <v>12</v>
+      </c>
+      <c r="AX252">
+        <v>8</v>
+      </c>
+      <c r="AY252">
+        <v>20</v>
+      </c>
+      <c r="AZ252">
+        <v>16</v>
+      </c>
+      <c r="BA252">
+        <v>4</v>
+      </c>
+      <c r="BB252">
+        <v>2</v>
+      </c>
+      <c r="BC252">
+        <v>6</v>
+      </c>
+      <c r="BD252">
+        <v>1.65</v>
+      </c>
+      <c r="BE252">
+        <v>6.5</v>
+      </c>
+      <c r="BF252">
+        <v>2.55</v>
+      </c>
+      <c r="BG252">
+        <v>1.35</v>
+      </c>
+      <c r="BH252">
+        <v>2.9</v>
+      </c>
+      <c r="BI252">
+        <v>1.58</v>
+      </c>
+      <c r="BJ252">
+        <v>2.17</v>
+      </c>
+      <c r="BK252">
+        <v>1.96</v>
+      </c>
+      <c r="BL252">
+        <v>1.73</v>
+      </c>
+      <c r="BM252">
+        <v>2.5</v>
+      </c>
+      <c r="BN252">
+        <v>1.46</v>
+      </c>
+      <c r="BO252">
+        <v>3.3</v>
+      </c>
+      <c r="BP252">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7491738</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45753.35416666666</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>82</v>
+      </c>
+      <c r="H253" t="s">
+        <v>79</v>
+      </c>
+      <c r="I253">
+        <v>3</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>3</v>
+      </c>
+      <c r="L253">
+        <v>6</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>6</v>
+      </c>
+      <c r="O253" t="s">
+        <v>258</v>
+      </c>
+      <c r="P253" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q253">
+        <v>1.95</v>
+      </c>
+      <c r="R253">
+        <v>2.4</v>
+      </c>
+      <c r="S253">
+        <v>6</v>
+      </c>
+      <c r="T253">
+        <v>1.33</v>
+      </c>
+      <c r="U253">
+        <v>3.25</v>
+      </c>
+      <c r="V253">
+        <v>2.5</v>
+      </c>
+      <c r="W253">
+        <v>1.5</v>
+      </c>
+      <c r="X253">
+        <v>6</v>
+      </c>
+      <c r="Y253">
+        <v>1.13</v>
+      </c>
+      <c r="Z253">
+        <v>1.45</v>
+      </c>
+      <c r="AA253">
+        <v>4.75</v>
+      </c>
+      <c r="AB253">
+        <v>7.3</v>
+      </c>
+      <c r="AC253">
+        <v>1.04</v>
+      </c>
+      <c r="AD253">
+        <v>10</v>
+      </c>
+      <c r="AE253">
+        <v>1.22</v>
+      </c>
+      <c r="AF253">
+        <v>4.2</v>
+      </c>
+      <c r="AG253">
+        <v>1.65</v>
+      </c>
+      <c r="AH253">
+        <v>2</v>
+      </c>
+      <c r="AI253">
+        <v>1.83</v>
+      </c>
+      <c r="AJ253">
+        <v>1.83</v>
+      </c>
+      <c r="AK253">
+        <v>1.12</v>
+      </c>
+      <c r="AL253">
+        <v>1.19</v>
+      </c>
+      <c r="AM253">
+        <v>2.6</v>
+      </c>
+      <c r="AN253">
+        <v>1.64</v>
+      </c>
+      <c r="AO253">
+        <v>0.08</v>
+      </c>
+      <c r="AP253">
+        <v>1.73</v>
+      </c>
+      <c r="AQ253">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR253">
+        <v>1.53</v>
+      </c>
+      <c r="AS253">
+        <v>1.25</v>
+      </c>
+      <c r="AT253">
+        <v>2.78</v>
+      </c>
+      <c r="AU253">
+        <v>8</v>
+      </c>
+      <c r="AV253">
+        <v>5</v>
+      </c>
+      <c r="AW253">
+        <v>7</v>
+      </c>
+      <c r="AX253">
+        <v>7</v>
+      </c>
+      <c r="AY253">
+        <v>17</v>
+      </c>
+      <c r="AZ253">
+        <v>17</v>
+      </c>
+      <c r="BA253">
+        <v>0</v>
+      </c>
+      <c r="BB253">
+        <v>3</v>
+      </c>
+      <c r="BC253">
+        <v>3</v>
+      </c>
+      <c r="BD253">
+        <v>1.32</v>
+      </c>
+      <c r="BE253">
+        <v>7.5</v>
+      </c>
+      <c r="BF253">
+        <v>3.65</v>
+      </c>
+      <c r="BG253">
+        <v>1.21</v>
+      </c>
+      <c r="BH253">
+        <v>3.7</v>
+      </c>
+      <c r="BI253">
+        <v>1.38</v>
+      </c>
+      <c r="BJ253">
+        <v>2.7</v>
+      </c>
+      <c r="BK253">
+        <v>1.63</v>
+      </c>
+      <c r="BL253">
+        <v>2.12</v>
+      </c>
+      <c r="BM253">
+        <v>1.98</v>
+      </c>
+      <c r="BN253">
+        <v>1.72</v>
+      </c>
+      <c r="BO253">
+        <v>2.48</v>
+      </c>
+      <c r="BP253">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -53615,10 +53615,10 @@
         <v>0</v>
       </c>
       <c r="BB253">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC253">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD253">
         <v>1.32</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Germany 2. Bundesliga_20242025.xlsx
@@ -2065,10 +2065,10 @@
         <v>1</v>
       </c>
       <c r="AY2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AZ2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA2">
         <v>6</v>
@@ -2271,10 +2271,10 @@
         <v>5</v>
       </c>
       <c r="AY3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA3">
         <v>7</v>
@@ -2477,10 +2477,10 @@
         <v>6</v>
       </c>
       <c r="AY4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2683,10 +2683,10 @@
         <v>4</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA5">
         <v>1</v>
@@ -2889,10 +2889,10 @@
         <v>4</v>
       </c>
       <c r="AY6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA6">
         <v>11</v>
@@ -3095,7 +3095,7 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
         <v>12</v>
@@ -3301,10 +3301,10 @@
         <v>5</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA8">
         <v>7</v>
@@ -3507,7 +3507,7 @@
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ9">
         <v>15</v>
@@ -3713,10 +3713,10 @@
         <v>6</v>
       </c>
       <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
         <v>12</v>
-      </c>
-      <c r="AZ10">
-        <v>14</v>
       </c>
       <c r="BA10">
         <v>6</v>
@@ -3919,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="AY11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -4125,10 +4125,10 @@
         <v>4</v>
       </c>
       <c r="AY12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA12">
         <v>8</v>
@@ -4331,10 +4331,10 @@
         <v>11</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA13">
         <v>1</v>
@@ -4537,10 +4537,10 @@
         <v>4</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ14">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BA14">
         <v>4</v>
@@ -4743,10 +4743,10 @@
         <v>4</v>
       </c>
       <c r="AY15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA15">
         <v>7</v>
@@ -4949,10 +4949,10 @@
         <v>5</v>
       </c>
       <c r="AY16">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA16">
         <v>9</v>
@@ -5155,10 +5155,10 @@
         <v>5</v>
       </c>
       <c r="AY17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA17">
         <v>7</v>
@@ -5361,10 +5361,10 @@
         <v>3</v>
       </c>
       <c r="AY18">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ18">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA18">
         <v>10</v>
@@ -5567,10 +5567,10 @@
         <v>7</v>
       </c>
       <c r="AY19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA19">
         <v>7</v>
@@ -5776,7 +5776,7 @@
         <v>13</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA20">
         <v>7</v>
@@ -5979,7 +5979,7 @@
         <v>9</v>
       </c>
       <c r="AY21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ21">
         <v>11</v>
@@ -6185,10 +6185,10 @@
         <v>2</v>
       </c>
       <c r="AY22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA22">
         <v>4</v>
@@ -6391,10 +6391,10 @@
         <v>6</v>
       </c>
       <c r="AY23">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AZ23">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA23">
         <v>7</v>
@@ -6597,10 +6597,10 @@
         <v>7</v>
       </c>
       <c r="AY24">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA24">
         <v>8</v>
@@ -6803,10 +6803,10 @@
         <v>2</v>
       </c>
       <c r="AY25">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA25">
         <v>8</v>
@@ -7009,10 +7009,10 @@
         <v>6</v>
       </c>
       <c r="AY26">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26">
         <v>6</v>
@@ -7215,10 +7215,10 @@
         <v>0</v>
       </c>
       <c r="AY27">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA27">
         <v>13</v>
@@ -7421,10 +7421,10 @@
         <v>2</v>
       </c>
       <c r="AY28">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ28">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA28">
         <v>9</v>
@@ -7627,10 +7627,10 @@
         <v>7</v>
       </c>
       <c r="AY29">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AZ29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA29">
         <v>8</v>
@@ -7833,10 +7833,10 @@
         <v>7</v>
       </c>
       <c r="AY30">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ30">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA30">
         <v>7</v>
@@ -8039,10 +8039,10 @@
         <v>9</v>
       </c>
       <c r="AY31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ31">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA31">
         <v>7</v>
@@ -8245,10 +8245,10 @@
         <v>5</v>
       </c>
       <c r="AY32">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ32">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA32">
         <v>8</v>
@@ -8451,10 +8451,10 @@
         <v>4</v>
       </c>
       <c r="AY33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ33">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA33">
         <v>3</v>
@@ -8657,10 +8657,10 @@
         <v>2</v>
       </c>
       <c r="AY34">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AZ34">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BA34">
         <v>11</v>
@@ -8863,10 +8863,10 @@
         <v>3</v>
       </c>
       <c r="AY35">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ35">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA35">
         <v>4</v>
@@ -9069,10 +9069,10 @@
         <v>4</v>
       </c>
       <c r="AY36">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA36">
         <v>6</v>
@@ -9275,10 +9275,10 @@
         <v>8</v>
       </c>
       <c r="AY37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ37">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA37">
         <v>1</v>
@@ -9481,10 +9481,10 @@
         <v>6</v>
       </c>
       <c r="AY38">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ38">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA38">
         <v>7</v>
@@ -9687,10 +9687,10 @@
         <v>6</v>
       </c>
       <c r="AY39">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA39">
         <v>4</v>
@@ -9893,10 +9893,10 @@
         <v>4</v>
       </c>
       <c r="AY40">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ40">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA40">
         <v>10</v>
@@ -10099,10 +10099,10 @@
         <v>1</v>
       </c>
       <c r="AY41">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ41">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA41">
         <v>2</v>
@@ -10305,10 +10305,10 @@
         <v>8</v>
       </c>
       <c r="AY42">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ42">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA42">
         <v>2</v>
@@ -10511,10 +10511,10 @@
         <v>4</v>
       </c>
       <c r="AY43">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AZ43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA43">
         <v>10</v>
@@ -10717,10 +10717,10 @@
         <v>7</v>
       </c>
       <c r="AY44">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ44">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA44">
         <v>8</v>
@@ -10923,10 +10923,10 @@
         <v>2</v>
       </c>
       <c r="AY45">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ45">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA45">
         <v>6</v>
@@ -11129,10 +11129,10 @@
         <v>3</v>
       </c>
       <c r="AY46">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ46">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA46">
         <v>5</v>
@@ -11335,10 +11335,10 @@
         <v>6</v>
       </c>
       <c r="AY47">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ47">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA47">
         <v>5</v>
@@ -11541,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="AY48">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ48">
         <v>11</v>
@@ -11747,10 +11747,10 @@
         <v>8</v>
       </c>
       <c r="AY49">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ49">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA49">
         <v>4</v>
@@ -11953,10 +11953,10 @@
         <v>7</v>
       </c>
       <c r="AY50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ50">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA50">
         <v>7</v>
@@ -12159,10 +12159,10 @@
         <v>6</v>
       </c>
       <c r="AY51">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA51">
         <v>8</v>
@@ -12365,10 +12365,10 @@
         <v>6</v>
       </c>
       <c r="AY52">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ52">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA52">
         <v>3</v>
@@ -12571,10 +12571,10 @@
         <v>10</v>
       </c>
       <c r="AY53">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AZ53">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA53">
         <v>9</v>
@@ -12777,10 +12777,10 @@
         <v>1</v>
       </c>
       <c r="AY54">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ54">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA54">
         <v>2</v>
@@ -12983,10 +12983,10 @@
         <v>1</v>
       </c>
       <c r="AY55">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ55">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA55">
         <v>7</v>
@@ -13189,10 +13189,10 @@
         <v>4</v>
       </c>
       <c r="AY56">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ56">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA56">
         <v>3</v>
@@ -13395,10 +13395,10 @@
         <v>7</v>
       </c>
       <c r="AY57">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ57">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA57">
         <v>6</v>
@@ -13601,10 +13601,10 @@
         <v>4</v>
       </c>
       <c r="AY58">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ58">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA58">
         <v>7</v>
@@ -13807,10 +13807,10 @@
         <v>4</v>
       </c>
       <c r="AY59">
+        <v>6</v>
+      </c>
+      <c r="AZ59">
         <v>9</v>
-      </c>
-      <c r="AZ59">
-        <v>11</v>
       </c>
       <c r="BA59">
         <v>4</v>
@@ -14013,10 +14013,10 @@
         <v>3</v>
       </c>
       <c r="AY60">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ60">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA60">
         <v>8</v>
@@ -14219,10 +14219,10 @@
         <v>3</v>
       </c>
       <c r="AY61">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ61">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA61">
         <v>7</v>
@@ -14425,10 +14425,10 @@
         <v>4</v>
       </c>
       <c r="AY62">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ62">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA62">
         <v>7</v>
@@ -14631,10 +14631,10 @@
         <v>0</v>
       </c>
       <c r="AY63">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ63">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA63">
         <v>7</v>
@@ -14837,10 +14837,10 @@
         <v>5</v>
       </c>
       <c r="AY64">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ64">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BA64">
         <v>3</v>
@@ -15043,10 +15043,10 @@
         <v>6</v>
       </c>
       <c r="AY65">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ65">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA65">
         <v>9</v>
@@ -15249,10 +15249,10 @@
         <v>10</v>
       </c>
       <c r="AY66">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ66">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA66">
         <v>3</v>
@@ -15455,7 +15455,7 @@
         <v>4</v>
       </c>
       <c r="AY67">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AZ67">
         <v>4</v>
@@ -15661,10 +15661,10 @@
         <v>11</v>
       </c>
       <c r="AY68">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ68">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA68">
         <v>6</v>
@@ -15867,10 +15867,10 @@
         <v>10</v>
       </c>
       <c r="AY69">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ69">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA69">
         <v>7</v>
@@ -17309,10 +17309,10 @@
         <v>8</v>
       </c>
       <c r="AY76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ76">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA76">
         <v>3</v>
@@ -17515,10 +17515,10 @@
         <v>4</v>
       </c>
       <c r="AY77">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ77">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA77">
         <v>4</v>
@@ -17721,10 +17721,10 @@
         <v>4</v>
       </c>
       <c r="AY78">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ78">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA78">
         <v>7</v>
@@ -17927,10 +17927,10 @@
         <v>7</v>
       </c>
       <c r="AY79">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ79">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA79">
         <v>5</v>
@@ -18751,10 +18751,10 @@
         <v>5</v>
       </c>
       <c r="AY83">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ83">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA83">
         <v>6</v>
@@ -18957,10 +18957,10 @@
         <v>6</v>
       </c>
       <c r="AY84">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ84">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA84">
         <v>3</v>
@@ -19163,10 +19163,10 @@
         <v>1</v>
       </c>
       <c r="AY85">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ85">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA85">
         <v>7</v>
@@ -19369,10 +19369,10 @@
         <v>4</v>
       </c>
       <c r="AY86">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ86">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA86">
         <v>6</v>
@@ -19575,10 +19575,10 @@
         <v>3</v>
       </c>
       <c r="AY87">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ87">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA87">
         <v>6</v>
@@ -19781,10 +19781,10 @@
         <v>5</v>
       </c>
       <c r="AY88">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ88">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA88">
         <v>4</v>
@@ -19987,10 +19987,10 @@
         <v>0</v>
       </c>
       <c r="AY89">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA89">
         <v>4</v>
@@ -20193,10 +20193,10 @@
         <v>2</v>
       </c>
       <c r="AY90">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ90">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA90">
         <v>10</v>
@@ -20399,10 +20399,10 @@
         <v>1</v>
       </c>
       <c r="AY91">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ91">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA91">
         <v>2</v>
@@ -20608,7 +20608,7 @@
         <v>7</v>
       </c>
       <c r="AZ92">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA92">
         <v>3</v>
@@ -20811,10 +20811,10 @@
         <v>2</v>
       </c>
       <c r="AY93">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ93">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BA93">
         <v>2</v>
@@ -21017,10 +21017,10 @@
         <v>6</v>
       </c>
       <c r="AY94">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ94">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA94">
         <v>6</v>
@@ -21223,10 +21223,10 @@
         <v>4</v>
       </c>
       <c r="AY95">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ95">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA95">
         <v>0</v>
@@ -21429,10 +21429,10 @@
         <v>4</v>
       </c>
       <c r="AY96">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ96">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA96">
         <v>6</v>
@@ -21635,10 +21635,10 @@
         <v>5</v>
       </c>
       <c r="AY97">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ97">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA97">
         <v>6</v>
@@ -21841,10 +21841,10 @@
         <v>3</v>
       </c>
       <c r="AY98">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ98">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA98">
         <v>11</v>
@@ -22047,10 +22047,10 @@
         <v>7</v>
       </c>
       <c r="AY99">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ99">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA99">
         <v>8</v>
@@ -22253,10 +22253,10 @@
         <v>4</v>
       </c>
       <c r="AY100">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ100">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA100">
         <v>5</v>
@@ -22459,10 +22459,10 @@
         <v>9</v>
       </c>
       <c r="AY101">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ101">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BA101">
         <v>3</v>
@@ -22665,10 +22665,10 @@
         <v>6</v>
       </c>
       <c r="AY102">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ102">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA102">
         <v>12</v>
@@ -22871,7 +22871,7 @@
         <v>2</v>
       </c>
       <c r="AY103">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ103">
         <v>5</v>
@@ -23077,10 +23077,10 @@
         <v>6</v>
       </c>
       <c r="AY104">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ104">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA104">
         <v>1</v>
@@ -23283,10 +23283,10 @@
         <v>1</v>
       </c>
       <c r="AY105">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ105">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BA105">
         <v>14</v>
@@ -23489,10 +23489,10 @@
         <v>4</v>
       </c>
       <c r="AY106">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ106">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA106">
         <v>5</v>
@@ -23695,10 +23695,10 @@
         <v>4</v>
       </c>
       <c r="AY107">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ107">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA107">
         <v>8</v>
@@ -23901,10 +23901,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ108">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA108">
         <v>6</v>
@@ -24107,10 +24107,10 @@
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AZ109">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA109">
         <v>15</v>
@@ -24519,10 +24519,10 @@
         <v>3</v>
       </c>
       <c r="AY111">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ111">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA111">
         <v>3</v>
@@ -24725,10 +24725,10 @@
         <v>7</v>
       </c>
       <c r="AY112">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ112">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA112">
         <v>7</v>
@@ -24937,13 +24937,13 @@
         <v>-1</v>
       </c>
       <c r="BA113">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BB113">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BC113">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BD113">
         <v>1.51</v>
@@ -25143,13 +25143,13 @@
         <v>-1</v>
       </c>
       <c r="BA114">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="BB114">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BC114">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="BD114">
         <v>1.75</v>
@@ -25349,13 +25349,13 @@
         <v>-1</v>
       </c>
       <c r="BA115">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BB115">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BC115">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BD115">
         <v>1.59</v>
@@ -26167,10 +26167,10 @@
         <v>1</v>
       </c>
       <c r="AY119">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ119">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -26373,10 +26373,10 @@
         <v>4</v>
       </c>
       <c r="AY120">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ120">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA120">
         <v>7</v>
@@ -26579,10 +26579,10 @@
         <v>1</v>
       </c>
       <c r="AY121">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ121">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA121">
         <v>10</v>
@@ -26785,10 +26785,10 @@
         <v>6</v>
       </c>
       <c r="AY122">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ122">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA122">
         <v>1</v>
@@ -26991,10 +26991,10 @@
         <v>6</v>
       </c>
       <c r="AY123">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ123">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA123">
         <v>2</v>
@@ -27197,7 +27197,7 @@
         <v>2</v>
       </c>
       <c r="AY124">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ124">
         <v>5</v>
@@ -27403,10 +27403,10 @@
         <v>7</v>
       </c>
       <c r="AY125">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ125">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA125">
         <v>7</v>
@@ -27815,10 +27815,10 @@
         <v>4</v>
       </c>
       <c r="AY127">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ127">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BA127">
         <v>4</v>
@@ -28021,10 +28021,10 @@
         <v>6</v>
       </c>
       <c r="AY128">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ128">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA128">
         <v>8</v>
@@ -28230,7 +28230,7 @@
         <v>6</v>
       </c>
       <c r="AZ129">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA129">
         <v>2</v>
@@ -28433,10 +28433,10 @@
         <v>5</v>
       </c>
       <c r="AY130">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ130">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA130">
         <v>3</v>
@@ -28639,10 +28639,10 @@
         <v>5</v>
       </c>
       <c r="AY131">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ131">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA131">
         <v>6</v>
@@ -28845,10 +28845,10 @@
         <v>4</v>
       </c>
       <c r="AY132">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AZ132">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA132">
         <v>7</v>
@@ -29051,10 +29051,10 @@
         <v>5</v>
       </c>
       <c r="AY133">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ133">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA133">
         <v>3</v>
@@ -29257,10 +29257,10 @@
         <v>10</v>
       </c>
       <c r="AY134">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ134">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA134">
         <v>2</v>
@@ -29463,10 +29463,10 @@
         <v>4</v>
       </c>
       <c r="AY135">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ135">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA135">
         <v>7</v>
@@ -29669,10 +29669,10 @@
         <v>7</v>
       </c>
       <c r="AY136">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ136">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA136">
         <v>4</v>
@@ -29875,10 +29875,10 @@
         <v>5</v>
       </c>
       <c r="AY137">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ137">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA137">
         <v>4</v>
@@ -30081,10 +30081,10 @@
         <v>4</v>
       </c>
       <c r="AY138">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ138">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA138">
         <v>9</v>
@@ -30287,10 +30287,10 @@
         <v>2</v>
       </c>
       <c r="AY139">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ139">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA139">
         <v>6</v>
@@ -30493,10 +30493,10 @@
         <v>3</v>
       </c>
       <c r="AY140">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ140">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA140">
         <v>7</v>
@@ -30699,7 +30699,7 @@
         <v>4</v>
       </c>
       <c r="AY141">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ141">
         <v>7</v>
@@ -31111,10 +31111,10 @@
         <v>7</v>
       </c>
       <c r="AY143">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AZ143">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA143">
         <v>3</v>
@@ -31317,10 +31317,10 @@
         <v>6</v>
       </c>
       <c r="AY144">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ144">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA144">
         <v>4</v>
@@ -31523,10 +31523,10 @@
         <v>6</v>
       </c>
       <c r="AY145">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ145">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA145">
         <v>6</v>
@@ -31729,10 +31729,10 @@
         <v>7</v>
       </c>
       <c r="AY146">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ146">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA146">
         <v>4</v>
@@ -31935,10 +31935,10 @@
         <v>3</v>
       </c>
       <c r="AY147">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ147">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA147">
         <v>4</v>
@@ -32141,10 +32141,10 @@
         <v>0</v>
       </c>
       <c r="AY148">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ148">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA148">
         <v>3</v>
@@ -32347,10 +32347,10 @@
         <v>6</v>
       </c>
       <c r="AY149">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ149">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA149">
         <v>1</v>
@@ -32553,10 +32553,10 @@
         <v>3</v>
       </c>
       <c r="AY150">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ150">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA150">
         <v>10</v>
@@ -32759,10 +32759,10 @@
         <v>2</v>
       </c>
       <c r="AY151">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ151">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA151">
         <v>7</v>
@@ -32965,10 +32965,10 @@
         <v>10</v>
       </c>
       <c r="AY152">
+        <v>12</v>
+      </c>
+      <c r="AZ152">
         <v>15</v>
-      </c>
-      <c r="AZ152">
-        <v>20</v>
       </c>
       <c r="BA152">
         <v>6</v>
@@ -33171,10 +33171,10 @@
         <v>8</v>
       </c>
       <c r="AY153">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ153">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA153">
         <v>7</v>
@@ -33377,10 +33377,10 @@
         <v>3</v>
       </c>
       <c r="AY154">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ154">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA154">
         <v>10</v>
@@ -33583,10 +33583,10 @@
         <v>9</v>
       </c>
       <c r="AY155">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ155">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA155">
         <v>7</v>
@@ -33789,10 +33789,10 @@
         <v>7</v>
       </c>
       <c r="AY156">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ156">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA156">
         <v>4</v>
@@ -33995,10 +33995,10 @@
         <v>6</v>
       </c>
       <c r="AY157">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ157">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA157">
         <v>7</v>
@@ -34204,7 +34204,7 @@
         <v>5</v>
       </c>
       <c r="AZ158">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA158">
         <v>0</v>
@@ -34407,10 +34407,10 @@
         <v>10</v>
       </c>
       <c r="AY159">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ159">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA159">
         <v>4</v>
@@ -34613,10 +34613,10 @@
         <v>5</v>
       </c>
       <c r="AY160">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ160">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA160">
         <v>6</v>
@@ -34819,10 +34819,10 @@
         <v>8</v>
       </c>
       <c r="AY161">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ161">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA161">
         <v>7</v>
@@ -35025,10 +35025,10 @@
         <v>10</v>
       </c>
       <c r="AY162">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ162">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA162">
         <v>6</v>
@@ -35231,10 +35231,10 @@
         <v>1</v>
       </c>
       <c r="AY163">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ163">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA163">
         <v>9</v>
@@ -35437,7 +35437,7 @@
         <v>5</v>
       </c>
       <c r="AY164">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ164">
         <v>8</v>
@@ -35643,10 +35643,10 @@
         <v>7</v>
       </c>
       <c r="AY165">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ165">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA165">
         <v>2</v>
@@ -36055,10 +36055,10 @@
         <v>9</v>
       </c>
       <c r="AY167">
+        <v>13</v>
+      </c>
+      <c r="AZ167">
         <v>15</v>
-      </c>
-      <c r="AZ167">
-        <v>17</v>
       </c>
       <c r="BA167">
         <v>6</v>
@@ -36467,7 +36467,7 @@
         <v>4</v>
       </c>
       <c r="AY169">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ169">
         <v>10</v>
@@ -36673,7 +36673,7 @@
         <v>4</v>
       </c>
       <c r="AY170">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ170">
         <v>6</v>
@@ -36879,10 +36879,10 @@
         <v>8</v>
       </c>
       <c r="AY171">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ171">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA171">
         <v>3</v>
@@ -37085,10 +37085,10 @@
         <v>8</v>
       </c>
       <c r="AY172">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ172">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA172">
         <v>6</v>
@@ -37291,10 +37291,10 @@
         <v>10</v>
       </c>
       <c r="AY173">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ173">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA173">
         <v>6</v>
@@ -37497,10 +37497,10 @@
         <v>10</v>
       </c>
       <c r="AY174">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ174">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA174">
         <v>7</v>
@@ -37703,10 +37703,10 @@
         <v>12</v>
       </c>
       <c r="AY175">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ175">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA175">
         <v>4</v>
@@ -37909,10 +37909,10 @@
         <v>9</v>
       </c>
       <c r="AY176">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ176">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA176">
         <v>10</v>
@@ -38115,10 +38115,10 @@
         <v>15</v>
       </c>
       <c r="AY177">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ177">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BA177">
         <v>0</v>
@@ -38321,10 +38321,10 @@
         <v>6</v>
       </c>
       <c r="AY178">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ178">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA178">
         <v>5</v>
@@ -38527,7 +38527,7 @@
         <v>4</v>
       </c>
       <c r="AY179">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ179">
         <v>11</v>
@@ -38733,19 +38733,19 @@
         <v>13</v>
       </c>
       <c r="AY180">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ180">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA180">
         <v>4</v>
       </c>
       <c r="BB180">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC180">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD180">
         <v>1.61</v>
@@ -38939,10 +38939,10 @@
         <v>12</v>
       </c>
       <c r="AY181">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ181">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA181">
         <v>6</v>
@@ -39145,10 +39145,10 @@
         <v>8</v>
       </c>
       <c r="AY182">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ182">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA182">
         <v>3</v>
@@ -39351,10 +39351,10 @@
         <v>11</v>
       </c>
       <c r="AY183">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ183">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA183">
         <v>9</v>
@@ -39557,10 +39557,10 @@
         <v>8</v>
       </c>
       <c r="AY184">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ184">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA184">
         <v>2</v>
@@ -39763,10 +39763,10 @@
         <v>4</v>
       </c>
       <c r="AY185">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ185">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA185">
         <v>10</v>
@@ -39972,7 +39972,7 @@
         <v>8</v>
       </c>
       <c r="AZ186">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA186">
         <v>4</v>
@@ -40175,10 +40175,10 @@
         <v>9</v>
       </c>
       <c r="AY187">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ187">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA187">
         <v>6</v>
@@ -40381,10 +40381,10 @@
         <v>9</v>
       </c>
       <c r="AY188">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ188">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA188">
         <v>4</v>
@@ -40587,10 +40587,10 @@
         <v>6</v>
       </c>
       <c r="AY189">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AZ189">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA189">
         <v>10</v>
@@ -40793,7 +40793,7 @@
         <v>4</v>
       </c>
       <c r="AY190">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ190">
         <v>7</v>
@@ -40999,10 +40999,10 @@
         <v>8</v>
       </c>
       <c r="AY191">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ191">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41205,10 +41205,10 @@
         <v>8</v>
       </c>
       <c r="AY192">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ192">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA192">
         <v>9</v>
@@ -41411,10 +41411,10 @@
         <v>7</v>
       </c>
       <c r="AY193">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ193">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA193">
         <v>6</v>
@@ -41617,10 +41617,10 @@
         <v>19</v>
       </c>
       <c r="AY194">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ194">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="BA194">
         <v>2</v>
@@ -41823,10 +41823,10 @@
         <v>10</v>
       </c>
       <c r="AY195">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ195">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA195">
         <v>3</v>
@@ -42029,10 +42029,10 @@
         <v>16</v>
       </c>
       <c r="AY196">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ196">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA196">
         <v>4</v>
@@ -42235,10 +42235,10 @@
         <v>5</v>
       </c>
       <c r="AY197">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ197">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA197">
         <v>9</v>
@@ -42441,10 +42441,10 @@
         <v>9</v>
       </c>
       <c r="AY198">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ198">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA198">
         <v>7</v>
@@ -42647,10 +42647,10 @@
         <v>5</v>
       </c>
       <c r="AY199">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ199">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA199">
         <v>11</v>
@@ -42853,10 +42853,10 @@
         <v>10</v>
       </c>
       <c r="AY200">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ200">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA200">
         <v>12</v>
@@ -43059,7 +43059,7 @@
         <v>0</v>
       </c>
       <c r="AY201">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ201">
         <v>5</v>
@@ -43268,7 +43268,7 @@
         <v>8</v>
       </c>
       <c r="AZ202">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA202">
         <v>3</v>
@@ -43474,7 +43474,7 @@
         <v>16</v>
       </c>
       <c r="AZ203">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA203">
         <v>5</v>
@@ -43677,10 +43677,10 @@
         <v>6</v>
       </c>
       <c r="AY204">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ204">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA204">
         <v>4</v>
@@ -43886,7 +43886,7 @@
         <v>8</v>
       </c>
       <c r="AZ205">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA205">
         <v>4</v>
@@ -44089,10 +44089,10 @@
         <v>9</v>
       </c>
       <c r="AY206">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ206">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA206">
         <v>7</v>
@@ -44295,10 +44295,10 @@
         <v>4</v>
       </c>
       <c r="AY207">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ207">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA207">
         <v>3</v>
@@ -44501,19 +44501,19 @@
         <v>6</v>
       </c>
       <c r="AY208">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ208">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA208">
         <v>3</v>
       </c>
       <c r="BB208">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC208">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD208">
         <v>1.73</v>
@@ -44707,10 +44707,10 @@
         <v>6</v>
       </c>
       <c r="AY209">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ209">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA209">
         <v>6</v>
@@ -44916,7 +44916,7 @@
         <v>16</v>
       </c>
       <c r="AZ210">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA210">
         <v>10</v>
@@ -45119,10 +45119,10 @@
         <v>7</v>
       </c>
       <c r="AY211">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ211">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA211">
         <v>8</v>
@@ -45325,10 +45325,10 @@
         <v>14</v>
       </c>
       <c r="AY212">
+        <v>17</v>
+      </c>
+      <c r="AZ212">
         <v>21</v>
-      </c>
-      <c r="AZ212">
-        <v>24</v>
       </c>
       <c r="BA212">
         <v>7</v>
@@ -45531,10 +45531,10 @@
         <v>9</v>
       </c>
       <c r="AY213">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ213">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA213">
         <v>4</v>
@@ -45737,10 +45737,10 @@
         <v>6</v>
       </c>
       <c r="AY214">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ214">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA214">
         <v>3</v>
@@ -45943,10 +45943,10 @@
         <v>8</v>
       </c>
       <c r="AY215">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ215">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA215">
         <v>12</v>
@@ -46149,10 +46149,10 @@
         <v>6</v>
       </c>
       <c r="AY216">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ216">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA216">
         <v>7</v>
@@ -46355,10 +46355,10 @@
         <v>10</v>
       </c>
       <c r="AY217">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ217">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA217">
         <v>9</v>
@@ -46561,10 +46561,10 @@
         <v>5</v>
       </c>
       <c r="AY218">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AZ218">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA218">
         <v>2</v>
@@ -46767,10 +46767,10 @@
         <v>2</v>
       </c>
       <c r="AY219">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ219">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA219">
         <v>7</v>
@@ -46976,7 +46976,7 @@
         <v>10</v>
       </c>
       <c r="AZ220">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA220">
         <v>1</v>
@@ -47179,10 +47179,10 @@
         <v>4</v>
       </c>
       <c r="AY221">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ221">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA221">
         <v>3</v>
@@ -47385,10 +47385,10 @@
         <v>9</v>
       </c>
       <c r="AY222">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ222">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA222">
         <v>3</v>
@@ -47591,10 +47591,10 @@
         <v>9</v>
       </c>
       <c r="AY223">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ223">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA223">
         <v>8</v>
@@ -48003,7 +48003,7 @@
         <v>8</v>
       </c>
       <c r="AY225">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ225">
         <v>15</v>
@@ -48212,7 +48212,7 @@
         <v>7</v>
       </c>
       <c r="AZ226">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA226">
         <v>3</v>
@@ -48418,7 +48418,7 @@
         <v>11</v>
       </c>
       <c r="AZ227">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA227">
         <v>5</v>
@@ -48621,10 +48621,10 @@
         <v>8</v>
       </c>
       <c r="AY228">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ228">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA228">
         <v>3</v>
@@ -48827,10 +48827,10 @@
         <v>5</v>
       </c>
       <c r="AY229">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ229">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA229">
         <v>4</v>
@@ -49033,10 +49033,10 @@
         <v>5</v>
       </c>
       <c r="AY230">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ230">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA230">
         <v>4</v>
@@ -49239,10 +49239,10 @@
         <v>9</v>
       </c>
       <c r="AY231">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ231">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA231">
         <v>5</v>
@@ -49445,7 +49445,7 @@
         <v>2</v>
       </c>
       <c r="AY232">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ232">
         <v>7</v>
@@ -49651,10 +49651,10 @@
         <v>5</v>
       </c>
       <c r="AY233">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ233">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA233">
         <v>1</v>
@@ -49857,10 +49857,10 @@
         <v>9</v>
       </c>
       <c r="AY234">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ234">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA234">
         <v>4</v>
@@ -50063,10 +50063,10 @@
         <v>3</v>
       </c>
       <c r="AY235">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ235">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA235">
         <v>4</v>
@@ -50269,10 +50269,10 @@
         <v>12</v>
       </c>
       <c r="AY236">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ236">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA236">
         <v>8</v>
@@ -50475,10 +50475,10 @@
         <v>15</v>
       </c>
       <c r="AY237">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ237">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BA237">
         <v>5</v>
@@ -50681,10 +50681,10 @@
         <v>10</v>
       </c>
       <c r="AY238">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ238">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA238">
         <v>12</v>
@@ -50887,10 +50887,10 @@
         <v>11</v>
       </c>
       <c r="AY239">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ239">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA239">
         <v>6</v>
@@ -51093,10 +51093,10 @@
         <v>10</v>
       </c>
       <c r="AY240">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ240">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA240">
         <v>4</v>
@@ -51299,10 +51299,10 @@
         <v>4</v>
       </c>
       <c r="AY241">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ241">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA241">
         <v>5</v>
@@ -51508,7 +51508,7 @@
         <v>13</v>
       </c>
       <c r="AZ242">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA242">
         <v>4</v>
@@ -51711,10 +51711,10 @@
         <v>7</v>
       </c>
       <c r="AY243">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ243">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA243">
         <v>4</v>
@@ -51917,10 +51917,10 @@
         <v>11</v>
       </c>
       <c r="AY244">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ244">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA244">
         <v>3</v>
@@ -52123,10 +52123,10 @@
         <v>15</v>
       </c>
       <c r="AY245">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ245">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA245">
         <v>5</v>
@@ -52329,10 +52329,10 @@
         <v>14</v>
       </c>
       <c r="AY246">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ246">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA246">
         <v>0</v>
@@ -52535,10 +52535,10 @@
         <v>4</v>
       </c>
       <c r="AY247">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ247">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA247">
         <v>6</v>
@@ -52741,10 +52741,10 @@
         <v>16</v>
       </c>
       <c r="AY248">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ248">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA248">
         <v>5</v>
@@ -52947,10 +52947,10 @@
         <v>15</v>
       </c>
       <c r="AY249">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ249">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BA249">
         <v>7</v>
@@ -53359,10 +53359,10 @@
         <v>16</v>
       </c>
       <c r="AY251">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ251">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA251">
         <v>3</v>
@@ -53565,10 +53565,10 @@
         <v>8</v>
       </c>
       <c r="AY252">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ252">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA252">
         <v>4</v>
@@ -53771,10 +53771,10 @@
         <v>7</v>
       </c>
       <c r="AY253">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ253">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA253">
         <v>0</v>
@@ -53977,19 +53977,19 @@
         <v>13</v>
       </c>
       <c r="AY254">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ254">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA254">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB254">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC254">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BD254">
         <v>1.38</v>
@@ -54183,19 +54183,19 @@
         <v>10</v>
       </c>
       <c r="AY255">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ255">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA255">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB255">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC255">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BD255">
         <v>2.3</v>
@@ -54389,10 +54389,10 @@
         <v>5</v>
       </c>
       <c r="AY256">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ256">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BA256">
         <v>5</v>
@@ -54598,7 +54598,7 @@
         <v>9</v>
       </c>
       <c r="AZ257">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA257">
         <v>6</v>
@@ -54804,7 +54804,7 @@
         <v>8</v>
       </c>
       <c r="AZ258">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BA258">
         <v>5</v>
@@ -55007,7 +55007,7 @@
         <v>1</v>
       </c>
       <c r="AY259">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AZ259">
         <v>6</v>
@@ -55213,10 +55213,10 @@
         <v>4</v>
       </c>
       <c r="AY260">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ260">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA260">
         <v>4</v>
@@ -55419,10 +55419,10 @@
         <v>6</v>
       </c>
       <c r="AY261">
+        <v>12</v>
+      </c>
+      <c r="AZ261">
         <v>13</v>
-      </c>
-      <c r="AZ261">
-        <v>16</v>
       </c>
       <c r="BA261">
         <v>8</v>
@@ -55625,10 +55625,10 @@
         <v>11</v>
       </c>
       <c r="AY262">
+        <v>12</v>
+      </c>
+      <c r="AZ262">
         <v>13</v>
-      </c>
-      <c r="AZ262">
-        <v>16</v>
       </c>
       <c r="BA262">
         <v>5</v>
@@ -55831,10 +55831,10 @@
         <v>10</v>
       </c>
       <c r="AY263">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AZ263">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA263">
         <v>6</v>
@@ -56040,7 +56040,7 @@
         <v>4</v>
       </c>
       <c r="AZ264">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA264">
         <v>3</v>
@@ -56243,7 +56243,7 @@
         <v>4</v>
       </c>
       <c r="AY265">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AZ265">
         <v>7</v>
@@ -56449,10 +56449,10 @@
         <v>13</v>
       </c>
       <c r="AY266">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ266">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BA266">
         <v>4</v>
@@ -56655,10 +56655,10 @@
         <v>5</v>
       </c>
       <c r="AY267">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ267">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA267">
         <v>10</v>
@@ -56861,10 +56861,10 @@
         <v>12</v>
       </c>
       <c r="AY268">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ268">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA268">
         <v>5</v>
@@ -57067,10 +57067,10 @@
         <v>8</v>
       </c>
       <c r="AY269">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ269">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA269">
         <v>4</v>
@@ -57273,10 +57273,10 @@
         <v>5</v>
       </c>
       <c r="AY270">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ270">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA270">
         <v>5</v>
@@ -57479,10 +57479,10 @@
         <v>12</v>
       </c>
       <c r="AY271">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ271">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA271">
         <v>4</v>
@@ -57685,10 +57685,10 @@
         <v>11</v>
       </c>
       <c r="AY272">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ272">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA272">
         <v>7</v>
@@ -57891,10 +57891,10 @@
         <v>14</v>
       </c>
       <c r="AY273">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ273">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA273">
         <v>4</v>
@@ -58097,10 +58097,10 @@
         <v>9</v>
       </c>
       <c r="AY274">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ274">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA274">
         <v>2</v>
@@ -58303,10 +58303,10 @@
         <v>8</v>
       </c>
       <c r="AY275">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ275">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA275">
         <v>2</v>
@@ -58512,7 +58512,7 @@
         <v>7</v>
       </c>
       <c r="AZ276">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA276">
         <v>7</v>
@@ -58715,10 +58715,10 @@
         <v>2</v>
       </c>
       <c r="AY277">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ277">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA277">
         <v>7</v>
@@ -59127,7 +59127,7 @@
         <v>8</v>
       </c>
       <c r="AY279">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ279">
         <v>10</v>
@@ -59333,10 +59333,10 @@
         <v>9</v>
       </c>
       <c r="AY280">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ280">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA280">
         <v>5</v>
@@ -59539,10 +59539,10 @@
         <v>6</v>
       </c>
       <c r="AY281">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ281">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA281">
         <v>7</v>
@@ -59745,10 +59745,10 @@
         <v>11</v>
       </c>
       <c r="AY282">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ282">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA282">
         <v>6</v>
@@ -59951,10 +59951,10 @@
         <v>8</v>
       </c>
       <c r="AY283">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ283">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA283">
         <v>7</v>
@@ -60157,10 +60157,10 @@
         <v>5</v>
       </c>
       <c r="AY284">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ284">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA284">
         <v>4</v>
@@ -60363,10 +60363,10 @@
         <v>3</v>
       </c>
       <c r="AY285">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ285">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA285">
         <v>4</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="AY286">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ286">
         <v>6</v>
@@ -60981,10 +60981,10 @@
         <v>6</v>
       </c>
       <c r="AY288">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ288">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA288">
         <v>2</v>
@@ -61187,10 +61187,10 @@
         <v>12</v>
       </c>
       <c r="AY289">
+        <v>12</v>
+      </c>
+      <c r="AZ289">
         <v>14</v>
-      </c>
-      <c r="AZ289">
-        <v>16</v>
       </c>
       <c r="BA289">
         <v>8</v>
@@ -61393,10 +61393,10 @@
         <v>5</v>
       </c>
       <c r="AY290">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ290">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA290">
         <v>2</v>
@@ -61602,7 +61602,7 @@
         <v>6</v>
       </c>
       <c r="AZ291">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BA291">
         <v>0</v>
@@ -61805,10 +61805,10 @@
         <v>5</v>
       </c>
       <c r="AY292">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ292">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA292">
         <v>5</v>
@@ -62217,10 +62217,10 @@
         <v>8</v>
       </c>
       <c r="AY294">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ294">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA294">
         <v>8</v>
@@ -62426,7 +62426,7 @@
         <v>15</v>
       </c>
       <c r="AZ295">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA295">
         <v>3</v>
@@ -62629,10 +62629,10 @@
         <v>14</v>
       </c>
       <c r="AY296">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AZ296">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA296">
         <v>5</v>
@@ -62835,10 +62835,10 @@
         <v>10</v>
       </c>
       <c r="AY297">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ297">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA297">
         <v>3</v>
@@ -63041,10 +63041,10 @@
         <v>12</v>
       </c>
       <c r="AY298">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ298">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA298">
         <v>5</v>
@@ -63247,10 +63247,10 @@
         <v>5</v>
       </c>
       <c r="AY299">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ299">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA299">
         <v>6</v>
@@ -63453,10 +63453,10 @@
         <v>4</v>
       </c>
       <c r="AY300">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ300">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA300">
         <v>6</v>
@@ -63659,10 +63659,10 @@
         <v>11</v>
       </c>
       <c r="AY301">
+        <v>14</v>
+      </c>
+      <c r="AZ301">
         <v>16</v>
-      </c>
-      <c r="AZ301">
-        <v>21</v>
       </c>
       <c r="BA301">
         <v>6</v>
@@ -63868,7 +63868,7 @@
         <v>10</v>
       </c>
       <c r="AZ302">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA302">
         <v>2</v>
@@ -64071,10 +64071,10 @@
         <v>9</v>
       </c>
       <c r="AY303">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ303">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA303">
         <v>4</v>
@@ -64277,10 +64277,10 @@
         <v>5</v>
       </c>
       <c r="AY304">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ304">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA304">
         <v>12</v>
@@ -64483,10 +64483,10 @@
         <v>3</v>
       </c>
       <c r="AY305">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ305">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA305">
         <v>7</v>
@@ -64689,10 +64689,10 @@
         <v>5</v>
       </c>
       <c r="AY306">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ306">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA306">
         <v>1</v>
@@ -64895,10 +64895,10 @@
         <v>4</v>
       </c>
       <c r="AY307">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ307">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA307">
         <v>0</v>
